--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3312,496 +3312,482 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" ht="28.5" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Span.IO</t>
+          <t>Passenger Clothing Limited</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NP22</t>
+          <t>NP3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PR18</t>
+          <t>PR1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PR18A</t>
+          <t>PR1A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FT1</t>
+          <t>DN1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>be40</t>
+          <t>bh10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2023.1.0.30.0</t>
+          <t>2023.1.0.37.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2023.1.0.30.0</t>
+          <t>2023.1.0.37</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bh10-004-euw</t>
+          <t>bh10-003-euw</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>exec-wms-gxo-span-les</t>
+          <t>exec-wms-gxo-passenger-les</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>be40-029-eus2</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
         </is>
       </c>
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
     </row>
     <row r="40" ht="28.5" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
       <c r="B40" t="n">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Passenger Clothing Limited</t>
+          <t>WH Smith</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NP3</t>
+          <t>NP24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>PR1A</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DN1</t>
+          <t>XNE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2023.1.0.37.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2023.1.0.37</t>
+          <t>2023.1.0.45.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>bh10-003-euw</t>
+          <t>bh10-002-euw</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>exec-wms-gxo-passenger-les</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>bh10-002-euw</t>
+          <t>exec-wms-gxo-wh-smith-les</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
+          <t>2353 US Highway 130
+Dayton, NJ 08810</t>
         </is>
       </c>
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B41" t="n">
-        <v>3033</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>WH Smith</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NP24</t>
+        <v>3034</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Project Phoenix Prenatal</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>NP6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR4</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>PR4A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>XNE</t>
+          <t>WNL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>be40</t>
+          <t>bh10</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2023.1.0.45.0</t>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>bh10-002-euw</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-wh-smith-les</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>2353 US Highway 130
-Dayton, NJ 08810</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="n"/>
-      <c r="Q41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="28.5" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3034</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Project Phoenix Prenatal</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>NP6</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>PR4</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>PR4A</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>WNL</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
           <t>bh10-006-euw</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>exec-wms-gxo-prenatal-les
 exec-wms-gxo-phoenix-les</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>bh10-009-euw</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>GXO Op Den Dries 1
 6019 RA Wessem, Netherlands</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>NP13 (PRENTAL AUTOMATION)</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="n"/>
-    </row>
-    <row r="43" ht="42.75" customHeight="1">
-      <c r="A43" t="inlineStr">
+      <c r="Q41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="42.75" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B42" t="n">
         <v>3035</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>RJR Plainfield</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NP29</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>PR21</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>PR21A</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>PIR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>be40-02n-eus2</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-plainfield-les</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>600 S Perry Rd
 Plainfield, IN 46168
 USA</t>
         </is>
       </c>
-      <c r="O43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="42.75" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="O42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="42.75" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B43" t="n">
         <v>3035</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>RJR Orlando</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NP32</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>PR23</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>PR23A</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>OFR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>be40-02p-eus2</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-orlando-les</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>be40-02i-eus2</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>7469 PRESIDENTS DRIVE
 ORLANDO, FL 32809
 USA</t>
         </is>
       </c>
-      <c r="O44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="39.75" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="O43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+    </row>
+    <row r="44" ht="39.75" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B44" t="n">
         <v>3036</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Kumho (EU)</t>
         </is>
       </c>
-      <c r="D45" s="111" t="inlineStr">
+      <c r="D44" s="111" t="inlineStr">
         <is>
           <t>NP4</t>
         </is>
       </c>
-      <c r="E45" s="111" t="inlineStr">
+      <c r="E44" s="111" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F45" s="111" t="n"/>
-      <c r="G45" t="inlineStr">
+      <c r="F44" s="111" t="n"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>GE1</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>bh10-004-euw</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>exec-wms-gxo-kumho-les</t>
         </is>
       </c>
-      <c r="N45" s="110" t="inlineStr">
+      <c r="N44" s="110" t="inlineStr">
         <is>
           <t>GXO Marchamalo 2 
 Calle el Ventorro
 19180 Guadalajara, ES</t>
         </is>
       </c>
+      <c r="O44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="28.5" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3037</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Commscope</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NP7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>bh10-00d-euw</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-commscope-les</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>GXO Veenendaal
+Arsenaal 2, 3905 Veenendaal, NL</t>
+        </is>
+      </c>
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" ht="28.5" customHeight="1">
+    <row r="46" ht="14.25" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3037</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Commscope</t>
+        <v>3038</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NP7</t>
+          <t>NP8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3811,7 +3797,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>VEE</t>
+          <t>FEG</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3826,55 +3812,59 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>bh10-00d-euw</t>
+          <t>bh10-00j-euw</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>exec-wms-gxo-commscope-les</t>
-        </is>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>GXO Veenendaal
-Arsenaal 2, 3905 Veenendaal, NL</t>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
         </is>
       </c>
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" ht="42.75" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>RJR Portland</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NP8</t>
+          <t>NP31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR24</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PR24A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FEG</t>
+          <t>RPO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3882,158 +3872,96 @@
           <t>2023.1.0.45.0</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>bh10-00j-euw</t>
+          <t>be40-02p-eus2</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="42.75" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3035</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>RJR Portland</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NP31</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>PR24</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>PR24A</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>RPO</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>be40-02p-eus2</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
           <t>exec-wms-gxo-rjr-portland-les</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>be40-02q-eus2</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>3591 YEON AVE
 PORTLAND, OR 97210
 USA</t>
         </is>
       </c>
-      <c r="O48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
-    </row>
-    <row r="49" ht="57" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="O47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="57" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B48" t="n">
         <v>3035</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>RJR  Rural Hall, NC</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NP34</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>PR22</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>PR22A</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>RHN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>be40-02w-eus2</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-ruralhall-les</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>RJR
 200 FORUM PARKWAY
@@ -4041,21 +3969,83 @@
 USA</t>
         </is>
       </c>
+      <c r="O48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="B49" s="134" t="n">
+        <v>3041</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>QL Template (EU)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NP5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Not Setup</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-les</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="B50" s="134" t="n">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>QL Template (EU)</t>
+          <t>QL Template (AMAPAC)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NP5</t>
+          <t>NP25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4075,12 +4065,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2023.1.0.42.0</t>
+          <t>2023.1.0.50.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4090,7 +4080,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Not Setup</t>
+          <t>be40-02j-eus2</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4107,141 +4097,106 @@
       <c r="Q50" s="4" t="n"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c r="B51" s="134" t="n">
-        <v>3042</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3043</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QL Template (AMAPAC)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NP25</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>NP10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2023.1.0.50.0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>be40-02j-eus2</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-les</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>bh10</t>
         </is>
       </c>
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
       <c r="B52" t="n">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>DEV-EU</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>NP10</t>
+          <t>NP11</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>bh10</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>bh10-00q-euw</t>
         </is>
       </c>
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B53" t="n">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DEV-EU</t>
+          <t>Bene</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>NP11</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>NP12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>bh10</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>bh10-00q-euw</t>
         </is>
       </c>
       <c r="O53" s="4" t="n"/>
@@ -4254,16 +4209,21 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bene</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>NP12</t>
+          <t>Castellbisbal multi client : GLOBAL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ES01</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4281,11 +4241,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GLOBAL</t>
+          <t>Castellbisbal multi client : SYNTHESIA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4313,11 +4273,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : SYNTHESIA</t>
+          <t>Castellbisbal multi client : INTERCOAT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4345,11 +4305,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : INTERCOAT</t>
+          <t>Castellbisbal multi client : INTERFAT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4377,11 +4337,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : INTERFAT</t>
+          <t>Castellbisbal multi client : DEMIX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4409,11 +4369,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : DEMIX</t>
+          <t>Castellbisbal multi client : GACHES</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4437,30 +4397,70 @@
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3051</v>
+        <v>3031</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GACHES</t>
+          <t>Span.IO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NP9</t>
+          <t>NP22</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PR18</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PR18A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ES01</t>
+          <t>FT1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>bh10</t>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>bh10-004-euw</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-span-les</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>be40-029-eus2</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
         </is>
       </c>
       <c r="O60" s="4" t="n"/>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30720" yWindow="-10815" windowWidth="24795" windowHeight="20100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -436,7 +436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -529,7 +529,6 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -538,12 +537,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -611,7 +608,6 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -674,6 +670,15 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -685,13 +690,13 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="171" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -780,7 +785,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN534" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN534"/>
+  <autoFilter ref="B1:AN534">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Affinity Petcare"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="B2:AN534">
+    <sortCondition ref="I1:I534"/>
+  </sortState>
   <tableColumns count="39">
     <tableColumn id="1" name="Client ID"/>
     <tableColumn id="2" name="Client"/>
@@ -831,9 +845,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -871,7 +885,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -977,7 +991,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1119,7 +1133,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1132,47 +1146,47 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R534"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.7109375" customWidth="1" min="1" max="1"/>
-    <col width="10.85546875" bestFit="1" customWidth="1" style="134" min="2" max="2"/>
-    <col width="33.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="56.42578125" customWidth="1" min="4" max="4"/>
+    <col width="15.6640625" customWidth="1" min="1" max="1"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="33.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="56.44140625" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="13.7109375" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" customWidth="1" min="7" max="7"/>
-    <col width="11.7109375" customWidth="1" min="8" max="8"/>
-    <col width="19.140625" customWidth="1" min="9" max="9"/>
+    <col width="25.88671875" customWidth="1" min="6" max="6"/>
+    <col width="15.109375" customWidth="1" min="7" max="7"/>
+    <col width="11.6640625" customWidth="1" min="8" max="8"/>
+    <col width="19.109375" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.140625" customWidth="1" min="11" max="11"/>
-    <col width="17.5703125" customWidth="1" min="12" max="12"/>
-    <col width="35.140625" customWidth="1" min="13" max="13"/>
-    <col width="25.28515625" customWidth="1" min="14" max="14"/>
-    <col width="33.42578125" customWidth="1" min="15" max="15"/>
+    <col width="18.109375" customWidth="1" min="11" max="11"/>
+    <col width="17.5546875" customWidth="1" min="12" max="12"/>
+    <col width="35.109375" customWidth="1" min="13" max="13"/>
+    <col width="25.33203125" customWidth="1" min="14" max="14"/>
+    <col width="33.44140625" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
+    <col width="35.88671875" customWidth="1" style="4" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.7109375" customWidth="1" min="20" max="20"/>
-    <col width="12.85546875" customWidth="1" min="21" max="23"/>
-    <col width="16.28515625" customWidth="1" min="24" max="24"/>
-    <col width="20.140625" customWidth="1" min="25" max="25"/>
-    <col width="20.5703125" customWidth="1" min="26" max="26"/>
-    <col width="14.85546875" customWidth="1" min="27" max="27"/>
+    <col width="27.6640625" customWidth="1" style="4" min="19" max="19"/>
+    <col width="14.6640625" customWidth="1" min="20" max="20"/>
+    <col width="12.88671875" customWidth="1" min="21" max="23"/>
+    <col width="16.33203125" customWidth="1" min="24" max="24"/>
+    <col width="20.109375" customWidth="1" min="25" max="25"/>
+    <col width="20.5546875" customWidth="1" min="26" max="26"/>
+    <col width="14.88671875" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5703125" customWidth="1" min="29" max="29"/>
-    <col width="16.140625" customWidth="1" min="30" max="30"/>
-    <col width="16.140625" customWidth="1" style="54" min="31" max="31"/>
-    <col width="22.85546875" customWidth="1" min="32" max="32"/>
-    <col width="17.28515625" customWidth="1" min="33" max="33"/>
-    <col width="16.28515625" customWidth="1" style="137" min="34" max="34"/>
-    <col width="22.85546875" customWidth="1" min="35" max="36"/>
-    <col width="31.85546875" customWidth="1" min="37" max="37"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.28515625" customWidth="1" min="41" max="41"/>
+    <col width="20.5546875" customWidth="1" min="29" max="29"/>
+    <col width="16.109375" customWidth="1" min="30" max="30"/>
+    <col width="16.109375" customWidth="1" style="139" min="31" max="31"/>
+    <col width="22.88671875" customWidth="1" min="32" max="32"/>
+    <col width="17.33203125" customWidth="1" min="33" max="33"/>
+    <col width="16.33203125" customWidth="1" style="140" min="34" max="34"/>
+    <col width="22.88671875" customWidth="1" min="35" max="36"/>
+    <col width="31.88671875" customWidth="1" min="37" max="37"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="33.33203125" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1264,8 +1278,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.25" customFormat="1" customHeight="1" s="65">
-      <c r="A2" s="64" t="n"/>
+    <row r="2" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="62">
+      <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
       </c>
@@ -1329,17 +1343,17 @@
           <t>1551 Normantown Rd, Romeoville, IL</t>
         </is>
       </c>
-      <c r="O2" s="94" t="inlineStr">
+      <c r="O2" s="91" t="inlineStr">
         <is>
           <t>6:30am - 12:30am M-F CST</t>
         </is>
       </c>
-      <c r="P2" s="128" t="inlineStr">
+      <c r="P2" s="124" t="inlineStr">
         <is>
           <t>hasbromanagement@gxo.com</t>
         </is>
       </c>
-      <c r="Q2" s="91" t="inlineStr">
+      <c r="Q2" s="88" t="inlineStr">
         <is>
           <t>cecelia.fox@gxo.com</t>
         </is>
@@ -1348,12 +1362,12 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="126" t="n"/>
+    <row r="3" hidden="1" ht="14.4" customHeight="1">
+      <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
       </c>
-      <c r="C3" s="98" t="inlineStr">
+      <c r="C3" s="95" t="inlineStr">
         <is>
           <t>Hasbro</t>
         </is>
@@ -1414,275 +1428,573 @@
         </is>
       </c>
       <c r="O3" s="26" t="n"/>
-      <c r="P3" s="128" t="n"/>
-      <c r="Q3" s="91" t="n"/>
+      <c r="P3" s="124" t="n"/>
+      <c r="Q3" s="88" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" thickBot="1">
+    <row r="4" hidden="1" ht="24" customHeight="1" thickBot="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Shawn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O4" s="95" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="23" t="n"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" t="n">
         <v>3001</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>LVMH - Loewe</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>NP3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>PR3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>PR3A</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>DJ1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2021.1.1.28.2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2021.1.1.28.2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>exec-wms-gxo-loewe-les</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>2353 U.S. 130, Dayton, NJ</t>
         </is>
       </c>
-      <c r="O5" s="26" t="inlineStr">
+      <c r="O4" s="137" t="inlineStr">
         <is>
           <t xml:space="preserve"> 7:00am – 3:30pm M-F EST</t>
         </is>
       </c>
-      <c r="P5" s="128" t="n"/>
-      <c r="Q5" s="91" t="inlineStr">
+      <c r="P4" s="124" t="n"/>
+      <c r="Q4" s="88" t="inlineStr">
         <is>
           <t>todd.pearce@gxo.com</t>
         </is>
       </c>
-      <c r="R5" s="23" t="n">
+      <c r="R4" s="23" t="n">
         <v>45148</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="5" hidden="1" ht="28.8" customHeight="1">
+      <c r="B5" s="27" t="n">
+        <v>3005</v>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Amyris</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>NP5</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>PR2</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>PR2A</t>
+        </is>
+      </c>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>HMA</t>
+        </is>
+      </c>
+      <c r="H5" s="63" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I5" s="63" t="n"/>
+      <c r="J5" s="63" t="n"/>
+      <c r="K5" s="63" t="n"/>
+      <c r="L5" s="63" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="63" t="inlineStr">
+        <is>
+          <t>Horn Lake, MS</t>
+        </is>
+      </c>
+      <c r="O5" s="64" t="inlineStr">
+        <is>
+          <t>8:00am CST</t>
+        </is>
+      </c>
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="65" t="inlineStr">
+        <is>
+          <t>steve.charnes@gxo.com, tim.serfess@gxo.com</t>
+        </is>
+      </c>
+      <c r="R5" s="66" t="n">
+        <v>45117</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" ht="14.4" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>3002</v>
-      </c>
-      <c r="O6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
+      <c r="B6" s="104" t="n">
+        <v>3006</v>
+      </c>
+      <c r="C6" s="104" t="inlineStr">
+        <is>
+          <t>Darigold</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>PR4</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>PR4A</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>BI1</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="n"/>
+      <c r="J6" s="27" t="n"/>
+      <c r="K6" s="27" t="n"/>
+      <c r="L6" s="27" t="n"/>
+      <c r="M6" s="27" t="n"/>
+      <c r="N6" s="27" t="inlineStr">
+        <is>
+          <t>4719 Market St, Boise, ID</t>
+        </is>
+      </c>
+      <c r="O6" s="108" t="inlineStr">
+        <is>
+          <t>5:00 AM-12:30 AM MTN</t>
+        </is>
+      </c>
+      <c r="P6" s="27" t="n"/>
+      <c r="Q6" s="65" t="inlineStr">
+        <is>
+          <t>john.ozmon@gxo.com</t>
+        </is>
+      </c>
+      <c r="R6" s="66" t="n">
+        <v>45140</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" ht="14.4" customHeight="1">
       <c r="B7" t="n">
-        <v>3003</v>
-      </c>
-      <c r="O7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
+        <v>3006</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Darigold</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NP6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PR5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PR5A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NI1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2021.1.1.28</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-darigold-les</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16570 Northside BLVD, Nampa, ID</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>24/7 MTN</t>
+        </is>
+      </c>
+      <c r="Q7" s="88" t="inlineStr">
+        <is>
+          <t>john.ozmon@gxo.com</t>
+        </is>
+      </c>
+      <c r="R7" s="23" t="n">
+        <v>45140</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" ht="14.4" customHeight="1">
       <c r="B8" t="n">
-        <v>3004</v>
-      </c>
-      <c r="O8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="23" t="n"/>
-    </row>
-    <row r="9" ht="30.75" customFormat="1" customHeight="1" s="27">
-      <c r="B9" s="27" t="n">
-        <v>3005</v>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>Amyris</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>NP5</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>PR2</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>PR2A</t>
-        </is>
-      </c>
-      <c r="G9" s="66" t="inlineStr">
-        <is>
-          <t>HMA</t>
-        </is>
-      </c>
-      <c r="H9" s="66" t="inlineStr">
+        <v>3008</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Alpargatas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PR6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PR6A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GO1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I9" s="66" t="n"/>
-      <c r="J9" s="66" t="n"/>
-      <c r="K9" s="66" t="n"/>
-      <c r="L9" s="66" t="n"/>
-      <c r="M9" s="66" t="n"/>
-      <c r="N9" s="66" t="inlineStr">
-        <is>
-          <t>Horn Lake, MS</t>
-        </is>
-      </c>
-      <c r="O9" s="67" t="inlineStr">
-        <is>
-          <t>8:00am CST</t>
-        </is>
-      </c>
-      <c r="P9" s="66" t="n"/>
-      <c r="Q9" s="68" t="inlineStr">
-        <is>
-          <t>steve.charnes@gxo.com, tim.serfess@gxo.com</t>
-        </is>
-      </c>
-      <c r="R9" s="69" t="n">
-        <v>45117</v>
-      </c>
-    </row>
-    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="27">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-alpargata-les</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3650 Brookham Drive , Grove City, OH</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t>6:30 am - 5:00 pm EST</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Routing.alps@gxo.com</t>
+        </is>
+      </c>
+      <c r="Q8" s="88" t="inlineStr">
+        <is>
+          <t>john.hunter001@gxo.com</t>
+        </is>
+      </c>
+      <c r="R8" s="23" t="n">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
+      <c r="B9" t="n">
+        <v>3009</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Soda Stream</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NP10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PR10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PR10A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MC1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-sodastream-west-les</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1336 Dupont Ct, Manteca, CA</t>
+        </is>
+      </c>
+      <c r="O9" s="26" t="inlineStr">
+        <is>
+          <t>7:00 am to 3:30 pm</t>
+        </is>
+      </c>
+      <c r="P9" s="124" t="inlineStr">
+        <is>
+          <t>SodaStreamManteca@gxo.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="88" t="inlineStr">
+        <is>
+          <t>rafa.duenas@gxo.com   , Ron.biggs@gxo.com</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="n">
+        <v>45299</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Shawn</t>
         </is>
       </c>
-      <c r="B10" s="108" t="n">
-        <v>3006</v>
-      </c>
-      <c r="C10" s="108" t="inlineStr">
-        <is>
-          <t>Darigold</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>PR4</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>PR4A</t>
-        </is>
-      </c>
-      <c r="G10" s="27" t="inlineStr">
-        <is>
-          <t>BI1</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="inlineStr">
+      <c r="B10" s="79" t="n">
+        <v>3009</v>
+      </c>
+      <c r="C10" s="79" t="inlineStr">
+        <is>
+          <t>Soda Stream</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NP12</t>
+        </is>
+      </c>
+      <c r="E10" s="79" t="inlineStr">
+        <is>
+          <t>PR13</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PR13A</t>
+        </is>
+      </c>
+      <c r="G10" s="79" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N10" s="27" t="inlineStr">
-        <is>
-          <t>4719 Market St, Boise, ID</t>
-        </is>
-      </c>
-      <c r="O10" s="112" t="inlineStr">
-        <is>
-          <t>5:00 AM-12:30 AM MTN</t>
-        </is>
-      </c>
-      <c r="Q10" s="68" t="inlineStr">
-        <is>
-          <t>john.ozmon@gxo.com</t>
-        </is>
-      </c>
-      <c r="R10" s="69" t="n">
-        <v>45140</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2021.1.1.66</t>
+        </is>
+      </c>
+      <c r="J10" s="79" t="inlineStr">
+        <is>
+          <t>2021.1.1.28.3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="79" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-sodastream-east-les</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="79" t="inlineStr">
+        <is>
+          <t>4406 Industrial Park Rd, Camp Hill, PA</t>
+        </is>
+      </c>
+      <c r="O10" s="80" t="inlineStr">
+        <is>
+          <t>5:30 am EST - 7 pm EST</t>
+        </is>
+      </c>
+      <c r="P10" s="79" t="n"/>
+      <c r="Q10" s="81" t="inlineStr">
+        <is>
+          <t>chris.menges@gxo.com</t>
+        </is>
+      </c>
+      <c r="R10" s="141" t="n">
+        <v>45516</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" ht="43.2" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3006</v>
+        <v>3010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Darigold</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NP6</t>
+          <t>NP14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PR5</t>
+          <t>PR14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PR5A</t>
+          <t>PR14A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NI1</t>
+          <t>LV1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1692,2276 +2004,1521 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2021.1.1.28</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-darigold-les</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>16570 Northside BLVD, Nampa, ID</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>24/7 MTN</t>
-        </is>
-      </c>
-      <c r="Q11" s="91" t="inlineStr">
-        <is>
-          <t>john.ozmon@gxo.com</t>
-        </is>
-      </c>
-      <c r="R11" s="23" t="n">
-        <v>45140</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customFormat="1" customHeight="1" s="27">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>Mike/Lisa</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="n">
-        <v>3007</v>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>Do not use, in service now as revival</t>
-        </is>
-      </c>
-      <c r="O12" s="112" t="n"/>
-      <c r="Q12" s="112" t="n"/>
-      <c r="R12" s="69" t="n"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="B13" t="n">
-        <v>3008</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Alpargatas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PR6</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PR6A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GO1</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.4</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-alpargata-les</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>3650 Brookham Drive , Grove City, OH</t>
-        </is>
-      </c>
-      <c r="O13" s="26" t="inlineStr">
-        <is>
-          <t>6:30 am - 5:00 pm EST</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Routing.alps@gxo.com</t>
-        </is>
-      </c>
-      <c r="Q13" s="91" t="inlineStr">
-        <is>
-          <t>john.hunter001@gxo.com</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="n">
-        <v>45231</v>
-      </c>
-    </row>
-    <row r="14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mike/Heather</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3009</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Soda Stream</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NP10</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PR10</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PR10A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MC1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-sodastream-west-les</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1336 Dupont Ct, Manteca, CA</t>
-        </is>
-      </c>
-      <c r="O14" s="26" t="inlineStr">
-        <is>
-          <t>7:00 am to 3:30 pm</t>
-        </is>
-      </c>
-      <c r="P14" s="128" t="inlineStr">
-        <is>
-          <t>SodaStreamManteca@gxo.com</t>
-        </is>
-      </c>
-      <c r="Q14" s="91" t="inlineStr">
-        <is>
-          <t>rafa.duenas@gxo.com   , Ron.biggs@gxo.com</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="n">
-        <v>45299</v>
-      </c>
-    </row>
-    <row r="15" ht="29.25" customFormat="1" customHeight="1" s="82">
-      <c r="A15" s="82" t="inlineStr">
-        <is>
-          <t>Lisa/Linda</t>
-        </is>
-      </c>
-      <c r="B15" s="82" t="n">
-        <v>3009</v>
-      </c>
-      <c r="C15" s="82" t="inlineStr">
-        <is>
-          <t>Soda Stream</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NP12</t>
-        </is>
-      </c>
-      <c r="E15" s="82" t="inlineStr">
-        <is>
-          <t>PR13</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PR13A</t>
-        </is>
-      </c>
-      <c r="G15" s="82" t="inlineStr">
-        <is>
-          <t>CPO</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2021.1.1.66</t>
-        </is>
-      </c>
-      <c r="J15" s="82" t="inlineStr">
-        <is>
-          <t>2021.1.1.28.3</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="82" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-sodastream-east-les</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="82" t="inlineStr">
-        <is>
-          <t>4406 Industrial Park Rd, Camp Hill, PA</t>
-        </is>
-      </c>
-      <c r="O15" s="83" t="inlineStr">
-        <is>
-          <t>5:30 am EST - 7 pm EST</t>
-        </is>
-      </c>
-      <c r="Q15" s="84" t="inlineStr">
-        <is>
-          <t>chris.menges@gxo.com</t>
-        </is>
-      </c>
-      <c r="R15" s="138" t="n">
-        <v>45516</v>
-      </c>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lisa/Linda</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3010</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Starbucks</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NP14</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PR14</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PR14A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LV1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="J16" s="94" t="inlineStr">
+      <c r="J11" s="91" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="K16" s="94" t="inlineStr">
+      <c r="K11" s="91" t="inlineStr">
         <is>
           <t>be40-01p-eus2</t>
         </is>
       </c>
-      <c r="L16" s="94" t="inlineStr">
+      <c r="L11" s="91" t="inlineStr">
         <is>
           <t>exec-wms-gxo-starbucks-les</t>
         </is>
       </c>
-      <c r="M16" s="94" t="inlineStr">
+      <c r="M11" s="91" t="inlineStr">
         <is>
           <t>gxoe-prod</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">
 2401 N Chain Drive
 FG8: F CDC Simi Valley, CA  93065</t>
         </is>
       </c>
-      <c r="O16" s="4" t="n"/>
-      <c r="Q16" s="91" t="inlineStr">
+      <c r="O11" s="4" t="n"/>
+      <c r="Q11" s="88" t="inlineStr">
         <is>
           <t>rick.kusimoto@gxo.com</t>
         </is>
       </c>
-      <c r="R16" s="23" t="n">
+      <c r="R11" s="23" t="n">
         <v>45733</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customFormat="1" customHeight="1" s="27">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>Colleen/Jeff</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="n">
+    <row r="12" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="27">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Mike/Lisa</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n">
         <v>3011</v>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>NP19</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>PR16</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>PR16A</t>
         </is>
       </c>
-      <c r="G17" s="27" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>FTL</t>
         </is>
       </c>
-      <c r="H17" s="27" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>2023.1.0.30.2</t>
         </is>
       </c>
-      <c r="L17" s="27" t="inlineStr">
+      <c r="L12" s="27" t="inlineStr">
         <is>
           <t>exec-wms-gxo-lg-les</t>
         </is>
       </c>
-      <c r="N17" s="27" t="inlineStr">
+      <c r="N12" s="27" t="inlineStr">
         <is>
           <t>14901 N Beach St, Fort Worth, TX</t>
         </is>
       </c>
-      <c r="O17" s="112" t="n"/>
-      <c r="Q17" s="112" t="inlineStr">
+      <c r="O12" s="108" t="n"/>
+      <c r="Q12" s="108" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="R17" s="113" t="n">
+      <c r="R12" s="109" t="n">
         <v>45754</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customFormat="1" customHeight="1" s="27">
-      <c r="B18" s="27" t="n">
-        <v>3012</v>
-      </c>
-      <c r="O18" s="112" t="n"/>
-      <c r="Q18" s="112" t="n"/>
-      <c r="R18" s="69" t="n"/>
-    </row>
-    <row r="19" ht="14.25" customFormat="1" customHeight="1" s="27">
-      <c r="B19" s="27" t="n">
-        <v>3013</v>
-      </c>
-      <c r="O19" s="112" t="n"/>
-      <c r="Q19" s="112" t="n"/>
-      <c r="R19" s="69" t="n"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="B20" t="n">
+    <row r="13" hidden="1" ht="14.4" customHeight="1">
+      <c r="B13" t="n">
         <v>3014</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Peloton Apparel &amp; Acc.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>NP7</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>PR8</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>PR8A</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>MP2</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2021.1.1.28.4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>exec-wms-gxo-peloton-les</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>341 Heinz St, Mechanicsburg, PA</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>M-F 0800-0130, Sat &amp; Sun 0600-2330 EST</t>
         </is>
       </c>
-      <c r="Q20" s="91" t="inlineStr">
+      <c r="Q13" s="88" t="inlineStr">
         <is>
           <t>john.hecker@gxo.com</t>
         </is>
       </c>
-      <c r="R20" s="23" t="n">
+      <c r="R13" s="23" t="n">
         <v>45201</v>
       </c>
     </row>
-    <row r="21" ht="33" customFormat="1" customHeight="1" s="27">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="n">
+    <row r="14" hidden="1" ht="30.75" customHeight="1" thickBot="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mike/Heather</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n">
         <v>3014</v>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Peloton Apparel &amp; Acc.</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>NP8</t>
         </is>
       </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>PR9</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>PR9A</t>
         </is>
       </c>
-      <c r="G21" s="27" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>BC1</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>3520 Cactus Ave, Bloomington, CA</t>
         </is>
       </c>
-      <c r="O21" s="112" t="inlineStr">
+      <c r="O14" s="108" t="inlineStr">
         <is>
           <t>6:00am - 6:00pm during Peak; 8:am-4:30pm Normal non-peak.  CST</t>
         </is>
       </c>
-      <c r="Q21" s="68" t="inlineStr">
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="65" t="inlineStr">
         <is>
           <t>jeremy.hoppe@gxo.com, levale.williams@gxo.com,savy.phauk@gxo.com</t>
         </is>
       </c>
-      <c r="R21" s="69" t="n">
+      <c r="R14" s="66" t="n">
         <v>45201</v>
       </c>
     </row>
-    <row r="22" ht="30.75" customHeight="1">
-      <c r="B22" t="n">
-        <v>3015</v>
-      </c>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="28.5" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="15" hidden="1" ht="29.25" customFormat="1" customHeight="1" s="79">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>Lisa/Linda</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>3016</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Corsair</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NP11</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>PR11</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>PR11A</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>XS1</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2021.1.1.28.3</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2021.1.1.28.3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>exec-wms-gxo-corsair-california-les</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>7140 N. CAJON BLVD.  San Bernandino, CA</t>
         </is>
       </c>
-      <c r="O23" s="94" t="inlineStr">
+      <c r="O15" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">
 7:00 am to 3:30 pm PST</t>
         </is>
       </c>
-      <c r="P23" s="128" t="inlineStr">
+      <c r="P15" s="124" t="inlineStr">
         <is>
           <t>CorsairSoCal@gxo.com</t>
         </is>
       </c>
-      <c r="Q23" s="91" t="inlineStr">
+      <c r="Q15" s="88" t="inlineStr">
         <is>
           <t>rafa.duenas@gxo.com</t>
         </is>
       </c>
-      <c r="R23" s="23" t="n">
+      <c r="R15" s="23" t="n">
         <v>45366</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Colleen</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="16" hidden="1" ht="48" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Lisa/Linda</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>3016</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Corsair</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NP27</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>PR20</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>PR20A</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>MON</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="K24" s="26" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>be40-02l-eus2</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>exec-wms-gxo-corsair-canada-les</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t>be40-02f-eus2</t>
         </is>
       </c>
-      <c r="N24" s="109" t="inlineStr">
+      <c r="N16" s="105" t="inlineStr">
         <is>
           <t>1695 Drew Rd. Unit 2, Mississauga, Ontario, CA, L5S 1J5</t>
         </is>
       </c>
-      <c r="O24" s="94" t="inlineStr">
+      <c r="O16" s="91" t="inlineStr">
         <is>
           <t>7:30 am to 4:30 pm EST</t>
         </is>
       </c>
-      <c r="P24" s="128" t="n"/>
-      <c r="Q24" s="91" t="n"/>
-      <c r="R24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="43.15" customHeight="1" thickBot="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Heather/Shawn</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+      <c r="P16" s="124" t="n"/>
+      <c r="Q16" s="88" t="n"/>
+      <c r="R16" s="23" t="n"/>
+    </row>
+    <row r="17" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Colleen/Jeff</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>3017</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Tobacco - Altria</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>PIN
 JMS
 WTN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" t="inlineStr">
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="O25" s="95" t="n"/>
-      <c r="Q25" s="91" t="inlineStr">
+      <c r="O17" s="4" t="n"/>
+      <c r="Q17" s="88" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
-      <c r="R25" s="23" t="n">
+      <c r="R17" s="23" t="n">
         <v>45677</v>
       </c>
     </row>
-    <row r="26" ht="42.75" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="18" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+      <c r="B18" t="n">
         <v>3018</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Tobacco - ITG</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>GXO funded</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>PIN
 JMS
 WTN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" t="inlineStr">
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="O26" s="4" t="n"/>
-      <c r="Q26" s="91" t="inlineStr">
+      <c r="O18" s="4" t="n"/>
+      <c r="Q18" s="88" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42.75" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="19" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+      <c r="B19" t="n">
         <v>3019</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Tobacco - CJ Logistics</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>GXO funded</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>PIN
 JMS
 WTN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" t="inlineStr">
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="O27" s="4" t="n"/>
-      <c r="Q27" s="91" t="inlineStr">
+      <c r="O19" s="4" t="n"/>
+      <c r="Q19" s="88" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42.75" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="20" hidden="1" ht="43.2" customHeight="1">
+      <c r="B20" t="n">
         <v>3020</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Tobacco - JTI</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>GXO funded</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>PIN
 JMS
 WTN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" t="inlineStr">
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n"/>
-      <c r="Q28" s="91" t="inlineStr">
+      <c r="O20" s="4" t="n"/>
+      <c r="Q20" s="88" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42.75" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="21" hidden="1" ht="33" customFormat="1" customHeight="1" s="27">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>3021</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Tobacco - Liggett</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>GXO funded</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>PIN
 JMS
 WTN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" t="inlineStr">
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n"/>
-      <c r="Q29" s="91" t="inlineStr">
+      <c r="O21" s="4" t="n"/>
+      <c r="Q21" s="88" t="inlineStr">
         <is>
           <t>brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28.5" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="22" hidden="1" ht="30.75" customHeight="1">
+      <c r="B22" t="n">
         <v>3022</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>AMIRI</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NP5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>PR2</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>PR2A</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>FBG</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2021.1.1.28.1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>2021.1.1.28.1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>exec-wms-gxo-amiri-les</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>4020 Falcon Parkway
 Flowery Branch, GA</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>7am EST - 7pm EST</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>mailto:brandon.conner@gxo.com</t>
-        </is>
-      </c>
-      <c r="R30" s="23" t="n">
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="23" t="n">
         <v>45397</v>
       </c>
     </row>
-    <row r="31" ht="28.5" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>Michael/Shawn</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="n">
+    <row r="23" hidden="1" ht="28.8" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="n">
         <v>3023</v>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Food52</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>NP13</t>
         </is>
       </c>
-      <c r="E31" s="27" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>PR12 - NO SSO</t>
         </is>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>PR12 - NO SSOA</t>
         </is>
       </c>
-      <c r="G31" s="27" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>HM1</t>
         </is>
       </c>
-      <c r="H31" s="27" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I31" s="27" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>2021.1.1.28.4</t>
         </is>
       </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="J23" s="27" t="inlineStr">
         <is>
           <t>2021.1.1.28.4</t>
         </is>
       </c>
-      <c r="K31" s="27" t="inlineStr">
+      <c r="K23" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L31" s="27" t="inlineStr">
+      <c r="L23" s="27" t="inlineStr">
         <is>
           <t>exec-wms-gxo-food52-les</t>
         </is>
       </c>
-      <c r="M31" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N31" s="136" t="inlineStr">
+      <c r="N23" s="132" t="inlineStr">
         <is>
           <t>6195 Highway 51 N, Suite 200, Horn Lake MS</t>
         </is>
       </c>
-      <c r="O31" s="67" t="inlineStr">
+      <c r="O23" s="64" t="inlineStr">
         <is>
           <t>8:00am CST-4:30 pm CST</t>
         </is>
       </c>
-      <c r="P31" s="27" t="n"/>
-      <c r="Q31" s="68" t="inlineStr">
+      <c r="P23" s="27" t="n"/>
+      <c r="Q23" s="65" t="inlineStr">
         <is>
           <t>steve.charnes@gxo.com, tim.serfess@gxo.com</t>
         </is>
       </c>
-      <c r="R31" s="69" t="n">
+      <c r="R23" s="66" t="n">
         <v>45432</v>
       </c>
     </row>
-    <row r="32" ht="54" customFormat="1" customHeight="1" s="27">
-      <c r="A32" s="27" t="inlineStr">
-        <is>
-          <t>Michael</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
+    <row r="24" hidden="1" ht="28.8" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Colleen</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="n">
         <v>3024</v>
       </c>
-      <c r="C32" s="27" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Dupont</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>NP18</t>
         </is>
       </c>
-      <c r="G32" s="27" t="inlineStr">
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="inlineStr">
         <is>
           <t>RVA</t>
         </is>
       </c>
-      <c r="H32" s="27" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="J32" s="27" t="inlineStr">
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="inlineStr">
         <is>
           <t>NOT ACTIVE</t>
         </is>
       </c>
-      <c r="K32" s="27" t="inlineStr">
+      <c r="K24" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M32" s="27" t="inlineStr">
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N32" s="112" t="inlineStr">
+      <c r="N24" s="108" t="inlineStr">
         <is>
           <t>1500 Bellwood Road, Richmond, VA, 23237</t>
         </is>
       </c>
-      <c r="O32" s="112" t="n"/>
-      <c r="Q32" s="68" t="inlineStr">
+      <c r="O24" s="108" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="65" t="inlineStr">
         <is>
           <t>dexter.sallet@gxo.com</t>
         </is>
       </c>
-      <c r="R32" s="69" t="inlineStr">
+      <c r="R24" s="66" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="42.75" customHeight="1">
-      <c r="B33" t="n">
+    <row r="25" hidden="1" ht="43.2" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Heather/Shawn</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>3025</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NP30</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>PR25</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>PR25A</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>XS1002</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>be40-02o-eus2</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>exec-wms-gxo-toast-les</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>7140 N. CAJON BLVD
 SAN BERNARDINO, CA 92407
 USA</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="O25" s="92" t="inlineStr">
         <is>
           <t>NEW TBD</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="B34" t="n">
+      <c r="Q25" s="4" t="n"/>
+    </row>
+    <row r="26" hidden="1" ht="14.4" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mike/Shawn</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>3026</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>PROJECT Bolt/Moonstone</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NP26 / NP35</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>PR49</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>PR49A</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>LGL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>be40-02k-eus2</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>exec-wms-gxo-on-les</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>125 Colvin Dr, Locust Grove, GA 30248</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>2 daily shifts and 1 shift on Saturday</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Mike/Jeff</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+      <c r="Q26" s="4" t="n"/>
+    </row>
+    <row r="27" hidden="1" ht="14.4" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mike/Shawn</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>3027</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Castore</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NP17</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>PR15</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>PR15A</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>XNI</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>be40-01y-eus2</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">exec-wms-gxo-castore-les </t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>be40-023-eus2</t>
         </is>
       </c>
-      <c r="O35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="28.5" customHeight="1">
-      <c r="B36" t="n">
+      <c r="O27" s="4" t="n"/>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>mailto:brandon.conner@gxo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" hidden="1" ht="28.8" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mike/Shawn</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>3028</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Mountain Warehouse</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NP21</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>PR17</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>PR17A</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>GPA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2023.1.0.30.0</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>2023.1.0.30.0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>be40-022-eus2</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>exec-wms-gxo-mw-les
 exec-wms-gxo-mt-les</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>be40-028-eus2</t>
         </is>
       </c>
-      <c r="N36" s="105" t="inlineStr">
+      <c r="N28" s="101" t="inlineStr">
         <is>
           <t>6111 Grayson Rd Harrisburg, PA</t>
         </is>
       </c>
-      <c r="O36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="42.75" customHeight="1">
-      <c r="B37" t="n">
+      <c r="O28" s="4" t="n"/>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>mailto:brandon.conner@gxo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" hidden="1" ht="43.2" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mike/Shawn</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>4025</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>HP Enterprise (HPE)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NP37</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>OMS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2023.1.0.50</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>6701 Legacy Blvd, Ste 101
 Olive Branch, MS 38654
 USA</t>
         </is>
       </c>
-      <c r="O37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="57" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3030</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Toolstation</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NP2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>PR2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>PR2A</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BNL</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2023.1.0.30.0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Not Setup</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-toolstation-les</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>DC1 - Brandpuntlaan Zuid 12, 2665 NZ Bleiswijk, Netherlands
-DC2 - Prismalaan Oost, 2665 Bleiswijk, Netherlands</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>IB/OB  - 5/12/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28.5" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3032</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Passenger Clothing Limited</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NP3</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PR1A</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>DN1</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2023.1.0.37.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2023.1.0.37</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>bh10-003-euw</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-passenger-les</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="O29" s="4" t="n"/>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>mailto:brandon.conner@gxo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" hidden="1" ht="28.8" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mike/Shawn</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3033</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WH Smith</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NP24</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>XNE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>bh10-002-euw</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="n"/>
-      <c r="Q39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="28.5" customHeight="1">
-      <c r="B40" t="n">
-        <v>3033</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>WH Smith</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NP24</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>XNE</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>bh10-002-euw</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>exec-wms-gxo-wh-smith-les</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>2353 US Highway 130
 Dayton, NJ 08810</t>
         </is>
       </c>
-      <c r="O40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
-    </row>
-    <row r="41" ht="28.5" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3034</v>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Project Phoenix Prenatal</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>NP6</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PR4</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>PR4A</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>WNL</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>bh10-006-euw</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-prenatal-les
-exec-wms-gxo-phoenix-les</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>bh10-009-euw</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>GXO Op Den Dries 1
-6019 RA Wessem, Netherlands</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>NP13 (PRENTAL AUTOMATION)</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="n"/>
-    </row>
-    <row r="42" ht="42.75" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+      <c r="O30" s="4" t="n"/>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>mailto:brandon.conner@gxo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" hidden="1" ht="43.2" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>Michael/Shawn</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>3035</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>RJR Plainfield</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NP29</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>PR21</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>PR21A</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>PIR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>be40-02n-eus2</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-plainfield-les</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>600 S Perry Rd
 Plainfield, IN 46168
 USA</t>
         </is>
       </c>
-      <c r="O42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n"/>
-    </row>
-    <row r="43" ht="42.75" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+      <c r="O31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+    </row>
+    <row r="32" hidden="1" ht="54" customFormat="1" customHeight="1" s="27">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>3035</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>RJR Orlando</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NP32</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>PR23</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>PR23A</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>OFR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>be40-02p-eus2</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-orlando-les</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>be40-02i-eus2</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>7469 PRESIDENTS DRIVE
 ORLANDO, FL 32809
 USA</t>
         </is>
       </c>
-      <c r="O43" s="4" t="n"/>
-      <c r="Q43" s="4" t="n"/>
-    </row>
-    <row r="44" ht="39.75" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3036</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Kumho (EU)</t>
-        </is>
-      </c>
-      <c r="D44" s="111" t="inlineStr">
-        <is>
-          <t>NP4</t>
-        </is>
-      </c>
-      <c r="E44" s="111" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F44" s="111" t="n"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>GE1</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>bh10-004-euw</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-kumho-les</t>
-        </is>
-      </c>
-      <c r="N44" s="110" t="inlineStr">
-        <is>
-          <t>GXO Marchamalo 2 
-Calle el Ventorro
-19180 Guadalajara, ES</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
-    </row>
-    <row r="45" ht="28.5" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3037</v>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Commscope</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NP7</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>VEE</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
+      <c r="O32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+    </row>
+    <row r="33" hidden="1" ht="43.2" customHeight="1">
+      <c r="B33" t="n">
+        <v>3035</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RJR Portland</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NP31</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PR24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PR24A</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RPO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>bh10-00d-euw</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-commscope-les</t>
-        </is>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>GXO Veenendaal
-Arsenaal 2, 3905 Veenendaal, NL</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3038</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Unilever</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n"/>
-    </row>
-    <row r="47" ht="42.75" customHeight="1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3035</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>RJR Portland</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NP31</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>PR24</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>PR24A</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>RPO</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>be40-02p-eus2</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-portland-les</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>be40-02q-eus2</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>3591 YEON AVE
 PORTLAND, OR 97210
 USA</t>
         </is>
       </c>
-      <c r="O47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="57" customHeight="1">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+      <c r="O33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+    </row>
+    <row r="34" hidden="1" ht="57.6" customHeight="1">
+      <c r="B34" t="n">
         <v>3035</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>RJR  Rural Hall, NC</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NP34</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>PR22</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>PR22A</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>RHN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>be40-02w-eus2</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-ruralhall-les</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>RJR
 200 FORUM PARKWAY
@@ -3969,795 +3526,1386 @@
 USA</t>
         </is>
       </c>
-      <c r="O48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
-    </row>
-    <row r="49" ht="14.25" customHeight="1">
-      <c r="B49" s="134" t="n">
-        <v>3041</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>QL Template (EU)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NP5</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="O34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n"/>
+    </row>
+    <row r="35" hidden="1" ht="14.4" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mike/Jeff</t>
+        </is>
+      </c>
+      <c r="B35" s="130" t="n">
+        <v>3042</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>QL Template (AMAPAC)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NP25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2023.1.0.50.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>be40-02j-eus2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-les</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n"/>
+    </row>
+    <row r="36" hidden="1" ht="14.4" customHeight="1">
+      <c r="B36" t="n">
+        <v>3031</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Span.IO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NP22</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PR18</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PR18A</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>FT1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>bh10-004-euw</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-span-les</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>be40-029-eus2</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n"/>
+    </row>
+    <row r="37" hidden="1" ht="14.4" customHeight="1">
+      <c r="B37" t="n">
+        <v>3056</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Riviana</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NP38</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>WIL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n"/>
+    </row>
+    <row r="38" hidden="1" ht="57.6" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Toolstation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NP2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PR2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PR2A</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>BNL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Not Setup</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-les</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
-    </row>
-    <row r="50" ht="14.25" customHeight="1">
-      <c r="B50" s="134" t="n">
-        <v>3042</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>QL Template (AMAPAC)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NP25</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-toolstation-les</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>DC1 - Brandpuntlaan Zuid 12, 2665 NZ Bleiswijk, Netherlands
+DC2 - Prismalaan Oost, 2665 Bleiswijk, Netherlands</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>IB/OB  - 5/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" hidden="1" ht="28.8" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3032</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Passenger Clothing Limited</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NP3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PR1A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DN1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2023.1.0.37.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2023.1.0.37</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>bh10-003-euw</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-passenger-les</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n"/>
+    </row>
+    <row r="40" hidden="1" ht="43.2" customHeight="1">
+      <c r="B40" t="n">
+        <v>3035</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RJR Fort Worth, TX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NP36</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PR27</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PR27A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>FTR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2023.1.0.50.0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>be40-02j-eus2</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-les</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
-    </row>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3043</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>NP10</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="B52" t="n">
-        <v>3044</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>DEV-EU</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>NP11</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>bh10-00q-euw</t>
-        </is>
-      </c>
-      <c r="O52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n"/>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3045</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>NP12</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O53" s="4" t="n"/>
-      <c r="Q53" s="4" t="n"/>
-    </row>
-    <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3046</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : GLOBAL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O54" s="4" t="n"/>
-      <c r="Q54" s="4" t="n"/>
-    </row>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3047</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : SYNTHESIA</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="14.25" customHeight="1">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3048</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : INTERCOAT</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O56" s="4" t="n"/>
-      <c r="Q56" s="4" t="n"/>
-    </row>
-    <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3049</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : INTERFAT</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="14.25" customHeight="1">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3050</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : DEMIX</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
-    </row>
-    <row r="59" ht="14.25" customHeight="1">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3051</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : GACHES</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n"/>
-    </row>
-    <row r="60" ht="14.25" customHeight="1">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3031</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Span.IO</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NP22</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>PR18</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>PR18A</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>FT1</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2023.1.0.30.0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2023.1.0.30.0</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>bh10-004-euw</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-span-les</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>be40-029-eus2</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
-        </is>
-      </c>
-      <c r="O60" s="4" t="n"/>
-      <c r="Q60" s="4" t="n"/>
-    </row>
-    <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>3052</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : MACDERMID</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3053</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : ENGIPLASTE</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
-    </row>
-    <row r="63" ht="14.25" customHeight="1">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3054</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : GLOKEM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3055</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : QUIMICALITE</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n"/>
-    </row>
-    <row r="65" ht="14.25" customHeight="1">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3056</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Riviana</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NP38</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>WIL</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="O65" s="4" t="n"/>
-      <c r="Q65" s="4" t="n"/>
-    </row>
-    <row r="66" ht="14.25" customHeight="1">
-      <c r="B66" s="135" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>QL Dev/Test Env for NP5</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NP14</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="O66" s="4" t="n"/>
-      <c r="Q66" s="4" t="n"/>
-    </row>
-    <row r="67" ht="14.25" customHeight="1">
-      <c r="B67" s="135" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>NP25 Dev/Test Env</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NP39</t>
-        </is>
-      </c>
-      <c r="O67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-    </row>
-    <row r="68" ht="42.75" customHeight="1">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>3035</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>RJR Fort Worth, TX</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NP36</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>PR27</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>PR27A</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>FTR</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>4801 Mercantile Dr
 Ft Worth, TX 76137
 USA</t>
         </is>
       </c>
-      <c r="O68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n"/>
-    </row>
-    <row r="69" ht="42.75" customHeight="1">
-      <c r="A69" t="inlineStr">
+      <c r="O40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n"/>
+    </row>
+    <row r="41" hidden="1" ht="28.8" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3034</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Project Phoenix Prenatal</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>NP6</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>WNL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>bh10-006-euw</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-prenatal-les
+exec-wms-gxo-phoenix-les</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>bh10-009-euw</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>GXO Op Den Dries 1
+6019 RA Wessem, Netherlands</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>NP13 (PRENTAL AUTOMATION)</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n"/>
+    </row>
+    <row r="42" hidden="1" ht="43.2" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B42" t="n">
         <v>3057</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Davine's Spa</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>NP40</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>MP1</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>336 Heinz St
 Mechanicsburg, PA 17055
 USA</t>
         </is>
       </c>
-      <c r="O69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n"/>
-    </row>
-    <row r="70" ht="42.75" customHeight="1">
+      <c r="O42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n"/>
+    </row>
+    <row r="43" hidden="1" ht="14.4" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1831</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NP41</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
+      <c r="Q43" s="4" t="n"/>
+    </row>
+    <row r="44" hidden="1" ht="41.4" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3036</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kumho (EU)</t>
+        </is>
+      </c>
+      <c r="D44" s="107" t="inlineStr">
+        <is>
+          <t>NP4</t>
+        </is>
+      </c>
+      <c r="E44" s="107" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F44" s="107" t="n"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>GE1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>bh10-004-euw</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-kumho-les</t>
+        </is>
+      </c>
+      <c r="N44" s="106" t="inlineStr">
+        <is>
+          <t>GXO Marchamalo 2 
+Calle el Ventorro
+19180 Guadalajara, ES</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n"/>
+    </row>
+    <row r="45" hidden="1" ht="28.8" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3037</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Commscope</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NP7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR5 </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PR5A</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>VEE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>bh10-00d-euw</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-commscope-les</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>GXO Veenendaal
+Arsenaal 2, 3905 Veenendaal, NL</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="n"/>
+      <c r="Q45" s="4" t="n"/>
+    </row>
+    <row r="46" hidden="1" ht="14.4" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3038</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unilever</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="n"/>
+      <c r="Q46" s="4" t="n"/>
+    </row>
+    <row r="47" hidden="1" ht="43.2" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3060</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oh Polly</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NP42</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>202 Park West Dr
+West Jefferson, OH
+USA</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+    </row>
+    <row r="48" hidden="1" ht="43.2" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3026</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GXO (Multi Tenant)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NP43</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MEV</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Calle Guadalupana Manzana 015
+54980 Santiago Teyahualco
+Estado de México</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+    </row>
+    <row r="49" hidden="1" ht="14.4" customHeight="1">
+      <c r="B49" s="130" t="n">
+        <v>3041</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>QL Template (EU)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NP5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Not Setup</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-les</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n"/>
+    </row>
+    <row r="50" hidden="1" ht="43.2" customHeight="1">
+      <c r="B50" t="n">
+        <v>3063</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nodor</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NP45</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DJ1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>2353 US-130
+Dayton, NJ 08810
+USA</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+    </row>
+    <row r="51" hidden="1" ht="14.4" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3043</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>NP10</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n"/>
+    </row>
+    <row r="52" hidden="1" ht="14.4" customHeight="1">
+      <c r="B52" t="n">
+        <v>3044</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DEV-EU</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>NP11</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>bh10-00q-euw</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+    </row>
+    <row r="53" hidden="1" ht="14.4" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3045</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>NP12</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="n"/>
+      <c r="Q53" s="4" t="n"/>
+    </row>
+    <row r="54" hidden="1" ht="14.4" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3046</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : GLOBAL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="n"/>
+      <c r="Q54" s="4" t="n"/>
+    </row>
+    <row r="55" hidden="1" ht="14.4" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3047</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : SYNTHESIA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n"/>
+    </row>
+    <row r="56" hidden="1" ht="14.4" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3048</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : INTERCOAT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+    </row>
+    <row r="57" hidden="1" ht="14.4" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3049</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : INTERFAT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n"/>
+    </row>
+    <row r="58" hidden="1" ht="14.4" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3050</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : DEMIX</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+    </row>
+    <row r="59" hidden="1" ht="14.4" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3051</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : GACHES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="n"/>
+      <c r="Q59" s="4" t="n"/>
+    </row>
+    <row r="60" hidden="1" ht="14.4" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O60" s="4" t="n"/>
+      <c r="Q60" s="4" t="n"/>
+      <c r="R60" s="23" t="n"/>
+    </row>
+    <row r="61" hidden="1" ht="14.4" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3052</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : MACDERMID</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n"/>
+    </row>
+    <row r="62" hidden="1" ht="14.4" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3053</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : ENGIPLASTE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="n"/>
+      <c r="Q62" s="4" t="n"/>
+    </row>
+    <row r="63" hidden="1" ht="14.4" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3054</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : GLOKEM</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n"/>
+    </row>
+    <row r="64" hidden="1" ht="14.4" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3055</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : QUIMICALITE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="n"/>
+      <c r="Q64" s="4" t="n"/>
+    </row>
+    <row r="65" hidden="1" ht="14.4" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3002</v>
+      </c>
+      <c r="O65" s="4" t="n"/>
+      <c r="Q65" s="4" t="n"/>
+      <c r="R65" s="23" t="n"/>
+    </row>
+    <row r="66" hidden="1" ht="14.4" customHeight="1">
+      <c r="B66" s="131" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>QL Dev/Test Env for NP5</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NP14</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="n"/>
+      <c r="Q66" s="4" t="n"/>
+    </row>
+    <row r="67" hidden="1" ht="14.4" customHeight="1">
+      <c r="B67" t="n">
+        <v>3003</v>
+      </c>
+      <c r="O67" s="4" t="n"/>
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="23" t="n"/>
+    </row>
+    <row r="68" hidden="1" ht="14.4" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3004</v>
+      </c>
+      <c r="O68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n"/>
+      <c r="R68" s="23" t="n"/>
+    </row>
+    <row r="69" hidden="1" ht="14.4" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="n">
+        <v>3007</v>
+      </c>
+      <c r="C69" s="27" t="inlineStr">
+        <is>
+          <t>Do not use, in service now as revival</t>
+        </is>
+      </c>
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="27" t="n"/>
+      <c r="F69" s="27" t="n"/>
+      <c r="G69" s="27" t="n"/>
+      <c r="H69" s="27" t="n"/>
+      <c r="I69" s="27" t="n"/>
+      <c r="J69" s="27" t="n"/>
+      <c r="K69" s="27" t="n"/>
+      <c r="L69" s="27" t="n"/>
+      <c r="M69" s="27" t="n"/>
+      <c r="N69" s="27" t="n"/>
+      <c r="O69" s="108" t="n"/>
+      <c r="P69" s="27" t="n"/>
+      <c r="Q69" s="108" t="n"/>
+      <c r="R69" s="66" t="n"/>
+    </row>
+    <row r="70" hidden="1" ht="43.2" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4796,40 +4944,33 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" hidden="1" ht="14.4" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1831</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ITG Tobacco</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NP41</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="n"/>
-      <c r="Q71" s="4" t="n"/>
-    </row>
-    <row r="72" ht="14.25" customHeight="1">
+      <c r="B71" s="27" t="n">
+        <v>3012</v>
+      </c>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
+      <c r="I71" s="27" t="n"/>
+      <c r="J71" s="27" t="n"/>
+      <c r="K71" s="27" t="n"/>
+      <c r="L71" s="27" t="n"/>
+      <c r="M71" s="27" t="n"/>
+      <c r="N71" s="27" t="n"/>
+      <c r="O71" s="108" t="n"/>
+      <c r="P71" s="27" t="n"/>
+      <c r="Q71" s="108" t="n"/>
+      <c r="R71" s="66" t="n"/>
+    </row>
+    <row r="72" hidden="1" ht="14.4" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4861,46 +5002,33 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" ht="42.75" customHeight="1">
+    <row r="73" hidden="1" ht="14.4" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>3060</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Vuori</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NP42</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N73" s="4" t="inlineStr">
-        <is>
-          <t>202 Park West Dr
-West Jefferson, OH
-USA</t>
-        </is>
-      </c>
-      <c r="O73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n"/>
-    </row>
-    <row r="74" ht="14.25" customHeight="1">
+      <c r="B73" s="27" t="n">
+        <v>3013</v>
+      </c>
+      <c r="C73" s="27" t="n"/>
+      <c r="D73" s="27" t="n"/>
+      <c r="E73" s="27" t="n"/>
+      <c r="F73" s="27" t="n"/>
+      <c r="G73" s="27" t="n"/>
+      <c r="H73" s="27" t="n"/>
+      <c r="I73" s="27" t="n"/>
+      <c r="J73" s="27" t="n"/>
+      <c r="K73" s="27" t="n"/>
+      <c r="L73" s="27" t="n"/>
+      <c r="M73" s="27" t="n"/>
+      <c r="N73" s="27" t="n"/>
+      <c r="O73" s="108" t="n"/>
+      <c r="P73" s="27" t="n"/>
+      <c r="Q73" s="108" t="n"/>
+      <c r="R73" s="66" t="n"/>
+    </row>
+    <row r="74" hidden="1" ht="14.4" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4932,7 +5060,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" hidden="1" ht="14.4" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4969,3203 +5097,3349 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" hidden="1" ht="43.2" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3026</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BY request: 05706575</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t>Calle Guadalupana Manzana 015
-54980 Santiago Teyahualco
-Estado de México</t>
-        </is>
-      </c>
+        <v>3015</v>
+      </c>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
-    </row>
-    <row r="77" ht="14.25" customHeight="1">
-      <c r="B77" t="n">
-        <v>3063</v>
+      <c r="R76" s="23" t="n"/>
+    </row>
+    <row r="77" hidden="1" ht="14.4" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B77" s="131" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NP25 Dev/Test Env</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NP39</t>
+        </is>
       </c>
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" ht="14.4" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B78" t="n">
         <v>3064</v>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Affinity Petcare</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NP19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>FR01</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" hidden="1" ht="57.6" customHeight="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B79" t="n">
         <v>3065</v>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Columbia Sportswear Distribution SaS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NP20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>FR02</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>1542 Avenue des Deux Vallees Parc d'Activites Actipole de l'A25
+9954 Raillencourt Sainte Olle
+France</t>
+        </is>
+      </c>
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" hidden="1" ht="43.2" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B80" t="n">
         <v>3066</v>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GXO (Multi Tenant)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NP21</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>IT02</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>Via della Libertà, 215
+28043 Bellinzago Novarese NO
+Italy</t>
+        </is>
+      </c>
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" hidden="1" ht="28.8" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B81" t="n">
         <v>3067</v>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nodor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NP3</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PR1A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>DN1</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2023.1.0.37.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2023.1.0.37</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>bh10-003-euw</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-passenger-les</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
+        </is>
+      </c>
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" hidden="1" ht="14.4" customHeight="1">
       <c r="B82" t="n">
         <v>3068</v>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" hidden="1" ht="14.4" customHeight="1">
       <c r="B83" t="n">
         <v>3069</v>
       </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" hidden="1" ht="14.4" customHeight="1">
       <c r="B84" t="n">
         <v>3070</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" hidden="1" ht="14.4" customHeight="1">
       <c r="B85" t="n">
         <v>3071</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" hidden="1" ht="14.4" customHeight="1">
       <c r="B86" t="n">
         <v>3072</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" hidden="1" ht="14.4" customHeight="1">
       <c r="B87" t="n">
         <v>3073</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" hidden="1" ht="14.4" customHeight="1">
       <c r="B88" t="n">
         <v>3074</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" hidden="1" ht="14.4" customHeight="1">
       <c r="B89" t="n">
         <v>3075</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" hidden="1" ht="14.4" customHeight="1">
       <c r="B90" t="n">
         <v>3076</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" hidden="1" ht="14.4" customHeight="1">
       <c r="B91" t="n">
         <v>3077</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" hidden="1" ht="14.4" customHeight="1">
       <c r="B92" t="n">
         <v>3078</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" hidden="1" ht="14.4" customHeight="1">
       <c r="B93" t="n">
         <v>3079</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" hidden="1" ht="14.4" customHeight="1">
       <c r="B94" t="n">
         <v>3080</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" hidden="1" ht="14.4" customHeight="1">
       <c r="B95" t="n">
         <v>3081</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" hidden="1" ht="14.4" customHeight="1">
       <c r="B96" t="n">
         <v>3082</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" hidden="1" ht="14.4" customHeight="1">
       <c r="B97" t="n">
         <v>3083</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" hidden="1" ht="14.4" customHeight="1">
       <c r="B98" t="n">
         <v>3084</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" hidden="1" ht="14.4" customHeight="1">
       <c r="B99" t="n">
         <v>3085</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" hidden="1" ht="14.4" customHeight="1">
       <c r="B100" t="n">
         <v>3086</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" hidden="1" ht="14.4" customHeight="1">
       <c r="B101" t="n">
         <v>3087</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" hidden="1" ht="14.4" customHeight="1">
       <c r="B102" t="n">
         <v>3088</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" hidden="1" ht="14.4" customHeight="1">
       <c r="B103" t="n">
         <v>3089</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" hidden="1" ht="14.4" customHeight="1">
       <c r="B104" t="n">
         <v>3090</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" hidden="1" ht="14.4" customHeight="1">
       <c r="B105" t="n">
         <v>3091</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" hidden="1" ht="14.4" customHeight="1">
       <c r="B106" t="n">
         <v>3092</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" hidden="1" ht="14.4" customHeight="1">
       <c r="B107" t="n">
         <v>3093</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" hidden="1" ht="14.4" customHeight="1">
       <c r="B108" t="n">
         <v>3094</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" hidden="1" ht="14.4" customHeight="1">
       <c r="B109" t="n">
         <v>3095</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" hidden="1" ht="14.4" customHeight="1">
       <c r="B110" t="n">
         <v>3096</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" hidden="1" ht="14.4" customHeight="1">
       <c r="B111" t="n">
         <v>3097</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" hidden="1" ht="14.4" customHeight="1">
       <c r="B112" t="n">
         <v>3098</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" hidden="1" ht="14.4" customHeight="1">
       <c r="B113" t="n">
         <v>3099</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" hidden="1" ht="14.4" customHeight="1">
       <c r="B114" t="n">
         <v>3100</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" hidden="1" ht="14.4" customHeight="1">
       <c r="B115" t="n">
         <v>3101</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" hidden="1" ht="14.4" customHeight="1">
       <c r="B116" t="n">
         <v>3102</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" hidden="1" ht="14.4" customHeight="1">
       <c r="B117" t="n">
         <v>3103</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" hidden="1" ht="14.4" customHeight="1">
       <c r="B118" t="n">
         <v>3104</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" hidden="1" ht="14.4" customHeight="1">
       <c r="B119" t="n">
         <v>3105</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" hidden="1" ht="14.4" customHeight="1">
       <c r="B120" t="n">
         <v>3106</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" hidden="1" ht="14.4" customHeight="1">
       <c r="B121" t="n">
         <v>3107</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" hidden="1" ht="14.4" customHeight="1">
       <c r="B122" t="n">
         <v>3108</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" hidden="1" ht="14.4" customHeight="1">
       <c r="B123" t="n">
         <v>3109</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" hidden="1" ht="14.4" customHeight="1">
       <c r="B124" t="n">
         <v>3110</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" hidden="1" ht="14.4" customHeight="1">
       <c r="B125" t="n">
         <v>3111</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" hidden="1" ht="14.4" customHeight="1">
       <c r="B126" t="n">
         <v>3112</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" hidden="1" ht="14.4" customHeight="1">
       <c r="B127" t="n">
         <v>3113</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" hidden="1" ht="14.4" customHeight="1">
       <c r="B128" t="n">
         <v>3114</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" hidden="1" ht="14.4" customHeight="1">
       <c r="B129" t="n">
         <v>3115</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" hidden="1" ht="14.4" customHeight="1">
       <c r="B130" t="n">
         <v>3116</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" hidden="1" ht="14.4" customHeight="1">
       <c r="B131" t="n">
         <v>3117</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" hidden="1" ht="14.4" customHeight="1">
       <c r="B132" t="n">
         <v>3118</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" hidden="1" ht="14.4" customHeight="1">
       <c r="B133" t="n">
         <v>3119</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" hidden="1" ht="14.4" customHeight="1">
       <c r="B134" t="n">
         <v>3120</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" hidden="1" ht="14.4" customHeight="1">
       <c r="B135" t="n">
         <v>3121</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" hidden="1" ht="14.4" customHeight="1">
       <c r="B136" t="n">
         <v>3122</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" hidden="1" ht="14.4" customHeight="1">
       <c r="B137" t="n">
         <v>3123</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" hidden="1" ht="14.4" customHeight="1">
       <c r="B138" t="n">
         <v>3124</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" hidden="1" ht="14.4" customHeight="1">
       <c r="B139" t="n">
         <v>3125</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" hidden="1" ht="14.4" customHeight="1">
       <c r="B140" t="n">
         <v>3126</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" hidden="1" ht="14.4" customHeight="1">
       <c r="B141" t="n">
         <v>3127</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" hidden="1" ht="14.4" customHeight="1">
       <c r="B142" t="n">
         <v>3128</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" hidden="1" ht="14.4" customHeight="1">
       <c r="B143" t="n">
         <v>3129</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" hidden="1" ht="14.4" customHeight="1">
       <c r="B144" t="n">
         <v>3130</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" hidden="1" ht="14.4" customHeight="1">
       <c r="B145" t="n">
         <v>3131</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" hidden="1" ht="14.4" customHeight="1">
       <c r="B146" t="n">
         <v>3132</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" hidden="1" ht="14.4" customHeight="1">
       <c r="B147" t="n">
         <v>3133</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" hidden="1" ht="14.4" customHeight="1">
       <c r="B148" t="n">
         <v>3134</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" hidden="1" ht="14.4" customHeight="1">
       <c r="B149" t="n">
         <v>3135</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" hidden="1" ht="14.4" customHeight="1">
       <c r="B150" t="n">
         <v>3136</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" hidden="1" ht="14.4" customHeight="1">
       <c r="B151" t="n">
         <v>3137</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" hidden="1" ht="14.4" customHeight="1">
       <c r="B152" t="n">
         <v>3138</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" hidden="1" ht="14.4" customHeight="1">
       <c r="B153" t="n">
         <v>3139</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" hidden="1" ht="14.4" customHeight="1">
       <c r="B154" t="n">
         <v>3140</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" hidden="1" ht="14.4" customHeight="1">
       <c r="B155" t="n">
         <v>3141</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" hidden="1" ht="14.4" customHeight="1">
       <c r="B156" t="n">
         <v>3142</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" hidden="1" ht="14.4" customHeight="1">
       <c r="B157" t="n">
         <v>3143</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" hidden="1" ht="14.4" customHeight="1">
       <c r="B158" t="n">
         <v>3144</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" hidden="1" ht="14.4" customHeight="1">
       <c r="B159" t="n">
         <v>3145</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" hidden="1" ht="14.4" customHeight="1">
       <c r="B160" t="n">
         <v>3146</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" hidden="1" ht="14.4" customHeight="1">
       <c r="B161" t="n">
         <v>3147</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" hidden="1" ht="14.4" customHeight="1">
       <c r="B162" t="n">
         <v>3148</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" hidden="1" ht="14.4" customHeight="1">
       <c r="B163" t="n">
         <v>3149</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" hidden="1" ht="14.4" customHeight="1">
       <c r="B164" t="n">
         <v>3150</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" hidden="1" ht="14.4" customHeight="1">
       <c r="B165" t="n">
         <v>3151</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" hidden="1" ht="14.4" customHeight="1">
       <c r="B166" t="n">
         <v>3152</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" hidden="1" ht="14.4" customHeight="1">
       <c r="B167" t="n">
         <v>3153</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" hidden="1" ht="14.4" customHeight="1">
       <c r="B168" t="n">
         <v>3154</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" hidden="1" ht="14.4" customHeight="1">
       <c r="B169" t="n">
         <v>3155</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" hidden="1" ht="14.4" customHeight="1">
       <c r="B170" t="n">
         <v>3156</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" hidden="1" ht="14.4" customHeight="1">
       <c r="B171" t="n">
         <v>3157</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" hidden="1" ht="14.4" customHeight="1">
       <c r="B172" t="n">
         <v>3158</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" hidden="1" ht="14.4" customHeight="1">
       <c r="B173" t="n">
         <v>3159</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" hidden="1" ht="14.4" customHeight="1">
       <c r="B174" t="n">
         <v>3160</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" hidden="1" ht="14.4" customHeight="1">
       <c r="B175" t="n">
         <v>3161</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" hidden="1" ht="14.4" customHeight="1">
       <c r="B176" t="n">
         <v>3162</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" hidden="1" ht="14.4" customHeight="1">
       <c r="B177" t="n">
         <v>3163</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" hidden="1" ht="14.4" customHeight="1">
       <c r="B178" t="n">
         <v>3164</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" hidden="1" ht="14.4" customHeight="1">
       <c r="B179" t="n">
         <v>3165</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" hidden="1" ht="14.4" customHeight="1">
       <c r="B180" t="n">
         <v>3166</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" hidden="1" ht="14.4" customHeight="1">
       <c r="B181" t="n">
         <v>3167</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" hidden="1" ht="14.4" customHeight="1">
       <c r="B182" t="n">
         <v>3168</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" hidden="1" ht="14.4" customHeight="1">
       <c r="B183" t="n">
         <v>3169</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" hidden="1" ht="14.4" customHeight="1">
       <c r="B184" t="n">
         <v>3170</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" hidden="1" ht="14.4" customHeight="1">
       <c r="B185" t="n">
         <v>3171</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" hidden="1" ht="14.4" customHeight="1">
       <c r="B186" t="n">
         <v>3172</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" hidden="1" ht="14.4" customHeight="1">
       <c r="B187" t="n">
         <v>3173</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" hidden="1" ht="14.4" customHeight="1">
       <c r="B188" t="n">
         <v>3174</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" hidden="1" ht="14.4" customHeight="1">
       <c r="B189" t="n">
         <v>3175</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" hidden="1" ht="14.4" customHeight="1">
       <c r="B190" t="n">
         <v>3176</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" hidden="1" ht="14.4" customHeight="1">
       <c r="B191" t="n">
         <v>3177</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" hidden="1" ht="14.4" customHeight="1">
       <c r="B192" t="n">
         <v>3178</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" hidden="1" ht="14.4" customHeight="1">
       <c r="B193" t="n">
         <v>3179</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" hidden="1" ht="14.4" customHeight="1">
       <c r="B194" t="n">
         <v>3180</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" hidden="1" ht="14.4" customHeight="1">
       <c r="B195" t="n">
         <v>3181</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" hidden="1" ht="14.4" customHeight="1">
       <c r="B196" t="n">
         <v>3182</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" hidden="1" ht="14.4" customHeight="1">
       <c r="B197" t="n">
         <v>3183</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" hidden="1" ht="14.4" customHeight="1">
       <c r="B198" t="n">
         <v>3184</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" hidden="1" ht="14.4" customHeight="1">
       <c r="B199" t="n">
         <v>3185</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" hidden="1" ht="14.4" customHeight="1">
       <c r="B200" t="n">
         <v>3186</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" hidden="1" ht="14.4" customHeight="1">
       <c r="B201" t="n">
         <v>3187</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" hidden="1" ht="14.4" customHeight="1">
       <c r="B202" t="n">
         <v>3188</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" hidden="1" ht="14.4" customHeight="1">
       <c r="B203" t="n">
         <v>3189</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" hidden="1" ht="14.4" customHeight="1">
       <c r="B204" t="n">
         <v>3190</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" hidden="1" ht="14.4" customHeight="1">
       <c r="B205" t="n">
         <v>3191</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" hidden="1" ht="14.4" customHeight="1">
       <c r="B206" t="n">
         <v>3192</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" hidden="1" ht="14.4" customHeight="1">
       <c r="B207" t="n">
         <v>3193</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" hidden="1" ht="14.4" customHeight="1">
       <c r="B208" t="n">
         <v>3194</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" hidden="1" ht="14.4" customHeight="1">
       <c r="B209" t="n">
         <v>3195</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" hidden="1" ht="14.4" customHeight="1">
       <c r="B210" t="n">
         <v>3196</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" hidden="1" ht="14.4" customHeight="1">
       <c r="B211" t="n">
         <v>3197</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" hidden="1" ht="14.4" customHeight="1">
       <c r="B212" t="n">
         <v>3198</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" hidden="1" ht="14.4" customHeight="1">
       <c r="B213" t="n">
         <v>3199</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" hidden="1" ht="14.4" customHeight="1">
       <c r="B214" t="n">
         <v>3200</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" hidden="1" ht="14.4" customHeight="1">
       <c r="B215" t="n">
         <v>3201</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" hidden="1" ht="14.4" customHeight="1">
       <c r="B216" t="n">
         <v>3202</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" hidden="1" ht="14.4" customHeight="1">
       <c r="B217" t="n">
         <v>3203</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" hidden="1" ht="14.4" customHeight="1">
       <c r="B218" t="n">
         <v>3204</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" hidden="1" ht="14.4" customHeight="1">
       <c r="B219" t="n">
         <v>3205</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" hidden="1" ht="14.4" customHeight="1">
       <c r="B220" t="n">
         <v>3206</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" hidden="1" ht="14.4" customHeight="1">
       <c r="B221" t="n">
         <v>3207</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" hidden="1" ht="14.4" customHeight="1">
       <c r="B222" t="n">
         <v>3208</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" hidden="1" ht="14.4" customHeight="1">
       <c r="B223" t="n">
         <v>3209</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" hidden="1" ht="14.4" customHeight="1">
       <c r="B224" t="n">
         <v>3210</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" hidden="1" ht="14.4" customHeight="1">
       <c r="B225" t="n">
         <v>3211</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" hidden="1" ht="14.4" customHeight="1">
       <c r="B226" t="n">
         <v>3212</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" hidden="1" ht="14.4" customHeight="1">
       <c r="B227" t="n">
         <v>3213</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" hidden="1" ht="14.4" customHeight="1">
       <c r="B228" t="n">
         <v>3214</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" hidden="1" ht="14.4" customHeight="1">
       <c r="B229" t="n">
         <v>3215</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" hidden="1" ht="14.4" customHeight="1">
       <c r="B230" t="n">
         <v>3216</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" hidden="1" ht="14.4" customHeight="1">
       <c r="B231" t="n">
         <v>3217</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" hidden="1" ht="14.4" customHeight="1">
       <c r="B232" t="n">
         <v>3218</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" hidden="1" ht="14.4" customHeight="1">
       <c r="B233" t="n">
         <v>3219</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" hidden="1" ht="14.4" customHeight="1">
       <c r="B234" t="n">
         <v>3220</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" hidden="1" ht="14.4" customHeight="1">
       <c r="B235" t="n">
         <v>3221</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" hidden="1" ht="14.4" customHeight="1">
       <c r="B236" t="n">
         <v>3222</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" ht="14.25" customHeight="1">
+    <row r="237" hidden="1" ht="14.4" customHeight="1">
       <c r="B237" t="n">
         <v>3223</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
+    <row r="238" hidden="1" ht="14.4" customHeight="1">
       <c r="B238" t="n">
         <v>3224</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" ht="14.25" customHeight="1">
+    <row r="239" hidden="1" ht="14.4" customHeight="1">
       <c r="B239" t="n">
         <v>3225</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" ht="14.25" customHeight="1">
+    <row r="240" hidden="1" ht="14.4" customHeight="1">
       <c r="B240" t="n">
         <v>3226</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" ht="14.25" customHeight="1">
+    <row r="241" hidden="1" ht="14.4" customHeight="1">
       <c r="B241" t="n">
         <v>3227</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" ht="14.25" customHeight="1">
+    <row r="242" hidden="1" ht="14.4" customHeight="1">
       <c r="B242" t="n">
         <v>3228</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" ht="14.25" customHeight="1">
+    <row r="243" hidden="1" ht="14.4" customHeight="1">
       <c r="B243" t="n">
         <v>3229</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" ht="14.25" customHeight="1">
+    <row r="244" hidden="1" ht="14.4" customHeight="1">
       <c r="B244" t="n">
         <v>3230</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" ht="14.25" customHeight="1">
+    <row r="245" hidden="1" ht="14.4" customHeight="1">
       <c r="B245" t="n">
         <v>3231</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" ht="14.25" customHeight="1">
+    <row r="246" hidden="1" ht="14.4" customHeight="1">
       <c r="B246" t="n">
         <v>3232</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" ht="14.25" customHeight="1">
+    <row r="247" hidden="1" ht="14.4" customHeight="1">
       <c r="B247" t="n">
         <v>3233</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" ht="14.25" customHeight="1">
+    <row r="248" hidden="1" ht="14.4" customHeight="1">
       <c r="B248" t="n">
         <v>3234</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" ht="14.25" customHeight="1">
+    <row r="249" hidden="1" ht="14.4" customHeight="1">
       <c r="B249" t="n">
         <v>3235</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" ht="14.25" customHeight="1">
+    <row r="250" hidden="1" ht="14.4" customHeight="1">
       <c r="B250" t="n">
         <v>3236</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" ht="14.25" customHeight="1">
+    <row r="251" hidden="1" ht="14.4" customHeight="1">
       <c r="B251" t="n">
         <v>3237</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" ht="14.25" customHeight="1">
+    <row r="252" hidden="1" ht="14.4" customHeight="1">
       <c r="B252" t="n">
         <v>3238</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" ht="14.25" customHeight="1">
+    <row r="253" hidden="1" ht="14.4" customHeight="1">
       <c r="B253" t="n">
         <v>3239</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" ht="14.25" customHeight="1">
+    <row r="254" hidden="1" ht="14.4" customHeight="1">
       <c r="B254" t="n">
         <v>3240</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" ht="14.25" customHeight="1">
+    <row r="255" hidden="1" ht="14.4" customHeight="1">
       <c r="B255" t="n">
         <v>3241</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" ht="14.25" customHeight="1">
+    <row r="256" hidden="1" ht="14.4" customHeight="1">
       <c r="B256" t="n">
         <v>3242</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" ht="14.25" customHeight="1">
+    <row r="257" hidden="1" ht="14.4" customHeight="1">
       <c r="B257" t="n">
         <v>3243</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" ht="14.25" customHeight="1">
+    <row r="258" hidden="1" ht="14.4" customHeight="1">
       <c r="B258" t="n">
         <v>3244</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" ht="14.25" customHeight="1">
+    <row r="259" hidden="1" ht="14.4" customHeight="1">
       <c r="B259" t="n">
         <v>3245</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" ht="14.25" customHeight="1">
+    <row r="260" hidden="1" ht="14.4" customHeight="1">
       <c r="B260" t="n">
         <v>3246</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" ht="14.25" customHeight="1">
+    <row r="261" hidden="1" ht="14.4" customHeight="1">
       <c r="B261" t="n">
         <v>3247</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" ht="14.25" customHeight="1">
+    <row r="262" hidden="1" ht="14.4" customHeight="1">
       <c r="B262" t="n">
         <v>3248</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" ht="14.25" customHeight="1">
+    <row r="263" hidden="1" ht="14.4" customHeight="1">
       <c r="B263" t="n">
         <v>3249</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" ht="14.25" customHeight="1">
+    <row r="264" hidden="1" ht="14.4" customHeight="1">
       <c r="B264" t="n">
         <v>3250</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" ht="14.25" customHeight="1">
+    <row r="265" hidden="1" ht="14.4" customHeight="1">
       <c r="B265" t="n">
         <v>3251</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" ht="14.25" customHeight="1">
+    <row r="266" hidden="1" ht="14.4" customHeight="1">
       <c r="B266" t="n">
         <v>3252</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" ht="14.25" customHeight="1">
+    <row r="267" hidden="1" ht="14.4" customHeight="1">
       <c r="B267" t="n">
         <v>3253</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" ht="14.25" customHeight="1">
+    <row r="268" hidden="1" ht="14.4" customHeight="1">
       <c r="B268" t="n">
         <v>3254</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" ht="14.25" customHeight="1">
+    <row r="269" hidden="1" ht="14.4" customHeight="1">
       <c r="B269" t="n">
         <v>3255</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" ht="14.25" customHeight="1">
+    <row r="270" hidden="1" ht="14.4" customHeight="1">
       <c r="B270" t="n">
         <v>3256</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" ht="14.25" customHeight="1">
+    <row r="271" hidden="1" ht="14.4" customHeight="1">
       <c r="B271" t="n">
         <v>3257</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" ht="14.25" customHeight="1">
+    <row r="272" hidden="1" ht="14.4" customHeight="1">
       <c r="B272" t="n">
         <v>3258</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" ht="14.25" customHeight="1">
+    <row r="273" hidden="1" ht="14.4" customHeight="1">
       <c r="B273" t="n">
         <v>3259</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" ht="14.25" customHeight="1">
+    <row r="274" hidden="1" ht="14.4" customHeight="1">
       <c r="B274" t="n">
         <v>3260</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" ht="14.25" customHeight="1">
+    <row r="275" hidden="1" ht="14.4" customHeight="1">
       <c r="B275" t="n">
         <v>3261</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" ht="14.25" customHeight="1">
+    <row r="276" hidden="1" ht="14.4" customHeight="1">
       <c r="B276" t="n">
         <v>3262</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" ht="14.25" customHeight="1">
+    <row r="277" hidden="1" ht="14.4" customHeight="1">
       <c r="B277" t="n">
         <v>3263</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" ht="14.25" customHeight="1">
+    <row r="278" hidden="1" ht="14.4" customHeight="1">
       <c r="B278" t="n">
         <v>3264</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" ht="14.25" customHeight="1">
+    <row r="279" hidden="1" ht="14.4" customHeight="1">
       <c r="B279" t="n">
         <v>3265</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" ht="14.25" customHeight="1">
+    <row r="280" hidden="1" ht="14.4" customHeight="1">
       <c r="B280" t="n">
         <v>3266</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" ht="14.25" customHeight="1">
+    <row r="281" hidden="1" ht="14.4" customHeight="1">
       <c r="B281" t="n">
         <v>3267</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" ht="14.25" customHeight="1">
+    <row r="282" hidden="1" ht="14.4" customHeight="1">
       <c r="B282" t="n">
         <v>3268</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" ht="14.25" customHeight="1">
+    <row r="283" hidden="1" ht="14.4" customHeight="1">
       <c r="B283" t="n">
         <v>3269</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" ht="14.25" customHeight="1">
+    <row r="284" hidden="1" ht="14.4" customHeight="1">
       <c r="B284" t="n">
         <v>3270</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" ht="14.25" customHeight="1">
+    <row r="285" hidden="1" ht="14.4" customHeight="1">
       <c r="B285" t="n">
         <v>3271</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" ht="14.25" customHeight="1">
+    <row r="286" hidden="1" ht="14.4" customHeight="1">
       <c r="B286" t="n">
         <v>3272</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" ht="14.25" customHeight="1">
+    <row r="287" hidden="1" ht="14.4" customHeight="1">
       <c r="B287" t="n">
         <v>3273</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" ht="14.25" customHeight="1">
+    <row r="288" hidden="1" ht="14.4" customHeight="1">
       <c r="B288" t="n">
         <v>3274</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" ht="14.25" customHeight="1">
+    <row r="289" hidden="1" ht="14.4" customHeight="1">
       <c r="B289" t="n">
         <v>3275</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" ht="14.25" customHeight="1">
+    <row r="290" hidden="1" ht="14.4" customHeight="1">
       <c r="B290" t="n">
         <v>3276</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" ht="14.25" customHeight="1">
+    <row r="291" hidden="1" ht="14.4" customHeight="1">
       <c r="B291" t="n">
         <v>3277</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" ht="14.25" customHeight="1">
+    <row r="292" hidden="1" ht="14.4" customHeight="1">
       <c r="B292" t="n">
         <v>3278</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" ht="14.25" customHeight="1">
+    <row r="293" hidden="1" ht="14.4" customHeight="1">
       <c r="B293" t="n">
         <v>3279</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" ht="14.25" customHeight="1">
+    <row r="294" hidden="1" ht="14.4" customHeight="1">
       <c r="B294" t="n">
         <v>3280</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" ht="14.25" customHeight="1">
+    <row r="295" hidden="1" ht="14.4" customHeight="1">
       <c r="B295" t="n">
         <v>3281</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" ht="14.25" customHeight="1">
+    <row r="296" hidden="1" ht="14.4" customHeight="1">
       <c r="B296" t="n">
         <v>3282</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" ht="14.25" customHeight="1">
+    <row r="297" hidden="1" ht="14.4" customHeight="1">
       <c r="B297" t="n">
         <v>3283</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" ht="14.25" customHeight="1">
+    <row r="298" hidden="1" ht="14.4" customHeight="1">
       <c r="B298" t="n">
         <v>3284</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" ht="14.25" customHeight="1">
+    <row r="299" hidden="1" ht="14.4" customHeight="1">
       <c r="B299" t="n">
         <v>3285</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" ht="14.25" customHeight="1">
+    <row r="300" hidden="1" ht="14.4" customHeight="1">
       <c r="B300" t="n">
         <v>3286</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" ht="14.25" customHeight="1">
+    <row r="301" hidden="1" ht="14.4" customHeight="1">
       <c r="B301" t="n">
         <v>3287</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" ht="14.25" customHeight="1">
+    <row r="302" hidden="1" ht="14.4" customHeight="1">
       <c r="B302" t="n">
         <v>3288</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" ht="14.25" customHeight="1">
+    <row r="303" hidden="1" ht="14.4" customHeight="1">
       <c r="B303" t="n">
         <v>3289</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" ht="14.25" customHeight="1">
+    <row r="304" hidden="1" ht="14.4" customHeight="1">
       <c r="B304" t="n">
         <v>3290</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" ht="14.25" customHeight="1">
+    <row r="305" hidden="1" ht="14.4" customHeight="1">
       <c r="B305" t="n">
         <v>3291</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" ht="14.25" customHeight="1">
+    <row r="306" hidden="1" ht="14.4" customHeight="1">
       <c r="B306" t="n">
         <v>3292</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" ht="14.25" customHeight="1">
+    <row r="307" hidden="1" ht="14.4" customHeight="1">
       <c r="B307" t="n">
         <v>3293</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" ht="14.25" customHeight="1">
+    <row r="308" hidden="1" ht="14.4" customHeight="1">
       <c r="B308" t="n">
         <v>3294</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" ht="14.25" customHeight="1">
+    <row r="309" hidden="1" ht="14.4" customHeight="1">
       <c r="B309" t="n">
         <v>3295</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" ht="14.25" customHeight="1">
+    <row r="310" hidden="1" ht="14.4" customHeight="1">
       <c r="B310" t="n">
         <v>3296</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" ht="14.25" customHeight="1">
+    <row r="311" hidden="1" ht="14.4" customHeight="1">
       <c r="B311" t="n">
         <v>3297</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" ht="14.25" customHeight="1">
+    <row r="312" hidden="1" ht="14.4" customHeight="1">
       <c r="B312" t="n">
         <v>3298</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" ht="14.25" customHeight="1">
+    <row r="313" hidden="1" ht="14.4" customHeight="1">
       <c r="B313" t="n">
         <v>3299</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" ht="14.25" customHeight="1">
+    <row r="314" hidden="1" ht="14.4" customHeight="1">
       <c r="B314" t="n">
         <v>3300</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" ht="14.25" customHeight="1">
+    <row r="315" hidden="1" ht="14.4" customHeight="1">
       <c r="B315" t="n">
         <v>3301</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" ht="14.25" customHeight="1">
+    <row r="316" hidden="1" ht="14.4" customHeight="1">
       <c r="B316" t="n">
         <v>3302</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" ht="14.25" customHeight="1">
+    <row r="317" hidden="1" ht="14.4" customHeight="1">
       <c r="B317" t="n">
         <v>3303</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" ht="14.25" customHeight="1">
+    <row r="318" hidden="1" ht="14.4" customHeight="1">
       <c r="B318" t="n">
         <v>3304</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" ht="14.25" customHeight="1">
+    <row r="319" hidden="1" ht="14.4" customHeight="1">
       <c r="B319" t="n">
         <v>3305</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" ht="14.25" customHeight="1">
+    <row r="320" hidden="1" ht="14.4" customHeight="1">
       <c r="B320" t="n">
         <v>3306</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" ht="14.25" customHeight="1">
+    <row r="321" hidden="1" ht="14.4" customHeight="1">
       <c r="B321" t="n">
         <v>3307</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" ht="14.25" customHeight="1">
+    <row r="322" hidden="1" ht="14.4" customHeight="1">
       <c r="B322" t="n">
         <v>3308</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" ht="14.25" customHeight="1">
+    <row r="323" hidden="1" ht="14.4" customHeight="1">
       <c r="B323" t="n">
         <v>3309</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" ht="14.25" customHeight="1">
+    <row r="324" hidden="1" ht="14.4" customHeight="1">
       <c r="B324" t="n">
         <v>3310</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" ht="14.25" customHeight="1">
+    <row r="325" hidden="1" ht="14.4" customHeight="1">
       <c r="B325" t="n">
         <v>3311</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" ht="14.25" customHeight="1">
+    <row r="326" hidden="1" ht="14.4" customHeight="1">
       <c r="B326" t="n">
         <v>3312</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" ht="14.25" customHeight="1">
+    <row r="327" hidden="1" ht="14.4" customHeight="1">
       <c r="B327" t="n">
         <v>3313</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" ht="14.25" customHeight="1">
+    <row r="328" hidden="1" ht="14.4" customHeight="1">
       <c r="B328" t="n">
         <v>3314</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" ht="14.25" customHeight="1">
+    <row r="329" hidden="1" ht="14.4" customHeight="1">
       <c r="B329" t="n">
         <v>3315</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" ht="14.25" customHeight="1">
+    <row r="330" hidden="1" ht="14.4" customHeight="1">
       <c r="B330" t="n">
         <v>3316</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" ht="14.25" customHeight="1">
+    <row r="331" hidden="1" ht="14.4" customHeight="1">
       <c r="B331" t="n">
         <v>3317</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" ht="14.25" customHeight="1">
+    <row r="332" hidden="1" ht="14.4" customHeight="1">
       <c r="B332" t="n">
         <v>3318</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" ht="14.25" customHeight="1">
+    <row r="333" hidden="1" ht="14.4" customHeight="1">
       <c r="B333" t="n">
         <v>3319</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" ht="14.25" customHeight="1">
+    <row r="334" hidden="1" ht="14.4" customHeight="1">
       <c r="B334" t="n">
         <v>3320</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" ht="14.25" customHeight="1">
+    <row r="335" hidden="1" ht="14.4" customHeight="1">
       <c r="B335" t="n">
         <v>3321</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" ht="14.25" customHeight="1">
+    <row r="336" hidden="1" ht="14.4" customHeight="1">
       <c r="B336" t="n">
         <v>3322</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" ht="14.25" customHeight="1">
+    <row r="337" hidden="1" ht="14.4" customHeight="1">
       <c r="B337" t="n">
         <v>3323</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" ht="14.25" customHeight="1">
+    <row r="338" hidden="1" ht="14.4" customHeight="1">
       <c r="B338" t="n">
         <v>3324</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" ht="14.25" customHeight="1">
+    <row r="339" hidden="1" ht="14.4" customHeight="1">
       <c r="B339" t="n">
         <v>3325</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" ht="14.25" customHeight="1">
+    <row r="340" hidden="1" ht="14.4" customHeight="1">
       <c r="B340" t="n">
         <v>3326</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" ht="14.25" customHeight="1">
+    <row r="341" hidden="1" ht="14.4" customHeight="1">
       <c r="B341" t="n">
         <v>3327</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" ht="14.25" customHeight="1">
+    <row r="342" hidden="1" ht="14.4" customHeight="1">
       <c r="B342" t="n">
         <v>3328</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" ht="14.25" customHeight="1">
+    <row r="343" hidden="1" ht="14.4" customHeight="1">
       <c r="B343" t="n">
         <v>3329</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" ht="14.25" customHeight="1">
+    <row r="344" hidden="1" ht="14.4" customHeight="1">
       <c r="B344" t="n">
         <v>3330</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" ht="14.25" customHeight="1">
+    <row r="345" hidden="1" ht="14.4" customHeight="1">
       <c r="B345" t="n">
         <v>3331</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" ht="14.25" customHeight="1">
+    <row r="346" hidden="1" ht="14.4" customHeight="1">
       <c r="B346" t="n">
         <v>3332</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" ht="14.25" customHeight="1">
+    <row r="347" hidden="1" ht="14.4" customHeight="1">
       <c r="B347" t="n">
         <v>3333</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" ht="14.25" customHeight="1">
+    <row r="348" hidden="1" ht="14.4" customHeight="1">
       <c r="B348" t="n">
         <v>3334</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" ht="14.25" customHeight="1">
+    <row r="349" hidden="1" ht="14.4" customHeight="1">
       <c r="B349" t="n">
         <v>3335</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" ht="14.25" customHeight="1">
+    <row r="350" hidden="1" ht="14.4" customHeight="1">
       <c r="B350" t="n">
         <v>3336</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" ht="14.25" customHeight="1">
+    <row r="351" hidden="1" ht="14.4" customHeight="1">
       <c r="B351" t="n">
         <v>3337</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" ht="14.25" customHeight="1">
+    <row r="352" hidden="1" ht="14.4" customHeight="1">
       <c r="B352" t="n">
         <v>3338</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" ht="14.25" customHeight="1">
+    <row r="353" hidden="1" ht="14.4" customHeight="1">
       <c r="B353" t="n">
         <v>3339</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" ht="14.25" customHeight="1">
+    <row r="354" hidden="1" ht="14.4" customHeight="1">
       <c r="B354" t="n">
         <v>3340</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" ht="14.25" customHeight="1">
+    <row r="355" hidden="1" ht="14.4" customHeight="1">
       <c r="B355" t="n">
         <v>3341</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" ht="14.25" customHeight="1">
+    <row r="356" hidden="1" ht="14.4" customHeight="1">
       <c r="B356" t="n">
         <v>3342</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" ht="14.25" customHeight="1">
+    <row r="357" hidden="1" ht="14.4" customHeight="1">
       <c r="B357" t="n">
         <v>3343</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" ht="14.25" customHeight="1">
+    <row r="358" hidden="1" ht="14.4" customHeight="1">
       <c r="B358" t="n">
         <v>3344</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" ht="14.25" customHeight="1">
+    <row r="359" hidden="1" ht="14.4" customHeight="1">
       <c r="B359" t="n">
         <v>3345</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" ht="14.25" customHeight="1">
+    <row r="360" hidden="1" ht="14.4" customHeight="1">
       <c r="B360" t="n">
         <v>3346</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" ht="14.25" customHeight="1">
+    <row r="361" hidden="1" ht="14.4" customHeight="1">
       <c r="B361" t="n">
         <v>3347</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" ht="14.25" customHeight="1">
+    <row r="362" hidden="1" ht="14.4" customHeight="1">
       <c r="B362" t="n">
         <v>3348</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" ht="14.25" customHeight="1">
+    <row r="363" hidden="1" ht="14.4" customHeight="1">
       <c r="B363" t="n">
         <v>3349</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" ht="14.25" customHeight="1">
+    <row r="364" hidden="1" ht="14.4" customHeight="1">
       <c r="B364" t="n">
         <v>3350</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" ht="14.25" customHeight="1">
+    <row r="365" hidden="1" ht="14.4" customHeight="1">
       <c r="B365" t="n">
         <v>3351</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" ht="14.25" customHeight="1">
+    <row r="366" hidden="1" ht="14.4" customHeight="1">
       <c r="B366" t="n">
         <v>3352</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" ht="14.25" customHeight="1">
+    <row r="367" hidden="1" ht="14.4" customHeight="1">
       <c r="B367" t="n">
         <v>3353</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" ht="14.25" customHeight="1">
+    <row r="368" hidden="1" ht="14.4" customHeight="1">
       <c r="B368" t="n">
         <v>3354</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" ht="14.25" customHeight="1">
+    <row r="369" hidden="1" ht="14.4" customHeight="1">
       <c r="B369" t="n">
         <v>3355</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" ht="14.25" customHeight="1">
+    <row r="370" hidden="1" ht="14.4" customHeight="1">
       <c r="B370" t="n">
         <v>3356</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" ht="14.25" customHeight="1">
+    <row r="371" hidden="1" ht="14.4" customHeight="1">
       <c r="B371" t="n">
         <v>3357</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" ht="14.25" customHeight="1">
+    <row r="372" hidden="1" ht="14.4" customHeight="1">
       <c r="B372" t="n">
         <v>3358</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" ht="14.25" customHeight="1">
+    <row r="373" hidden="1" ht="14.4" customHeight="1">
       <c r="B373" t="n">
         <v>3359</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" ht="14.25" customHeight="1">
+    <row r="374" hidden="1" ht="14.4" customHeight="1">
       <c r="B374" t="n">
         <v>3360</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" ht="14.25" customHeight="1">
+    <row r="375" hidden="1" ht="14.4" customHeight="1">
       <c r="B375" t="n">
         <v>3361</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" ht="14.25" customHeight="1">
+    <row r="376" hidden="1" ht="14.4" customHeight="1">
       <c r="B376" t="n">
         <v>3362</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" ht="14.25" customHeight="1">
+    <row r="377" hidden="1" ht="14.4" customHeight="1">
       <c r="B377" t="n">
         <v>3363</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" ht="14.25" customHeight="1">
+    <row r="378" hidden="1" ht="14.4" customHeight="1">
       <c r="B378" t="n">
         <v>3364</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" ht="14.25" customHeight="1">
+    <row r="379" hidden="1" ht="14.4" customHeight="1">
       <c r="B379" t="n">
         <v>3365</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" ht="14.25" customHeight="1">
+    <row r="380" hidden="1" ht="14.4" customHeight="1">
       <c r="B380" t="n">
         <v>3366</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" ht="14.25" customHeight="1">
+    <row r="381" hidden="1" ht="14.4" customHeight="1">
       <c r="B381" t="n">
         <v>3367</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" ht="14.25" customHeight="1">
+    <row r="382" hidden="1" ht="14.4" customHeight="1">
       <c r="B382" t="n">
         <v>3368</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" ht="14.25" customHeight="1">
+    <row r="383" hidden="1" ht="14.4" customHeight="1">
       <c r="B383" t="n">
         <v>3369</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" ht="14.25" customHeight="1">
+    <row r="384" hidden="1" ht="14.4" customHeight="1">
       <c r="B384" t="n">
         <v>3370</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" ht="14.25" customHeight="1">
+    <row r="385" hidden="1" ht="14.4" customHeight="1">
       <c r="B385" t="n">
         <v>3371</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" ht="14.25" customHeight="1">
+    <row r="386" hidden="1" ht="14.4" customHeight="1">
       <c r="B386" t="n">
         <v>3372</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" ht="14.25" customHeight="1">
+    <row r="387" hidden="1" ht="14.4" customHeight="1">
       <c r="B387" t="n">
         <v>3373</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" ht="14.25" customHeight="1">
+    <row r="388" hidden="1" ht="14.4" customHeight="1">
       <c r="B388" t="n">
         <v>3374</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" ht="14.25" customHeight="1">
+    <row r="389" hidden="1" ht="14.4" customHeight="1">
       <c r="B389" t="n">
         <v>3375</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" ht="14.25" customHeight="1">
+    <row r="390" hidden="1" ht="14.4" customHeight="1">
       <c r="B390" t="n">
         <v>3376</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" ht="14.25" customHeight="1">
+    <row r="391" hidden="1" ht="14.4" customHeight="1">
       <c r="B391" t="n">
         <v>3377</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" ht="14.25" customHeight="1">
+    <row r="392" hidden="1" ht="14.4" customHeight="1">
       <c r="B392" t="n">
         <v>3378</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" ht="14.25" customHeight="1">
+    <row r="393" hidden="1" ht="14.4" customHeight="1">
       <c r="B393" t="n">
         <v>3379</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" ht="14.25" customHeight="1">
+    <row r="394" hidden="1" ht="14.4" customHeight="1">
       <c r="B394" t="n">
         <v>3380</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" ht="14.25" customHeight="1">
+    <row r="395" hidden="1" ht="14.4" customHeight="1">
       <c r="B395" t="n">
         <v>3381</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" ht="14.25" customHeight="1">
+    <row r="396" hidden="1" ht="14.4" customHeight="1">
       <c r="B396" t="n">
         <v>3382</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" ht="14.25" customHeight="1">
+    <row r="397" hidden="1" ht="14.4" customHeight="1">
       <c r="B397" t="n">
         <v>3383</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" ht="14.25" customHeight="1">
+    <row r="398" hidden="1" ht="14.4" customHeight="1">
       <c r="B398" t="n">
         <v>3384</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" ht="14.25" customHeight="1">
+    <row r="399" hidden="1" ht="14.4" customHeight="1">
       <c r="B399" t="n">
         <v>3385</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" ht="14.25" customHeight="1">
+    <row r="400" hidden="1" ht="14.4" customHeight="1">
       <c r="B400" t="n">
         <v>3386</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" ht="14.25" customHeight="1">
+    <row r="401" hidden="1" ht="14.4" customHeight="1">
       <c r="B401" t="n">
         <v>3387</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" ht="14.25" customHeight="1">
+    <row r="402" hidden="1" ht="14.4" customHeight="1">
       <c r="B402" t="n">
         <v>3388</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" ht="14.25" customHeight="1">
+    <row r="403" hidden="1" ht="14.4" customHeight="1">
       <c r="B403" t="n">
         <v>3389</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" ht="14.25" customHeight="1">
+    <row r="404" hidden="1" ht="14.4" customHeight="1">
       <c r="B404" t="n">
         <v>3390</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" ht="14.25" customHeight="1">
+    <row r="405" hidden="1" ht="14.4" customHeight="1">
       <c r="B405" t="n">
         <v>3391</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" ht="14.25" customHeight="1">
+    <row r="406" hidden="1" ht="14.4" customHeight="1">
       <c r="B406" t="n">
         <v>3392</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" ht="14.25" customHeight="1">
+    <row r="407" hidden="1" ht="14.4" customHeight="1">
       <c r="B407" t="n">
         <v>3393</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" ht="14.25" customHeight="1">
+    <row r="408" hidden="1" ht="14.4" customHeight="1">
       <c r="B408" t="n">
         <v>3394</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" ht="14.25" customHeight="1">
+    <row r="409" hidden="1" ht="14.4" customHeight="1">
       <c r="B409" t="n">
         <v>3395</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" ht="14.25" customHeight="1">
+    <row r="410" hidden="1" ht="14.4" customHeight="1">
       <c r="B410" t="n">
         <v>3396</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" ht="14.25" customHeight="1">
+    <row r="411" hidden="1" ht="14.4" customHeight="1">
       <c r="B411" t="n">
         <v>3397</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" ht="14.25" customHeight="1">
+    <row r="412" hidden="1" ht="14.4" customHeight="1">
       <c r="B412" t="n">
         <v>3398</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" ht="14.25" customHeight="1">
+    <row r="413" hidden="1" ht="14.4" customHeight="1">
       <c r="B413" t="n">
         <v>3399</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" ht="14.25" customHeight="1">
+    <row r="414" hidden="1" ht="14.4" customHeight="1">
       <c r="B414" t="n">
         <v>3400</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" ht="14.25" customHeight="1">
+    <row r="415" hidden="1" ht="14.4" customHeight="1">
       <c r="B415" t="n">
         <v>3401</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" ht="14.25" customHeight="1">
+    <row r="416" hidden="1" ht="14.4" customHeight="1">
       <c r="B416" t="n">
         <v>3402</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" ht="14.25" customHeight="1">
+    <row r="417" hidden="1" ht="14.4" customHeight="1">
       <c r="B417" t="n">
         <v>3403</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" ht="14.25" customHeight="1">
+    <row r="418" hidden="1" ht="14.4" customHeight="1">
       <c r="B418" t="n">
         <v>3404</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" ht="14.25" customHeight="1">
+    <row r="419" hidden="1" ht="14.4" customHeight="1">
       <c r="B419" t="n">
         <v>3405</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" ht="14.25" customHeight="1">
+    <row r="420" hidden="1" ht="14.4" customHeight="1">
       <c r="B420" t="n">
         <v>3406</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" ht="14.25" customHeight="1">
+    <row r="421" hidden="1" ht="14.4" customHeight="1">
       <c r="B421" t="n">
         <v>3407</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" ht="14.25" customHeight="1">
+    <row r="422" hidden="1" ht="14.4" customHeight="1">
       <c r="B422" t="n">
         <v>3408</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" ht="14.25" customHeight="1">
+    <row r="423" hidden="1" ht="14.4" customHeight="1">
       <c r="B423" t="n">
         <v>3409</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" ht="14.25" customHeight="1">
+    <row r="424" hidden="1" ht="14.4" customHeight="1">
       <c r="B424" t="n">
         <v>3410</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" ht="14.25" customHeight="1">
+    <row r="425" hidden="1" ht="14.4" customHeight="1">
       <c r="B425" t="n">
         <v>3411</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" ht="14.25" customHeight="1">
+    <row r="426" hidden="1" ht="14.4" customHeight="1">
       <c r="B426" t="n">
         <v>3412</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" ht="14.25" customHeight="1">
+    <row r="427" hidden="1" ht="14.4" customHeight="1">
       <c r="B427" t="n">
         <v>3413</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" ht="14.25" customHeight="1">
+    <row r="428" hidden="1" ht="14.4" customHeight="1">
       <c r="B428" t="n">
         <v>3414</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" ht="14.25" customHeight="1">
+    <row r="429" hidden="1" ht="14.4" customHeight="1">
       <c r="B429" t="n">
         <v>3415</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" ht="14.25" customHeight="1">
+    <row r="430" hidden="1" ht="14.4" customHeight="1">
       <c r="B430" t="n">
         <v>3416</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" ht="14.25" customHeight="1">
+    <row r="431" hidden="1" ht="14.4" customHeight="1">
       <c r="B431" t="n">
         <v>3417</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" ht="14.25" customHeight="1">
+    <row r="432" hidden="1" ht="14.4" customHeight="1">
       <c r="B432" t="n">
         <v>3418</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" ht="14.25" customHeight="1">
+    <row r="433" hidden="1" ht="14.4" customHeight="1">
       <c r="B433" t="n">
         <v>3419</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" ht="14.25" customHeight="1">
+    <row r="434" hidden="1" ht="14.4" customHeight="1">
       <c r="B434" t="n">
         <v>3420</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" ht="14.25" customHeight="1">
+    <row r="435" hidden="1" ht="14.4" customHeight="1">
       <c r="B435" t="n">
         <v>3421</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" ht="14.25" customHeight="1">
+    <row r="436" hidden="1" ht="14.4" customHeight="1">
       <c r="B436" t="n">
         <v>3422</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" ht="14.25" customHeight="1">
+    <row r="437" hidden="1" ht="14.4" customHeight="1">
       <c r="B437" t="n">
         <v>3423</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" ht="14.25" customHeight="1">
+    <row r="438" hidden="1" ht="14.4" customHeight="1">
       <c r="B438" t="n">
         <v>3424</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" ht="14.25" customHeight="1">
+    <row r="439" hidden="1" ht="14.4" customHeight="1">
       <c r="B439" t="n">
         <v>3425</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" ht="14.25" customHeight="1">
+    <row r="440" hidden="1" ht="14.4" customHeight="1">
       <c r="B440" t="n">
         <v>3426</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" ht="14.25" customHeight="1">
+    <row r="441" hidden="1" ht="14.4" customHeight="1">
       <c r="B441" t="n">
         <v>3427</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" ht="14.25" customHeight="1">
+    <row r="442" hidden="1" ht="14.4" customHeight="1">
       <c r="B442" t="n">
         <v>3428</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" ht="14.25" customHeight="1">
+    <row r="443" hidden="1" ht="14.4" customHeight="1">
       <c r="B443" t="n">
         <v>3429</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" ht="14.25" customHeight="1">
+    <row r="444" hidden="1" ht="14.4" customHeight="1">
       <c r="B444" t="n">
         <v>3430</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" ht="14.25" customHeight="1">
+    <row r="445" hidden="1" ht="14.4" customHeight="1">
       <c r="B445" t="n">
         <v>3431</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" ht="14.25" customHeight="1">
+    <row r="446" hidden="1" ht="14.4" customHeight="1">
       <c r="B446" t="n">
         <v>3432</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" ht="14.25" customHeight="1">
+    <row r="447" hidden="1" ht="14.4" customHeight="1">
       <c r="B447" t="n">
         <v>3433</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" ht="14.25" customHeight="1">
+    <row r="448" hidden="1" ht="14.4" customHeight="1">
       <c r="B448" t="n">
         <v>3434</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" ht="14.25" customHeight="1">
+    <row r="449" hidden="1" ht="14.4" customHeight="1">
       <c r="B449" t="n">
         <v>3435</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" ht="14.25" customHeight="1">
+    <row r="450" hidden="1" ht="14.4" customHeight="1">
       <c r="B450" t="n">
         <v>3436</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" ht="14.25" customHeight="1">
+    <row r="451" hidden="1" ht="14.4" customHeight="1">
       <c r="B451" t="n">
         <v>3437</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" ht="14.25" customHeight="1">
+    <row r="452" hidden="1" ht="14.4" customHeight="1">
       <c r="B452" t="n">
         <v>3438</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" ht="14.25" customHeight="1">
+    <row r="453" hidden="1" ht="14.4" customHeight="1">
       <c r="B453" t="n">
         <v>3439</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" ht="14.25" customHeight="1">
+    <row r="454" hidden="1" ht="14.4" customHeight="1">
       <c r="B454" t="n">
         <v>3440</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" ht="14.25" customHeight="1">
+    <row r="455" hidden="1" ht="14.4" customHeight="1">
       <c r="B455" t="n">
         <v>3441</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" ht="14.25" customHeight="1">
+    <row r="456" hidden="1" ht="14.4" customHeight="1">
       <c r="B456" t="n">
         <v>3442</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" ht="14.25" customHeight="1">
+    <row r="457" hidden="1" ht="14.4" customHeight="1">
       <c r="B457" t="n">
         <v>3443</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" ht="14.25" customHeight="1">
+    <row r="458" hidden="1" ht="14.4" customHeight="1">
       <c r="B458" t="n">
         <v>3444</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" ht="14.25" customHeight="1">
+    <row r="459" hidden="1" ht="14.4" customHeight="1">
       <c r="B459" t="n">
         <v>3445</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" ht="14.25" customHeight="1">
+    <row r="460" hidden="1" ht="14.4" customHeight="1">
       <c r="B460" t="n">
         <v>3446</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" ht="14.25" customHeight="1">
+    <row r="461" hidden="1" ht="14.4" customHeight="1">
       <c r="B461" t="n">
         <v>3447</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" ht="14.25" customHeight="1">
+    <row r="462" hidden="1" ht="14.4" customHeight="1">
       <c r="B462" t="n">
         <v>3448</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" ht="14.25" customHeight="1">
+    <row r="463" hidden="1" ht="14.4" customHeight="1">
       <c r="B463" t="n">
         <v>3449</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" ht="14.25" customHeight="1">
+    <row r="464" hidden="1" ht="14.4" customHeight="1">
       <c r="B464" t="n">
         <v>3450</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" ht="14.25" customHeight="1">
+    <row r="465" hidden="1" ht="14.4" customHeight="1">
       <c r="B465" t="n">
         <v>3451</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" ht="14.25" customHeight="1">
+    <row r="466" hidden="1" ht="14.4" customHeight="1">
       <c r="B466" t="n">
         <v>3452</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" ht="14.25" customHeight="1">
+    <row r="467" hidden="1" ht="14.4" customHeight="1">
       <c r="B467" t="n">
         <v>3453</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" ht="14.25" customHeight="1">
+    <row r="468" hidden="1" ht="14.4" customHeight="1">
       <c r="B468" t="n">
         <v>3454</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" ht="14.25" customHeight="1">
+    <row r="469" hidden="1" ht="14.4" customHeight="1">
       <c r="B469" t="n">
         <v>3455</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" ht="14.25" customHeight="1">
+    <row r="470" hidden="1" ht="14.4" customHeight="1">
       <c r="B470" t="n">
         <v>3456</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" ht="14.25" customHeight="1">
+    <row r="471" hidden="1" ht="14.4" customHeight="1">
       <c r="B471" t="n">
         <v>3457</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" ht="14.25" customHeight="1">
+    <row r="472" hidden="1" ht="14.4" customHeight="1">
       <c r="B472" t="n">
         <v>3458</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" ht="14.25" customHeight="1">
+    <row r="473" hidden="1" ht="14.4" customHeight="1">
       <c r="B473" t="n">
         <v>3459</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" ht="14.25" customHeight="1">
+    <row r="474" hidden="1" ht="14.4" customHeight="1">
       <c r="B474" t="n">
         <v>3460</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" ht="14.25" customHeight="1">
+    <row r="475" hidden="1" ht="14.4" customHeight="1">
       <c r="B475" t="n">
         <v>3461</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" ht="14.25" customHeight="1">
+    <row r="476" hidden="1" ht="14.4" customHeight="1">
       <c r="B476" t="n">
         <v>3462</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" ht="14.25" customHeight="1">
+    <row r="477" hidden="1" ht="14.4" customHeight="1">
       <c r="B477" t="n">
         <v>3463</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" ht="14.25" customHeight="1">
+    <row r="478" hidden="1" ht="14.4" customHeight="1">
       <c r="B478" t="n">
         <v>3464</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" ht="14.25" customHeight="1">
+    <row r="479" hidden="1" ht="14.4" customHeight="1">
       <c r="B479" t="n">
         <v>3465</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" ht="14.25" customHeight="1">
+    <row r="480" hidden="1" ht="14.4" customHeight="1">
       <c r="B480" t="n">
         <v>3466</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" ht="14.25" customHeight="1">
+    <row r="481" hidden="1" ht="14.4" customHeight="1">
       <c r="B481" t="n">
         <v>3467</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" ht="14.25" customHeight="1">
+    <row r="482" hidden="1" ht="14.4" customHeight="1">
       <c r="B482" t="n">
         <v>3468</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" ht="14.25" customHeight="1">
+    <row r="483" hidden="1" ht="14.4" customHeight="1">
       <c r="B483" t="n">
         <v>3469</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" ht="14.25" customHeight="1">
+    <row r="484" hidden="1" ht="14.4" customHeight="1">
       <c r="B484" t="n">
         <v>3470</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" ht="14.25" customHeight="1">
+    <row r="485" hidden="1" ht="14.4" customHeight="1">
       <c r="B485" t="n">
         <v>3471</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" ht="14.25" customHeight="1">
+    <row r="486" hidden="1" ht="14.4" customHeight="1">
       <c r="B486" t="n">
         <v>3472</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" ht="14.25" customHeight="1">
+    <row r="487" hidden="1" ht="14.4" customHeight="1">
       <c r="B487" t="n">
         <v>3473</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" ht="14.25" customHeight="1">
+    <row r="488" hidden="1" ht="14.4" customHeight="1">
       <c r="B488" t="n">
         <v>3474</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" ht="14.25" customHeight="1">
+    <row r="489" hidden="1" ht="14.4" customHeight="1">
       <c r="B489" t="n">
         <v>3475</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" ht="14.25" customHeight="1">
+    <row r="490" hidden="1" ht="14.4" customHeight="1">
       <c r="B490" t="n">
         <v>3476</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" ht="14.25" customHeight="1">
+    <row r="491" hidden="1" ht="14.4" customHeight="1">
       <c r="B491" t="n">
         <v>3477</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" ht="14.25" customHeight="1">
+    <row r="492" hidden="1" ht="14.4" customHeight="1">
       <c r="B492" t="n">
         <v>3478</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" ht="14.25" customHeight="1">
+    <row r="493" hidden="1" ht="14.4" customHeight="1">
       <c r="B493" t="n">
         <v>3479</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" ht="14.25" customHeight="1">
+    <row r="494" hidden="1" ht="14.4" customHeight="1">
       <c r="B494" t="n">
         <v>3480</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" ht="14.25" customHeight="1">
+    <row r="495" hidden="1" ht="14.4" customHeight="1">
       <c r="B495" t="n">
         <v>3481</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" ht="14.25" customHeight="1">
+    <row r="496" hidden="1" ht="14.4" customHeight="1">
       <c r="B496" t="n">
         <v>3482</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" ht="14.25" customHeight="1">
+    <row r="497" hidden="1" ht="14.4" customHeight="1">
       <c r="B497" t="n">
         <v>3483</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" ht="14.25" customHeight="1">
+    <row r="498" hidden="1" ht="14.4" customHeight="1">
       <c r="B498" t="n">
         <v>3484</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" ht="14.25" customHeight="1">
+    <row r="499" hidden="1" ht="14.4" customHeight="1">
       <c r="B499" t="n">
         <v>3485</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" ht="14.25" customHeight="1">
+    <row r="500" hidden="1" ht="14.4" customHeight="1">
       <c r="B500" t="n">
         <v>3486</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" ht="14.25" customHeight="1">
+    <row r="501" hidden="1" ht="14.4" customHeight="1">
       <c r="B501" t="n">
         <v>3487</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" ht="14.25" customHeight="1">
+    <row r="502" hidden="1" ht="14.4" customHeight="1">
       <c r="B502" t="n">
         <v>3488</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" ht="14.25" customHeight="1">
+    <row r="503" hidden="1" ht="14.4" customHeight="1">
       <c r="B503" t="n">
         <v>3489</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" ht="14.25" customHeight="1">
+    <row r="504" hidden="1" ht="14.4" customHeight="1">
       <c r="B504" t="n">
         <v>3490</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" ht="14.25" customHeight="1">
+    <row r="505" hidden="1" ht="14.4" customHeight="1">
       <c r="B505" t="n">
         <v>3491</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" ht="14.25" customHeight="1">
+    <row r="506" hidden="1" ht="14.4" customHeight="1">
       <c r="B506" t="n">
         <v>3492</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" ht="14.25" customHeight="1">
+    <row r="507" hidden="1" ht="14.4" customHeight="1">
       <c r="B507" t="n">
         <v>3493</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" ht="14.25" customHeight="1">
+    <row r="508" hidden="1" ht="14.4" customHeight="1">
       <c r="B508" t="n">
         <v>3494</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" ht="14.25" customHeight="1">
+    <row r="509" hidden="1" ht="14.4" customHeight="1">
       <c r="B509" t="n">
         <v>3495</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" ht="14.25" customHeight="1">
+    <row r="510" hidden="1" ht="14.4" customHeight="1">
       <c r="B510" t="n">
         <v>3496</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" ht="14.25" customHeight="1">
+    <row r="511" hidden="1" ht="14.4" customHeight="1">
       <c r="B511" t="n">
         <v>3497</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" ht="14.25" customHeight="1">
+    <row r="512" hidden="1" ht="14.4" customHeight="1">
       <c r="B512" t="n">
         <v>3498</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" ht="14.25" customHeight="1">
+    <row r="513" hidden="1" ht="14.4" customHeight="1">
       <c r="B513" t="n">
         <v>3499</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" ht="14.25" customHeight="1">
+    <row r="514" hidden="1" ht="14.4" customHeight="1">
       <c r="B514" t="n">
         <v>3500</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" ht="14.25" customHeight="1">
+    <row r="515" hidden="1" ht="14.4" customHeight="1">
       <c r="B515" t="n">
         <v>3501</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" ht="14.25" customHeight="1">
+    <row r="516" hidden="1" ht="14.4" customHeight="1">
       <c r="B516" t="n">
         <v>3502</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" ht="14.25" customHeight="1">
+    <row r="517" hidden="1" ht="14.4" customHeight="1">
       <c r="B517" t="n">
         <v>3503</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" ht="14.25" customHeight="1">
+    <row r="518" hidden="1" ht="14.4" customHeight="1">
       <c r="B518" t="n">
         <v>3504</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" ht="14.25" customHeight="1">
+    <row r="519" hidden="1" ht="14.4" customHeight="1">
       <c r="B519" t="n">
         <v>3505</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" ht="14.25" customHeight="1">
+    <row r="520" hidden="1" ht="14.4" customHeight="1">
       <c r="B520" t="n">
         <v>3506</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" ht="14.25" customHeight="1">
+    <row r="521" hidden="1" ht="14.4" customHeight="1">
       <c r="B521" t="n">
         <v>3507</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" ht="14.25" customHeight="1">
+    <row r="522" hidden="1" ht="14.4" customHeight="1">
       <c r="B522" t="n">
         <v>3508</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" ht="14.25" customHeight="1">
+    <row r="523" hidden="1" ht="14.4" customHeight="1">
       <c r="B523" t="n">
         <v>3509</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" ht="14.25" customHeight="1">
+    <row r="524" hidden="1" ht="14.4" customHeight="1">
       <c r="B524" t="n">
         <v>3510</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" ht="14.25" customHeight="1">
+    <row r="525" hidden="1" ht="14.4" customHeight="1">
       <c r="B525" t="n">
         <v>3511</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" ht="14.25" customHeight="1">
+    <row r="526" hidden="1" ht="14.4" customHeight="1">
       <c r="B526" t="n">
         <v>3512</v>
       </c>
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
-    <row r="527" ht="15" customHeight="1">
+    <row r="527" hidden="1" ht="15" customHeight="1">
       <c r="B527" t="n">
         <v>3513</v>
       </c>
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
-    <row r="528" ht="15" customHeight="1">
+    <row r="528" hidden="1" ht="15" customHeight="1">
       <c r="B528" t="n">
         <v>3514</v>
       </c>
@@ -8177,7 +8451,7 @@
       <c r="O528" s="4" t="n"/>
       <c r="Q528" s="4" t="n"/>
     </row>
-    <row r="529" ht="15" customHeight="1">
+    <row r="529" hidden="1" ht="15" customHeight="1">
       <c r="B529" t="n">
         <v>3515</v>
       </c>
@@ -8189,7 +8463,7 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
-    <row r="530" ht="15" customHeight="1">
+    <row r="530" hidden="1" ht="15" customHeight="1">
       <c r="F530" t="inlineStr">
         <is>
           <t>A</t>
@@ -8198,7 +8472,7 @@
       <c r="O530" s="4" t="n"/>
       <c r="Q530" s="4" t="n"/>
     </row>
-    <row r="531" ht="15" customHeight="1">
+    <row r="531" hidden="1" ht="15" customHeight="1">
       <c r="F531" t="inlineStr">
         <is>
           <t>A</t>
@@ -8207,7 +8481,7 @@
       <c r="O531" s="4" t="n"/>
       <c r="Q531" s="4" t="n"/>
     </row>
-    <row r="532" ht="15" customHeight="1">
+    <row r="532" hidden="1" ht="15" customHeight="1">
       <c r="F532" t="inlineStr">
         <is>
           <t>A</t>
@@ -8216,7 +8490,7 @@
       <c r="O532" s="4" t="n"/>
       <c r="Q532" s="4" t="n"/>
     </row>
-    <row r="533" ht="15" customHeight="1">
+    <row r="533" hidden="1" ht="15" customHeight="1">
       <c r="F533" t="inlineStr">
         <is>
           <t>A</t>
@@ -8225,7 +8499,7 @@
       <c r="O533" s="4" t="n"/>
       <c r="Q533" s="4" t="n"/>
     </row>
-    <row r="534" ht="15" customHeight="1">
+    <row r="534" hidden="1" ht="15" customHeight="1">
       <c r="F534" t="inlineStr">
         <is>
           <t>A</t>
@@ -8239,26 +8513,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R25" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" display="brandon.conner@gxo.com" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" display="brandon.conner@gxo.com" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" display="brandon.conner@gxo.com" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" display="brandon.conner@gxo.com" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" display="brandon.conner@gxo.com" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" display="brandon.conner@gxo.com" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" display="brandon.conner@gxo.com" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" display="brandon.conner@gxo.com" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -436,7 +436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -678,7 +678,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -690,13 +689,13 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -845,9 +844,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -885,7 +884,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -991,7 +990,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1133,7 +1132,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1146,47 +1145,47 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R534"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.6640625" customWidth="1" min="1" max="1"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
-    <col width="33.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="56.44140625" customWidth="1" min="4" max="4"/>
+    <col width="15.7109375" customWidth="1" min="1" max="1"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="33.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="56.42578125" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25.88671875" customWidth="1" min="6" max="6"/>
-    <col width="15.109375" customWidth="1" min="7" max="7"/>
-    <col width="11.6640625" customWidth="1" min="8" max="8"/>
-    <col width="19.109375" customWidth="1" min="9" max="9"/>
+    <col width="25.85546875" customWidth="1" min="6" max="6"/>
+    <col width="15.140625" customWidth="1" min="7" max="7"/>
+    <col width="11.7109375" customWidth="1" min="8" max="8"/>
+    <col width="19.140625" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.109375" customWidth="1" min="11" max="11"/>
-    <col width="17.5546875" customWidth="1" min="12" max="12"/>
-    <col width="35.109375" customWidth="1" min="13" max="13"/>
-    <col width="25.33203125" customWidth="1" min="14" max="14"/>
-    <col width="33.44140625" customWidth="1" min="15" max="15"/>
+    <col width="18.140625" customWidth="1" min="11" max="11"/>
+    <col width="17.5703125" customWidth="1" min="12" max="12"/>
+    <col width="35.140625" customWidth="1" min="13" max="13"/>
+    <col width="25.28515625" customWidth="1" min="14" max="14"/>
+    <col width="33.42578125" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="35.88671875" customWidth="1" style="4" min="17" max="17"/>
+    <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="27.6640625" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.6640625" customWidth="1" min="20" max="20"/>
-    <col width="12.88671875" customWidth="1" min="21" max="23"/>
-    <col width="16.33203125" customWidth="1" min="24" max="24"/>
-    <col width="20.109375" customWidth="1" min="25" max="25"/>
-    <col width="20.5546875" customWidth="1" min="26" max="26"/>
-    <col width="14.88671875" customWidth="1" min="27" max="27"/>
+    <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
+    <col width="14.7109375" customWidth="1" min="20" max="20"/>
+    <col width="12.85546875" customWidth="1" min="21" max="23"/>
+    <col width="16.28515625" customWidth="1" min="24" max="24"/>
+    <col width="20.140625" customWidth="1" min="25" max="25"/>
+    <col width="20.5703125" customWidth="1" min="26" max="26"/>
+    <col width="14.85546875" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5546875" customWidth="1" min="29" max="29"/>
-    <col width="16.109375" customWidth="1" min="30" max="30"/>
-    <col width="16.109375" customWidth="1" style="139" min="31" max="31"/>
-    <col width="22.88671875" customWidth="1" min="32" max="32"/>
-    <col width="17.33203125" customWidth="1" min="33" max="33"/>
-    <col width="16.33203125" customWidth="1" style="140" min="34" max="34"/>
-    <col width="22.88671875" customWidth="1" min="35" max="36"/>
-    <col width="31.88671875" customWidth="1" min="37" max="37"/>
-    <col width="13.44140625" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.33203125" customWidth="1" min="41" max="41"/>
+    <col width="20.5703125" customWidth="1" min="29" max="29"/>
+    <col width="16.140625" customWidth="1" min="30" max="30"/>
+    <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
+    <col width="22.85546875" customWidth="1" min="32" max="32"/>
+    <col width="17.28515625" customWidth="1" min="33" max="33"/>
+    <col width="16.28515625" customWidth="1" style="139" min="34" max="34"/>
+    <col width="22.85546875" customWidth="1" min="35" max="36"/>
+    <col width="31.85546875" customWidth="1" min="37" max="37"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="33.28515625" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customHeight="1">
+    <row r="1" ht="28.9" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1278,7 +1277,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="62">
+    <row r="2" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1362,7 +1361,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" hidden="1" ht="14.4" customHeight="1">
+    <row r="3" hidden="1" ht="14.45" customHeight="1">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1516,7 +1515,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" hidden="1" ht="28.8" customHeight="1">
+    <row r="5" hidden="1" ht="28.9" customHeight="1">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1575,7 +1574,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6" hidden="1" ht="14.4" customHeight="1">
+    <row r="6" hidden="1" ht="14.45" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1635,7 +1634,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7" hidden="1" ht="14.4" customHeight="1">
+    <row r="7" hidden="1" ht="14.45" customHeight="1">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1713,7 +1712,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" hidden="1" ht="14.4" customHeight="1">
+    <row r="8" hidden="1" ht="14.45" customHeight="1">
       <c r="B8" t="n">
         <v>3008</v>
       </c>
@@ -1959,11 +1958,11 @@
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R10" s="141" t="n">
+      <c r="R10" s="140" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="11" hidden="1" ht="43.2" customHeight="1">
+    <row r="11" hidden="1" ht="43.15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2044,7 +2043,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="12" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="27">
+    <row r="12" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="27">
       <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2108,7 +2107,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="13" hidden="1" ht="14.4" customHeight="1">
+    <row r="13" hidden="1" ht="14.45" customHeight="1">
       <c r="B13" t="n">
         <v>3014</v>
       </c>
@@ -2412,7 +2411,7 @@
       <c r="Q16" s="88" t="n"/>
       <c r="R16" s="23" t="n"/>
     </row>
-    <row r="17" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="17" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2457,7 +2456,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="18" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="18" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B18" t="n">
         <v>3018</v>
       </c>
@@ -2499,7 +2498,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="19" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B19" t="n">
         <v>3019</v>
       </c>
@@ -2541,7 +2540,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" ht="43.2" customHeight="1">
+    <row r="20" hidden="1" ht="43.15" customHeight="1">
       <c r="B20" t="n">
         <v>3020</v>
       </c>
@@ -2705,7 +2704,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="23" hidden="1" ht="28.8" customHeight="1">
+    <row r="23" hidden="1" ht="28.9" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2789,7 +2788,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="24" hidden="1" ht="28.8" customHeight="1">
+    <row r="24" hidden="1" ht="28.9" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2855,7 +2854,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" ht="43.2" customHeight="1">
+    <row r="25" hidden="1" ht="43.15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2923,7 +2922,7 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" hidden="1" ht="14.4" customHeight="1">
+    <row r="26" hidden="1" ht="14.45" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -2999,7 +2998,7 @@
       </c>
       <c r="Q26" s="4" t="n"/>
     </row>
-    <row r="27" hidden="1" ht="14.4" customHeight="1">
+    <row r="27" hidden="1" ht="14.45" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3070,7 +3069,7 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" ht="28.8" customHeight="1">
+    <row r="28" hidden="1" ht="28.9" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3147,7 +3146,7 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" ht="43.2" customHeight="1">
+    <row r="29" hidden="1" ht="43.15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3195,7 +3194,7 @@
         </is>
       </c>
     </row>
-    <row r="30" hidden="1" ht="28.8" customHeight="1">
+    <row r="30" hidden="1" ht="28.9" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3257,7 +3256,7 @@
         </is>
       </c>
     </row>
-    <row r="31" hidden="1" ht="43.2" customHeight="1">
+    <row r="31" hidden="1" ht="43.15" customHeight="1">
       <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3395,7 +3394,7 @@
       <c r="O32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
     </row>
-    <row r="33" hidden="1" ht="43.2" customHeight="1">
+    <row r="33" hidden="1" ht="43.15" customHeight="1">
       <c r="B33" t="n">
         <v>3035</v>
       </c>
@@ -3529,7 +3528,7 @@
       <c r="O34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
     </row>
-    <row r="35" hidden="1" ht="14.4" customHeight="1">
+    <row r="35" hidden="1" ht="14.45" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Mike/Jeff</t>
@@ -3596,7 +3595,7 @@
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" hidden="1" ht="14.4" customHeight="1">
+    <row r="36" hidden="1" ht="14.45" customHeight="1">
       <c r="B36" t="n">
         <v>3031</v>
       </c>
@@ -3663,7 +3662,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" hidden="1" ht="14.4" customHeight="1">
+    <row r="37" hidden="1" ht="14.45" customHeight="1">
       <c r="B37" t="n">
         <v>3056</v>
       </c>
@@ -3758,7 +3757,7 @@
         </is>
       </c>
     </row>
-    <row r="39" hidden="1" ht="28.8" customHeight="1">
+    <row r="39" hidden="1" ht="28.9" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3830,7 +3829,7 @@
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
     </row>
-    <row r="40" hidden="1" ht="43.2" customHeight="1">
+    <row r="40" hidden="1" ht="43.15" customHeight="1">
       <c r="B40" t="n">
         <v>3035</v>
       </c>
@@ -3874,7 +3873,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" hidden="1" ht="28.8" customHeight="1">
+    <row r="41" hidden="1" ht="28.9" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3947,7 +3946,7 @@
       </c>
       <c r="Q41" s="4" t="n"/>
     </row>
-    <row r="42" hidden="1" ht="43.2" customHeight="1">
+    <row r="42" hidden="1" ht="43.15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
@@ -3986,7 +3985,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" hidden="1" ht="14.4" customHeight="1">
+    <row r="43" hidden="1" ht="14.45" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
@@ -4019,7 +4018,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" hidden="1" ht="41.4" customHeight="1">
+    <row r="44" hidden="1" ht="41.45" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4079,7 +4078,7 @@
       <c r="O44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45" hidden="1" ht="28.8" customHeight="1">
+    <row r="45" hidden="1" ht="28.9" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4142,7 +4141,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" hidden="1" ht="14.4" customHeight="1">
+    <row r="46" hidden="1" ht="14.45" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4199,7 +4198,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" hidden="1" ht="43.2" customHeight="1">
+    <row r="47" hidden="1" ht="43.15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>US</t>
@@ -4238,7 +4237,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48" hidden="1" ht="43.2" customHeight="1">
+    <row r="48" hidden="1" ht="43.15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>US</t>
@@ -4282,7 +4281,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" hidden="1" ht="14.4" customHeight="1">
+    <row r="49" hidden="1" ht="14.45" customHeight="1">
       <c r="B49" s="130" t="n">
         <v>3041</v>
       </c>
@@ -4344,7 +4343,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" hidden="1" ht="43.2" customHeight="1">
+    <row r="50" hidden="1" ht="43.15" customHeight="1">
       <c r="B50" t="n">
         <v>3063</v>
       </c>
@@ -4378,7 +4377,7 @@
       <c r="O50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
     </row>
-    <row r="51" hidden="1" ht="14.4" customHeight="1">
+    <row r="51" hidden="1" ht="14.45" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4405,7 +4404,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="14.4" customHeight="1">
+    <row r="52" hidden="1" ht="14.45" customHeight="1">
       <c r="B52" t="n">
         <v>3044</v>
       </c>
@@ -4457,7 +4456,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" hidden="1" ht="14.4" customHeight="1">
+    <row r="53" hidden="1" ht="14.45" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4484,7 +4483,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="14.4" customHeight="1">
+    <row r="54" hidden="1" ht="14.45" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4516,7 +4515,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" hidden="1" ht="14.4" customHeight="1">
+    <row r="55" hidden="1" ht="14.45" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4548,7 +4547,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" hidden="1" ht="14.4" customHeight="1">
+    <row r="56" hidden="1" ht="14.45" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4580,7 +4579,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="14.4" customHeight="1">
+    <row r="57" hidden="1" ht="14.45" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4612,7 +4611,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="14.4" customHeight="1">
+    <row r="58" hidden="1" ht="14.45" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4644,7 +4643,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" hidden="1" ht="14.4" customHeight="1">
+    <row r="59" hidden="1" ht="14.45" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4676,7 +4675,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="14.4" customHeight="1">
+    <row r="60" hidden="1" ht="14.45" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -4689,7 +4688,7 @@
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="23" t="n"/>
     </row>
-    <row r="61" hidden="1" ht="14.4" customHeight="1">
+    <row r="61" hidden="1" ht="14.45" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4721,7 +4720,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62" hidden="1" ht="14.4" customHeight="1">
+    <row r="62" hidden="1" ht="14.45" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4753,7 +4752,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" hidden="1" ht="14.4" customHeight="1">
+    <row r="63" hidden="1" ht="14.45" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4785,7 +4784,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" hidden="1" ht="14.4" customHeight="1">
+    <row r="64" hidden="1" ht="14.45" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4817,7 +4816,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" hidden="1" ht="14.4" customHeight="1">
+    <row r="65" hidden="1" ht="14.45" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4830,7 +4829,7 @@
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="23" t="n"/>
     </row>
-    <row r="66" hidden="1" ht="14.4" customHeight="1">
+    <row r="66" hidden="1" ht="14.45" customHeight="1">
       <c r="B66" s="131" t="inlineStr">
         <is>
           <t>----</t>
@@ -4854,7 +4853,7 @@
       <c r="O66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
     </row>
-    <row r="67" hidden="1" ht="14.4" customHeight="1">
+    <row r="67" hidden="1" ht="14.45" customHeight="1">
       <c r="B67" t="n">
         <v>3003</v>
       </c>
@@ -4862,7 +4861,7 @@
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="23" t="n"/>
     </row>
-    <row r="68" hidden="1" ht="14.4" customHeight="1">
+    <row r="68" hidden="1" ht="14.45" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>US</t>
@@ -4875,7 +4874,7 @@
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="23" t="n"/>
     </row>
-    <row r="69" hidden="1" ht="14.4" customHeight="1">
+    <row r="69" hidden="1" ht="14.45" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>US</t>
@@ -4905,7 +4904,7 @@
       <c r="Q69" s="108" t="n"/>
       <c r="R69" s="66" t="n"/>
     </row>
-    <row r="70" hidden="1" ht="43.2" customHeight="1">
+    <row r="70" hidden="1" ht="43.15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4944,7 +4943,7 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" hidden="1" ht="14.4" customHeight="1">
+    <row r="71" hidden="1" ht="14.45" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>US</t>
@@ -4970,7 +4969,7 @@
       <c r="Q71" s="108" t="n"/>
       <c r="R71" s="66" t="n"/>
     </row>
-    <row r="72" hidden="1" ht="14.4" customHeight="1">
+    <row r="72" hidden="1" ht="14.45" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5002,7 +5001,7 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" hidden="1" ht="14.4" customHeight="1">
+    <row r="73" hidden="1" ht="14.45" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>US</t>
@@ -5028,7 +5027,7 @@
       <c r="Q73" s="108" t="n"/>
       <c r="R73" s="66" t="n"/>
     </row>
-    <row r="74" hidden="1" ht="14.4" customHeight="1">
+    <row r="74" hidden="1" ht="14.45" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5060,7 +5059,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" hidden="1" ht="14.4" customHeight="1">
+    <row r="75" hidden="1" ht="14.45" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5097,7 +5096,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="43.2" customHeight="1">
+    <row r="76" hidden="1" ht="43.15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>US</t>
@@ -5111,7 +5110,7 @@
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="23" t="n"/>
     </row>
-    <row r="77" hidden="1" ht="14.4" customHeight="1">
+    <row r="77" hidden="1" ht="14.45" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5135,7 +5134,7 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78" ht="14.45" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5206,7 +5205,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" hidden="1" ht="43.2" customHeight="1">
+    <row r="80" hidden="1" ht="43.15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5245,7 +5244,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" hidden="1" ht="28.8" customHeight="1">
+    <row r="81" hidden="1" ht="28.9" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5317,3115 +5316,3140 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" hidden="1" ht="14.4" customHeight="1">
+    <row r="82" hidden="1" ht="14.45" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B82" t="n">
         <v>3068</v>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NP42</t>
+        </is>
+      </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" hidden="1" ht="14.4" customHeight="1">
+    <row r="83" hidden="1" ht="14.45" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B83" t="n">
         <v>3069</v>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Allied Air</t>
+        </is>
+      </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" hidden="1" ht="14.4" customHeight="1">
+    <row r="84" hidden="1" ht="14.45" customHeight="1">
       <c r="B84" t="n">
         <v>3070</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" hidden="1" ht="14.4" customHeight="1">
+    <row r="85" hidden="1" ht="14.45" customHeight="1">
       <c r="B85" t="n">
         <v>3071</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" hidden="1" ht="14.4" customHeight="1">
+    <row r="86" hidden="1" ht="14.45" customHeight="1">
       <c r="B86" t="n">
         <v>3072</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" hidden="1" ht="14.4" customHeight="1">
+    <row r="87" hidden="1" ht="14.45" customHeight="1">
       <c r="B87" t="n">
         <v>3073</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" hidden="1" ht="14.4" customHeight="1">
+    <row r="88" hidden="1" ht="14.45" customHeight="1">
       <c r="B88" t="n">
         <v>3074</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" hidden="1" ht="14.4" customHeight="1">
+    <row r="89" hidden="1" ht="14.45" customHeight="1">
       <c r="B89" t="n">
         <v>3075</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" hidden="1" ht="14.4" customHeight="1">
+    <row r="90" hidden="1" ht="14.45" customHeight="1">
       <c r="B90" t="n">
         <v>3076</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" hidden="1" ht="14.4" customHeight="1">
+    <row r="91" hidden="1" ht="14.45" customHeight="1">
       <c r="B91" t="n">
         <v>3077</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" hidden="1" ht="14.4" customHeight="1">
+    <row r="92" hidden="1" ht="14.45" customHeight="1">
       <c r="B92" t="n">
         <v>3078</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" hidden="1" ht="14.4" customHeight="1">
+    <row r="93" hidden="1" ht="14.45" customHeight="1">
       <c r="B93" t="n">
         <v>3079</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" hidden="1" ht="14.4" customHeight="1">
+    <row r="94" hidden="1" ht="14.45" customHeight="1">
       <c r="B94" t="n">
         <v>3080</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" hidden="1" ht="14.4" customHeight="1">
+    <row r="95" hidden="1" ht="14.45" customHeight="1">
       <c r="B95" t="n">
         <v>3081</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" hidden="1" ht="14.4" customHeight="1">
+    <row r="96" hidden="1" ht="14.45" customHeight="1">
       <c r="B96" t="n">
         <v>3082</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" hidden="1" ht="14.4" customHeight="1">
+    <row r="97" hidden="1" ht="14.45" customHeight="1">
       <c r="B97" t="n">
         <v>3083</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" hidden="1" ht="14.4" customHeight="1">
+    <row r="98" hidden="1" ht="14.45" customHeight="1">
       <c r="B98" t="n">
         <v>3084</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" hidden="1" ht="14.4" customHeight="1">
+    <row r="99" hidden="1" ht="14.45" customHeight="1">
       <c r="B99" t="n">
         <v>3085</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" hidden="1" ht="14.4" customHeight="1">
+    <row r="100" hidden="1" ht="14.45" customHeight="1">
       <c r="B100" t="n">
         <v>3086</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" hidden="1" ht="14.4" customHeight="1">
+    <row r="101" hidden="1" ht="14.45" customHeight="1">
       <c r="B101" t="n">
         <v>3087</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" hidden="1" ht="14.4" customHeight="1">
+    <row r="102" hidden="1" ht="14.45" customHeight="1">
       <c r="B102" t="n">
         <v>3088</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" hidden="1" ht="14.4" customHeight="1">
+    <row r="103" hidden="1" ht="14.45" customHeight="1">
       <c r="B103" t="n">
         <v>3089</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" hidden="1" ht="14.4" customHeight="1">
+    <row r="104" hidden="1" ht="14.45" customHeight="1">
       <c r="B104" t="n">
         <v>3090</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" hidden="1" ht="14.4" customHeight="1">
+    <row r="105" hidden="1" ht="14.45" customHeight="1">
       <c r="B105" t="n">
         <v>3091</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" hidden="1" ht="14.4" customHeight="1">
+    <row r="106" hidden="1" ht="14.45" customHeight="1">
       <c r="B106" t="n">
         <v>3092</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" hidden="1" ht="14.4" customHeight="1">
+    <row r="107" hidden="1" ht="14.45" customHeight="1">
       <c r="B107" t="n">
         <v>3093</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" hidden="1" ht="14.4" customHeight="1">
+    <row r="108" hidden="1" ht="14.45" customHeight="1">
       <c r="B108" t="n">
         <v>3094</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" hidden="1" ht="14.4" customHeight="1">
+    <row r="109" hidden="1" ht="14.45" customHeight="1">
       <c r="B109" t="n">
         <v>3095</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" hidden="1" ht="14.4" customHeight="1">
+    <row r="110" hidden="1" ht="14.45" customHeight="1">
       <c r="B110" t="n">
         <v>3096</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" hidden="1" ht="14.4" customHeight="1">
+    <row r="111" hidden="1" ht="14.45" customHeight="1">
       <c r="B111" t="n">
         <v>3097</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" hidden="1" ht="14.4" customHeight="1">
+    <row r="112" hidden="1" ht="14.45" customHeight="1">
       <c r="B112" t="n">
         <v>3098</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" hidden="1" ht="14.4" customHeight="1">
+    <row r="113" hidden="1" ht="14.45" customHeight="1">
       <c r="B113" t="n">
         <v>3099</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" hidden="1" ht="14.4" customHeight="1">
+    <row r="114" hidden="1" ht="14.45" customHeight="1">
       <c r="B114" t="n">
         <v>3100</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" hidden="1" ht="14.4" customHeight="1">
+    <row r="115" hidden="1" ht="14.45" customHeight="1">
       <c r="B115" t="n">
         <v>3101</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" hidden="1" ht="14.4" customHeight="1">
+    <row r="116" hidden="1" ht="14.45" customHeight="1">
       <c r="B116" t="n">
         <v>3102</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" hidden="1" ht="14.4" customHeight="1">
+    <row r="117" hidden="1" ht="14.45" customHeight="1">
       <c r="B117" t="n">
         <v>3103</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" hidden="1" ht="14.4" customHeight="1">
+    <row r="118" hidden="1" ht="14.45" customHeight="1">
       <c r="B118" t="n">
         <v>3104</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" hidden="1" ht="14.4" customHeight="1">
+    <row r="119" hidden="1" ht="14.45" customHeight="1">
       <c r="B119" t="n">
         <v>3105</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" hidden="1" ht="14.4" customHeight="1">
+    <row r="120" hidden="1" ht="14.45" customHeight="1">
       <c r="B120" t="n">
         <v>3106</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" hidden="1" ht="14.4" customHeight="1">
+    <row r="121" hidden="1" ht="14.45" customHeight="1">
       <c r="B121" t="n">
         <v>3107</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" hidden="1" ht="14.4" customHeight="1">
+    <row r="122" hidden="1" ht="14.45" customHeight="1">
       <c r="B122" t="n">
         <v>3108</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" hidden="1" ht="14.4" customHeight="1">
+    <row r="123" hidden="1" ht="14.45" customHeight="1">
       <c r="B123" t="n">
         <v>3109</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" hidden="1" ht="14.4" customHeight="1">
+    <row r="124" hidden="1" ht="14.45" customHeight="1">
       <c r="B124" t="n">
         <v>3110</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" hidden="1" ht="14.4" customHeight="1">
+    <row r="125" hidden="1" ht="14.45" customHeight="1">
       <c r="B125" t="n">
         <v>3111</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" hidden="1" ht="14.4" customHeight="1">
+    <row r="126" hidden="1" ht="14.45" customHeight="1">
       <c r="B126" t="n">
         <v>3112</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" hidden="1" ht="14.4" customHeight="1">
+    <row r="127" hidden="1" ht="14.45" customHeight="1">
       <c r="B127" t="n">
         <v>3113</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" hidden="1" ht="14.4" customHeight="1">
+    <row r="128" hidden="1" ht="14.45" customHeight="1">
       <c r="B128" t="n">
         <v>3114</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" hidden="1" ht="14.4" customHeight="1">
+    <row r="129" hidden="1" ht="14.45" customHeight="1">
       <c r="B129" t="n">
         <v>3115</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" hidden="1" ht="14.4" customHeight="1">
+    <row r="130" hidden="1" ht="14.45" customHeight="1">
       <c r="B130" t="n">
         <v>3116</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" hidden="1" ht="14.4" customHeight="1">
+    <row r="131" hidden="1" ht="14.45" customHeight="1">
       <c r="B131" t="n">
         <v>3117</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" hidden="1" ht="14.4" customHeight="1">
+    <row r="132" hidden="1" ht="14.45" customHeight="1">
       <c r="B132" t="n">
         <v>3118</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" hidden="1" ht="14.4" customHeight="1">
+    <row r="133" hidden="1" ht="14.45" customHeight="1">
       <c r="B133" t="n">
         <v>3119</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" hidden="1" ht="14.4" customHeight="1">
+    <row r="134" hidden="1" ht="14.45" customHeight="1">
       <c r="B134" t="n">
         <v>3120</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" hidden="1" ht="14.4" customHeight="1">
+    <row r="135" hidden="1" ht="14.45" customHeight="1">
       <c r="B135" t="n">
         <v>3121</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" hidden="1" ht="14.4" customHeight="1">
+    <row r="136" hidden="1" ht="14.45" customHeight="1">
       <c r="B136" t="n">
         <v>3122</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" hidden="1" ht="14.4" customHeight="1">
+    <row r="137" hidden="1" ht="14.45" customHeight="1">
       <c r="B137" t="n">
         <v>3123</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" hidden="1" ht="14.4" customHeight="1">
+    <row r="138" hidden="1" ht="14.45" customHeight="1">
       <c r="B138" t="n">
         <v>3124</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" hidden="1" ht="14.4" customHeight="1">
+    <row r="139" hidden="1" ht="14.45" customHeight="1">
       <c r="B139" t="n">
         <v>3125</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" hidden="1" ht="14.4" customHeight="1">
+    <row r="140" hidden="1" ht="14.45" customHeight="1">
       <c r="B140" t="n">
         <v>3126</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" hidden="1" ht="14.4" customHeight="1">
+    <row r="141" hidden="1" ht="14.45" customHeight="1">
       <c r="B141" t="n">
         <v>3127</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" hidden="1" ht="14.4" customHeight="1">
+    <row r="142" hidden="1" ht="14.45" customHeight="1">
       <c r="B142" t="n">
         <v>3128</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" hidden="1" ht="14.4" customHeight="1">
+    <row r="143" hidden="1" ht="14.45" customHeight="1">
       <c r="B143" t="n">
         <v>3129</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" hidden="1" ht="14.4" customHeight="1">
+    <row r="144" hidden="1" ht="14.45" customHeight="1">
       <c r="B144" t="n">
         <v>3130</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" hidden="1" ht="14.4" customHeight="1">
+    <row r="145" hidden="1" ht="14.45" customHeight="1">
       <c r="B145" t="n">
         <v>3131</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" hidden="1" ht="14.4" customHeight="1">
+    <row r="146" hidden="1" ht="14.45" customHeight="1">
       <c r="B146" t="n">
         <v>3132</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" hidden="1" ht="14.4" customHeight="1">
+    <row r="147" hidden="1" ht="14.45" customHeight="1">
       <c r="B147" t="n">
         <v>3133</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" hidden="1" ht="14.4" customHeight="1">
+    <row r="148" hidden="1" ht="14.45" customHeight="1">
       <c r="B148" t="n">
         <v>3134</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" hidden="1" ht="14.4" customHeight="1">
+    <row r="149" hidden="1" ht="14.45" customHeight="1">
       <c r="B149" t="n">
         <v>3135</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" hidden="1" ht="14.4" customHeight="1">
+    <row r="150" hidden="1" ht="14.45" customHeight="1">
       <c r="B150" t="n">
         <v>3136</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" hidden="1" ht="14.4" customHeight="1">
+    <row r="151" hidden="1" ht="14.45" customHeight="1">
       <c r="B151" t="n">
         <v>3137</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" hidden="1" ht="14.4" customHeight="1">
+    <row r="152" hidden="1" ht="14.45" customHeight="1">
       <c r="B152" t="n">
         <v>3138</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" hidden="1" ht="14.4" customHeight="1">
+    <row r="153" hidden="1" ht="14.45" customHeight="1">
       <c r="B153" t="n">
         <v>3139</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" hidden="1" ht="14.4" customHeight="1">
+    <row r="154" hidden="1" ht="14.45" customHeight="1">
       <c r="B154" t="n">
         <v>3140</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" hidden="1" ht="14.4" customHeight="1">
+    <row r="155" hidden="1" ht="14.45" customHeight="1">
       <c r="B155" t="n">
         <v>3141</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" hidden="1" ht="14.4" customHeight="1">
+    <row r="156" hidden="1" ht="14.45" customHeight="1">
       <c r="B156" t="n">
         <v>3142</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" hidden="1" ht="14.4" customHeight="1">
+    <row r="157" hidden="1" ht="14.45" customHeight="1">
       <c r="B157" t="n">
         <v>3143</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" hidden="1" ht="14.4" customHeight="1">
+    <row r="158" hidden="1" ht="14.45" customHeight="1">
       <c r="B158" t="n">
         <v>3144</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" hidden="1" ht="14.4" customHeight="1">
+    <row r="159" hidden="1" ht="14.45" customHeight="1">
       <c r="B159" t="n">
         <v>3145</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" hidden="1" ht="14.4" customHeight="1">
+    <row r="160" hidden="1" ht="14.45" customHeight="1">
       <c r="B160" t="n">
         <v>3146</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" hidden="1" ht="14.4" customHeight="1">
+    <row r="161" hidden="1" ht="14.45" customHeight="1">
       <c r="B161" t="n">
         <v>3147</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" hidden="1" ht="14.4" customHeight="1">
+    <row r="162" hidden="1" ht="14.45" customHeight="1">
       <c r="B162" t="n">
         <v>3148</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" hidden="1" ht="14.4" customHeight="1">
+    <row r="163" hidden="1" ht="14.45" customHeight="1">
       <c r="B163" t="n">
         <v>3149</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" hidden="1" ht="14.4" customHeight="1">
+    <row r="164" hidden="1" ht="14.45" customHeight="1">
       <c r="B164" t="n">
         <v>3150</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" hidden="1" ht="14.4" customHeight="1">
+    <row r="165" hidden="1" ht="14.45" customHeight="1">
       <c r="B165" t="n">
         <v>3151</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" hidden="1" ht="14.4" customHeight="1">
+    <row r="166" hidden="1" ht="14.45" customHeight="1">
       <c r="B166" t="n">
         <v>3152</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" hidden="1" ht="14.4" customHeight="1">
+    <row r="167" hidden="1" ht="14.45" customHeight="1">
       <c r="B167" t="n">
         <v>3153</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" hidden="1" ht="14.4" customHeight="1">
+    <row r="168" hidden="1" ht="14.45" customHeight="1">
       <c r="B168" t="n">
         <v>3154</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" hidden="1" ht="14.4" customHeight="1">
+    <row r="169" hidden="1" ht="14.45" customHeight="1">
       <c r="B169" t="n">
         <v>3155</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" hidden="1" ht="14.4" customHeight="1">
+    <row r="170" hidden="1" ht="14.45" customHeight="1">
       <c r="B170" t="n">
         <v>3156</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" hidden="1" ht="14.4" customHeight="1">
+    <row r="171" hidden="1" ht="14.45" customHeight="1">
       <c r="B171" t="n">
         <v>3157</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" hidden="1" ht="14.4" customHeight="1">
+    <row r="172" hidden="1" ht="14.45" customHeight="1">
       <c r="B172" t="n">
         <v>3158</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" hidden="1" ht="14.4" customHeight="1">
+    <row r="173" hidden="1" ht="14.45" customHeight="1">
       <c r="B173" t="n">
         <v>3159</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" hidden="1" ht="14.4" customHeight="1">
+    <row r="174" hidden="1" ht="14.45" customHeight="1">
       <c r="B174" t="n">
         <v>3160</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" hidden="1" ht="14.4" customHeight="1">
+    <row r="175" hidden="1" ht="14.45" customHeight="1">
       <c r="B175" t="n">
         <v>3161</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" hidden="1" ht="14.4" customHeight="1">
+    <row r="176" hidden="1" ht="14.45" customHeight="1">
       <c r="B176" t="n">
         <v>3162</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" hidden="1" ht="14.4" customHeight="1">
+    <row r="177" hidden="1" ht="14.45" customHeight="1">
       <c r="B177" t="n">
         <v>3163</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" hidden="1" ht="14.4" customHeight="1">
+    <row r="178" hidden="1" ht="14.45" customHeight="1">
       <c r="B178" t="n">
         <v>3164</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" hidden="1" ht="14.4" customHeight="1">
+    <row r="179" hidden="1" ht="14.45" customHeight="1">
       <c r="B179" t="n">
         <v>3165</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" hidden="1" ht="14.4" customHeight="1">
+    <row r="180" hidden="1" ht="14.45" customHeight="1">
       <c r="B180" t="n">
         <v>3166</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" hidden="1" ht="14.4" customHeight="1">
+    <row r="181" hidden="1" ht="14.45" customHeight="1">
       <c r="B181" t="n">
         <v>3167</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" hidden="1" ht="14.4" customHeight="1">
+    <row r="182" hidden="1" ht="14.45" customHeight="1">
       <c r="B182" t="n">
         <v>3168</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" hidden="1" ht="14.4" customHeight="1">
+    <row r="183" hidden="1" ht="14.45" customHeight="1">
       <c r="B183" t="n">
         <v>3169</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" hidden="1" ht="14.4" customHeight="1">
+    <row r="184" hidden="1" ht="14.45" customHeight="1">
       <c r="B184" t="n">
         <v>3170</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" hidden="1" ht="14.4" customHeight="1">
+    <row r="185" hidden="1" ht="14.45" customHeight="1">
       <c r="B185" t="n">
         <v>3171</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" hidden="1" ht="14.4" customHeight="1">
+    <row r="186" hidden="1" ht="14.45" customHeight="1">
       <c r="B186" t="n">
         <v>3172</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" hidden="1" ht="14.4" customHeight="1">
+    <row r="187" hidden="1" ht="14.45" customHeight="1">
       <c r="B187" t="n">
         <v>3173</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" hidden="1" ht="14.4" customHeight="1">
+    <row r="188" hidden="1" ht="14.45" customHeight="1">
       <c r="B188" t="n">
         <v>3174</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" hidden="1" ht="14.4" customHeight="1">
+    <row r="189" hidden="1" ht="14.45" customHeight="1">
       <c r="B189" t="n">
         <v>3175</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" hidden="1" ht="14.4" customHeight="1">
+    <row r="190" hidden="1" ht="14.45" customHeight="1">
       <c r="B190" t="n">
         <v>3176</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" hidden="1" ht="14.4" customHeight="1">
+    <row r="191" hidden="1" ht="14.45" customHeight="1">
       <c r="B191" t="n">
         <v>3177</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" hidden="1" ht="14.4" customHeight="1">
+    <row r="192" hidden="1" ht="14.45" customHeight="1">
       <c r="B192" t="n">
         <v>3178</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" hidden="1" ht="14.4" customHeight="1">
+    <row r="193" hidden="1" ht="14.45" customHeight="1">
       <c r="B193" t="n">
         <v>3179</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" hidden="1" ht="14.4" customHeight="1">
+    <row r="194" hidden="1" ht="14.45" customHeight="1">
       <c r="B194" t="n">
         <v>3180</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" hidden="1" ht="14.4" customHeight="1">
+    <row r="195" hidden="1" ht="14.45" customHeight="1">
       <c r="B195" t="n">
         <v>3181</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" hidden="1" ht="14.4" customHeight="1">
+    <row r="196" hidden="1" ht="14.45" customHeight="1">
       <c r="B196" t="n">
         <v>3182</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" hidden="1" ht="14.4" customHeight="1">
+    <row r="197" hidden="1" ht="14.45" customHeight="1">
       <c r="B197" t="n">
         <v>3183</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" hidden="1" ht="14.4" customHeight="1">
+    <row r="198" hidden="1" ht="14.45" customHeight="1">
       <c r="B198" t="n">
         <v>3184</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" hidden="1" ht="14.4" customHeight="1">
+    <row r="199" hidden="1" ht="14.45" customHeight="1">
       <c r="B199" t="n">
         <v>3185</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" hidden="1" ht="14.4" customHeight="1">
+    <row r="200" hidden="1" ht="14.45" customHeight="1">
       <c r="B200" t="n">
         <v>3186</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" hidden="1" ht="14.4" customHeight="1">
+    <row r="201" hidden="1" ht="14.45" customHeight="1">
       <c r="B201" t="n">
         <v>3187</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" hidden="1" ht="14.4" customHeight="1">
+    <row r="202" hidden="1" ht="14.45" customHeight="1">
       <c r="B202" t="n">
         <v>3188</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" hidden="1" ht="14.4" customHeight="1">
+    <row r="203" hidden="1" ht="14.45" customHeight="1">
       <c r="B203" t="n">
         <v>3189</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" hidden="1" ht="14.4" customHeight="1">
+    <row r="204" hidden="1" ht="14.45" customHeight="1">
       <c r="B204" t="n">
         <v>3190</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" hidden="1" ht="14.4" customHeight="1">
+    <row r="205" hidden="1" ht="14.45" customHeight="1">
       <c r="B205" t="n">
         <v>3191</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" hidden="1" ht="14.4" customHeight="1">
+    <row r="206" hidden="1" ht="14.45" customHeight="1">
       <c r="B206" t="n">
         <v>3192</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" hidden="1" ht="14.4" customHeight="1">
+    <row r="207" hidden="1" ht="14.45" customHeight="1">
       <c r="B207" t="n">
         <v>3193</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" hidden="1" ht="14.4" customHeight="1">
+    <row r="208" hidden="1" ht="14.45" customHeight="1">
       <c r="B208" t="n">
         <v>3194</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" hidden="1" ht="14.4" customHeight="1">
+    <row r="209" hidden="1" ht="14.45" customHeight="1">
       <c r="B209" t="n">
         <v>3195</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" hidden="1" ht="14.4" customHeight="1">
+    <row r="210" hidden="1" ht="14.45" customHeight="1">
       <c r="B210" t="n">
         <v>3196</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" hidden="1" ht="14.4" customHeight="1">
+    <row r="211" hidden="1" ht="14.45" customHeight="1">
       <c r="B211" t="n">
         <v>3197</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" hidden="1" ht="14.4" customHeight="1">
+    <row r="212" hidden="1" ht="14.45" customHeight="1">
       <c r="B212" t="n">
         <v>3198</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" hidden="1" ht="14.4" customHeight="1">
+    <row r="213" hidden="1" ht="14.45" customHeight="1">
       <c r="B213" t="n">
         <v>3199</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" hidden="1" ht="14.4" customHeight="1">
+    <row r="214" hidden="1" ht="14.45" customHeight="1">
       <c r="B214" t="n">
         <v>3200</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" hidden="1" ht="14.4" customHeight="1">
+    <row r="215" hidden="1" ht="14.45" customHeight="1">
       <c r="B215" t="n">
         <v>3201</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" hidden="1" ht="14.4" customHeight="1">
+    <row r="216" hidden="1" ht="14.45" customHeight="1">
       <c r="B216" t="n">
         <v>3202</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" hidden="1" ht="14.4" customHeight="1">
+    <row r="217" hidden="1" ht="14.45" customHeight="1">
       <c r="B217" t="n">
         <v>3203</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" hidden="1" ht="14.4" customHeight="1">
+    <row r="218" hidden="1" ht="14.45" customHeight="1">
       <c r="B218" t="n">
         <v>3204</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" hidden="1" ht="14.4" customHeight="1">
+    <row r="219" hidden="1" ht="14.45" customHeight="1">
       <c r="B219" t="n">
         <v>3205</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" hidden="1" ht="14.4" customHeight="1">
+    <row r="220" hidden="1" ht="14.45" customHeight="1">
       <c r="B220" t="n">
         <v>3206</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" hidden="1" ht="14.4" customHeight="1">
+    <row r="221" hidden="1" ht="14.45" customHeight="1">
       <c r="B221" t="n">
         <v>3207</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" hidden="1" ht="14.4" customHeight="1">
+    <row r="222" hidden="1" ht="14.45" customHeight="1">
       <c r="B222" t="n">
         <v>3208</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" hidden="1" ht="14.4" customHeight="1">
+    <row r="223" hidden="1" ht="14.45" customHeight="1">
       <c r="B223" t="n">
         <v>3209</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" hidden="1" ht="14.4" customHeight="1">
+    <row r="224" hidden="1" ht="14.45" customHeight="1">
       <c r="B224" t="n">
         <v>3210</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" hidden="1" ht="14.4" customHeight="1">
+    <row r="225" hidden="1" ht="14.45" customHeight="1">
       <c r="B225" t="n">
         <v>3211</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" hidden="1" ht="14.4" customHeight="1">
+    <row r="226" hidden="1" ht="14.45" customHeight="1">
       <c r="B226" t="n">
         <v>3212</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" hidden="1" ht="14.4" customHeight="1">
+    <row r="227" hidden="1" ht="14.45" customHeight="1">
       <c r="B227" t="n">
         <v>3213</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" hidden="1" ht="14.4" customHeight="1">
+    <row r="228" hidden="1" ht="14.45" customHeight="1">
       <c r="B228" t="n">
         <v>3214</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" hidden="1" ht="14.4" customHeight="1">
+    <row r="229" hidden="1" ht="14.45" customHeight="1">
       <c r="B229" t="n">
         <v>3215</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" hidden="1" ht="14.4" customHeight="1">
+    <row r="230" hidden="1" ht="14.45" customHeight="1">
       <c r="B230" t="n">
         <v>3216</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" hidden="1" ht="14.4" customHeight="1">
+    <row r="231" hidden="1" ht="14.45" customHeight="1">
       <c r="B231" t="n">
         <v>3217</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" hidden="1" ht="14.4" customHeight="1">
+    <row r="232" hidden="1" ht="14.45" customHeight="1">
       <c r="B232" t="n">
         <v>3218</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" hidden="1" ht="14.4" customHeight="1">
+    <row r="233" hidden="1" ht="14.45" customHeight="1">
       <c r="B233" t="n">
         <v>3219</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" hidden="1" ht="14.4" customHeight="1">
+    <row r="234" hidden="1" ht="14.45" customHeight="1">
       <c r="B234" t="n">
         <v>3220</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" hidden="1" ht="14.4" customHeight="1">
+    <row r="235" hidden="1" ht="14.45" customHeight="1">
       <c r="B235" t="n">
         <v>3221</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" hidden="1" ht="14.4" customHeight="1">
+    <row r="236" hidden="1" ht="14.45" customHeight="1">
       <c r="B236" t="n">
         <v>3222</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" hidden="1" ht="14.4" customHeight="1">
+    <row r="237" hidden="1" ht="14.45" customHeight="1">
       <c r="B237" t="n">
         <v>3223</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" hidden="1" ht="14.4" customHeight="1">
+    <row r="238" hidden="1" ht="14.45" customHeight="1">
       <c r="B238" t="n">
         <v>3224</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" hidden="1" ht="14.4" customHeight="1">
+    <row r="239" hidden="1" ht="14.45" customHeight="1">
       <c r="B239" t="n">
         <v>3225</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" hidden="1" ht="14.4" customHeight="1">
+    <row r="240" hidden="1" ht="14.45" customHeight="1">
       <c r="B240" t="n">
         <v>3226</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" hidden="1" ht="14.4" customHeight="1">
+    <row r="241" hidden="1" ht="14.45" customHeight="1">
       <c r="B241" t="n">
         <v>3227</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" hidden="1" ht="14.4" customHeight="1">
+    <row r="242" hidden="1" ht="14.45" customHeight="1">
       <c r="B242" t="n">
         <v>3228</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" hidden="1" ht="14.4" customHeight="1">
+    <row r="243" hidden="1" ht="14.45" customHeight="1">
       <c r="B243" t="n">
         <v>3229</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" hidden="1" ht="14.4" customHeight="1">
+    <row r="244" hidden="1" ht="14.45" customHeight="1">
       <c r="B244" t="n">
         <v>3230</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" hidden="1" ht="14.4" customHeight="1">
+    <row r="245" hidden="1" ht="14.45" customHeight="1">
       <c r="B245" t="n">
         <v>3231</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" hidden="1" ht="14.4" customHeight="1">
+    <row r="246" hidden="1" ht="14.45" customHeight="1">
       <c r="B246" t="n">
         <v>3232</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" hidden="1" ht="14.4" customHeight="1">
+    <row r="247" hidden="1" ht="14.45" customHeight="1">
       <c r="B247" t="n">
         <v>3233</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" hidden="1" ht="14.4" customHeight="1">
+    <row r="248" hidden="1" ht="14.45" customHeight="1">
       <c r="B248" t="n">
         <v>3234</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" hidden="1" ht="14.4" customHeight="1">
+    <row r="249" hidden="1" ht="14.45" customHeight="1">
       <c r="B249" t="n">
         <v>3235</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" hidden="1" ht="14.4" customHeight="1">
+    <row r="250" hidden="1" ht="14.45" customHeight="1">
       <c r="B250" t="n">
         <v>3236</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" hidden="1" ht="14.4" customHeight="1">
+    <row r="251" hidden="1" ht="14.45" customHeight="1">
       <c r="B251" t="n">
         <v>3237</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" hidden="1" ht="14.4" customHeight="1">
+    <row r="252" hidden="1" ht="14.45" customHeight="1">
       <c r="B252" t="n">
         <v>3238</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" hidden="1" ht="14.4" customHeight="1">
+    <row r="253" hidden="1" ht="14.45" customHeight="1">
       <c r="B253" t="n">
         <v>3239</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" hidden="1" ht="14.4" customHeight="1">
+    <row r="254" hidden="1" ht="14.45" customHeight="1">
       <c r="B254" t="n">
         <v>3240</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" hidden="1" ht="14.4" customHeight="1">
+    <row r="255" hidden="1" ht="14.45" customHeight="1">
       <c r="B255" t="n">
         <v>3241</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" hidden="1" ht="14.4" customHeight="1">
+    <row r="256" hidden="1" ht="14.45" customHeight="1">
       <c r="B256" t="n">
         <v>3242</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" hidden="1" ht="14.4" customHeight="1">
+    <row r="257" hidden="1" ht="14.45" customHeight="1">
       <c r="B257" t="n">
         <v>3243</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" hidden="1" ht="14.4" customHeight="1">
+    <row r="258" hidden="1" ht="14.45" customHeight="1">
       <c r="B258" t="n">
         <v>3244</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" hidden="1" ht="14.4" customHeight="1">
+    <row r="259" hidden="1" ht="14.45" customHeight="1">
       <c r="B259" t="n">
         <v>3245</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" hidden="1" ht="14.4" customHeight="1">
+    <row r="260" hidden="1" ht="14.45" customHeight="1">
       <c r="B260" t="n">
         <v>3246</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" hidden="1" ht="14.4" customHeight="1">
+    <row r="261" hidden="1" ht="14.45" customHeight="1">
       <c r="B261" t="n">
         <v>3247</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" hidden="1" ht="14.4" customHeight="1">
+    <row r="262" hidden="1" ht="14.45" customHeight="1">
       <c r="B262" t="n">
         <v>3248</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" hidden="1" ht="14.4" customHeight="1">
+    <row r="263" hidden="1" ht="14.45" customHeight="1">
       <c r="B263" t="n">
         <v>3249</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" hidden="1" ht="14.4" customHeight="1">
+    <row r="264" hidden="1" ht="14.45" customHeight="1">
       <c r="B264" t="n">
         <v>3250</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" hidden="1" ht="14.4" customHeight="1">
+    <row r="265" hidden="1" ht="14.45" customHeight="1">
       <c r="B265" t="n">
         <v>3251</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" hidden="1" ht="14.4" customHeight="1">
+    <row r="266" hidden="1" ht="14.45" customHeight="1">
       <c r="B266" t="n">
         <v>3252</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" hidden="1" ht="14.4" customHeight="1">
+    <row r="267" hidden="1" ht="14.45" customHeight="1">
       <c r="B267" t="n">
         <v>3253</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" hidden="1" ht="14.4" customHeight="1">
+    <row r="268" hidden="1" ht="14.45" customHeight="1">
       <c r="B268" t="n">
         <v>3254</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" hidden="1" ht="14.4" customHeight="1">
+    <row r="269" hidden="1" ht="14.45" customHeight="1">
       <c r="B269" t="n">
         <v>3255</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" hidden="1" ht="14.4" customHeight="1">
+    <row r="270" hidden="1" ht="14.45" customHeight="1">
       <c r="B270" t="n">
         <v>3256</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" hidden="1" ht="14.4" customHeight="1">
+    <row r="271" hidden="1" ht="14.45" customHeight="1">
       <c r="B271" t="n">
         <v>3257</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" hidden="1" ht="14.4" customHeight="1">
+    <row r="272" hidden="1" ht="14.45" customHeight="1">
       <c r="B272" t="n">
         <v>3258</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" hidden="1" ht="14.4" customHeight="1">
+    <row r="273" hidden="1" ht="14.45" customHeight="1">
       <c r="B273" t="n">
         <v>3259</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" hidden="1" ht="14.4" customHeight="1">
+    <row r="274" hidden="1" ht="14.45" customHeight="1">
       <c r="B274" t="n">
         <v>3260</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" hidden="1" ht="14.4" customHeight="1">
+    <row r="275" hidden="1" ht="14.45" customHeight="1">
       <c r="B275" t="n">
         <v>3261</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" hidden="1" ht="14.4" customHeight="1">
+    <row r="276" hidden="1" ht="14.45" customHeight="1">
       <c r="B276" t="n">
         <v>3262</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" hidden="1" ht="14.4" customHeight="1">
+    <row r="277" hidden="1" ht="14.45" customHeight="1">
       <c r="B277" t="n">
         <v>3263</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" hidden="1" ht="14.4" customHeight="1">
+    <row r="278" hidden="1" ht="14.45" customHeight="1">
       <c r="B278" t="n">
         <v>3264</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" hidden="1" ht="14.4" customHeight="1">
+    <row r="279" hidden="1" ht="14.45" customHeight="1">
       <c r="B279" t="n">
         <v>3265</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" hidden="1" ht="14.4" customHeight="1">
+    <row r="280" hidden="1" ht="14.45" customHeight="1">
       <c r="B280" t="n">
         <v>3266</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" hidden="1" ht="14.4" customHeight="1">
+    <row r="281" hidden="1" ht="14.45" customHeight="1">
       <c r="B281" t="n">
         <v>3267</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" hidden="1" ht="14.4" customHeight="1">
+    <row r="282" hidden="1" ht="14.45" customHeight="1">
       <c r="B282" t="n">
         <v>3268</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" hidden="1" ht="14.4" customHeight="1">
+    <row r="283" hidden="1" ht="14.45" customHeight="1">
       <c r="B283" t="n">
         <v>3269</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" hidden="1" ht="14.4" customHeight="1">
+    <row r="284" hidden="1" ht="14.45" customHeight="1">
       <c r="B284" t="n">
         <v>3270</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" hidden="1" ht="14.4" customHeight="1">
+    <row r="285" hidden="1" ht="14.45" customHeight="1">
       <c r="B285" t="n">
         <v>3271</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" hidden="1" ht="14.4" customHeight="1">
+    <row r="286" hidden="1" ht="14.45" customHeight="1">
       <c r="B286" t="n">
         <v>3272</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" hidden="1" ht="14.4" customHeight="1">
+    <row r="287" hidden="1" ht="14.45" customHeight="1">
       <c r="B287" t="n">
         <v>3273</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" hidden="1" ht="14.4" customHeight="1">
+    <row r="288" hidden="1" ht="14.45" customHeight="1">
       <c r="B288" t="n">
         <v>3274</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" hidden="1" ht="14.4" customHeight="1">
+    <row r="289" hidden="1" ht="14.45" customHeight="1">
       <c r="B289" t="n">
         <v>3275</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" hidden="1" ht="14.4" customHeight="1">
+    <row r="290" hidden="1" ht="14.45" customHeight="1">
       <c r="B290" t="n">
         <v>3276</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" hidden="1" ht="14.4" customHeight="1">
+    <row r="291" hidden="1" ht="14.45" customHeight="1">
       <c r="B291" t="n">
         <v>3277</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" hidden="1" ht="14.4" customHeight="1">
+    <row r="292" hidden="1" ht="14.45" customHeight="1">
       <c r="B292" t="n">
         <v>3278</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" hidden="1" ht="14.4" customHeight="1">
+    <row r="293" hidden="1" ht="14.45" customHeight="1">
       <c r="B293" t="n">
         <v>3279</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" hidden="1" ht="14.4" customHeight="1">
+    <row r="294" hidden="1" ht="14.45" customHeight="1">
       <c r="B294" t="n">
         <v>3280</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" hidden="1" ht="14.4" customHeight="1">
+    <row r="295" hidden="1" ht="14.45" customHeight="1">
       <c r="B295" t="n">
         <v>3281</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" hidden="1" ht="14.4" customHeight="1">
+    <row r="296" hidden="1" ht="14.45" customHeight="1">
       <c r="B296" t="n">
         <v>3282</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" hidden="1" ht="14.4" customHeight="1">
+    <row r="297" hidden="1" ht="14.45" customHeight="1">
       <c r="B297" t="n">
         <v>3283</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" hidden="1" ht="14.4" customHeight="1">
+    <row r="298" hidden="1" ht="14.45" customHeight="1">
       <c r="B298" t="n">
         <v>3284</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" hidden="1" ht="14.4" customHeight="1">
+    <row r="299" hidden="1" ht="14.45" customHeight="1">
       <c r="B299" t="n">
         <v>3285</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" hidden="1" ht="14.4" customHeight="1">
+    <row r="300" hidden="1" ht="14.45" customHeight="1">
       <c r="B300" t="n">
         <v>3286</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" hidden="1" ht="14.4" customHeight="1">
+    <row r="301" hidden="1" ht="14.45" customHeight="1">
       <c r="B301" t="n">
         <v>3287</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" hidden="1" ht="14.4" customHeight="1">
+    <row r="302" hidden="1" ht="14.45" customHeight="1">
       <c r="B302" t="n">
         <v>3288</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" hidden="1" ht="14.4" customHeight="1">
+    <row r="303" hidden="1" ht="14.45" customHeight="1">
       <c r="B303" t="n">
         <v>3289</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" hidden="1" ht="14.4" customHeight="1">
+    <row r="304" hidden="1" ht="14.45" customHeight="1">
       <c r="B304" t="n">
         <v>3290</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" hidden="1" ht="14.4" customHeight="1">
+    <row r="305" hidden="1" ht="14.45" customHeight="1">
       <c r="B305" t="n">
         <v>3291</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" hidden="1" ht="14.4" customHeight="1">
+    <row r="306" hidden="1" ht="14.45" customHeight="1">
       <c r="B306" t="n">
         <v>3292</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" hidden="1" ht="14.4" customHeight="1">
+    <row r="307" hidden="1" ht="14.45" customHeight="1">
       <c r="B307" t="n">
         <v>3293</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" hidden="1" ht="14.4" customHeight="1">
+    <row r="308" hidden="1" ht="14.45" customHeight="1">
       <c r="B308" t="n">
         <v>3294</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" hidden="1" ht="14.4" customHeight="1">
+    <row r="309" hidden="1" ht="14.45" customHeight="1">
       <c r="B309" t="n">
         <v>3295</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" hidden="1" ht="14.4" customHeight="1">
+    <row r="310" hidden="1" ht="14.45" customHeight="1">
       <c r="B310" t="n">
         <v>3296</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" hidden="1" ht="14.4" customHeight="1">
+    <row r="311" hidden="1" ht="14.45" customHeight="1">
       <c r="B311" t="n">
         <v>3297</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" hidden="1" ht="14.4" customHeight="1">
+    <row r="312" hidden="1" ht="14.45" customHeight="1">
       <c r="B312" t="n">
         <v>3298</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" hidden="1" ht="14.4" customHeight="1">
+    <row r="313" hidden="1" ht="14.45" customHeight="1">
       <c r="B313" t="n">
         <v>3299</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" hidden="1" ht="14.4" customHeight="1">
+    <row r="314" hidden="1" ht="14.45" customHeight="1">
       <c r="B314" t="n">
         <v>3300</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" hidden="1" ht="14.4" customHeight="1">
+    <row r="315" hidden="1" ht="14.45" customHeight="1">
       <c r="B315" t="n">
         <v>3301</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" hidden="1" ht="14.4" customHeight="1">
+    <row r="316" hidden="1" ht="14.45" customHeight="1">
       <c r="B316" t="n">
         <v>3302</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" hidden="1" ht="14.4" customHeight="1">
+    <row r="317" hidden="1" ht="14.45" customHeight="1">
       <c r="B317" t="n">
         <v>3303</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" hidden="1" ht="14.4" customHeight="1">
+    <row r="318" hidden="1" ht="14.45" customHeight="1">
       <c r="B318" t="n">
         <v>3304</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" hidden="1" ht="14.4" customHeight="1">
+    <row r="319" hidden="1" ht="14.45" customHeight="1">
       <c r="B319" t="n">
         <v>3305</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" hidden="1" ht="14.4" customHeight="1">
+    <row r="320" hidden="1" ht="14.45" customHeight="1">
       <c r="B320" t="n">
         <v>3306</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" hidden="1" ht="14.4" customHeight="1">
+    <row r="321" hidden="1" ht="14.45" customHeight="1">
       <c r="B321" t="n">
         <v>3307</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" hidden="1" ht="14.4" customHeight="1">
+    <row r="322" hidden="1" ht="14.45" customHeight="1">
       <c r="B322" t="n">
         <v>3308</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" hidden="1" ht="14.4" customHeight="1">
+    <row r="323" hidden="1" ht="14.45" customHeight="1">
       <c r="B323" t="n">
         <v>3309</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" hidden="1" ht="14.4" customHeight="1">
+    <row r="324" hidden="1" ht="14.45" customHeight="1">
       <c r="B324" t="n">
         <v>3310</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" hidden="1" ht="14.4" customHeight="1">
+    <row r="325" hidden="1" ht="14.45" customHeight="1">
       <c r="B325" t="n">
         <v>3311</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" hidden="1" ht="14.4" customHeight="1">
+    <row r="326" hidden="1" ht="14.45" customHeight="1">
       <c r="B326" t="n">
         <v>3312</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" hidden="1" ht="14.4" customHeight="1">
+    <row r="327" hidden="1" ht="14.45" customHeight="1">
       <c r="B327" t="n">
         <v>3313</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" hidden="1" ht="14.4" customHeight="1">
+    <row r="328" hidden="1" ht="14.45" customHeight="1">
       <c r="B328" t="n">
         <v>3314</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" hidden="1" ht="14.4" customHeight="1">
+    <row r="329" hidden="1" ht="14.45" customHeight="1">
       <c r="B329" t="n">
         <v>3315</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" hidden="1" ht="14.4" customHeight="1">
+    <row r="330" hidden="1" ht="14.45" customHeight="1">
       <c r="B330" t="n">
         <v>3316</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" hidden="1" ht="14.4" customHeight="1">
+    <row r="331" hidden="1" ht="14.45" customHeight="1">
       <c r="B331" t="n">
         <v>3317</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" hidden="1" ht="14.4" customHeight="1">
+    <row r="332" hidden="1" ht="14.45" customHeight="1">
       <c r="B332" t="n">
         <v>3318</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" hidden="1" ht="14.4" customHeight="1">
+    <row r="333" hidden="1" ht="14.45" customHeight="1">
       <c r="B333" t="n">
         <v>3319</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" hidden="1" ht="14.4" customHeight="1">
+    <row r="334" hidden="1" ht="14.45" customHeight="1">
       <c r="B334" t="n">
         <v>3320</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" hidden="1" ht="14.4" customHeight="1">
+    <row r="335" hidden="1" ht="14.45" customHeight="1">
       <c r="B335" t="n">
         <v>3321</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" hidden="1" ht="14.4" customHeight="1">
+    <row r="336" hidden="1" ht="14.45" customHeight="1">
       <c r="B336" t="n">
         <v>3322</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" hidden="1" ht="14.4" customHeight="1">
+    <row r="337" hidden="1" ht="14.45" customHeight="1">
       <c r="B337" t="n">
         <v>3323</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" hidden="1" ht="14.4" customHeight="1">
+    <row r="338" hidden="1" ht="14.45" customHeight="1">
       <c r="B338" t="n">
         <v>3324</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" hidden="1" ht="14.4" customHeight="1">
+    <row r="339" hidden="1" ht="14.45" customHeight="1">
       <c r="B339" t="n">
         <v>3325</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" hidden="1" ht="14.4" customHeight="1">
+    <row r="340" hidden="1" ht="14.45" customHeight="1">
       <c r="B340" t="n">
         <v>3326</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" hidden="1" ht="14.4" customHeight="1">
+    <row r="341" hidden="1" ht="14.45" customHeight="1">
       <c r="B341" t="n">
         <v>3327</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" hidden="1" ht="14.4" customHeight="1">
+    <row r="342" hidden="1" ht="14.45" customHeight="1">
       <c r="B342" t="n">
         <v>3328</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" hidden="1" ht="14.4" customHeight="1">
+    <row r="343" hidden="1" ht="14.45" customHeight="1">
       <c r="B343" t="n">
         <v>3329</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" hidden="1" ht="14.4" customHeight="1">
+    <row r="344" hidden="1" ht="14.45" customHeight="1">
       <c r="B344" t="n">
         <v>3330</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" hidden="1" ht="14.4" customHeight="1">
+    <row r="345" hidden="1" ht="14.45" customHeight="1">
       <c r="B345" t="n">
         <v>3331</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" hidden="1" ht="14.4" customHeight="1">
+    <row r="346" hidden="1" ht="14.45" customHeight="1">
       <c r="B346" t="n">
         <v>3332</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" hidden="1" ht="14.4" customHeight="1">
+    <row r="347" hidden="1" ht="14.45" customHeight="1">
       <c r="B347" t="n">
         <v>3333</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" hidden="1" ht="14.4" customHeight="1">
+    <row r="348" hidden="1" ht="14.45" customHeight="1">
       <c r="B348" t="n">
         <v>3334</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" hidden="1" ht="14.4" customHeight="1">
+    <row r="349" hidden="1" ht="14.45" customHeight="1">
       <c r="B349" t="n">
         <v>3335</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" hidden="1" ht="14.4" customHeight="1">
+    <row r="350" hidden="1" ht="14.45" customHeight="1">
       <c r="B350" t="n">
         <v>3336</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" hidden="1" ht="14.4" customHeight="1">
+    <row r="351" hidden="1" ht="14.45" customHeight="1">
       <c r="B351" t="n">
         <v>3337</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" hidden="1" ht="14.4" customHeight="1">
+    <row r="352" hidden="1" ht="14.45" customHeight="1">
       <c r="B352" t="n">
         <v>3338</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" hidden="1" ht="14.4" customHeight="1">
+    <row r="353" hidden="1" ht="14.45" customHeight="1">
       <c r="B353" t="n">
         <v>3339</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" hidden="1" ht="14.4" customHeight="1">
+    <row r="354" hidden="1" ht="14.45" customHeight="1">
       <c r="B354" t="n">
         <v>3340</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" hidden="1" ht="14.4" customHeight="1">
+    <row r="355" hidden="1" ht="14.45" customHeight="1">
       <c r="B355" t="n">
         <v>3341</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" hidden="1" ht="14.4" customHeight="1">
+    <row r="356" hidden="1" ht="14.45" customHeight="1">
       <c r="B356" t="n">
         <v>3342</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" hidden="1" ht="14.4" customHeight="1">
+    <row r="357" hidden="1" ht="14.45" customHeight="1">
       <c r="B357" t="n">
         <v>3343</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" hidden="1" ht="14.4" customHeight="1">
+    <row r="358" hidden="1" ht="14.45" customHeight="1">
       <c r="B358" t="n">
         <v>3344</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" hidden="1" ht="14.4" customHeight="1">
+    <row r="359" hidden="1" ht="14.45" customHeight="1">
       <c r="B359" t="n">
         <v>3345</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" hidden="1" ht="14.4" customHeight="1">
+    <row r="360" hidden="1" ht="14.45" customHeight="1">
       <c r="B360" t="n">
         <v>3346</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" hidden="1" ht="14.4" customHeight="1">
+    <row r="361" hidden="1" ht="14.45" customHeight="1">
       <c r="B361" t="n">
         <v>3347</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" hidden="1" ht="14.4" customHeight="1">
+    <row r="362" hidden="1" ht="14.45" customHeight="1">
       <c r="B362" t="n">
         <v>3348</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" hidden="1" ht="14.4" customHeight="1">
+    <row r="363" hidden="1" ht="14.45" customHeight="1">
       <c r="B363" t="n">
         <v>3349</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" hidden="1" ht="14.4" customHeight="1">
+    <row r="364" hidden="1" ht="14.45" customHeight="1">
       <c r="B364" t="n">
         <v>3350</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" hidden="1" ht="14.4" customHeight="1">
+    <row r="365" hidden="1" ht="14.45" customHeight="1">
       <c r="B365" t="n">
         <v>3351</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" hidden="1" ht="14.4" customHeight="1">
+    <row r="366" hidden="1" ht="14.45" customHeight="1">
       <c r="B366" t="n">
         <v>3352</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" hidden="1" ht="14.4" customHeight="1">
+    <row r="367" hidden="1" ht="14.45" customHeight="1">
       <c r="B367" t="n">
         <v>3353</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" hidden="1" ht="14.4" customHeight="1">
+    <row r="368" hidden="1" ht="14.45" customHeight="1">
       <c r="B368" t="n">
         <v>3354</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" hidden="1" ht="14.4" customHeight="1">
+    <row r="369" hidden="1" ht="14.45" customHeight="1">
       <c r="B369" t="n">
         <v>3355</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" hidden="1" ht="14.4" customHeight="1">
+    <row r="370" hidden="1" ht="14.45" customHeight="1">
       <c r="B370" t="n">
         <v>3356</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" hidden="1" ht="14.4" customHeight="1">
+    <row r="371" hidden="1" ht="14.45" customHeight="1">
       <c r="B371" t="n">
         <v>3357</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" hidden="1" ht="14.4" customHeight="1">
+    <row r="372" hidden="1" ht="14.45" customHeight="1">
       <c r="B372" t="n">
         <v>3358</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" hidden="1" ht="14.4" customHeight="1">
+    <row r="373" hidden="1" ht="14.45" customHeight="1">
       <c r="B373" t="n">
         <v>3359</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" hidden="1" ht="14.4" customHeight="1">
+    <row r="374" hidden="1" ht="14.45" customHeight="1">
       <c r="B374" t="n">
         <v>3360</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" hidden="1" ht="14.4" customHeight="1">
+    <row r="375" hidden="1" ht="14.45" customHeight="1">
       <c r="B375" t="n">
         <v>3361</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" hidden="1" ht="14.4" customHeight="1">
+    <row r="376" hidden="1" ht="14.45" customHeight="1">
       <c r="B376" t="n">
         <v>3362</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" hidden="1" ht="14.4" customHeight="1">
+    <row r="377" hidden="1" ht="14.45" customHeight="1">
       <c r="B377" t="n">
         <v>3363</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" hidden="1" ht="14.4" customHeight="1">
+    <row r="378" hidden="1" ht="14.45" customHeight="1">
       <c r="B378" t="n">
         <v>3364</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" hidden="1" ht="14.4" customHeight="1">
+    <row r="379" hidden="1" ht="14.45" customHeight="1">
       <c r="B379" t="n">
         <v>3365</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" hidden="1" ht="14.4" customHeight="1">
+    <row r="380" hidden="1" ht="14.45" customHeight="1">
       <c r="B380" t="n">
         <v>3366</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" hidden="1" ht="14.4" customHeight="1">
+    <row r="381" hidden="1" ht="14.45" customHeight="1">
       <c r="B381" t="n">
         <v>3367</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" hidden="1" ht="14.4" customHeight="1">
+    <row r="382" hidden="1" ht="14.45" customHeight="1">
       <c r="B382" t="n">
         <v>3368</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" hidden="1" ht="14.4" customHeight="1">
+    <row r="383" hidden="1" ht="14.45" customHeight="1">
       <c r="B383" t="n">
         <v>3369</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" hidden="1" ht="14.4" customHeight="1">
+    <row r="384" hidden="1" ht="14.45" customHeight="1">
       <c r="B384" t="n">
         <v>3370</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" hidden="1" ht="14.4" customHeight="1">
+    <row r="385" hidden="1" ht="14.45" customHeight="1">
       <c r="B385" t="n">
         <v>3371</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" hidden="1" ht="14.4" customHeight="1">
+    <row r="386" hidden="1" ht="14.45" customHeight="1">
       <c r="B386" t="n">
         <v>3372</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" hidden="1" ht="14.4" customHeight="1">
+    <row r="387" hidden="1" ht="14.45" customHeight="1">
       <c r="B387" t="n">
         <v>3373</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" hidden="1" ht="14.4" customHeight="1">
+    <row r="388" hidden="1" ht="14.45" customHeight="1">
       <c r="B388" t="n">
         <v>3374</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" hidden="1" ht="14.4" customHeight="1">
+    <row r="389" hidden="1" ht="14.45" customHeight="1">
       <c r="B389" t="n">
         <v>3375</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" hidden="1" ht="14.4" customHeight="1">
+    <row r="390" hidden="1" ht="14.45" customHeight="1">
       <c r="B390" t="n">
         <v>3376</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" hidden="1" ht="14.4" customHeight="1">
+    <row r="391" hidden="1" ht="14.45" customHeight="1">
       <c r="B391" t="n">
         <v>3377</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" hidden="1" ht="14.4" customHeight="1">
+    <row r="392" hidden="1" ht="14.45" customHeight="1">
       <c r="B392" t="n">
         <v>3378</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" hidden="1" ht="14.4" customHeight="1">
+    <row r="393" hidden="1" ht="14.45" customHeight="1">
       <c r="B393" t="n">
         <v>3379</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" hidden="1" ht="14.4" customHeight="1">
+    <row r="394" hidden="1" ht="14.45" customHeight="1">
       <c r="B394" t="n">
         <v>3380</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" hidden="1" ht="14.4" customHeight="1">
+    <row r="395" hidden="1" ht="14.45" customHeight="1">
       <c r="B395" t="n">
         <v>3381</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" hidden="1" ht="14.4" customHeight="1">
+    <row r="396" hidden="1" ht="14.45" customHeight="1">
       <c r="B396" t="n">
         <v>3382</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" hidden="1" ht="14.4" customHeight="1">
+    <row r="397" hidden="1" ht="14.45" customHeight="1">
       <c r="B397" t="n">
         <v>3383</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" hidden="1" ht="14.4" customHeight="1">
+    <row r="398" hidden="1" ht="14.45" customHeight="1">
       <c r="B398" t="n">
         <v>3384</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" hidden="1" ht="14.4" customHeight="1">
+    <row r="399" hidden="1" ht="14.45" customHeight="1">
       <c r="B399" t="n">
         <v>3385</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" hidden="1" ht="14.4" customHeight="1">
+    <row r="400" hidden="1" ht="14.45" customHeight="1">
       <c r="B400" t="n">
         <v>3386</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" hidden="1" ht="14.4" customHeight="1">
+    <row r="401" hidden="1" ht="14.45" customHeight="1">
       <c r="B401" t="n">
         <v>3387</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" hidden="1" ht="14.4" customHeight="1">
+    <row r="402" hidden="1" ht="14.45" customHeight="1">
       <c r="B402" t="n">
         <v>3388</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" hidden="1" ht="14.4" customHeight="1">
+    <row r="403" hidden="1" ht="14.45" customHeight="1">
       <c r="B403" t="n">
         <v>3389</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" hidden="1" ht="14.4" customHeight="1">
+    <row r="404" hidden="1" ht="14.45" customHeight="1">
       <c r="B404" t="n">
         <v>3390</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" hidden="1" ht="14.4" customHeight="1">
+    <row r="405" hidden="1" ht="14.45" customHeight="1">
       <c r="B405" t="n">
         <v>3391</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" hidden="1" ht="14.4" customHeight="1">
+    <row r="406" hidden="1" ht="14.45" customHeight="1">
       <c r="B406" t="n">
         <v>3392</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" hidden="1" ht="14.4" customHeight="1">
+    <row r="407" hidden="1" ht="14.45" customHeight="1">
       <c r="B407" t="n">
         <v>3393</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" hidden="1" ht="14.4" customHeight="1">
+    <row r="408" hidden="1" ht="14.45" customHeight="1">
       <c r="B408" t="n">
         <v>3394</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" hidden="1" ht="14.4" customHeight="1">
+    <row r="409" hidden="1" ht="14.45" customHeight="1">
       <c r="B409" t="n">
         <v>3395</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" hidden="1" ht="14.4" customHeight="1">
+    <row r="410" hidden="1" ht="14.45" customHeight="1">
       <c r="B410" t="n">
         <v>3396</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" hidden="1" ht="14.4" customHeight="1">
+    <row r="411" hidden="1" ht="14.45" customHeight="1">
       <c r="B411" t="n">
         <v>3397</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" hidden="1" ht="14.4" customHeight="1">
+    <row r="412" hidden="1" ht="14.45" customHeight="1">
       <c r="B412" t="n">
         <v>3398</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" hidden="1" ht="14.4" customHeight="1">
+    <row r="413" hidden="1" ht="14.45" customHeight="1">
       <c r="B413" t="n">
         <v>3399</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" hidden="1" ht="14.4" customHeight="1">
+    <row r="414" hidden="1" ht="14.45" customHeight="1">
       <c r="B414" t="n">
         <v>3400</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" hidden="1" ht="14.4" customHeight="1">
+    <row r="415" hidden="1" ht="14.45" customHeight="1">
       <c r="B415" t="n">
         <v>3401</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" hidden="1" ht="14.4" customHeight="1">
+    <row r="416" hidden="1" ht="14.45" customHeight="1">
       <c r="B416" t="n">
         <v>3402</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" hidden="1" ht="14.4" customHeight="1">
+    <row r="417" hidden="1" ht="14.45" customHeight="1">
       <c r="B417" t="n">
         <v>3403</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" hidden="1" ht="14.4" customHeight="1">
+    <row r="418" hidden="1" ht="14.45" customHeight="1">
       <c r="B418" t="n">
         <v>3404</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" hidden="1" ht="14.4" customHeight="1">
+    <row r="419" hidden="1" ht="14.45" customHeight="1">
       <c r="B419" t="n">
         <v>3405</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" hidden="1" ht="14.4" customHeight="1">
+    <row r="420" hidden="1" ht="14.45" customHeight="1">
       <c r="B420" t="n">
         <v>3406</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" hidden="1" ht="14.4" customHeight="1">
+    <row r="421" hidden="1" ht="14.45" customHeight="1">
       <c r="B421" t="n">
         <v>3407</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" hidden="1" ht="14.4" customHeight="1">
+    <row r="422" hidden="1" ht="14.45" customHeight="1">
       <c r="B422" t="n">
         <v>3408</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" hidden="1" ht="14.4" customHeight="1">
+    <row r="423" hidden="1" ht="14.45" customHeight="1">
       <c r="B423" t="n">
         <v>3409</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" hidden="1" ht="14.4" customHeight="1">
+    <row r="424" hidden="1" ht="14.45" customHeight="1">
       <c r="B424" t="n">
         <v>3410</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" hidden="1" ht="14.4" customHeight="1">
+    <row r="425" hidden="1" ht="14.45" customHeight="1">
       <c r="B425" t="n">
         <v>3411</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" hidden="1" ht="14.4" customHeight="1">
+    <row r="426" hidden="1" ht="14.45" customHeight="1">
       <c r="B426" t="n">
         <v>3412</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" hidden="1" ht="14.4" customHeight="1">
+    <row r="427" hidden="1" ht="14.45" customHeight="1">
       <c r="B427" t="n">
         <v>3413</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" hidden="1" ht="14.4" customHeight="1">
+    <row r="428" hidden="1" ht="14.45" customHeight="1">
       <c r="B428" t="n">
         <v>3414</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" hidden="1" ht="14.4" customHeight="1">
+    <row r="429" hidden="1" ht="14.45" customHeight="1">
       <c r="B429" t="n">
         <v>3415</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" hidden="1" ht="14.4" customHeight="1">
+    <row r="430" hidden="1" ht="14.45" customHeight="1">
       <c r="B430" t="n">
         <v>3416</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" hidden="1" ht="14.4" customHeight="1">
+    <row r="431" hidden="1" ht="14.45" customHeight="1">
       <c r="B431" t="n">
         <v>3417</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" hidden="1" ht="14.4" customHeight="1">
+    <row r="432" hidden="1" ht="14.45" customHeight="1">
       <c r="B432" t="n">
         <v>3418</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" hidden="1" ht="14.4" customHeight="1">
+    <row r="433" hidden="1" ht="14.45" customHeight="1">
       <c r="B433" t="n">
         <v>3419</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" hidden="1" ht="14.4" customHeight="1">
+    <row r="434" hidden="1" ht="14.45" customHeight="1">
       <c r="B434" t="n">
         <v>3420</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" hidden="1" ht="14.4" customHeight="1">
+    <row r="435" hidden="1" ht="14.45" customHeight="1">
       <c r="B435" t="n">
         <v>3421</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" hidden="1" ht="14.4" customHeight="1">
+    <row r="436" hidden="1" ht="14.45" customHeight="1">
       <c r="B436" t="n">
         <v>3422</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" hidden="1" ht="14.4" customHeight="1">
+    <row r="437" hidden="1" ht="14.45" customHeight="1">
       <c r="B437" t="n">
         <v>3423</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" hidden="1" ht="14.4" customHeight="1">
+    <row r="438" hidden="1" ht="14.45" customHeight="1">
       <c r="B438" t="n">
         <v>3424</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" hidden="1" ht="14.4" customHeight="1">
+    <row r="439" hidden="1" ht="14.45" customHeight="1">
       <c r="B439" t="n">
         <v>3425</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" hidden="1" ht="14.4" customHeight="1">
+    <row r="440" hidden="1" ht="14.45" customHeight="1">
       <c r="B440" t="n">
         <v>3426</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" hidden="1" ht="14.4" customHeight="1">
+    <row r="441" hidden="1" ht="14.45" customHeight="1">
       <c r="B441" t="n">
         <v>3427</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" hidden="1" ht="14.4" customHeight="1">
+    <row r="442" hidden="1" ht="14.45" customHeight="1">
       <c r="B442" t="n">
         <v>3428</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" hidden="1" ht="14.4" customHeight="1">
+    <row r="443" hidden="1" ht="14.45" customHeight="1">
       <c r="B443" t="n">
         <v>3429</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" hidden="1" ht="14.4" customHeight="1">
+    <row r="444" hidden="1" ht="14.45" customHeight="1">
       <c r="B444" t="n">
         <v>3430</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" hidden="1" ht="14.4" customHeight="1">
+    <row r="445" hidden="1" ht="14.45" customHeight="1">
       <c r="B445" t="n">
         <v>3431</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" hidden="1" ht="14.4" customHeight="1">
+    <row r="446" hidden="1" ht="14.45" customHeight="1">
       <c r="B446" t="n">
         <v>3432</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" hidden="1" ht="14.4" customHeight="1">
+    <row r="447" hidden="1" ht="14.45" customHeight="1">
       <c r="B447" t="n">
         <v>3433</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" hidden="1" ht="14.4" customHeight="1">
+    <row r="448" hidden="1" ht="14.45" customHeight="1">
       <c r="B448" t="n">
         <v>3434</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" hidden="1" ht="14.4" customHeight="1">
+    <row r="449" hidden="1" ht="14.45" customHeight="1">
       <c r="B449" t="n">
         <v>3435</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" hidden="1" ht="14.4" customHeight="1">
+    <row r="450" hidden="1" ht="14.45" customHeight="1">
       <c r="B450" t="n">
         <v>3436</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" hidden="1" ht="14.4" customHeight="1">
+    <row r="451" hidden="1" ht="14.45" customHeight="1">
       <c r="B451" t="n">
         <v>3437</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" hidden="1" ht="14.4" customHeight="1">
+    <row r="452" hidden="1" ht="14.45" customHeight="1">
       <c r="B452" t="n">
         <v>3438</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" hidden="1" ht="14.4" customHeight="1">
+    <row r="453" hidden="1" ht="14.45" customHeight="1">
       <c r="B453" t="n">
         <v>3439</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" hidden="1" ht="14.4" customHeight="1">
+    <row r="454" hidden="1" ht="14.45" customHeight="1">
       <c r="B454" t="n">
         <v>3440</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" hidden="1" ht="14.4" customHeight="1">
+    <row r="455" hidden="1" ht="14.45" customHeight="1">
       <c r="B455" t="n">
         <v>3441</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" hidden="1" ht="14.4" customHeight="1">
+    <row r="456" hidden="1" ht="14.45" customHeight="1">
       <c r="B456" t="n">
         <v>3442</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" hidden="1" ht="14.4" customHeight="1">
+    <row r="457" hidden="1" ht="14.45" customHeight="1">
       <c r="B457" t="n">
         <v>3443</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" hidden="1" ht="14.4" customHeight="1">
+    <row r="458" hidden="1" ht="14.45" customHeight="1">
       <c r="B458" t="n">
         <v>3444</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" hidden="1" ht="14.4" customHeight="1">
+    <row r="459" hidden="1" ht="14.45" customHeight="1">
       <c r="B459" t="n">
         <v>3445</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" hidden="1" ht="14.4" customHeight="1">
+    <row r="460" hidden="1" ht="14.45" customHeight="1">
       <c r="B460" t="n">
         <v>3446</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" hidden="1" ht="14.4" customHeight="1">
+    <row r="461" hidden="1" ht="14.45" customHeight="1">
       <c r="B461" t="n">
         <v>3447</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" hidden="1" ht="14.4" customHeight="1">
+    <row r="462" hidden="1" ht="14.45" customHeight="1">
       <c r="B462" t="n">
         <v>3448</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" hidden="1" ht="14.4" customHeight="1">
+    <row r="463" hidden="1" ht="14.45" customHeight="1">
       <c r="B463" t="n">
         <v>3449</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" hidden="1" ht="14.4" customHeight="1">
+    <row r="464" hidden="1" ht="14.45" customHeight="1">
       <c r="B464" t="n">
         <v>3450</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" hidden="1" ht="14.4" customHeight="1">
+    <row r="465" hidden="1" ht="14.45" customHeight="1">
       <c r="B465" t="n">
         <v>3451</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" hidden="1" ht="14.4" customHeight="1">
+    <row r="466" hidden="1" ht="14.45" customHeight="1">
       <c r="B466" t="n">
         <v>3452</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" hidden="1" ht="14.4" customHeight="1">
+    <row r="467" hidden="1" ht="14.45" customHeight="1">
       <c r="B467" t="n">
         <v>3453</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" hidden="1" ht="14.4" customHeight="1">
+    <row r="468" hidden="1" ht="14.45" customHeight="1">
       <c r="B468" t="n">
         <v>3454</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" hidden="1" ht="14.4" customHeight="1">
+    <row r="469" hidden="1" ht="14.45" customHeight="1">
       <c r="B469" t="n">
         <v>3455</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" hidden="1" ht="14.4" customHeight="1">
+    <row r="470" hidden="1" ht="14.45" customHeight="1">
       <c r="B470" t="n">
         <v>3456</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" hidden="1" ht="14.4" customHeight="1">
+    <row r="471" hidden="1" ht="14.45" customHeight="1">
       <c r="B471" t="n">
         <v>3457</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" hidden="1" ht="14.4" customHeight="1">
+    <row r="472" hidden="1" ht="14.45" customHeight="1">
       <c r="B472" t="n">
         <v>3458</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" hidden="1" ht="14.4" customHeight="1">
+    <row r="473" hidden="1" ht="14.45" customHeight="1">
       <c r="B473" t="n">
         <v>3459</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" hidden="1" ht="14.4" customHeight="1">
+    <row r="474" hidden="1" ht="14.45" customHeight="1">
       <c r="B474" t="n">
         <v>3460</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" hidden="1" ht="14.4" customHeight="1">
+    <row r="475" hidden="1" ht="14.45" customHeight="1">
       <c r="B475" t="n">
         <v>3461</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" hidden="1" ht="14.4" customHeight="1">
+    <row r="476" hidden="1" ht="14.45" customHeight="1">
       <c r="B476" t="n">
         <v>3462</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" hidden="1" ht="14.4" customHeight="1">
+    <row r="477" hidden="1" ht="14.45" customHeight="1">
       <c r="B477" t="n">
         <v>3463</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" hidden="1" ht="14.4" customHeight="1">
+    <row r="478" hidden="1" ht="14.45" customHeight="1">
       <c r="B478" t="n">
         <v>3464</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" hidden="1" ht="14.4" customHeight="1">
+    <row r="479" hidden="1" ht="14.45" customHeight="1">
       <c r="B479" t="n">
         <v>3465</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" hidden="1" ht="14.4" customHeight="1">
+    <row r="480" hidden="1" ht="14.45" customHeight="1">
       <c r="B480" t="n">
         <v>3466</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" hidden="1" ht="14.4" customHeight="1">
+    <row r="481" hidden="1" ht="14.45" customHeight="1">
       <c r="B481" t="n">
         <v>3467</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" hidden="1" ht="14.4" customHeight="1">
+    <row r="482" hidden="1" ht="14.45" customHeight="1">
       <c r="B482" t="n">
         <v>3468</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" hidden="1" ht="14.4" customHeight="1">
+    <row r="483" hidden="1" ht="14.45" customHeight="1">
       <c r="B483" t="n">
         <v>3469</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" hidden="1" ht="14.4" customHeight="1">
+    <row r="484" hidden="1" ht="14.45" customHeight="1">
       <c r="B484" t="n">
         <v>3470</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" hidden="1" ht="14.4" customHeight="1">
+    <row r="485" hidden="1" ht="14.45" customHeight="1">
       <c r="B485" t="n">
         <v>3471</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" hidden="1" ht="14.4" customHeight="1">
+    <row r="486" hidden="1" ht="14.45" customHeight="1">
       <c r="B486" t="n">
         <v>3472</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" hidden="1" ht="14.4" customHeight="1">
+    <row r="487" hidden="1" ht="14.45" customHeight="1">
       <c r="B487" t="n">
         <v>3473</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" hidden="1" ht="14.4" customHeight="1">
+    <row r="488" hidden="1" ht="14.45" customHeight="1">
       <c r="B488" t="n">
         <v>3474</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" hidden="1" ht="14.4" customHeight="1">
+    <row r="489" hidden="1" ht="14.45" customHeight="1">
       <c r="B489" t="n">
         <v>3475</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" hidden="1" ht="14.4" customHeight="1">
+    <row r="490" hidden="1" ht="14.45" customHeight="1">
       <c r="B490" t="n">
         <v>3476</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" hidden="1" ht="14.4" customHeight="1">
+    <row r="491" hidden="1" ht="14.45" customHeight="1">
       <c r="B491" t="n">
         <v>3477</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" hidden="1" ht="14.4" customHeight="1">
+    <row r="492" hidden="1" ht="14.45" customHeight="1">
       <c r="B492" t="n">
         <v>3478</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" hidden="1" ht="14.4" customHeight="1">
+    <row r="493" hidden="1" ht="14.45" customHeight="1">
       <c r="B493" t="n">
         <v>3479</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" hidden="1" ht="14.4" customHeight="1">
+    <row r="494" hidden="1" ht="14.45" customHeight="1">
       <c r="B494" t="n">
         <v>3480</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" hidden="1" ht="14.4" customHeight="1">
+    <row r="495" hidden="1" ht="14.45" customHeight="1">
       <c r="B495" t="n">
         <v>3481</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" hidden="1" ht="14.4" customHeight="1">
+    <row r="496" hidden="1" ht="14.45" customHeight="1">
       <c r="B496" t="n">
         <v>3482</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" hidden="1" ht="14.4" customHeight="1">
+    <row r="497" hidden="1" ht="14.45" customHeight="1">
       <c r="B497" t="n">
         <v>3483</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" hidden="1" ht="14.4" customHeight="1">
+    <row r="498" hidden="1" ht="14.45" customHeight="1">
       <c r="B498" t="n">
         <v>3484</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" hidden="1" ht="14.4" customHeight="1">
+    <row r="499" hidden="1" ht="14.45" customHeight="1">
       <c r="B499" t="n">
         <v>3485</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" hidden="1" ht="14.4" customHeight="1">
+    <row r="500" hidden="1" ht="14.45" customHeight="1">
       <c r="B500" t="n">
         <v>3486</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" hidden="1" ht="14.4" customHeight="1">
+    <row r="501" hidden="1" ht="14.45" customHeight="1">
       <c r="B501" t="n">
         <v>3487</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" hidden="1" ht="14.4" customHeight="1">
+    <row r="502" hidden="1" ht="14.45" customHeight="1">
       <c r="B502" t="n">
         <v>3488</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" hidden="1" ht="14.4" customHeight="1">
+    <row r="503" hidden="1" ht="14.45" customHeight="1">
       <c r="B503" t="n">
         <v>3489</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" hidden="1" ht="14.4" customHeight="1">
+    <row r="504" hidden="1" ht="14.45" customHeight="1">
       <c r="B504" t="n">
         <v>3490</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" hidden="1" ht="14.4" customHeight="1">
+    <row r="505" hidden="1" ht="14.45" customHeight="1">
       <c r="B505" t="n">
         <v>3491</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" hidden="1" ht="14.4" customHeight="1">
+    <row r="506" hidden="1" ht="14.45" customHeight="1">
       <c r="B506" t="n">
         <v>3492</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" hidden="1" ht="14.4" customHeight="1">
+    <row r="507" hidden="1" ht="14.45" customHeight="1">
       <c r="B507" t="n">
         <v>3493</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" hidden="1" ht="14.4" customHeight="1">
+    <row r="508" hidden="1" ht="14.45" customHeight="1">
       <c r="B508" t="n">
         <v>3494</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" hidden="1" ht="14.4" customHeight="1">
+    <row r="509" hidden="1" ht="14.45" customHeight="1">
       <c r="B509" t="n">
         <v>3495</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" hidden="1" ht="14.4" customHeight="1">
+    <row r="510" hidden="1" ht="14.45" customHeight="1">
       <c r="B510" t="n">
         <v>3496</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" hidden="1" ht="14.4" customHeight="1">
+    <row r="511" hidden="1" ht="14.45" customHeight="1">
       <c r="B511" t="n">
         <v>3497</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" hidden="1" ht="14.4" customHeight="1">
+    <row r="512" hidden="1" ht="14.45" customHeight="1">
       <c r="B512" t="n">
         <v>3498</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" hidden="1" ht="14.4" customHeight="1">
+    <row r="513" hidden="1" ht="14.45" customHeight="1">
       <c r="B513" t="n">
         <v>3499</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" hidden="1" ht="14.4" customHeight="1">
+    <row r="514" hidden="1" ht="14.45" customHeight="1">
       <c r="B514" t="n">
         <v>3500</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" hidden="1" ht="14.4" customHeight="1">
+    <row r="515" hidden="1" ht="14.45" customHeight="1">
       <c r="B515" t="n">
         <v>3501</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" hidden="1" ht="14.4" customHeight="1">
+    <row r="516" hidden="1" ht="14.45" customHeight="1">
       <c r="B516" t="n">
         <v>3502</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" hidden="1" ht="14.4" customHeight="1">
+    <row r="517" hidden="1" ht="14.45" customHeight="1">
       <c r="B517" t="n">
         <v>3503</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" hidden="1" ht="14.4" customHeight="1">
+    <row r="518" hidden="1" ht="14.45" customHeight="1">
       <c r="B518" t="n">
         <v>3504</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" hidden="1" ht="14.4" customHeight="1">
+    <row r="519" hidden="1" ht="14.45" customHeight="1">
       <c r="B519" t="n">
         <v>3505</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" hidden="1" ht="14.4" customHeight="1">
+    <row r="520" hidden="1" ht="14.45" customHeight="1">
       <c r="B520" t="n">
         <v>3506</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" hidden="1" ht="14.4" customHeight="1">
+    <row r="521" hidden="1" ht="14.45" customHeight="1">
       <c r="B521" t="n">
         <v>3507</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" hidden="1" ht="14.4" customHeight="1">
+    <row r="522" hidden="1" ht="14.45" customHeight="1">
       <c r="B522" t="n">
         <v>3508</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" hidden="1" ht="14.4" customHeight="1">
+    <row r="523" hidden="1" ht="14.45" customHeight="1">
       <c r="B523" t="n">
         <v>3509</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" hidden="1" ht="14.4" customHeight="1">
+    <row r="524" hidden="1" ht="14.45" customHeight="1">
       <c r="B524" t="n">
         <v>3510</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" hidden="1" ht="14.4" customHeight="1">
+    <row r="525" hidden="1" ht="14.45" customHeight="1">
       <c r="B525" t="n">
         <v>3511</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" hidden="1" ht="14.4" customHeight="1">
+    <row r="526" hidden="1" ht="14.45" customHeight="1">
       <c r="B526" t="n">
         <v>3512</v>
       </c>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,14 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30720" yWindow="-10815" windowWidth="24795" windowHeight="20100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Info'!$I$535</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -436,7 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -678,6 +676,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -689,13 +688,13 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="171" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -783,16 +782,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN534" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN534">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN533" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="B1:AN533">
     <filterColumn colId="1" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="Affinity Petcare"/>
+        <filter val="Unilever"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState ref="B2:AN534">
-    <sortCondition ref="I1:I534"/>
+  <sortState ref="B2:AN533">
+    <sortCondition ref="I1:I533"/>
   </sortState>
   <tableColumns count="39">
     <tableColumn id="1" name="Client ID"/>
@@ -844,9 +843,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -884,7 +883,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -990,7 +989,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1132,7 +1131,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1144,48 +1143,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R534"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:R533"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.7109375" customWidth="1" min="1" max="1"/>
-    <col width="10.85546875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
-    <col width="33.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="56.42578125" customWidth="1" min="4" max="4"/>
+    <col width="15.6640625" customWidth="1" min="1" max="1"/>
+    <col width="10.88671875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="33.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="56.44140625" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25.85546875" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" customWidth="1" min="7" max="7"/>
-    <col width="11.7109375" customWidth="1" min="8" max="8"/>
-    <col width="19.140625" customWidth="1" min="9" max="9"/>
+    <col width="25.88671875" customWidth="1" min="6" max="6"/>
+    <col width="15.109375" customWidth="1" min="7" max="7"/>
+    <col width="11.6640625" customWidth="1" min="8" max="8"/>
+    <col width="19.109375" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.140625" customWidth="1" min="11" max="11"/>
-    <col width="17.5703125" customWidth="1" min="12" max="12"/>
-    <col width="35.140625" customWidth="1" min="13" max="13"/>
-    <col width="25.28515625" customWidth="1" min="14" max="14"/>
-    <col width="33.42578125" customWidth="1" min="15" max="15"/>
+    <col width="18.109375" customWidth="1" min="11" max="11"/>
+    <col width="17.5546875" customWidth="1" min="12" max="12"/>
+    <col width="35.109375" customWidth="1" min="13" max="13"/>
+    <col width="25.33203125" customWidth="1" min="14" max="14"/>
+    <col width="33.44140625" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
+    <col width="35.88671875" customWidth="1" style="4" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.7109375" customWidth="1" min="20" max="20"/>
-    <col width="12.85546875" customWidth="1" min="21" max="23"/>
-    <col width="16.28515625" customWidth="1" min="24" max="24"/>
-    <col width="20.140625" customWidth="1" min="25" max="25"/>
-    <col width="20.5703125" customWidth="1" min="26" max="26"/>
-    <col width="14.85546875" customWidth="1" min="27" max="27"/>
+    <col width="27.6640625" customWidth="1" style="4" min="19" max="19"/>
+    <col width="14.6640625" customWidth="1" min="20" max="20"/>
+    <col width="12.88671875" customWidth="1" min="21" max="23"/>
+    <col width="16.33203125" customWidth="1" min="24" max="24"/>
+    <col width="20.109375" customWidth="1" min="25" max="25"/>
+    <col width="20.5546875" customWidth="1" min="26" max="26"/>
+    <col width="14.88671875" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5703125" customWidth="1" min="29" max="29"/>
-    <col width="16.140625" customWidth="1" min="30" max="30"/>
-    <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
-    <col width="22.85546875" customWidth="1" min="32" max="32"/>
-    <col width="17.28515625" customWidth="1" min="33" max="33"/>
-    <col width="16.28515625" customWidth="1" style="139" min="34" max="34"/>
-    <col width="22.85546875" customWidth="1" min="35" max="36"/>
-    <col width="31.85546875" customWidth="1" min="37" max="37"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.28515625" customWidth="1" min="41" max="41"/>
+    <col width="20.5546875" customWidth="1" min="29" max="29"/>
+    <col width="16.109375" customWidth="1" min="30" max="30"/>
+    <col width="16.109375" customWidth="1" style="139" min="31" max="31"/>
+    <col width="22.88671875" customWidth="1" min="32" max="32"/>
+    <col width="17.33203125" customWidth="1" min="33" max="33"/>
+    <col width="16.33203125" customWidth="1" style="140" min="34" max="34"/>
+    <col width="22.88671875" customWidth="1" min="35" max="36"/>
+    <col width="31.88671875" customWidth="1" min="37" max="37"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="33.33203125" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.9" customHeight="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1277,7 +1276,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="62">
+    <row r="2" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1361,7 +1360,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" hidden="1" ht="14.45" customHeight="1">
+    <row r="3" hidden="1" ht="14.4" customHeight="1">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1515,7 +1514,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" hidden="1" ht="28.9" customHeight="1">
+    <row r="5" hidden="1" ht="28.8" customHeight="1">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1574,7 +1573,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6" hidden="1" ht="14.45" customHeight="1">
+    <row r="6" hidden="1" ht="14.4" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1634,7 +1633,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7" hidden="1" ht="14.45" customHeight="1">
+    <row r="7" hidden="1" ht="14.4" customHeight="1">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" hidden="1" ht="14.45" customHeight="1">
+    <row r="8" hidden="1" ht="14.4" customHeight="1">
       <c r="B8" t="n">
         <v>3008</v>
       </c>
@@ -1958,11 +1957,11 @@
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R10" s="140" t="n">
+      <c r="R10" s="141" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="11" hidden="1" ht="43.15" customHeight="1">
+    <row r="11" hidden="1" ht="43.2" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2043,7 +2042,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="12" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="27">
+    <row r="12" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="27">
       <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2107,7 +2106,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="13" hidden="1" ht="14.45" customHeight="1">
+    <row r="13" hidden="1" ht="14.4" customHeight="1">
       <c r="B13" t="n">
         <v>3014</v>
       </c>
@@ -2411,7 +2410,7 @@
       <c r="Q16" s="88" t="n"/>
       <c r="R16" s="23" t="n"/>
     </row>
-    <row r="17" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="17" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2456,7 +2455,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="18" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="18" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="B18" t="n">
         <v>3018</v>
       </c>
@@ -2498,7 +2497,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="19" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="B19" t="n">
         <v>3019</v>
       </c>
@@ -2540,7 +2539,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" ht="43.15" customHeight="1">
+    <row r="20" hidden="1" ht="43.2" customHeight="1">
       <c r="B20" t="n">
         <v>3020</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="23" hidden="1" ht="28.9" customHeight="1">
+    <row r="23" hidden="1" ht="28.8" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2788,7 +2787,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="24" hidden="1" ht="28.9" customHeight="1">
+    <row r="24" hidden="1" ht="28.8" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2854,7 +2853,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" ht="43.15" customHeight="1">
+    <row r="25" hidden="1" ht="43.8" customHeight="1" thickBot="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2922,7 +2921,7 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" hidden="1" ht="14.45" customHeight="1">
+    <row r="26" hidden="1" ht="14.4" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -2998,7 +2997,7 @@
       </c>
       <c r="Q26" s="4" t="n"/>
     </row>
-    <row r="27" hidden="1" ht="14.45" customHeight="1">
+    <row r="27" hidden="1" ht="14.4" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3069,7 +3068,7 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" ht="28.9" customHeight="1">
+    <row r="28" hidden="1" ht="28.8" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3146,7 +3145,7 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" ht="43.15" customHeight="1">
+    <row r="29" hidden="1" ht="43.2" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3194,7 +3193,7 @@
         </is>
       </c>
     </row>
-    <row r="30" hidden="1" ht="28.9" customHeight="1">
+    <row r="30" hidden="1" ht="28.8" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3256,7 +3255,7 @@
         </is>
       </c>
     </row>
-    <row r="31" hidden="1" ht="43.15" customHeight="1">
+    <row r="31" hidden="1" ht="43.2" customHeight="1">
       <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3394,7 +3393,7 @@
       <c r="O32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
     </row>
-    <row r="33" hidden="1" ht="43.15" customHeight="1">
+    <row r="33" hidden="1" ht="43.2" customHeight="1">
       <c r="B33" t="n">
         <v>3035</v>
       </c>
@@ -3528,7 +3527,7 @@
       <c r="O34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
     </row>
-    <row r="35" hidden="1" ht="14.45" customHeight="1">
+    <row r="35" hidden="1" ht="14.4" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Mike/Jeff</t>
@@ -3595,7 +3594,7 @@
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" hidden="1" ht="14.45" customHeight="1">
+    <row r="36" hidden="1" ht="14.4" customHeight="1">
       <c r="B36" t="n">
         <v>3031</v>
       </c>
@@ -3662,7 +3661,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" hidden="1" ht="14.45" customHeight="1">
+    <row r="37" hidden="1" ht="14.4" customHeight="1">
       <c r="B37" t="n">
         <v>3056</v>
       </c>
@@ -3757,7 +3756,7 @@
         </is>
       </c>
     </row>
-    <row r="39" hidden="1" ht="28.9" customHeight="1">
+    <row r="39" hidden="1" ht="28.8" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3829,7 +3828,7 @@
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
     </row>
-    <row r="40" hidden="1" ht="43.15" customHeight="1">
+    <row r="40" hidden="1" ht="43.2" customHeight="1">
       <c r="B40" t="n">
         <v>3035</v>
       </c>
@@ -3873,7 +3872,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" hidden="1" ht="28.9" customHeight="1">
+    <row r="41" hidden="1" ht="28.8" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3946,7 +3945,7 @@
       </c>
       <c r="Q41" s="4" t="n"/>
     </row>
-    <row r="42" hidden="1" ht="43.15" customHeight="1">
+    <row r="42" hidden="1" ht="43.2" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
@@ -3985,7 +3984,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" hidden="1" ht="14.45" customHeight="1">
+    <row r="43" hidden="1" ht="14.4" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
@@ -4018,7 +4017,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" hidden="1" ht="41.45" customHeight="1">
+    <row r="44" hidden="1" ht="41.4" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4078,7 +4077,7 @@
       <c r="O44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45" hidden="1" ht="28.9" customHeight="1">
+    <row r="45" hidden="1" ht="28.8" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4141,7 +4140,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" hidden="1" ht="14.45" customHeight="1">
+    <row r="46" ht="14.4" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4198,7 +4197,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" hidden="1" ht="43.15" customHeight="1">
+    <row r="47" hidden="1" ht="43.2" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>US</t>
@@ -4237,7 +4236,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48" hidden="1" ht="43.15" customHeight="1">
+    <row r="48" hidden="1" ht="43.2" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>US</t>
@@ -4281,7 +4280,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" hidden="1" ht="14.45" customHeight="1">
+    <row r="49" hidden="1" ht="14.4" customHeight="1">
       <c r="B49" s="130" t="n">
         <v>3041</v>
       </c>
@@ -4343,7 +4342,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" hidden="1" ht="43.15" customHeight="1">
+    <row r="50" hidden="1" ht="43.2" customHeight="1">
       <c r="B50" t="n">
         <v>3063</v>
       </c>
@@ -4377,7 +4376,7 @@
       <c r="O50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
     </row>
-    <row r="51" hidden="1" ht="14.45" customHeight="1">
+    <row r="51" hidden="1" ht="14.4" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4404,7 +4403,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="14.45" customHeight="1">
+    <row r="52" hidden="1" ht="14.4" customHeight="1">
       <c r="B52" t="n">
         <v>3044</v>
       </c>
@@ -4456,7 +4455,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" hidden="1" ht="14.45" customHeight="1">
+    <row r="53" hidden="1" ht="14.4" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4483,7 +4482,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="14.45" customHeight="1">
+    <row r="54" hidden="1" ht="14.4" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4515,7 +4514,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" hidden="1" ht="14.45" customHeight="1">
+    <row r="55" hidden="1" ht="14.4" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4547,7 +4546,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" hidden="1" ht="14.45" customHeight="1">
+    <row r="56" hidden="1" ht="14.4" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4579,7 +4578,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="14.45" customHeight="1">
+    <row r="57" hidden="1" ht="14.4" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4611,7 +4610,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="14.45" customHeight="1">
+    <row r="58" hidden="1" ht="14.4" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4643,7 +4642,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" hidden="1" ht="14.45" customHeight="1">
+    <row r="59" hidden="1" ht="14.4" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4675,7 +4674,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="14.45" customHeight="1">
+    <row r="60" hidden="1" ht="14.4" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -4688,7 +4687,7 @@
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="23" t="n"/>
     </row>
-    <row r="61" hidden="1" ht="14.45" customHeight="1">
+    <row r="61" hidden="1" ht="14.4" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4720,7 +4719,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62" hidden="1" ht="14.45" customHeight="1">
+    <row r="62" hidden="1" ht="14.4" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4752,7 +4751,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" hidden="1" ht="14.45" customHeight="1">
+    <row r="63" hidden="1" ht="14.4" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4784,7 +4783,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" hidden="1" ht="14.45" customHeight="1">
+    <row r="64" hidden="1" ht="14.4" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4816,7 +4815,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" hidden="1" ht="14.45" customHeight="1">
+    <row r="65" hidden="1" ht="14.4" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4829,7 +4828,7 @@
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="23" t="n"/>
     </row>
-    <row r="66" hidden="1" ht="14.45" customHeight="1">
+    <row r="66" hidden="1" ht="14.4" customHeight="1">
       <c r="B66" s="131" t="inlineStr">
         <is>
           <t>----</t>
@@ -4853,7 +4852,7 @@
       <c r="O66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
     </row>
-    <row r="67" hidden="1" ht="14.45" customHeight="1">
+    <row r="67" hidden="1" ht="14.4" customHeight="1">
       <c r="B67" t="n">
         <v>3003</v>
       </c>
@@ -4861,7 +4860,7 @@
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="23" t="n"/>
     </row>
-    <row r="68" hidden="1" ht="14.45" customHeight="1">
+    <row r="68" hidden="1" ht="14.4" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>US</t>
@@ -4874,7 +4873,7 @@
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="23" t="n"/>
     </row>
-    <row r="69" hidden="1" ht="14.45" customHeight="1">
+    <row r="69" hidden="1" ht="14.4" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>US</t>
@@ -4904,7 +4903,7 @@
       <c r="Q69" s="108" t="n"/>
       <c r="R69" s="66" t="n"/>
     </row>
-    <row r="70" hidden="1" ht="43.15" customHeight="1">
+    <row r="70" hidden="1" ht="43.2" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4943,7 +4942,7 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" hidden="1" ht="14.45" customHeight="1">
+    <row r="71" hidden="1" ht="14.4" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>US</t>
@@ -4969,7 +4968,7 @@
       <c r="Q71" s="108" t="n"/>
       <c r="R71" s="66" t="n"/>
     </row>
-    <row r="72" hidden="1" ht="14.45" customHeight="1">
+    <row r="72" hidden="1" ht="14.4" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5001,7 +5000,7 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" hidden="1" ht="14.45" customHeight="1">
+    <row r="73" hidden="1" ht="14.4" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>US</t>
@@ -5027,7 +5026,7 @@
       <c r="Q73" s="108" t="n"/>
       <c r="R73" s="66" t="n"/>
     </row>
-    <row r="74" hidden="1" ht="14.45" customHeight="1">
+    <row r="74" hidden="1" ht="14.4" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5059,7 +5058,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" hidden="1" ht="14.45" customHeight="1">
+    <row r="75" hidden="1" ht="14.4" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5096,7 +5095,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="43.15" customHeight="1">
+    <row r="76" hidden="1" ht="43.2" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>US</t>
@@ -5110,7 +5109,7 @@
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="23" t="n"/>
     </row>
-    <row r="77" hidden="1" ht="14.45" customHeight="1">
+    <row r="77" hidden="1" ht="14.4" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5134,14 +5133,16 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" ht="14.45" customHeight="1">
+    <row r="78" hidden="1" ht="14.4" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>3064</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3064 &amp; 3070</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -5205,7 +5206,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" hidden="1" ht="43.15" customHeight="1">
+    <row r="80" hidden="1" ht="43.2" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5244,7 +5245,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" hidden="1" ht="28.9" customHeight="1">
+    <row r="81" hidden="1" ht="28.8" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5316,7 +5317,7 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" hidden="1" ht="14.45" customHeight="1">
+    <row r="82" hidden="1" ht="14.4" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>US</t>
@@ -5338,7 +5339,7 @@
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" hidden="1" ht="14.45" customHeight="1">
+    <row r="83" hidden="1" ht="14.4" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>US</t>
@@ -5355,3117 +5356,3122 @@
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" hidden="1" ht="14.45" customHeight="1">
+    <row r="84" hidden="1" ht="14.4" customHeight="1">
       <c r="B84" t="n">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" hidden="1" ht="14.45" customHeight="1">
+    <row r="85" hidden="1" ht="14.4" customHeight="1">
       <c r="B85" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" hidden="1" ht="14.45" customHeight="1">
+    <row r="86" hidden="1" ht="14.4" customHeight="1">
       <c r="B86" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" hidden="1" ht="14.45" customHeight="1">
+    <row r="87" hidden="1" ht="14.4" customHeight="1">
       <c r="B87" t="n">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" hidden="1" ht="14.45" customHeight="1">
+    <row r="88" hidden="1" ht="14.4" customHeight="1">
       <c r="B88" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" hidden="1" ht="14.45" customHeight="1">
+    <row r="89" hidden="1" ht="14.4" customHeight="1">
       <c r="B89" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" hidden="1" ht="14.45" customHeight="1">
+    <row r="90" hidden="1" ht="14.4" customHeight="1">
       <c r="B90" t="n">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" hidden="1" ht="14.45" customHeight="1">
+    <row r="91" hidden="1" ht="14.4" customHeight="1">
       <c r="B91" t="n">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" hidden="1" ht="14.45" customHeight="1">
+    <row r="92" hidden="1" ht="14.4" customHeight="1">
       <c r="B92" t="n">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" hidden="1" ht="14.45" customHeight="1">
+    <row r="93" hidden="1" ht="14.4" customHeight="1">
       <c r="B93" t="n">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" hidden="1" ht="14.45" customHeight="1">
+    <row r="94" hidden="1" ht="14.4" customHeight="1">
       <c r="B94" t="n">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" hidden="1" ht="14.45" customHeight="1">
+    <row r="95" hidden="1" ht="14.4" customHeight="1">
       <c r="B95" t="n">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" hidden="1" ht="14.45" customHeight="1">
+    <row r="96" hidden="1" ht="14.4" customHeight="1">
       <c r="B96" t="n">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" hidden="1" ht="14.45" customHeight="1">
+    <row r="97" hidden="1" ht="14.4" customHeight="1">
       <c r="B97" t="n">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" hidden="1" ht="14.45" customHeight="1">
+    <row r="98" hidden="1" ht="14.4" customHeight="1">
       <c r="B98" t="n">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" hidden="1" ht="14.45" customHeight="1">
+    <row r="99" hidden="1" ht="14.4" customHeight="1">
       <c r="B99" t="n">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" hidden="1" ht="14.45" customHeight="1">
+    <row r="100" hidden="1" ht="14.4" customHeight="1">
       <c r="B100" t="n">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" hidden="1" ht="14.45" customHeight="1">
+    <row r="101" hidden="1" ht="14.4" customHeight="1">
       <c r="B101" t="n">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" hidden="1" ht="14.45" customHeight="1">
+    <row r="102" hidden="1" ht="14.4" customHeight="1">
       <c r="B102" t="n">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" hidden="1" ht="14.45" customHeight="1">
+    <row r="103" hidden="1" ht="14.4" customHeight="1">
       <c r="B103" t="n">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" hidden="1" ht="14.45" customHeight="1">
+    <row r="104" hidden="1" ht="14.4" customHeight="1">
       <c r="B104" t="n">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" hidden="1" ht="14.45" customHeight="1">
+    <row r="105" hidden="1" ht="14.4" customHeight="1">
       <c r="B105" t="n">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" hidden="1" ht="14.45" customHeight="1">
+    <row r="106" hidden="1" ht="14.4" customHeight="1">
       <c r="B106" t="n">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" hidden="1" ht="14.45" customHeight="1">
+    <row r="107" hidden="1" ht="14.4" customHeight="1">
       <c r="B107" t="n">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" hidden="1" ht="14.45" customHeight="1">
+    <row r="108" hidden="1" ht="14.4" customHeight="1">
       <c r="B108" t="n">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" hidden="1" ht="14.45" customHeight="1">
+    <row r="109" hidden="1" ht="14.4" customHeight="1">
       <c r="B109" t="n">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" hidden="1" ht="14.45" customHeight="1">
+    <row r="110" hidden="1" ht="14.4" customHeight="1">
       <c r="B110" t="n">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" hidden="1" ht="14.45" customHeight="1">
+    <row r="111" hidden="1" ht="14.4" customHeight="1">
       <c r="B111" t="n">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" hidden="1" ht="14.45" customHeight="1">
+    <row r="112" hidden="1" ht="14.4" customHeight="1">
       <c r="B112" t="n">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" hidden="1" ht="14.45" customHeight="1">
+    <row r="113" hidden="1" ht="14.4" customHeight="1">
       <c r="B113" t="n">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" hidden="1" ht="14.45" customHeight="1">
+    <row r="114" hidden="1" ht="14.4" customHeight="1">
       <c r="B114" t="n">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" hidden="1" ht="14.45" customHeight="1">
+    <row r="115" hidden="1" ht="14.4" customHeight="1">
       <c r="B115" t="n">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" hidden="1" ht="14.45" customHeight="1">
+    <row r="116" hidden="1" ht="14.4" customHeight="1">
       <c r="B116" t="n">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" hidden="1" ht="14.45" customHeight="1">
+    <row r="117" hidden="1" ht="14.4" customHeight="1">
       <c r="B117" t="n">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" hidden="1" ht="14.45" customHeight="1">
+    <row r="118" hidden="1" ht="14.4" customHeight="1">
       <c r="B118" t="n">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" hidden="1" ht="14.45" customHeight="1">
+    <row r="119" hidden="1" ht="14.4" customHeight="1">
       <c r="B119" t="n">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" hidden="1" ht="14.45" customHeight="1">
+    <row r="120" hidden="1" ht="14.4" customHeight="1">
       <c r="B120" t="n">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" hidden="1" ht="14.45" customHeight="1">
+    <row r="121" hidden="1" ht="14.4" customHeight="1">
       <c r="B121" t="n">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" hidden="1" ht="14.45" customHeight="1">
+    <row r="122" hidden="1" ht="14.4" customHeight="1">
       <c r="B122" t="n">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" hidden="1" ht="14.45" customHeight="1">
+    <row r="123" hidden="1" ht="14.4" customHeight="1">
       <c r="B123" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" hidden="1" ht="14.45" customHeight="1">
+    <row r="124" hidden="1" ht="14.4" customHeight="1">
       <c r="B124" t="n">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" hidden="1" ht="14.45" customHeight="1">
+    <row r="125" hidden="1" ht="14.4" customHeight="1">
       <c r="B125" t="n">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" hidden="1" ht="14.45" customHeight="1">
+    <row r="126" hidden="1" ht="14.4" customHeight="1">
       <c r="B126" t="n">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" hidden="1" ht="14.45" customHeight="1">
+    <row r="127" hidden="1" ht="14.4" customHeight="1">
       <c r="B127" t="n">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" hidden="1" ht="14.45" customHeight="1">
+    <row r="128" hidden="1" ht="14.4" customHeight="1">
       <c r="B128" t="n">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" hidden="1" ht="14.45" customHeight="1">
+    <row r="129" hidden="1" ht="14.4" customHeight="1">
       <c r="B129" t="n">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" hidden="1" ht="14.45" customHeight="1">
+    <row r="130" hidden="1" ht="14.4" customHeight="1">
       <c r="B130" t="n">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" hidden="1" ht="14.45" customHeight="1">
+    <row r="131" hidden="1" ht="14.4" customHeight="1">
       <c r="B131" t="n">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" hidden="1" ht="14.45" customHeight="1">
+    <row r="132" hidden="1" ht="14.4" customHeight="1">
       <c r="B132" t="n">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" hidden="1" ht="14.45" customHeight="1">
+    <row r="133" hidden="1" ht="14.4" customHeight="1">
       <c r="B133" t="n">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" hidden="1" ht="14.45" customHeight="1">
+    <row r="134" hidden="1" ht="14.4" customHeight="1">
       <c r="B134" t="n">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" hidden="1" ht="14.45" customHeight="1">
+    <row r="135" hidden="1" ht="14.4" customHeight="1">
       <c r="B135" t="n">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" hidden="1" ht="14.45" customHeight="1">
+    <row r="136" hidden="1" ht="14.4" customHeight="1">
       <c r="B136" t="n">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" hidden="1" ht="14.45" customHeight="1">
+    <row r="137" hidden="1" ht="14.4" customHeight="1">
       <c r="B137" t="n">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" hidden="1" ht="14.45" customHeight="1">
+    <row r="138" hidden="1" ht="14.4" customHeight="1">
       <c r="B138" t="n">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" hidden="1" ht="14.45" customHeight="1">
+    <row r="139" hidden="1" ht="14.4" customHeight="1">
       <c r="B139" t="n">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" hidden="1" ht="14.45" customHeight="1">
+    <row r="140" hidden="1" ht="14.4" customHeight="1">
       <c r="B140" t="n">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" hidden="1" ht="14.45" customHeight="1">
+    <row r="141" hidden="1" ht="14.4" customHeight="1">
       <c r="B141" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" hidden="1" ht="14.45" customHeight="1">
+    <row r="142" hidden="1" ht="14.4" customHeight="1">
       <c r="B142" t="n">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" hidden="1" ht="14.45" customHeight="1">
+    <row r="143" hidden="1" ht="14.4" customHeight="1">
       <c r="B143" t="n">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" hidden="1" ht="14.45" customHeight="1">
+    <row r="144" hidden="1" ht="14.4" customHeight="1">
       <c r="B144" t="n">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" hidden="1" ht="14.45" customHeight="1">
+    <row r="145" hidden="1" ht="14.4" customHeight="1">
       <c r="B145" t="n">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" hidden="1" ht="14.45" customHeight="1">
+    <row r="146" hidden="1" ht="14.4" customHeight="1">
       <c r="B146" t="n">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" hidden="1" ht="14.45" customHeight="1">
+    <row r="147" hidden="1" ht="14.4" customHeight="1">
       <c r="B147" t="n">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" hidden="1" ht="14.45" customHeight="1">
+    <row r="148" hidden="1" ht="14.4" customHeight="1">
       <c r="B148" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" hidden="1" ht="14.45" customHeight="1">
+    <row r="149" hidden="1" ht="14.4" customHeight="1">
       <c r="B149" t="n">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" hidden="1" ht="14.45" customHeight="1">
+    <row r="150" hidden="1" ht="14.4" customHeight="1">
       <c r="B150" t="n">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" hidden="1" ht="14.45" customHeight="1">
+    <row r="151" hidden="1" ht="14.4" customHeight="1">
       <c r="B151" t="n">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" hidden="1" ht="14.45" customHeight="1">
+    <row r="152" hidden="1" ht="14.4" customHeight="1">
       <c r="B152" t="n">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" hidden="1" ht="14.45" customHeight="1">
+    <row r="153" hidden="1" ht="14.4" customHeight="1">
       <c r="B153" t="n">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" hidden="1" ht="14.45" customHeight="1">
+    <row r="154" hidden="1" ht="14.4" customHeight="1">
       <c r="B154" t="n">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" hidden="1" ht="14.45" customHeight="1">
+    <row r="155" hidden="1" ht="14.4" customHeight="1">
       <c r="B155" t="n">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" hidden="1" ht="14.45" customHeight="1">
+    <row r="156" hidden="1" ht="14.4" customHeight="1">
       <c r="B156" t="n">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" hidden="1" ht="14.45" customHeight="1">
+    <row r="157" hidden="1" ht="14.4" customHeight="1">
       <c r="B157" t="n">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" hidden="1" ht="14.45" customHeight="1">
+    <row r="158" hidden="1" ht="14.4" customHeight="1">
       <c r="B158" t="n">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" hidden="1" ht="14.45" customHeight="1">
+    <row r="159" hidden="1" ht="14.4" customHeight="1">
       <c r="B159" t="n">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" hidden="1" ht="14.45" customHeight="1">
+    <row r="160" hidden="1" ht="14.4" customHeight="1">
       <c r="B160" t="n">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" hidden="1" ht="14.45" customHeight="1">
+    <row r="161" hidden="1" ht="14.4" customHeight="1">
       <c r="B161" t="n">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" hidden="1" ht="14.45" customHeight="1">
+    <row r="162" hidden="1" ht="14.4" customHeight="1">
       <c r="B162" t="n">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" hidden="1" ht="14.45" customHeight="1">
+    <row r="163" hidden="1" ht="14.4" customHeight="1">
       <c r="B163" t="n">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" hidden="1" ht="14.45" customHeight="1">
+    <row r="164" hidden="1" ht="14.4" customHeight="1">
       <c r="B164" t="n">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" hidden="1" ht="14.45" customHeight="1">
+    <row r="165" hidden="1" ht="14.4" customHeight="1">
       <c r="B165" t="n">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" hidden="1" ht="14.45" customHeight="1">
+    <row r="166" hidden="1" ht="14.4" customHeight="1">
       <c r="B166" t="n">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" hidden="1" ht="14.45" customHeight="1">
+    <row r="167" hidden="1" ht="14.4" customHeight="1">
       <c r="B167" t="n">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" hidden="1" ht="14.45" customHeight="1">
+    <row r="168" hidden="1" ht="14.4" customHeight="1">
       <c r="B168" t="n">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" hidden="1" ht="14.45" customHeight="1">
+    <row r="169" hidden="1" ht="14.4" customHeight="1">
       <c r="B169" t="n">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" hidden="1" ht="14.45" customHeight="1">
+    <row r="170" hidden="1" ht="14.4" customHeight="1">
       <c r="B170" t="n">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" hidden="1" ht="14.45" customHeight="1">
+    <row r="171" hidden="1" ht="14.4" customHeight="1">
       <c r="B171" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" hidden="1" ht="14.45" customHeight="1">
+    <row r="172" hidden="1" ht="14.4" customHeight="1">
       <c r="B172" t="n">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" hidden="1" ht="14.45" customHeight="1">
+    <row r="173" hidden="1" ht="14.4" customHeight="1">
       <c r="B173" t="n">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" hidden="1" ht="14.45" customHeight="1">
+    <row r="174" hidden="1" ht="14.4" customHeight="1">
       <c r="B174" t="n">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" hidden="1" ht="14.45" customHeight="1">
+    <row r="175" hidden="1" ht="14.4" customHeight="1">
       <c r="B175" t="n">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" hidden="1" ht="14.45" customHeight="1">
+    <row r="176" hidden="1" ht="14.4" customHeight="1">
       <c r="B176" t="n">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" hidden="1" ht="14.45" customHeight="1">
+    <row r="177" hidden="1" ht="14.4" customHeight="1">
       <c r="B177" t="n">
-        <v>3163</v>
+        <v>3164</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" hidden="1" ht="14.45" customHeight="1">
+    <row r="178" hidden="1" ht="14.4" customHeight="1">
       <c r="B178" t="n">
-        <v>3164</v>
+        <v>3165</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" hidden="1" ht="14.45" customHeight="1">
+    <row r="179" hidden="1" ht="14.4" customHeight="1">
       <c r="B179" t="n">
-        <v>3165</v>
+        <v>3166</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" hidden="1" ht="14.45" customHeight="1">
+    <row r="180" hidden="1" ht="14.4" customHeight="1">
       <c r="B180" t="n">
-        <v>3166</v>
+        <v>3167</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" hidden="1" ht="14.45" customHeight="1">
+    <row r="181" hidden="1" ht="14.4" customHeight="1">
       <c r="B181" t="n">
-        <v>3167</v>
+        <v>3168</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" hidden="1" ht="14.45" customHeight="1">
+    <row r="182" hidden="1" ht="14.4" customHeight="1">
       <c r="B182" t="n">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" hidden="1" ht="14.45" customHeight="1">
+    <row r="183" hidden="1" ht="14.4" customHeight="1">
       <c r="B183" t="n">
-        <v>3169</v>
+        <v>3170</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" hidden="1" ht="14.45" customHeight="1">
+    <row r="184" hidden="1" ht="14.4" customHeight="1">
       <c r="B184" t="n">
-        <v>3170</v>
+        <v>3171</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" hidden="1" ht="14.45" customHeight="1">
+    <row r="185" hidden="1" ht="14.4" customHeight="1">
       <c r="B185" t="n">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" hidden="1" ht="14.45" customHeight="1">
+    <row r="186" hidden="1" ht="14.4" customHeight="1">
       <c r="B186" t="n">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" hidden="1" ht="14.45" customHeight="1">
+    <row r="187" hidden="1" ht="14.4" customHeight="1">
       <c r="B187" t="n">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" hidden="1" ht="14.45" customHeight="1">
+    <row r="188" hidden="1" ht="14.4" customHeight="1">
       <c r="B188" t="n">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" hidden="1" ht="14.45" customHeight="1">
+    <row r="189" hidden="1" ht="14.4" customHeight="1">
       <c r="B189" t="n">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" hidden="1" ht="14.45" customHeight="1">
+    <row r="190" hidden="1" ht="14.4" customHeight="1">
       <c r="B190" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" hidden="1" ht="14.45" customHeight="1">
+    <row r="191" hidden="1" ht="14.4" customHeight="1">
       <c r="B191" t="n">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" hidden="1" ht="14.45" customHeight="1">
+    <row r="192" hidden="1" ht="14.4" customHeight="1">
       <c r="B192" t="n">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" hidden="1" ht="14.45" customHeight="1">
+    <row r="193" hidden="1" ht="14.4" customHeight="1">
       <c r="B193" t="n">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" hidden="1" ht="14.45" customHeight="1">
+    <row r="194" hidden="1" ht="14.4" customHeight="1">
       <c r="B194" t="n">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" hidden="1" ht="14.45" customHeight="1">
+    <row r="195" hidden="1" ht="14.4" customHeight="1">
       <c r="B195" t="n">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" hidden="1" ht="14.45" customHeight="1">
+    <row r="196" hidden="1" ht="14.4" customHeight="1">
       <c r="B196" t="n">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" hidden="1" ht="14.45" customHeight="1">
+    <row r="197" hidden="1" ht="14.4" customHeight="1">
       <c r="B197" t="n">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" hidden="1" ht="14.45" customHeight="1">
+    <row r="198" hidden="1" ht="14.4" customHeight="1">
       <c r="B198" t="n">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" hidden="1" ht="14.45" customHeight="1">
+    <row r="199" hidden="1" ht="14.4" customHeight="1">
       <c r="B199" t="n">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" hidden="1" ht="14.45" customHeight="1">
+    <row r="200" hidden="1" ht="14.4" customHeight="1">
       <c r="B200" t="n">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" hidden="1" ht="14.45" customHeight="1">
+    <row r="201" hidden="1" ht="14.4" customHeight="1">
       <c r="B201" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" hidden="1" ht="14.45" customHeight="1">
+    <row r="202" hidden="1" ht="14.4" customHeight="1">
       <c r="B202" t="n">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" hidden="1" ht="14.45" customHeight="1">
+    <row r="203" hidden="1" ht="14.4" customHeight="1">
       <c r="B203" t="n">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" hidden="1" ht="14.45" customHeight="1">
+    <row r="204" hidden="1" ht="14.4" customHeight="1">
       <c r="B204" t="n">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" hidden="1" ht="14.45" customHeight="1">
+    <row r="205" hidden="1" ht="14.4" customHeight="1">
       <c r="B205" t="n">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" hidden="1" ht="14.45" customHeight="1">
+    <row r="206" hidden="1" ht="14.4" customHeight="1">
       <c r="B206" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" hidden="1" ht="14.45" customHeight="1">
+    <row r="207" hidden="1" ht="14.4" customHeight="1">
       <c r="B207" t="n">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" hidden="1" ht="14.45" customHeight="1">
+    <row r="208" hidden="1" ht="14.4" customHeight="1">
       <c r="B208" t="n">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" hidden="1" ht="14.45" customHeight="1">
+    <row r="209" hidden="1" ht="14.4" customHeight="1">
       <c r="B209" t="n">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" hidden="1" ht="14.45" customHeight="1">
+    <row r="210" hidden="1" ht="14.4" customHeight="1">
       <c r="B210" t="n">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" hidden="1" ht="14.45" customHeight="1">
+    <row r="211" hidden="1" ht="14.4" customHeight="1">
       <c r="B211" t="n">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" hidden="1" ht="14.45" customHeight="1">
+    <row r="212" hidden="1" ht="14.4" customHeight="1">
       <c r="B212" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" hidden="1" ht="14.45" customHeight="1">
+    <row r="213" hidden="1" ht="14.4" customHeight="1">
       <c r="B213" t="n">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" hidden="1" ht="14.45" customHeight="1">
+    <row r="214" hidden="1" ht="14.4" customHeight="1">
       <c r="B214" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" hidden="1" ht="14.45" customHeight="1">
+    <row r="215" hidden="1" ht="14.4" customHeight="1">
       <c r="B215" t="n">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" hidden="1" ht="14.45" customHeight="1">
+    <row r="216" hidden="1" ht="14.4" customHeight="1">
       <c r="B216" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" hidden="1" ht="14.45" customHeight="1">
+    <row r="217" hidden="1" ht="14.4" customHeight="1">
       <c r="B217" t="n">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" hidden="1" ht="14.45" customHeight="1">
+    <row r="218" hidden="1" ht="14.4" customHeight="1">
       <c r="B218" t="n">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" hidden="1" ht="14.45" customHeight="1">
+    <row r="219" hidden="1" ht="14.4" customHeight="1">
       <c r="B219" t="n">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" hidden="1" ht="14.45" customHeight="1">
+    <row r="220" hidden="1" ht="14.4" customHeight="1">
       <c r="B220" t="n">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" hidden="1" ht="14.45" customHeight="1">
+    <row r="221" hidden="1" ht="14.4" customHeight="1">
       <c r="B221" t="n">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" hidden="1" ht="14.45" customHeight="1">
+    <row r="222" hidden="1" ht="14.4" customHeight="1">
       <c r="B222" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" hidden="1" ht="14.45" customHeight="1">
+    <row r="223" hidden="1" ht="14.4" customHeight="1">
       <c r="B223" t="n">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" hidden="1" ht="14.45" customHeight="1">
+    <row r="224" hidden="1" ht="14.4" customHeight="1">
       <c r="B224" t="n">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" hidden="1" ht="14.45" customHeight="1">
+    <row r="225" hidden="1" ht="14.4" customHeight="1">
       <c r="B225" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" hidden="1" ht="14.45" customHeight="1">
+    <row r="226" hidden="1" ht="14.4" customHeight="1">
       <c r="B226" t="n">
-        <v>3212</v>
+        <v>3213</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" hidden="1" ht="14.45" customHeight="1">
+    <row r="227" hidden="1" ht="14.4" customHeight="1">
       <c r="B227" t="n">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" hidden="1" ht="14.45" customHeight="1">
+    <row r="228" hidden="1" ht="14.4" customHeight="1">
       <c r="B228" t="n">
-        <v>3214</v>
+        <v>3215</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" hidden="1" ht="14.45" customHeight="1">
+    <row r="229" hidden="1" ht="14.4" customHeight="1">
       <c r="B229" t="n">
-        <v>3215</v>
+        <v>3216</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" hidden="1" ht="14.45" customHeight="1">
+    <row r="230" hidden="1" ht="14.4" customHeight="1">
       <c r="B230" t="n">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" hidden="1" ht="14.45" customHeight="1">
+    <row r="231" hidden="1" ht="14.4" customHeight="1">
       <c r="B231" t="n">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" hidden="1" ht="14.45" customHeight="1">
+    <row r="232" hidden="1" ht="14.4" customHeight="1">
       <c r="B232" t="n">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" hidden="1" ht="14.45" customHeight="1">
+    <row r="233" hidden="1" ht="14.4" customHeight="1">
       <c r="B233" t="n">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" hidden="1" ht="14.45" customHeight="1">
+    <row r="234" hidden="1" ht="14.4" customHeight="1">
       <c r="B234" t="n">
-        <v>3220</v>
+        <v>3221</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" hidden="1" ht="14.45" customHeight="1">
+    <row r="235" hidden="1" ht="14.4" customHeight="1">
       <c r="B235" t="n">
-        <v>3221</v>
+        <v>3222</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" hidden="1" ht="14.45" customHeight="1">
+    <row r="236" hidden="1" ht="14.4" customHeight="1">
       <c r="B236" t="n">
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" hidden="1" ht="14.45" customHeight="1">
+    <row r="237" hidden="1" ht="14.4" customHeight="1">
       <c r="B237" t="n">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" hidden="1" ht="14.45" customHeight="1">
+    <row r="238" hidden="1" ht="14.4" customHeight="1">
       <c r="B238" t="n">
-        <v>3224</v>
+        <v>3225</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" hidden="1" ht="14.45" customHeight="1">
+    <row r="239" hidden="1" ht="14.4" customHeight="1">
       <c r="B239" t="n">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" hidden="1" ht="14.45" customHeight="1">
+    <row r="240" hidden="1" ht="14.4" customHeight="1">
       <c r="B240" t="n">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" hidden="1" ht="14.45" customHeight="1">
+    <row r="241" hidden="1" ht="14.4" customHeight="1">
       <c r="B241" t="n">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" hidden="1" ht="14.45" customHeight="1">
+    <row r="242" hidden="1" ht="14.4" customHeight="1">
       <c r="B242" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" hidden="1" ht="14.45" customHeight="1">
+    <row r="243" hidden="1" ht="14.4" customHeight="1">
       <c r="B243" t="n">
-        <v>3229</v>
+        <v>3230</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" hidden="1" ht="14.45" customHeight="1">
+    <row r="244" hidden="1" ht="14.4" customHeight="1">
       <c r="B244" t="n">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" hidden="1" ht="14.45" customHeight="1">
+    <row r="245" hidden="1" ht="14.4" customHeight="1">
       <c r="B245" t="n">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" hidden="1" ht="14.45" customHeight="1">
+    <row r="246" hidden="1" ht="14.4" customHeight="1">
       <c r="B246" t="n">
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" hidden="1" ht="14.45" customHeight="1">
+    <row r="247" hidden="1" ht="14.4" customHeight="1">
       <c r="B247" t="n">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" hidden="1" ht="14.45" customHeight="1">
+    <row r="248" hidden="1" ht="14.4" customHeight="1">
       <c r="B248" t="n">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" hidden="1" ht="14.45" customHeight="1">
+    <row r="249" hidden="1" ht="14.4" customHeight="1">
       <c r="B249" t="n">
-        <v>3235</v>
+        <v>3236</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" hidden="1" ht="14.45" customHeight="1">
+    <row r="250" hidden="1" ht="14.4" customHeight="1">
       <c r="B250" t="n">
-        <v>3236</v>
+        <v>3237</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" hidden="1" ht="14.45" customHeight="1">
+    <row r="251" hidden="1" ht="14.4" customHeight="1">
       <c r="B251" t="n">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" hidden="1" ht="14.45" customHeight="1">
+    <row r="252" hidden="1" ht="14.4" customHeight="1">
       <c r="B252" t="n">
-        <v>3238</v>
+        <v>3239</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" hidden="1" ht="14.45" customHeight="1">
+    <row r="253" hidden="1" ht="14.4" customHeight="1">
       <c r="B253" t="n">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" hidden="1" ht="14.45" customHeight="1">
+    <row r="254" hidden="1" ht="14.4" customHeight="1">
       <c r="B254" t="n">
-        <v>3240</v>
+        <v>3241</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" hidden="1" ht="14.45" customHeight="1">
+    <row r="255" hidden="1" ht="14.4" customHeight="1">
       <c r="B255" t="n">
-        <v>3241</v>
+        <v>3242</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" hidden="1" ht="14.45" customHeight="1">
+    <row r="256" hidden="1" ht="14.4" customHeight="1">
       <c r="B256" t="n">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" hidden="1" ht="14.45" customHeight="1">
+    <row r="257" hidden="1" ht="14.4" customHeight="1">
       <c r="B257" t="n">
-        <v>3243</v>
+        <v>3244</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" hidden="1" ht="14.45" customHeight="1">
+    <row r="258" hidden="1" ht="14.4" customHeight="1">
       <c r="B258" t="n">
-        <v>3244</v>
+        <v>3245</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" hidden="1" ht="14.45" customHeight="1">
+    <row r="259" hidden="1" ht="14.4" customHeight="1">
       <c r="B259" t="n">
-        <v>3245</v>
+        <v>3246</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" hidden="1" ht="14.45" customHeight="1">
+    <row r="260" hidden="1" ht="14.4" customHeight="1">
       <c r="B260" t="n">
-        <v>3246</v>
+        <v>3247</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" hidden="1" ht="14.45" customHeight="1">
+    <row r="261" hidden="1" ht="14.4" customHeight="1">
       <c r="B261" t="n">
-        <v>3247</v>
+        <v>3248</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" hidden="1" ht="14.45" customHeight="1">
+    <row r="262" hidden="1" ht="14.4" customHeight="1">
       <c r="B262" t="n">
-        <v>3248</v>
+        <v>3249</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" hidden="1" ht="14.45" customHeight="1">
+    <row r="263" hidden="1" ht="14.4" customHeight="1">
       <c r="B263" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" hidden="1" ht="14.45" customHeight="1">
+    <row r="264" hidden="1" ht="14.4" customHeight="1">
       <c r="B264" t="n">
-        <v>3250</v>
+        <v>3251</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" hidden="1" ht="14.45" customHeight="1">
+    <row r="265" hidden="1" ht="14.4" customHeight="1">
       <c r="B265" t="n">
-        <v>3251</v>
+        <v>3252</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" hidden="1" ht="14.45" customHeight="1">
+    <row r="266" hidden="1" ht="14.4" customHeight="1">
       <c r="B266" t="n">
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" hidden="1" ht="14.45" customHeight="1">
+    <row r="267" hidden="1" ht="14.4" customHeight="1">
       <c r="B267" t="n">
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" hidden="1" ht="14.45" customHeight="1">
+    <row r="268" hidden="1" ht="14.4" customHeight="1">
       <c r="B268" t="n">
-        <v>3254</v>
+        <v>3255</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" hidden="1" ht="14.45" customHeight="1">
+    <row r="269" hidden="1" ht="14.4" customHeight="1">
       <c r="B269" t="n">
-        <v>3255</v>
+        <v>3256</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" hidden="1" ht="14.45" customHeight="1">
+    <row r="270" hidden="1" ht="14.4" customHeight="1">
       <c r="B270" t="n">
-        <v>3256</v>
+        <v>3257</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" hidden="1" ht="14.45" customHeight="1">
+    <row r="271" hidden="1" ht="14.4" customHeight="1">
       <c r="B271" t="n">
-        <v>3257</v>
+        <v>3258</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" hidden="1" ht="14.45" customHeight="1">
+    <row r="272" hidden="1" ht="14.4" customHeight="1">
       <c r="B272" t="n">
-        <v>3258</v>
+        <v>3259</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" hidden="1" ht="14.45" customHeight="1">
+    <row r="273" hidden="1" ht="14.4" customHeight="1">
       <c r="B273" t="n">
-        <v>3259</v>
+        <v>3260</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" hidden="1" ht="14.45" customHeight="1">
+    <row r="274" hidden="1" ht="14.4" customHeight="1">
       <c r="B274" t="n">
-        <v>3260</v>
+        <v>3261</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" hidden="1" ht="14.45" customHeight="1">
+    <row r="275" hidden="1" ht="14.4" customHeight="1">
       <c r="B275" t="n">
-        <v>3261</v>
+        <v>3262</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" hidden="1" ht="14.45" customHeight="1">
+    <row r="276" hidden="1" ht="14.4" customHeight="1">
       <c r="B276" t="n">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" hidden="1" ht="14.45" customHeight="1">
+    <row r="277" hidden="1" ht="14.4" customHeight="1">
       <c r="B277" t="n">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" hidden="1" ht="14.45" customHeight="1">
+    <row r="278" hidden="1" ht="14.4" customHeight="1">
       <c r="B278" t="n">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" hidden="1" ht="14.45" customHeight="1">
+    <row r="279" hidden="1" ht="14.4" customHeight="1">
       <c r="B279" t="n">
-        <v>3265</v>
+        <v>3266</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" hidden="1" ht="14.45" customHeight="1">
+    <row r="280" hidden="1" ht="14.4" customHeight="1">
       <c r="B280" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" hidden="1" ht="14.45" customHeight="1">
+    <row r="281" hidden="1" ht="14.4" customHeight="1">
       <c r="B281" t="n">
-        <v>3267</v>
+        <v>3268</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" hidden="1" ht="14.45" customHeight="1">
+    <row r="282" hidden="1" ht="14.4" customHeight="1">
       <c r="B282" t="n">
-        <v>3268</v>
+        <v>3269</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" hidden="1" ht="14.45" customHeight="1">
+    <row r="283" hidden="1" ht="14.4" customHeight="1">
       <c r="B283" t="n">
-        <v>3269</v>
+        <v>3270</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" hidden="1" ht="14.45" customHeight="1">
+    <row r="284" hidden="1" ht="14.4" customHeight="1">
       <c r="B284" t="n">
-        <v>3270</v>
+        <v>3271</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" hidden="1" ht="14.45" customHeight="1">
+    <row r="285" hidden="1" ht="14.4" customHeight="1">
       <c r="B285" t="n">
-        <v>3271</v>
+        <v>3272</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" hidden="1" ht="14.45" customHeight="1">
+    <row r="286" hidden="1" ht="14.4" customHeight="1">
       <c r="B286" t="n">
-        <v>3272</v>
+        <v>3273</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" hidden="1" ht="14.45" customHeight="1">
+    <row r="287" hidden="1" ht="14.4" customHeight="1">
       <c r="B287" t="n">
-        <v>3273</v>
+        <v>3274</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" hidden="1" ht="14.45" customHeight="1">
+    <row r="288" hidden="1" ht="14.4" customHeight="1">
       <c r="B288" t="n">
-        <v>3274</v>
+        <v>3275</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" hidden="1" ht="14.45" customHeight="1">
+    <row r="289" hidden="1" ht="14.4" customHeight="1">
       <c r="B289" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" hidden="1" ht="14.45" customHeight="1">
+    <row r="290" hidden="1" ht="14.4" customHeight="1">
       <c r="B290" t="n">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" hidden="1" ht="14.45" customHeight="1">
+    <row r="291" hidden="1" ht="14.4" customHeight="1">
       <c r="B291" t="n">
-        <v>3277</v>
+        <v>3278</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" hidden="1" ht="14.45" customHeight="1">
+    <row r="292" hidden="1" ht="14.4" customHeight="1">
       <c r="B292" t="n">
-        <v>3278</v>
+        <v>3279</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" hidden="1" ht="14.45" customHeight="1">
+    <row r="293" hidden="1" ht="14.4" customHeight="1">
       <c r="B293" t="n">
-        <v>3279</v>
+        <v>3280</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" hidden="1" ht="14.45" customHeight="1">
+    <row r="294" hidden="1" ht="14.4" customHeight="1">
       <c r="B294" t="n">
-        <v>3280</v>
+        <v>3281</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" hidden="1" ht="14.45" customHeight="1">
+    <row r="295" hidden="1" ht="14.4" customHeight="1">
       <c r="B295" t="n">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" hidden="1" ht="14.45" customHeight="1">
+    <row r="296" hidden="1" ht="14.4" customHeight="1">
       <c r="B296" t="n">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" hidden="1" ht="14.45" customHeight="1">
+    <row r="297" hidden="1" ht="14.4" customHeight="1">
       <c r="B297" t="n">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" hidden="1" ht="14.45" customHeight="1">
+    <row r="298" hidden="1" ht="14.4" customHeight="1">
       <c r="B298" t="n">
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" hidden="1" ht="14.45" customHeight="1">
+    <row r="299" hidden="1" ht="14.4" customHeight="1">
       <c r="B299" t="n">
-        <v>3285</v>
+        <v>3286</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" hidden="1" ht="14.45" customHeight="1">
+    <row r="300" hidden="1" ht="14.4" customHeight="1">
       <c r="B300" t="n">
-        <v>3286</v>
+        <v>3287</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" hidden="1" ht="14.45" customHeight="1">
+    <row r="301" hidden="1" ht="14.4" customHeight="1">
       <c r="B301" t="n">
-        <v>3287</v>
+        <v>3288</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" hidden="1" ht="14.45" customHeight="1">
+    <row r="302" hidden="1" ht="14.4" customHeight="1">
       <c r="B302" t="n">
-        <v>3288</v>
+        <v>3289</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" hidden="1" ht="14.45" customHeight="1">
+    <row r="303" hidden="1" ht="14.4" customHeight="1">
       <c r="B303" t="n">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" hidden="1" ht="14.45" customHeight="1">
+    <row r="304" hidden="1" ht="14.4" customHeight="1">
       <c r="B304" t="n">
-        <v>3290</v>
+        <v>3291</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" hidden="1" ht="14.45" customHeight="1">
+    <row r="305" hidden="1" ht="14.4" customHeight="1">
       <c r="B305" t="n">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" hidden="1" ht="14.45" customHeight="1">
+    <row r="306" hidden="1" ht="14.4" customHeight="1">
       <c r="B306" t="n">
-        <v>3292</v>
+        <v>3293</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" hidden="1" ht="14.45" customHeight="1">
+    <row r="307" hidden="1" ht="14.4" customHeight="1">
       <c r="B307" t="n">
-        <v>3293</v>
+        <v>3294</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" hidden="1" ht="14.45" customHeight="1">
+    <row r="308" hidden="1" ht="14.4" customHeight="1">
       <c r="B308" t="n">
-        <v>3294</v>
+        <v>3295</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" hidden="1" ht="14.45" customHeight="1">
+    <row r="309" hidden="1" ht="14.4" customHeight="1">
       <c r="B309" t="n">
-        <v>3295</v>
+        <v>3296</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" hidden="1" ht="14.45" customHeight="1">
+    <row r="310" hidden="1" ht="14.4" customHeight="1">
       <c r="B310" t="n">
-        <v>3296</v>
+        <v>3297</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" hidden="1" ht="14.45" customHeight="1">
+    <row r="311" hidden="1" ht="14.4" customHeight="1">
       <c r="B311" t="n">
-        <v>3297</v>
+        <v>3298</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" hidden="1" ht="14.45" customHeight="1">
+    <row r="312" hidden="1" ht="14.4" customHeight="1">
       <c r="B312" t="n">
-        <v>3298</v>
+        <v>3299</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" hidden="1" ht="14.45" customHeight="1">
+    <row r="313" hidden="1" ht="14.4" customHeight="1">
       <c r="B313" t="n">
-        <v>3299</v>
+        <v>3300</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" hidden="1" ht="14.45" customHeight="1">
+    <row r="314" hidden="1" ht="14.4" customHeight="1">
       <c r="B314" t="n">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" hidden="1" ht="14.45" customHeight="1">
+    <row r="315" hidden="1" ht="14.4" customHeight="1">
       <c r="B315" t="n">
-        <v>3301</v>
+        <v>3302</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" hidden="1" ht="14.45" customHeight="1">
+    <row r="316" hidden="1" ht="14.4" customHeight="1">
       <c r="B316" t="n">
-        <v>3302</v>
+        <v>3303</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" hidden="1" ht="14.45" customHeight="1">
+    <row r="317" hidden="1" ht="14.4" customHeight="1">
       <c r="B317" t="n">
-        <v>3303</v>
+        <v>3304</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" hidden="1" ht="14.45" customHeight="1">
+    <row r="318" hidden="1" ht="14.4" customHeight="1">
       <c r="B318" t="n">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" hidden="1" ht="14.45" customHeight="1">
+    <row r="319" hidden="1" ht="14.4" customHeight="1">
       <c r="B319" t="n">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" hidden="1" ht="14.45" customHeight="1">
+    <row r="320" hidden="1" ht="14.4" customHeight="1">
       <c r="B320" t="n">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" hidden="1" ht="14.45" customHeight="1">
+    <row r="321" hidden="1" ht="14.4" customHeight="1">
       <c r="B321" t="n">
-        <v>3307</v>
+        <v>3308</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" hidden="1" ht="14.45" customHeight="1">
+    <row r="322" hidden="1" ht="14.4" customHeight="1">
       <c r="B322" t="n">
-        <v>3308</v>
+        <v>3309</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" hidden="1" ht="14.45" customHeight="1">
+    <row r="323" hidden="1" ht="14.4" customHeight="1">
       <c r="B323" t="n">
-        <v>3309</v>
+        <v>3310</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" hidden="1" ht="14.45" customHeight="1">
+    <row r="324" hidden="1" ht="14.4" customHeight="1">
       <c r="B324" t="n">
-        <v>3310</v>
+        <v>3311</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" hidden="1" ht="14.45" customHeight="1">
+    <row r="325" hidden="1" ht="14.4" customHeight="1">
       <c r="B325" t="n">
-        <v>3311</v>
+        <v>3312</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" hidden="1" ht="14.45" customHeight="1">
+    <row r="326" hidden="1" ht="14.4" customHeight="1">
       <c r="B326" t="n">
-        <v>3312</v>
+        <v>3313</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" hidden="1" ht="14.45" customHeight="1">
+    <row r="327" hidden="1" ht="14.4" customHeight="1">
       <c r="B327" t="n">
-        <v>3313</v>
+        <v>3314</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" hidden="1" ht="14.45" customHeight="1">
+    <row r="328" hidden="1" ht="14.4" customHeight="1">
       <c r="B328" t="n">
-        <v>3314</v>
+        <v>3315</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" hidden="1" ht="14.45" customHeight="1">
+    <row r="329" hidden="1" ht="14.4" customHeight="1">
       <c r="B329" t="n">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" hidden="1" ht="14.45" customHeight="1">
+    <row r="330" hidden="1" ht="14.4" customHeight="1">
       <c r="B330" t="n">
-        <v>3316</v>
+        <v>3317</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" hidden="1" ht="14.45" customHeight="1">
+    <row r="331" hidden="1" ht="14.4" customHeight="1">
       <c r="B331" t="n">
-        <v>3317</v>
+        <v>3318</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" hidden="1" ht="14.45" customHeight="1">
+    <row r="332" hidden="1" ht="14.4" customHeight="1">
       <c r="B332" t="n">
-        <v>3318</v>
+        <v>3319</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" hidden="1" ht="14.45" customHeight="1">
+    <row r="333" hidden="1" ht="14.4" customHeight="1">
       <c r="B333" t="n">
-        <v>3319</v>
+        <v>3320</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" hidden="1" ht="14.45" customHeight="1">
+    <row r="334" hidden="1" ht="14.4" customHeight="1">
       <c r="B334" t="n">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" hidden="1" ht="14.45" customHeight="1">
+    <row r="335" hidden="1" ht="14.4" customHeight="1">
       <c r="B335" t="n">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" hidden="1" ht="14.45" customHeight="1">
+    <row r="336" hidden="1" ht="14.4" customHeight="1">
       <c r="B336" t="n">
-        <v>3322</v>
+        <v>3323</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" hidden="1" ht="14.45" customHeight="1">
+    <row r="337" hidden="1" ht="14.4" customHeight="1">
       <c r="B337" t="n">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" hidden="1" ht="14.45" customHeight="1">
+    <row r="338" hidden="1" ht="14.4" customHeight="1">
       <c r="B338" t="n">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" hidden="1" ht="14.45" customHeight="1">
+    <row r="339" hidden="1" ht="14.4" customHeight="1">
       <c r="B339" t="n">
-        <v>3325</v>
+        <v>3326</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" hidden="1" ht="14.45" customHeight="1">
+    <row r="340" hidden="1" ht="14.4" customHeight="1">
       <c r="B340" t="n">
-        <v>3326</v>
+        <v>3327</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" hidden="1" ht="14.45" customHeight="1">
+    <row r="341" hidden="1" ht="14.4" customHeight="1">
       <c r="B341" t="n">
-        <v>3327</v>
+        <v>3328</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" hidden="1" ht="14.45" customHeight="1">
+    <row r="342" hidden="1" ht="14.4" customHeight="1">
       <c r="B342" t="n">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" hidden="1" ht="14.45" customHeight="1">
+    <row r="343" hidden="1" ht="14.4" customHeight="1">
       <c r="B343" t="n">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" hidden="1" ht="14.45" customHeight="1">
+    <row r="344" hidden="1" ht="14.4" customHeight="1">
       <c r="B344" t="n">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" hidden="1" ht="14.45" customHeight="1">
+    <row r="345" hidden="1" ht="14.4" customHeight="1">
       <c r="B345" t="n">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" hidden="1" ht="14.45" customHeight="1">
+    <row r="346" hidden="1" ht="14.4" customHeight="1">
       <c r="B346" t="n">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" hidden="1" ht="14.45" customHeight="1">
+    <row r="347" hidden="1" ht="14.4" customHeight="1">
       <c r="B347" t="n">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" hidden="1" ht="14.45" customHeight="1">
+    <row r="348" hidden="1" ht="14.4" customHeight="1">
       <c r="B348" t="n">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" hidden="1" ht="14.45" customHeight="1">
+    <row r="349" hidden="1" ht="14.4" customHeight="1">
       <c r="B349" t="n">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" hidden="1" ht="14.45" customHeight="1">
+    <row r="350" hidden="1" ht="14.4" customHeight="1">
       <c r="B350" t="n">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" hidden="1" ht="14.45" customHeight="1">
+    <row r="351" hidden="1" ht="14.4" customHeight="1">
       <c r="B351" t="n">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" hidden="1" ht="14.45" customHeight="1">
+    <row r="352" hidden="1" ht="14.4" customHeight="1">
       <c r="B352" t="n">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" hidden="1" ht="14.45" customHeight="1">
+    <row r="353" hidden="1" ht="14.4" customHeight="1">
       <c r="B353" t="n">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" hidden="1" ht="14.45" customHeight="1">
+    <row r="354" hidden="1" ht="14.4" customHeight="1">
       <c r="B354" t="n">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" hidden="1" ht="14.45" customHeight="1">
+    <row r="355" hidden="1" ht="14.4" customHeight="1">
       <c r="B355" t="n">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" hidden="1" ht="14.45" customHeight="1">
+    <row r="356" hidden="1" ht="14.4" customHeight="1">
       <c r="B356" t="n">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" hidden="1" ht="14.45" customHeight="1">
+    <row r="357" hidden="1" ht="14.4" customHeight="1">
       <c r="B357" t="n">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" hidden="1" ht="14.45" customHeight="1">
+    <row r="358" hidden="1" ht="14.4" customHeight="1">
       <c r="B358" t="n">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" hidden="1" ht="14.45" customHeight="1">
+    <row r="359" hidden="1" ht="14.4" customHeight="1">
       <c r="B359" t="n">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" hidden="1" ht="14.45" customHeight="1">
+    <row r="360" hidden="1" ht="14.4" customHeight="1">
       <c r="B360" t="n">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" hidden="1" ht="14.45" customHeight="1">
+    <row r="361" hidden="1" ht="14.4" customHeight="1">
       <c r="B361" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" hidden="1" ht="14.45" customHeight="1">
+    <row r="362" hidden="1" ht="14.4" customHeight="1">
       <c r="B362" t="n">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" hidden="1" ht="14.45" customHeight="1">
+    <row r="363" hidden="1" ht="14.4" customHeight="1">
       <c r="B363" t="n">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" hidden="1" ht="14.45" customHeight="1">
+    <row r="364" hidden="1" ht="14.4" customHeight="1">
       <c r="B364" t="n">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" hidden="1" ht="14.45" customHeight="1">
+    <row r="365" hidden="1" ht="14.4" customHeight="1">
       <c r="B365" t="n">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" hidden="1" ht="14.45" customHeight="1">
+    <row r="366" hidden="1" ht="14.4" customHeight="1">
       <c r="B366" t="n">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" hidden="1" ht="14.45" customHeight="1">
+    <row r="367" hidden="1" ht="14.4" customHeight="1">
       <c r="B367" t="n">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" hidden="1" ht="14.45" customHeight="1">
+    <row r="368" hidden="1" ht="14.4" customHeight="1">
       <c r="B368" t="n">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" hidden="1" ht="14.45" customHeight="1">
+    <row r="369" hidden="1" ht="14.4" customHeight="1">
       <c r="B369" t="n">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" hidden="1" ht="14.45" customHeight="1">
+    <row r="370" hidden="1" ht="14.4" customHeight="1">
       <c r="B370" t="n">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" hidden="1" ht="14.45" customHeight="1">
+    <row r="371" hidden="1" ht="14.4" customHeight="1">
       <c r="B371" t="n">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" hidden="1" ht="14.45" customHeight="1">
+    <row r="372" hidden="1" ht="14.4" customHeight="1">
       <c r="B372" t="n">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" hidden="1" ht="14.45" customHeight="1">
+    <row r="373" hidden="1" ht="14.4" customHeight="1">
       <c r="B373" t="n">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" hidden="1" ht="14.45" customHeight="1">
+    <row r="374" hidden="1" ht="14.4" customHeight="1">
       <c r="B374" t="n">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" hidden="1" ht="14.45" customHeight="1">
+    <row r="375" hidden="1" ht="14.4" customHeight="1">
       <c r="B375" t="n">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" hidden="1" ht="14.45" customHeight="1">
+    <row r="376" hidden="1" ht="14.4" customHeight="1">
       <c r="B376" t="n">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" hidden="1" ht="14.45" customHeight="1">
+    <row r="377" hidden="1" ht="14.4" customHeight="1">
       <c r="B377" t="n">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" hidden="1" ht="14.45" customHeight="1">
+    <row r="378" hidden="1" ht="14.4" customHeight="1">
       <c r="B378" t="n">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" hidden="1" ht="14.45" customHeight="1">
+    <row r="379" hidden="1" ht="14.4" customHeight="1">
       <c r="B379" t="n">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" hidden="1" ht="14.45" customHeight="1">
+    <row r="380" hidden="1" ht="14.4" customHeight="1">
       <c r="B380" t="n">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" hidden="1" ht="14.45" customHeight="1">
+    <row r="381" hidden="1" ht="14.4" customHeight="1">
       <c r="B381" t="n">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" hidden="1" ht="14.45" customHeight="1">
+    <row r="382" hidden="1" ht="14.4" customHeight="1">
       <c r="B382" t="n">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" hidden="1" ht="14.45" customHeight="1">
+    <row r="383" hidden="1" ht="14.4" customHeight="1">
       <c r="B383" t="n">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" hidden="1" ht="14.45" customHeight="1">
+    <row r="384" hidden="1" ht="14.4" customHeight="1">
       <c r="B384" t="n">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" hidden="1" ht="14.45" customHeight="1">
+    <row r="385" hidden="1" ht="14.4" customHeight="1">
       <c r="B385" t="n">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" hidden="1" ht="14.45" customHeight="1">
+    <row r="386" hidden="1" ht="14.4" customHeight="1">
       <c r="B386" t="n">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" hidden="1" ht="14.45" customHeight="1">
+    <row r="387" hidden="1" ht="14.4" customHeight="1">
       <c r="B387" t="n">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" hidden="1" ht="14.45" customHeight="1">
+    <row r="388" hidden="1" ht="14.4" customHeight="1">
       <c r="B388" t="n">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" hidden="1" ht="14.45" customHeight="1">
+    <row r="389" hidden="1" ht="14.4" customHeight="1">
       <c r="B389" t="n">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" hidden="1" ht="14.45" customHeight="1">
+    <row r="390" hidden="1" ht="14.4" customHeight="1">
       <c r="B390" t="n">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" hidden="1" ht="14.45" customHeight="1">
+    <row r="391" hidden="1" ht="14.4" customHeight="1">
       <c r="B391" t="n">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" hidden="1" ht="14.45" customHeight="1">
+    <row r="392" hidden="1" ht="14.4" customHeight="1">
       <c r="B392" t="n">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" hidden="1" ht="14.45" customHeight="1">
+    <row r="393" hidden="1" ht="14.4" customHeight="1">
       <c r="B393" t="n">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" hidden="1" ht="14.45" customHeight="1">
+    <row r="394" hidden="1" ht="14.4" customHeight="1">
       <c r="B394" t="n">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" hidden="1" ht="14.45" customHeight="1">
+    <row r="395" hidden="1" ht="14.4" customHeight="1">
       <c r="B395" t="n">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" hidden="1" ht="14.45" customHeight="1">
+    <row r="396" hidden="1" ht="14.4" customHeight="1">
       <c r="B396" t="n">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" hidden="1" ht="14.45" customHeight="1">
+    <row r="397" hidden="1" ht="14.4" customHeight="1">
       <c r="B397" t="n">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" hidden="1" ht="14.45" customHeight="1">
+    <row r="398" hidden="1" ht="14.4" customHeight="1">
       <c r="B398" t="n">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" hidden="1" ht="14.45" customHeight="1">
+    <row r="399" hidden="1" ht="14.4" customHeight="1">
       <c r="B399" t="n">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" hidden="1" ht="14.45" customHeight="1">
+    <row r="400" hidden="1" ht="14.4" customHeight="1">
       <c r="B400" t="n">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" hidden="1" ht="14.45" customHeight="1">
+    <row r="401" hidden="1" ht="14.4" customHeight="1">
       <c r="B401" t="n">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" hidden="1" ht="14.45" customHeight="1">
+    <row r="402" hidden="1" ht="14.4" customHeight="1">
       <c r="B402" t="n">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" hidden="1" ht="14.45" customHeight="1">
+    <row r="403" hidden="1" ht="14.4" customHeight="1">
       <c r="B403" t="n">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" hidden="1" ht="14.45" customHeight="1">
+    <row r="404" hidden="1" ht="14.4" customHeight="1">
       <c r="B404" t="n">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" hidden="1" ht="14.45" customHeight="1">
+    <row r="405" hidden="1" ht="14.4" customHeight="1">
       <c r="B405" t="n">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" hidden="1" ht="14.45" customHeight="1">
+    <row r="406" hidden="1" ht="14.4" customHeight="1">
       <c r="B406" t="n">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" hidden="1" ht="14.45" customHeight="1">
+    <row r="407" hidden="1" ht="14.4" customHeight="1">
       <c r="B407" t="n">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" hidden="1" ht="14.45" customHeight="1">
+    <row r="408" hidden="1" ht="14.4" customHeight="1">
       <c r="B408" t="n">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" hidden="1" ht="14.45" customHeight="1">
+    <row r="409" hidden="1" ht="14.4" customHeight="1">
       <c r="B409" t="n">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" hidden="1" ht="14.45" customHeight="1">
+    <row r="410" hidden="1" ht="14.4" customHeight="1">
       <c r="B410" t="n">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" hidden="1" ht="14.45" customHeight="1">
+    <row r="411" hidden="1" ht="14.4" customHeight="1">
       <c r="B411" t="n">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" hidden="1" ht="14.45" customHeight="1">
+    <row r="412" hidden="1" ht="14.4" customHeight="1">
       <c r="B412" t="n">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" hidden="1" ht="14.45" customHeight="1">
+    <row r="413" hidden="1" ht="14.4" customHeight="1">
       <c r="B413" t="n">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" hidden="1" ht="14.45" customHeight="1">
+    <row r="414" hidden="1" ht="14.4" customHeight="1">
       <c r="B414" t="n">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" hidden="1" ht="14.45" customHeight="1">
+    <row r="415" hidden="1" ht="14.4" customHeight="1">
       <c r="B415" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" hidden="1" ht="14.45" customHeight="1">
+    <row r="416" hidden="1" ht="14.4" customHeight="1">
       <c r="B416" t="n">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" hidden="1" ht="14.45" customHeight="1">
+    <row r="417" hidden="1" ht="14.4" customHeight="1">
       <c r="B417" t="n">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" hidden="1" ht="14.45" customHeight="1">
+    <row r="418" hidden="1" ht="14.4" customHeight="1">
       <c r="B418" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" hidden="1" ht="14.45" customHeight="1">
+    <row r="419" hidden="1" ht="14.4" customHeight="1">
       <c r="B419" t="n">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" hidden="1" ht="14.45" customHeight="1">
+    <row r="420" hidden="1" ht="14.4" customHeight="1">
       <c r="B420" t="n">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" hidden="1" ht="14.45" customHeight="1">
+    <row r="421" hidden="1" ht="14.4" customHeight="1">
       <c r="B421" t="n">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" hidden="1" ht="14.45" customHeight="1">
+    <row r="422" hidden="1" ht="14.4" customHeight="1">
       <c r="B422" t="n">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" hidden="1" ht="14.45" customHeight="1">
+    <row r="423" hidden="1" ht="14.4" customHeight="1">
       <c r="B423" t="n">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" hidden="1" ht="14.45" customHeight="1">
+    <row r="424" hidden="1" ht="14.4" customHeight="1">
       <c r="B424" t="n">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" hidden="1" ht="14.45" customHeight="1">
+    <row r="425" hidden="1" ht="14.4" customHeight="1">
       <c r="B425" t="n">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" hidden="1" ht="14.45" customHeight="1">
+    <row r="426" hidden="1" ht="14.4" customHeight="1">
       <c r="B426" t="n">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" hidden="1" ht="14.45" customHeight="1">
+    <row r="427" hidden="1" ht="14.4" customHeight="1">
       <c r="B427" t="n">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" hidden="1" ht="14.45" customHeight="1">
+    <row r="428" hidden="1" ht="14.4" customHeight="1">
       <c r="B428" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" hidden="1" ht="14.45" customHeight="1">
+    <row r="429" hidden="1" ht="14.4" customHeight="1">
       <c r="B429" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" hidden="1" ht="14.45" customHeight="1">
+    <row r="430" hidden="1" ht="14.4" customHeight="1">
       <c r="B430" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" hidden="1" ht="14.45" customHeight="1">
+    <row r="431" hidden="1" ht="14.4" customHeight="1">
       <c r="B431" t="n">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" hidden="1" ht="14.45" customHeight="1">
+    <row r="432" hidden="1" ht="14.4" customHeight="1">
       <c r="B432" t="n">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" hidden="1" ht="14.45" customHeight="1">
+    <row r="433" hidden="1" ht="14.4" customHeight="1">
       <c r="B433" t="n">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" hidden="1" ht="14.45" customHeight="1">
+    <row r="434" hidden="1" ht="14.4" customHeight="1">
       <c r="B434" t="n">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" hidden="1" ht="14.45" customHeight="1">
+    <row r="435" hidden="1" ht="14.4" customHeight="1">
       <c r="B435" t="n">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" hidden="1" ht="14.45" customHeight="1">
+    <row r="436" hidden="1" ht="14.4" customHeight="1">
       <c r="B436" t="n">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" hidden="1" ht="14.45" customHeight="1">
+    <row r="437" hidden="1" ht="14.4" customHeight="1">
       <c r="B437" t="n">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" hidden="1" ht="14.45" customHeight="1">
+    <row r="438" hidden="1" ht="14.4" customHeight="1">
       <c r="B438" t="n">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" hidden="1" ht="14.45" customHeight="1">
+    <row r="439" hidden="1" ht="14.4" customHeight="1">
       <c r="B439" t="n">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" hidden="1" ht="14.45" customHeight="1">
+    <row r="440" hidden="1" ht="14.4" customHeight="1">
       <c r="B440" t="n">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" hidden="1" ht="14.45" customHeight="1">
+    <row r="441" hidden="1" ht="14.4" customHeight="1">
       <c r="B441" t="n">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" hidden="1" ht="14.45" customHeight="1">
+    <row r="442" hidden="1" ht="14.4" customHeight="1">
       <c r="B442" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" hidden="1" ht="14.45" customHeight="1">
+    <row r="443" hidden="1" ht="14.4" customHeight="1">
       <c r="B443" t="n">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" hidden="1" ht="14.45" customHeight="1">
+    <row r="444" hidden="1" ht="14.4" customHeight="1">
       <c r="B444" t="n">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" hidden="1" ht="14.45" customHeight="1">
+    <row r="445" hidden="1" ht="14.4" customHeight="1">
       <c r="B445" t="n">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" hidden="1" ht="14.45" customHeight="1">
+    <row r="446" hidden="1" ht="14.4" customHeight="1">
       <c r="B446" t="n">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" hidden="1" ht="14.45" customHeight="1">
+    <row r="447" hidden="1" ht="14.4" customHeight="1">
       <c r="B447" t="n">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" hidden="1" ht="14.45" customHeight="1">
+    <row r="448" hidden="1" ht="14.4" customHeight="1">
       <c r="B448" t="n">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" hidden="1" ht="14.45" customHeight="1">
+    <row r="449" hidden="1" ht="14.4" customHeight="1">
       <c r="B449" t="n">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" hidden="1" ht="14.45" customHeight="1">
+    <row r="450" hidden="1" ht="14.4" customHeight="1">
       <c r="B450" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" hidden="1" ht="14.45" customHeight="1">
+    <row r="451" hidden="1" ht="14.4" customHeight="1">
       <c r="B451" t="n">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" hidden="1" ht="14.45" customHeight="1">
+    <row r="452" hidden="1" ht="14.4" customHeight="1">
       <c r="B452" t="n">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" hidden="1" ht="14.45" customHeight="1">
+    <row r="453" hidden="1" ht="14.4" customHeight="1">
       <c r="B453" t="n">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" hidden="1" ht="14.45" customHeight="1">
+    <row r="454" hidden="1" ht="14.4" customHeight="1">
       <c r="B454" t="n">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" hidden="1" ht="14.45" customHeight="1">
+    <row r="455" hidden="1" ht="14.4" customHeight="1">
       <c r="B455" t="n">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" hidden="1" ht="14.45" customHeight="1">
+    <row r="456" hidden="1" ht="14.4" customHeight="1">
       <c r="B456" t="n">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" hidden="1" ht="14.45" customHeight="1">
+    <row r="457" hidden="1" ht="14.4" customHeight="1">
       <c r="B457" t="n">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" hidden="1" ht="14.45" customHeight="1">
+    <row r="458" hidden="1" ht="14.4" customHeight="1">
       <c r="B458" t="n">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" hidden="1" ht="14.45" customHeight="1">
+    <row r="459" hidden="1" ht="14.4" customHeight="1">
       <c r="B459" t="n">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" hidden="1" ht="14.45" customHeight="1">
+    <row r="460" hidden="1" ht="14.4" customHeight="1">
       <c r="B460" t="n">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" hidden="1" ht="14.45" customHeight="1">
+    <row r="461" hidden="1" ht="14.4" customHeight="1">
       <c r="B461" t="n">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" hidden="1" ht="14.45" customHeight="1">
+    <row r="462" hidden="1" ht="14.4" customHeight="1">
       <c r="B462" t="n">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" hidden="1" ht="14.45" customHeight="1">
+    <row r="463" hidden="1" ht="14.4" customHeight="1">
       <c r="B463" t="n">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" hidden="1" ht="14.45" customHeight="1">
+    <row r="464" hidden="1" ht="14.4" customHeight="1">
       <c r="B464" t="n">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" hidden="1" ht="14.45" customHeight="1">
+    <row r="465" hidden="1" ht="14.4" customHeight="1">
       <c r="B465" t="n">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" hidden="1" ht="14.45" customHeight="1">
+    <row r="466" hidden="1" ht="14.4" customHeight="1">
       <c r="B466" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" hidden="1" ht="14.45" customHeight="1">
+    <row r="467" hidden="1" ht="14.4" customHeight="1">
       <c r="B467" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" hidden="1" ht="14.45" customHeight="1">
+    <row r="468" hidden="1" ht="14.4" customHeight="1">
       <c r="B468" t="n">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" hidden="1" ht="14.45" customHeight="1">
+    <row r="469" hidden="1" ht="14.4" customHeight="1">
       <c r="B469" t="n">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" hidden="1" ht="14.45" customHeight="1">
+    <row r="470" hidden="1" ht="14.4" customHeight="1">
       <c r="B470" t="n">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" hidden="1" ht="14.45" customHeight="1">
+    <row r="471" hidden="1" ht="14.4" customHeight="1">
       <c r="B471" t="n">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" hidden="1" ht="14.45" customHeight="1">
+    <row r="472" hidden="1" ht="14.4" customHeight="1">
       <c r="B472" t="n">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" hidden="1" ht="14.45" customHeight="1">
+    <row r="473" hidden="1" ht="14.4" customHeight="1">
       <c r="B473" t="n">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" hidden="1" ht="14.45" customHeight="1">
+    <row r="474" hidden="1" ht="14.4" customHeight="1">
       <c r="B474" t="n">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" hidden="1" ht="14.45" customHeight="1">
+    <row r="475" hidden="1" ht="14.4" customHeight="1">
       <c r="B475" t="n">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" hidden="1" ht="14.45" customHeight="1">
+    <row r="476" hidden="1" ht="14.4" customHeight="1">
       <c r="B476" t="n">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" hidden="1" ht="14.45" customHeight="1">
+    <row r="477" hidden="1" ht="14.4" customHeight="1">
       <c r="B477" t="n">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" hidden="1" ht="14.45" customHeight="1">
+    <row r="478" hidden="1" ht="14.4" customHeight="1">
       <c r="B478" t="n">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" hidden="1" ht="14.45" customHeight="1">
+    <row r="479" hidden="1" ht="14.4" customHeight="1">
       <c r="B479" t="n">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" hidden="1" ht="14.45" customHeight="1">
+    <row r="480" hidden="1" ht="14.4" customHeight="1">
       <c r="B480" t="n">
-        <v>3466</v>
+        <v>3467</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" hidden="1" ht="14.45" customHeight="1">
+    <row r="481" hidden="1" ht="14.4" customHeight="1">
       <c r="B481" t="n">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" hidden="1" ht="14.45" customHeight="1">
+    <row r="482" hidden="1" ht="14.4" customHeight="1">
       <c r="B482" t="n">
-        <v>3468</v>
+        <v>3469</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" hidden="1" ht="14.45" customHeight="1">
+    <row r="483" hidden="1" ht="14.4" customHeight="1">
       <c r="B483" t="n">
-        <v>3469</v>
+        <v>3470</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" hidden="1" ht="14.45" customHeight="1">
+    <row r="484" hidden="1" ht="14.4" customHeight="1">
       <c r="B484" t="n">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" hidden="1" ht="14.45" customHeight="1">
+    <row r="485" hidden="1" ht="14.4" customHeight="1">
       <c r="B485" t="n">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" hidden="1" ht="14.45" customHeight="1">
+    <row r="486" hidden="1" ht="14.4" customHeight="1">
       <c r="B486" t="n">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" hidden="1" ht="14.45" customHeight="1">
+    <row r="487" hidden="1" ht="14.4" customHeight="1">
       <c r="B487" t="n">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" hidden="1" ht="14.45" customHeight="1">
+    <row r="488" hidden="1" ht="14.4" customHeight="1">
       <c r="B488" t="n">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" hidden="1" ht="14.45" customHeight="1">
+    <row r="489" hidden="1" ht="14.4" customHeight="1">
       <c r="B489" t="n">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" hidden="1" ht="14.45" customHeight="1">
+    <row r="490" hidden="1" ht="14.4" customHeight="1">
       <c r="B490" t="n">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" hidden="1" ht="14.45" customHeight="1">
+    <row r="491" hidden="1" ht="14.4" customHeight="1">
       <c r="B491" t="n">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" hidden="1" ht="14.45" customHeight="1">
+    <row r="492" hidden="1" ht="14.4" customHeight="1">
       <c r="B492" t="n">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" hidden="1" ht="14.45" customHeight="1">
+    <row r="493" hidden="1" ht="14.4" customHeight="1">
       <c r="B493" t="n">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" hidden="1" ht="14.45" customHeight="1">
+    <row r="494" hidden="1" ht="14.4" customHeight="1">
       <c r="B494" t="n">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" hidden="1" ht="14.45" customHeight="1">
+    <row r="495" hidden="1" ht="14.4" customHeight="1">
       <c r="B495" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" hidden="1" ht="14.45" customHeight="1">
+    <row r="496" hidden="1" ht="14.4" customHeight="1">
       <c r="B496" t="n">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" hidden="1" ht="14.45" customHeight="1">
+    <row r="497" hidden="1" ht="14.4" customHeight="1">
       <c r="B497" t="n">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" hidden="1" ht="14.45" customHeight="1">
+    <row r="498" hidden="1" ht="14.4" customHeight="1">
       <c r="B498" t="n">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" hidden="1" ht="14.45" customHeight="1">
+    <row r="499" hidden="1" ht="14.4" customHeight="1">
       <c r="B499" t="n">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" hidden="1" ht="14.45" customHeight="1">
+    <row r="500" hidden="1" ht="14.4" customHeight="1">
       <c r="B500" t="n">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" hidden="1" ht="14.45" customHeight="1">
+    <row r="501" hidden="1" ht="14.4" customHeight="1">
       <c r="B501" t="n">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" hidden="1" ht="14.45" customHeight="1">
+    <row r="502" hidden="1" ht="14.4" customHeight="1">
       <c r="B502" t="n">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" hidden="1" ht="14.45" customHeight="1">
+    <row r="503" hidden="1" ht="14.4" customHeight="1">
       <c r="B503" t="n">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" hidden="1" ht="14.45" customHeight="1">
+    <row r="504" hidden="1" ht="14.4" customHeight="1">
       <c r="B504" t="n">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" hidden="1" ht="14.45" customHeight="1">
+    <row r="505" hidden="1" ht="14.4" customHeight="1">
       <c r="B505" t="n">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" hidden="1" ht="14.45" customHeight="1">
+    <row r="506" hidden="1" ht="14.4" customHeight="1">
       <c r="B506" t="n">
-        <v>3492</v>
+        <v>3493</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" hidden="1" ht="14.45" customHeight="1">
+    <row r="507" hidden="1" ht="14.4" customHeight="1">
       <c r="B507" t="n">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" hidden="1" ht="14.45" customHeight="1">
+    <row r="508" hidden="1" ht="14.4" customHeight="1">
       <c r="B508" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" hidden="1" ht="14.45" customHeight="1">
+    <row r="509" hidden="1" ht="14.4" customHeight="1">
       <c r="B509" t="n">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" hidden="1" ht="14.45" customHeight="1">
+    <row r="510" hidden="1" ht="14.4" customHeight="1">
       <c r="B510" t="n">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" hidden="1" ht="14.45" customHeight="1">
+    <row r="511" hidden="1" ht="14.4" customHeight="1">
       <c r="B511" t="n">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" hidden="1" ht="14.45" customHeight="1">
+    <row r="512" hidden="1" ht="14.4" customHeight="1">
       <c r="B512" t="n">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" hidden="1" ht="14.45" customHeight="1">
+    <row r="513" hidden="1" ht="14.4" customHeight="1">
       <c r="B513" t="n">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" hidden="1" ht="14.45" customHeight="1">
+    <row r="514" hidden="1" ht="14.4" customHeight="1">
       <c r="B514" t="n">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" hidden="1" ht="14.45" customHeight="1">
+    <row r="515" hidden="1" ht="14.4" customHeight="1">
       <c r="B515" t="n">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" hidden="1" ht="14.45" customHeight="1">
+    <row r="516" hidden="1" ht="14.4" customHeight="1">
       <c r="B516" t="n">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" hidden="1" ht="14.45" customHeight="1">
+    <row r="517" hidden="1" ht="14.4" customHeight="1">
       <c r="B517" t="n">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" hidden="1" ht="14.45" customHeight="1">
+    <row r="518" hidden="1" ht="14.4" customHeight="1">
       <c r="B518" t="n">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" hidden="1" ht="14.45" customHeight="1">
+    <row r="519" hidden="1" ht="14.4" customHeight="1">
       <c r="B519" t="n">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" hidden="1" ht="14.45" customHeight="1">
+    <row r="520" hidden="1" ht="14.4" customHeight="1">
       <c r="B520" t="n">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" hidden="1" ht="14.45" customHeight="1">
+    <row r="521" hidden="1" ht="14.4" customHeight="1">
       <c r="B521" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" hidden="1" ht="14.45" customHeight="1">
+    <row r="522" hidden="1" ht="14.4" customHeight="1">
       <c r="B522" t="n">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" hidden="1" ht="14.45" customHeight="1">
+    <row r="523" hidden="1" ht="14.4" customHeight="1">
       <c r="B523" t="n">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" hidden="1" ht="14.45" customHeight="1">
+    <row r="524" hidden="1" ht="14.4" customHeight="1">
       <c r="B524" t="n">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" hidden="1" ht="14.45" customHeight="1">
+    <row r="525" hidden="1" ht="14.4" customHeight="1">
       <c r="B525" t="n">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" hidden="1" ht="14.45" customHeight="1">
+    <row r="526" hidden="1" ht="15" customHeight="1">
       <c r="B526" t="n">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
     <row r="527" hidden="1" ht="15" customHeight="1">
       <c r="B527" t="n">
-        <v>3513</v>
+        <v>3514</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
     <row r="528" hidden="1" ht="15" customHeight="1">
       <c r="B528" t="n">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -8476,9 +8482,6 @@
       <c r="Q528" s="4" t="n"/>
     </row>
     <row r="529" hidden="1" ht="15" customHeight="1">
-      <c r="B529" t="n">
-        <v>3515</v>
-      </c>
       <c r="F529" t="inlineStr">
         <is>
           <t>A</t>
@@ -8523,17 +8526,7 @@
       <c r="O533" s="4" t="n"/>
       <c r="Q533" s="4" t="n"/>
     </row>
-    <row r="534" hidden="1" ht="15" customHeight="1">
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O534" s="4" t="n"/>
-      <c r="Q534" s="4" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="I535"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10200" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -783,13 +783,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN533" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN533">
-    <filterColumn colId="1" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="Unilever"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AN533"/>
   <sortState ref="B2:AN533">
     <sortCondition ref="I1:I533"/>
   </sortState>
@@ -1147,8 +1141,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="15.6640625" customWidth="1" min="1" max="1"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
-    <col width="33.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="36.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="56.44140625" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="25.88671875" customWidth="1" min="6" max="6"/>
@@ -1276,7 +1270,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="62">
+    <row r="2" ht="14.4" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1360,7 +1354,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" hidden="1" ht="14.4" customHeight="1">
+    <row r="3" ht="14.4" customHeight="1">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1430,7 +1424,7 @@
       <c r="Q3" s="88" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
-    <row r="4" hidden="1" ht="24" customHeight="1" thickBot="1">
+    <row r="4" ht="24" customHeight="1" thickBot="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1514,7 +1508,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" hidden="1" ht="28.8" customHeight="1">
+    <row r="5" ht="28.8" customHeight="1">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1573,7 +1567,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6" hidden="1" ht="14.4" customHeight="1">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1633,7 +1627,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7" hidden="1" ht="14.4" customHeight="1">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1711,7 +1705,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" hidden="1" ht="14.4" customHeight="1">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="B8" t="n">
         <v>3008</v>
       </c>
@@ -1794,7 +1788,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="9" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="9" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="B9" t="n">
         <v>3009</v>
       </c>
@@ -1877,7 +1871,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="10" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1961,7 +1955,7 @@
         <v>45516</v>
       </c>
     </row>
-    <row r="11" hidden="1" ht="43.2" customHeight="1">
+    <row r="11" ht="43.2" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2042,7 +2036,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="12" hidden="1" ht="14.4" customFormat="1" customHeight="1" s="27">
+    <row r="12" ht="14.4" customFormat="1" customHeight="1" s="27">
       <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2106,7 +2100,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="13" hidden="1" ht="14.4" customHeight="1">
+    <row r="13" ht="14.4" customHeight="1">
       <c r="B13" t="n">
         <v>3014</v>
       </c>
@@ -2179,7 +2173,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="14" hidden="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="14" ht="30.75" customHeight="1" thickBot="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Mike/Heather</t>
@@ -2243,7 +2237,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="15" hidden="1" ht="29.25" customFormat="1" customHeight="1" s="79">
+    <row r="15" ht="29.25" customFormat="1" customHeight="1" s="79">
       <c r="A15" s="79" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2332,7 +2326,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="16" hidden="1" ht="48" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2410,7 +2404,7 @@
       <c r="Q16" s="88" t="n"/>
       <c r="R16" s="23" t="n"/>
     </row>
-    <row r="17" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="17" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2455,7 +2449,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="18" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="18" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="B18" t="n">
         <v>3018</v>
       </c>
@@ -2497,7 +2491,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="19" ht="43.2" customFormat="1" customHeight="1" s="27">
       <c r="B19" t="n">
         <v>3019</v>
       </c>
@@ -2539,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" ht="43.2" customHeight="1">
+    <row r="20" ht="43.2" customHeight="1">
       <c r="B20" t="n">
         <v>3020</v>
       </c>
@@ -2581,7 +2575,7 @@
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" ht="33" customFormat="1" customHeight="1" s="27">
+    <row r="21" ht="33" customFormat="1" customHeight="1" s="27">
       <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -2628,7 +2622,7 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" ht="30.75" customHeight="1">
+    <row r="22" ht="30.75" customHeight="1">
       <c r="B22" t="n">
         <v>3022</v>
       </c>
@@ -2703,7 +2697,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="23" hidden="1" ht="28.8" customHeight="1">
+    <row r="23" ht="28.8" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2787,7 +2781,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="24" hidden="1" ht="28.8" customHeight="1">
+    <row r="24" ht="28.8" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2853,7 +2847,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" ht="43.8" customHeight="1" thickBot="1">
+    <row r="25" ht="43.8" customHeight="1" thickBot="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2921,7 +2915,7 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" hidden="1" ht="14.4" customHeight="1">
+    <row r="26" ht="14.4" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -2997,7 +2991,7 @@
       </c>
       <c r="Q26" s="4" t="n"/>
     </row>
-    <row r="27" hidden="1" ht="14.4" customHeight="1">
+    <row r="27" ht="14.4" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3068,7 +3062,7 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" ht="28.8" customHeight="1">
+    <row r="28" ht="28.8" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3145,7 +3139,7 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" ht="43.2" customHeight="1">
+    <row r="29" ht="43.2" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3193,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="30" hidden="1" ht="28.8" customHeight="1">
+    <row r="30" ht="28.8" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3255,7 +3249,7 @@
         </is>
       </c>
     </row>
-    <row r="31" hidden="1" ht="43.2" customHeight="1">
+    <row r="31" ht="43.2" customHeight="1">
       <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3319,7 +3313,7 @@
       <c r="O31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
     </row>
-    <row r="32" hidden="1" ht="54" customFormat="1" customHeight="1" s="27">
+    <row r="32" ht="54" customFormat="1" customHeight="1" s="27">
       <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -3393,7 +3387,7 @@
       <c r="O32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
     </row>
-    <row r="33" hidden="1" ht="43.2" customHeight="1">
+    <row r="33" ht="43.2" customHeight="1">
       <c r="B33" t="n">
         <v>3035</v>
       </c>
@@ -3462,7 +3456,7 @@
       <c r="O33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
     </row>
-    <row r="34" hidden="1" ht="57.6" customHeight="1">
+    <row r="34" ht="57.6" customHeight="1">
       <c r="B34" t="n">
         <v>3035</v>
       </c>
@@ -3527,7 +3521,7 @@
       <c r="O34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
     </row>
-    <row r="35" hidden="1" ht="14.4" customHeight="1">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Mike/Jeff</t>
@@ -3594,7 +3588,7 @@
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" hidden="1" ht="14.4" customHeight="1">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="B36" t="n">
         <v>3031</v>
       </c>
@@ -3661,7 +3655,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" hidden="1" ht="14.4" customHeight="1">
+    <row r="37" ht="14.4" customHeight="1">
       <c r="B37" t="n">
         <v>3056</v>
       </c>
@@ -3688,7 +3682,7 @@
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" hidden="1" ht="57.6" customHeight="1">
+    <row r="38" ht="57.6" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3756,7 +3750,7 @@
         </is>
       </c>
     </row>
-    <row r="39" hidden="1" ht="28.8" customHeight="1">
+    <row r="39" ht="28.8" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3828,7 +3822,7 @@
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
     </row>
-    <row r="40" hidden="1" ht="43.2" customHeight="1">
+    <row r="40" ht="43.2" customHeight="1">
       <c r="B40" t="n">
         <v>3035</v>
       </c>
@@ -3872,7 +3866,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" hidden="1" ht="28.8" customHeight="1">
+    <row r="41" ht="28.8" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3945,7 +3939,7 @@
       </c>
       <c r="Q41" s="4" t="n"/>
     </row>
-    <row r="42" hidden="1" ht="43.2" customHeight="1">
+    <row r="42" ht="43.2" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
@@ -3984,7 +3978,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" hidden="1" ht="14.4" customHeight="1">
+    <row r="43" ht="14.4" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
@@ -4017,7 +4011,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" hidden="1" ht="41.4" customHeight="1">
+    <row r="44" ht="41.4" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4077,7 +4071,7 @@
       <c r="O44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45" hidden="1" ht="28.8" customHeight="1">
+    <row r="45" ht="28.8" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4197,7 +4191,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" hidden="1" ht="43.2" customHeight="1">
+    <row r="47" ht="43.2" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>US</t>
@@ -4236,7 +4230,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48" hidden="1" ht="43.2" customHeight="1">
+    <row r="48" ht="43.2" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>US</t>
@@ -4280,7 +4274,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" hidden="1" ht="14.4" customHeight="1">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="B49" s="130" t="n">
         <v>3041</v>
       </c>
@@ -4342,7 +4336,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" hidden="1" ht="43.2" customHeight="1">
+    <row r="50" ht="43.2" customHeight="1">
       <c r="B50" t="n">
         <v>3063</v>
       </c>
@@ -4376,7 +4370,7 @@
       <c r="O50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
     </row>
-    <row r="51" hidden="1" ht="14.4" customHeight="1">
+    <row r="51" ht="14.4" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4403,7 +4397,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="14.4" customHeight="1">
+    <row r="52" ht="14.4" customHeight="1">
       <c r="B52" t="n">
         <v>3044</v>
       </c>
@@ -4455,7 +4449,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" hidden="1" ht="14.4" customHeight="1">
+    <row r="53" ht="14.4" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4482,7 +4476,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="14.4" customHeight="1">
+    <row r="54" ht="14.4" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4514,7 +4508,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" hidden="1" ht="14.4" customHeight="1">
+    <row r="55" ht="14.4" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4546,7 +4540,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" hidden="1" ht="14.4" customHeight="1">
+    <row r="56" ht="14.4" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4578,7 +4572,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="14.4" customHeight="1">
+    <row r="57" ht="14.4" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4610,7 +4604,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="14.4" customHeight="1">
+    <row r="58" ht="14.4" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4642,7 +4636,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" hidden="1" ht="14.4" customHeight="1">
+    <row r="59" ht="14.4" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4674,7 +4668,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="14.4" customHeight="1">
+    <row r="60" ht="14.4" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -4687,7 +4681,7 @@
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="23" t="n"/>
     </row>
-    <row r="61" hidden="1" ht="14.4" customHeight="1">
+    <row r="61" ht="14.4" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4719,7 +4713,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62" hidden="1" ht="14.4" customHeight="1">
+    <row r="62" ht="14.4" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4751,7 +4745,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" hidden="1" ht="14.4" customHeight="1">
+    <row r="63" ht="14.4" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4783,7 +4777,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" hidden="1" ht="14.4" customHeight="1">
+    <row r="64" ht="14.4" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4815,7 +4809,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" hidden="1" ht="14.4" customHeight="1">
+    <row r="65" ht="14.4" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4828,7 +4822,7 @@
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="23" t="n"/>
     </row>
-    <row r="66" hidden="1" ht="14.4" customHeight="1">
+    <row r="66" ht="14.4" customHeight="1">
       <c r="B66" s="131" t="inlineStr">
         <is>
           <t>----</t>
@@ -4852,7 +4846,7 @@
       <c r="O66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
     </row>
-    <row r="67" hidden="1" ht="14.4" customHeight="1">
+    <row r="67" ht="14.4" customHeight="1">
       <c r="B67" t="n">
         <v>3003</v>
       </c>
@@ -4860,7 +4854,7 @@
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="23" t="n"/>
     </row>
-    <row r="68" hidden="1" ht="14.4" customHeight="1">
+    <row r="68" ht="14.4" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>US</t>
@@ -4873,7 +4867,7 @@
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="23" t="n"/>
     </row>
-    <row r="69" hidden="1" ht="14.4" customHeight="1">
+    <row r="69" ht="14.4" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>US</t>
@@ -4903,7 +4897,7 @@
       <c r="Q69" s="108" t="n"/>
       <c r="R69" s="66" t="n"/>
     </row>
-    <row r="70" hidden="1" ht="43.2" customHeight="1">
+    <row r="70" ht="43.2" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4942,7 +4936,7 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" hidden="1" ht="14.4" customHeight="1">
+    <row r="71" ht="14.4" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>US</t>
@@ -4968,7 +4962,7 @@
       <c r="Q71" s="108" t="n"/>
       <c r="R71" s="66" t="n"/>
     </row>
-    <row r="72" hidden="1" ht="14.4" customHeight="1">
+    <row r="72" ht="14.4" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5000,7 +4994,7 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" hidden="1" ht="14.4" customHeight="1">
+    <row r="73" ht="14.4" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>US</t>
@@ -5026,7 +5020,7 @@
       <c r="Q73" s="108" t="n"/>
       <c r="R73" s="66" t="n"/>
     </row>
-    <row r="74" hidden="1" ht="14.4" customHeight="1">
+    <row r="74" ht="14.4" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5058,7 +5052,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" hidden="1" ht="14.4" customHeight="1">
+    <row r="75" ht="14.4" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5095,7 +5089,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="43.2" customHeight="1">
+    <row r="76" ht="43.2" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>US</t>
@@ -5109,7 +5103,7 @@
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="23" t="n"/>
     </row>
-    <row r="77" hidden="1" ht="14.4" customHeight="1">
+    <row r="77" ht="14.4" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5133,7 +5127,7 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" hidden="1" ht="14.4" customHeight="1">
+    <row r="78" ht="14.4" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5167,7 +5161,7 @@
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" hidden="1" ht="57.6" customHeight="1">
+    <row r="79" ht="57.6" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5206,7 +5200,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" hidden="1" ht="43.2" customHeight="1">
+    <row r="80" ht="43.2" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5245,7 +5239,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" hidden="1" ht="28.8" customHeight="1">
+    <row r="81" ht="28.8" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5317,7 +5311,7 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" hidden="1" ht="14.4" customHeight="1">
+    <row r="82" ht="14.4" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>US</t>
@@ -5339,7 +5333,7 @@
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" hidden="1" ht="14.4" customHeight="1">
+    <row r="83" ht="14.4" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>US</t>
@@ -5356,3108 +5350,3258 @@
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" hidden="1" ht="14.4" customHeight="1">
+    <row r="84" ht="14.4" customHeight="1">
       <c r="B84" t="n">
         <v>3071</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" hidden="1" ht="14.4" customHeight="1">
+    <row r="85" ht="14.4" customHeight="1">
       <c r="B85" t="n">
         <v>3072</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" hidden="1" ht="14.4" customHeight="1">
+    <row r="86" ht="14.4" customHeight="1">
       <c r="B86" t="n">
         <v>3073</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" hidden="1" ht="14.4" customHeight="1">
+    <row r="87" ht="14.4" customHeight="1">
       <c r="B87" t="n">
         <v>3074</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" hidden="1" ht="14.4" customHeight="1">
+    <row r="88" ht="14.4" customHeight="1">
       <c r="B88" t="n">
         <v>3075</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" hidden="1" ht="14.4" customHeight="1">
+    <row r="89" ht="14.4" customHeight="1">
       <c r="B89" t="n">
         <v>3076</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" hidden="1" ht="14.4" customHeight="1">
+    <row r="90" ht="14.4" customHeight="1">
       <c r="B90" t="n">
         <v>3077</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" hidden="1" ht="14.4" customHeight="1">
+    <row r="91" ht="14.4" customHeight="1">
       <c r="B91" t="n">
         <v>3078</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" hidden="1" ht="14.4" customHeight="1">
+    <row r="92" ht="14.4" customHeight="1">
       <c r="B92" t="n">
         <v>3079</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" hidden="1" ht="14.4" customHeight="1">
+    <row r="93" ht="14.4" customHeight="1">
       <c r="B93" t="n">
         <v>3080</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" hidden="1" ht="14.4" customHeight="1">
+    <row r="94" ht="14.4" customHeight="1">
       <c r="B94" t="n">
         <v>3081</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" hidden="1" ht="14.4" customHeight="1">
+    <row r="95" ht="14.4" customHeight="1">
       <c r="B95" t="n">
         <v>3082</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" hidden="1" ht="14.4" customHeight="1">
+    <row r="96" ht="14.4" customHeight="1">
       <c r="B96" t="n">
         <v>3083</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" hidden="1" ht="14.4" customHeight="1">
+    <row r="97" ht="14.4" customHeight="1">
       <c r="B97" t="n">
         <v>3084</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" hidden="1" ht="14.4" customHeight="1">
+    <row r="98" ht="14.4" customHeight="1">
       <c r="B98" t="n">
         <v>3085</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" hidden="1" ht="14.4" customHeight="1">
+    <row r="99" ht="14.4" customHeight="1">
       <c r="B99" t="n">
         <v>3086</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" hidden="1" ht="14.4" customHeight="1">
+    <row r="100" ht="14.4" customHeight="1">
       <c r="B100" t="n">
         <v>3087</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" hidden="1" ht="14.4" customHeight="1">
+    <row r="101" ht="14.4" customHeight="1">
       <c r="B101" t="n">
         <v>3088</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" hidden="1" ht="14.4" customHeight="1">
+    <row r="102" ht="14.4" customHeight="1">
       <c r="B102" t="n">
         <v>3089</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" hidden="1" ht="14.4" customHeight="1">
+    <row r="103" ht="14.4" customHeight="1">
       <c r="B103" t="n">
         <v>3090</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" hidden="1" ht="14.4" customHeight="1">
+    <row r="104" ht="14.4" customHeight="1">
       <c r="B104" t="n">
         <v>3091</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" hidden="1" ht="14.4" customHeight="1">
+    <row r="105" ht="14.4" customHeight="1">
       <c r="B105" t="n">
         <v>3092</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" hidden="1" ht="14.4" customHeight="1">
+    <row r="106" ht="14.4" customHeight="1">
       <c r="B106" t="n">
         <v>3093</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" hidden="1" ht="14.4" customHeight="1">
+    <row r="107" ht="14.4" customHeight="1">
       <c r="B107" t="n">
         <v>3094</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" hidden="1" ht="14.4" customHeight="1">
+    <row r="108" ht="14.4" customHeight="1">
       <c r="B108" t="n">
         <v>3095</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" hidden="1" ht="14.4" customHeight="1">
+    <row r="109" ht="14.4" customHeight="1">
       <c r="B109" t="n">
         <v>3096</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" hidden="1" ht="14.4" customHeight="1">
+    <row r="110" ht="14.4" customHeight="1">
       <c r="B110" t="n">
         <v>3097</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" hidden="1" ht="14.4" customHeight="1">
+    <row r="111" ht="14.4" customHeight="1">
       <c r="B111" t="n">
         <v>3098</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" hidden="1" ht="14.4" customHeight="1">
+    <row r="112" ht="14.4" customHeight="1">
       <c r="B112" t="n">
         <v>3099</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" hidden="1" ht="14.4" customHeight="1">
+    <row r="113" ht="14.4" customHeight="1">
       <c r="B113" t="n">
         <v>3100</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" hidden="1" ht="14.4" customHeight="1">
+    <row r="114" ht="14.4" customHeight="1">
       <c r="B114" t="n">
         <v>3101</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" hidden="1" ht="14.4" customHeight="1">
+    <row r="115" ht="14.4" customHeight="1">
       <c r="B115" t="n">
         <v>3102</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" hidden="1" ht="14.4" customHeight="1">
+    <row r="116" ht="14.4" customHeight="1">
       <c r="B116" t="n">
         <v>3103</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" hidden="1" ht="14.4" customHeight="1">
+    <row r="117" ht="14.4" customHeight="1">
       <c r="B117" t="n">
         <v>3104</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" hidden="1" ht="14.4" customHeight="1">
+    <row r="118" ht="14.4" customHeight="1">
       <c r="B118" t="n">
         <v>3105</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" hidden="1" ht="14.4" customHeight="1">
+    <row r="119" ht="14.4" customHeight="1">
       <c r="B119" t="n">
         <v>3106</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" hidden="1" ht="14.4" customHeight="1">
+    <row r="120" ht="14.4" customHeight="1">
       <c r="B120" t="n">
         <v>3107</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" hidden="1" ht="14.4" customHeight="1">
+    <row r="121" ht="14.4" customHeight="1">
       <c r="B121" t="n">
         <v>3108</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" hidden="1" ht="14.4" customHeight="1">
+    <row r="122" ht="14.4" customHeight="1">
       <c r="B122" t="n">
         <v>3109</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" hidden="1" ht="14.4" customHeight="1">
+    <row r="123" ht="14.4" customHeight="1">
       <c r="B123" t="n">
         <v>3110</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" hidden="1" ht="14.4" customHeight="1">
+    <row r="124" ht="14.4" customHeight="1">
       <c r="B124" t="n">
         <v>3111</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" hidden="1" ht="14.4" customHeight="1">
+    <row r="125" ht="14.4" customHeight="1">
       <c r="B125" t="n">
         <v>3112</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" hidden="1" ht="14.4" customHeight="1">
+    <row r="126" ht="14.4" customHeight="1">
       <c r="B126" t="n">
         <v>3113</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" hidden="1" ht="14.4" customHeight="1">
+    <row r="127" ht="14.4" customHeight="1">
       <c r="B127" t="n">
         <v>3114</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" hidden="1" ht="14.4" customHeight="1">
+    <row r="128" ht="14.4" customHeight="1">
       <c r="B128" t="n">
         <v>3115</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" hidden="1" ht="14.4" customHeight="1">
+    <row r="129" ht="14.4" customHeight="1">
       <c r="B129" t="n">
         <v>3116</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" hidden="1" ht="14.4" customHeight="1">
+    <row r="130" ht="14.4" customHeight="1">
       <c r="B130" t="n">
         <v>3117</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" hidden="1" ht="14.4" customHeight="1">
+    <row r="131" ht="14.4" customHeight="1">
       <c r="B131" t="n">
         <v>3118</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" hidden="1" ht="14.4" customHeight="1">
+    <row r="132" ht="14.4" customHeight="1">
       <c r="B132" t="n">
         <v>3119</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" hidden="1" ht="14.4" customHeight="1">
+    <row r="133" ht="14.4" customHeight="1">
       <c r="B133" t="n">
         <v>3120</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" hidden="1" ht="14.4" customHeight="1">
+    <row r="134" ht="14.4" customHeight="1">
       <c r="B134" t="n">
         <v>3121</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" hidden="1" ht="14.4" customHeight="1">
+    <row r="135" ht="14.4" customHeight="1">
       <c r="B135" t="n">
         <v>3122</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" hidden="1" ht="14.4" customHeight="1">
+    <row r="136" ht="14.4" customHeight="1">
       <c r="B136" t="n">
         <v>3123</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" hidden="1" ht="14.4" customHeight="1">
+    <row r="137" ht="14.4" customHeight="1">
       <c r="B137" t="n">
         <v>3124</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" hidden="1" ht="14.4" customHeight="1">
+    <row r="138" ht="14.4" customHeight="1">
       <c r="B138" t="n">
         <v>3125</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" hidden="1" ht="14.4" customHeight="1">
+    <row r="139" ht="14.4" customHeight="1">
       <c r="B139" t="n">
         <v>3126</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" hidden="1" ht="14.4" customHeight="1">
+    <row r="140" ht="14.4" customHeight="1">
       <c r="B140" t="n">
         <v>3127</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" hidden="1" ht="14.4" customHeight="1">
+    <row r="141" ht="14.4" customHeight="1">
       <c r="B141" t="n">
         <v>3128</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" hidden="1" ht="14.4" customHeight="1">
+    <row r="142" ht="14.4" customHeight="1">
       <c r="B142" t="n">
         <v>3129</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" hidden="1" ht="14.4" customHeight="1">
+    <row r="143" ht="14.4" customHeight="1">
       <c r="B143" t="n">
         <v>3130</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" hidden="1" ht="14.4" customHeight="1">
+    <row r="144" ht="14.4" customHeight="1">
       <c r="B144" t="n">
         <v>3131</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" hidden="1" ht="14.4" customHeight="1">
+    <row r="145" ht="14.4" customHeight="1">
       <c r="B145" t="n">
         <v>3132</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" hidden="1" ht="14.4" customHeight="1">
+    <row r="146" ht="14.4" customHeight="1">
       <c r="B146" t="n">
         <v>3133</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" hidden="1" ht="14.4" customHeight="1">
+    <row r="147" ht="14.4" customHeight="1">
       <c r="B147" t="n">
         <v>3134</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" hidden="1" ht="14.4" customHeight="1">
+    <row r="148" ht="14.4" customHeight="1">
       <c r="B148" t="n">
         <v>3135</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" hidden="1" ht="14.4" customHeight="1">
+    <row r="149" ht="14.4" customHeight="1">
       <c r="B149" t="n">
         <v>3136</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" hidden="1" ht="14.4" customHeight="1">
+    <row r="150" ht="14.4" customHeight="1">
       <c r="B150" t="n">
         <v>3137</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" hidden="1" ht="14.4" customHeight="1">
+    <row r="151" ht="14.4" customHeight="1">
       <c r="B151" t="n">
         <v>3138</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" hidden="1" ht="14.4" customHeight="1">
+    <row r="152" ht="14.4" customHeight="1">
       <c r="B152" t="n">
         <v>3139</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" hidden="1" ht="14.4" customHeight="1">
+    <row r="153" ht="14.4" customHeight="1">
       <c r="B153" t="n">
         <v>3140</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" hidden="1" ht="14.4" customHeight="1">
+    <row r="154" ht="14.4" customHeight="1">
       <c r="B154" t="n">
         <v>3141</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" hidden="1" ht="14.4" customHeight="1">
+    <row r="155" ht="14.4" customHeight="1">
       <c r="B155" t="n">
         <v>3142</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" hidden="1" ht="14.4" customHeight="1">
+    <row r="156" ht="14.4" customHeight="1">
       <c r="B156" t="n">
         <v>3143</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" hidden="1" ht="14.4" customHeight="1">
+    <row r="157" ht="14.4" customHeight="1">
       <c r="B157" t="n">
         <v>3144</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" hidden="1" ht="14.4" customHeight="1">
+    <row r="158" ht="14.4" customHeight="1">
       <c r="B158" t="n">
         <v>3145</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" hidden="1" ht="14.4" customHeight="1">
+    <row r="159" ht="14.4" customHeight="1">
       <c r="B159" t="n">
         <v>3146</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" hidden="1" ht="14.4" customHeight="1">
+    <row r="160" ht="14.4" customHeight="1">
       <c r="B160" t="n">
         <v>3147</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" hidden="1" ht="14.4" customHeight="1">
+    <row r="161" ht="14.4" customHeight="1">
       <c r="B161" t="n">
         <v>3148</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" hidden="1" ht="14.4" customHeight="1">
+    <row r="162" ht="14.4" customHeight="1">
       <c r="B162" t="n">
         <v>3149</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" hidden="1" ht="14.4" customHeight="1">
+    <row r="163" ht="14.4" customHeight="1">
       <c r="B163" t="n">
         <v>3150</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" hidden="1" ht="14.4" customHeight="1">
+    <row r="164" ht="14.4" customHeight="1">
       <c r="B164" t="n">
         <v>3151</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" hidden="1" ht="14.4" customHeight="1">
+    <row r="165" ht="14.4" customHeight="1">
       <c r="B165" t="n">
         <v>3152</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" hidden="1" ht="14.4" customHeight="1">
+    <row r="166" ht="14.4" customHeight="1">
       <c r="B166" t="n">
         <v>3153</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" hidden="1" ht="14.4" customHeight="1">
+    <row r="167" ht="14.4" customHeight="1">
       <c r="B167" t="n">
         <v>3154</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" hidden="1" ht="14.4" customHeight="1">
+    <row r="168" ht="14.4" customHeight="1">
       <c r="B168" t="n">
         <v>3155</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" hidden="1" ht="14.4" customHeight="1">
+    <row r="169" ht="14.4" customHeight="1">
       <c r="B169" t="n">
         <v>3156</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" hidden="1" ht="14.4" customHeight="1">
+    <row r="170" ht="14.4" customHeight="1">
       <c r="B170" t="n">
         <v>3157</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" hidden="1" ht="14.4" customHeight="1">
+    <row r="171" ht="14.4" customHeight="1">
       <c r="B171" t="n">
         <v>3158</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" hidden="1" ht="14.4" customHeight="1">
+    <row r="172" ht="14.4" customHeight="1">
       <c r="B172" t="n">
         <v>3159</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" hidden="1" ht="14.4" customHeight="1">
+    <row r="173" ht="14.4" customHeight="1">
       <c r="B173" t="n">
         <v>3160</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" hidden="1" ht="14.4" customHeight="1">
+    <row r="174" ht="14.4" customHeight="1">
       <c r="B174" t="n">
         <v>3161</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" hidden="1" ht="14.4" customHeight="1">
+    <row r="175" ht="14.4" customHeight="1">
       <c r="B175" t="n">
         <v>3162</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" hidden="1" ht="14.4" customHeight="1">
+    <row r="176" ht="14.4" customHeight="1">
       <c r="B176" t="n">
         <v>3163</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" hidden="1" ht="14.4" customHeight="1">
+    <row r="177" ht="14.4" customHeight="1">
       <c r="B177" t="n">
         <v>3164</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" hidden="1" ht="14.4" customHeight="1">
+    <row r="178" ht="14.4" customHeight="1">
       <c r="B178" t="n">
         <v>3165</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" hidden="1" ht="14.4" customHeight="1">
+    <row r="179" ht="14.4" customHeight="1">
       <c r="B179" t="n">
         <v>3166</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" hidden="1" ht="14.4" customHeight="1">
+    <row r="180" ht="14.4" customHeight="1">
       <c r="B180" t="n">
         <v>3167</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" hidden="1" ht="14.4" customHeight="1">
+    <row r="181" ht="14.4" customHeight="1">
       <c r="B181" t="n">
         <v>3168</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" hidden="1" ht="14.4" customHeight="1">
+    <row r="182" ht="14.4" customHeight="1">
       <c r="B182" t="n">
         <v>3169</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" hidden="1" ht="14.4" customHeight="1">
+    <row r="183" ht="14.4" customHeight="1">
       <c r="B183" t="n">
         <v>3170</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" hidden="1" ht="14.4" customHeight="1">
+    <row r="184" ht="14.4" customHeight="1">
       <c r="B184" t="n">
         <v>3171</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" hidden="1" ht="14.4" customHeight="1">
+    <row r="185" ht="14.4" customHeight="1">
       <c r="B185" t="n">
         <v>3172</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" hidden="1" ht="14.4" customHeight="1">
+    <row r="186" ht="14.4" customHeight="1">
       <c r="B186" t="n">
         <v>3173</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" hidden="1" ht="14.4" customHeight="1">
+    <row r="187" ht="14.4" customHeight="1">
       <c r="B187" t="n">
         <v>3174</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" hidden="1" ht="14.4" customHeight="1">
+    <row r="188" ht="14.4" customHeight="1">
       <c r="B188" t="n">
         <v>3175</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" hidden="1" ht="14.4" customHeight="1">
+    <row r="189" ht="14.4" customHeight="1">
       <c r="B189" t="n">
         <v>3176</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" hidden="1" ht="14.4" customHeight="1">
+    <row r="190" ht="14.4" customHeight="1">
       <c r="B190" t="n">
         <v>3177</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" hidden="1" ht="14.4" customHeight="1">
+    <row r="191" ht="14.4" customHeight="1">
       <c r="B191" t="n">
         <v>3178</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" hidden="1" ht="14.4" customHeight="1">
+    <row r="192" ht="14.4" customHeight="1">
       <c r="B192" t="n">
         <v>3179</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" hidden="1" ht="14.4" customHeight="1">
+    <row r="193" ht="14.4" customHeight="1">
       <c r="B193" t="n">
         <v>3180</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" hidden="1" ht="14.4" customHeight="1">
+    <row r="194" ht="14.4" customHeight="1">
       <c r="B194" t="n">
         <v>3181</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" hidden="1" ht="14.4" customHeight="1">
+    <row r="195" ht="14.4" customHeight="1">
       <c r="B195" t="n">
         <v>3182</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" hidden="1" ht="14.4" customHeight="1">
+    <row r="196" ht="14.4" customHeight="1">
       <c r="B196" t="n">
         <v>3183</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" hidden="1" ht="14.4" customHeight="1">
+    <row r="197" ht="14.4" customHeight="1">
       <c r="B197" t="n">
         <v>3184</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" hidden="1" ht="14.4" customHeight="1">
+    <row r="198" ht="14.4" customHeight="1">
       <c r="B198" t="n">
         <v>3185</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" hidden="1" ht="14.4" customHeight="1">
+    <row r="199" ht="14.4" customHeight="1">
       <c r="B199" t="n">
         <v>3186</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" hidden="1" ht="14.4" customHeight="1">
+    <row r="200" ht="14.4" customHeight="1">
       <c r="B200" t="n">
         <v>3187</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" hidden="1" ht="14.4" customHeight="1">
+    <row r="201" ht="14.4" customHeight="1">
       <c r="B201" t="n">
         <v>3188</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" hidden="1" ht="14.4" customHeight="1">
+    <row r="202" ht="14.4" customHeight="1">
       <c r="B202" t="n">
         <v>3189</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" hidden="1" ht="14.4" customHeight="1">
+    <row r="203" ht="14.4" customHeight="1">
       <c r="B203" t="n">
         <v>3190</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" hidden="1" ht="14.4" customHeight="1">
+    <row r="204" ht="14.4" customHeight="1">
       <c r="B204" t="n">
         <v>3191</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" hidden="1" ht="14.4" customHeight="1">
+    <row r="205" ht="14.4" customHeight="1">
       <c r="B205" t="n">
         <v>3192</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" hidden="1" ht="14.4" customHeight="1">
+    <row r="206" ht="14.4" customHeight="1">
       <c r="B206" t="n">
         <v>3193</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" hidden="1" ht="14.4" customHeight="1">
+    <row r="207" ht="14.4" customHeight="1">
       <c r="B207" t="n">
         <v>3194</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" hidden="1" ht="14.4" customHeight="1">
+    <row r="208" ht="14.4" customHeight="1">
       <c r="B208" t="n">
         <v>3195</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" hidden="1" ht="14.4" customHeight="1">
+    <row r="209" ht="14.4" customHeight="1">
       <c r="B209" t="n">
         <v>3196</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" hidden="1" ht="14.4" customHeight="1">
+    <row r="210" ht="14.4" customHeight="1">
       <c r="B210" t="n">
         <v>3197</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" hidden="1" ht="14.4" customHeight="1">
+    <row r="211" ht="14.4" customHeight="1">
       <c r="B211" t="n">
         <v>3198</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" hidden="1" ht="14.4" customHeight="1">
+    <row r="212" ht="14.4" customHeight="1">
       <c r="B212" t="n">
         <v>3199</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" hidden="1" ht="14.4" customHeight="1">
+    <row r="213" ht="14.4" customHeight="1">
       <c r="B213" t="n">
         <v>3200</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" hidden="1" ht="14.4" customHeight="1">
+    <row r="214" ht="14.4" customHeight="1">
       <c r="B214" t="n">
         <v>3201</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" hidden="1" ht="14.4" customHeight="1">
+    <row r="215" ht="14.4" customHeight="1">
       <c r="B215" t="n">
         <v>3202</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" hidden="1" ht="14.4" customHeight="1">
+    <row r="216" ht="14.4" customHeight="1">
       <c r="B216" t="n">
         <v>3203</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" hidden="1" ht="14.4" customHeight="1">
+    <row r="217" ht="14.4" customHeight="1">
       <c r="B217" t="n">
         <v>3204</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" hidden="1" ht="14.4" customHeight="1">
+    <row r="218" ht="14.4" customHeight="1">
       <c r="B218" t="n">
         <v>3205</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" hidden="1" ht="14.4" customHeight="1">
+    <row r="219" ht="14.4" customHeight="1">
       <c r="B219" t="n">
         <v>3206</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" hidden="1" ht="14.4" customHeight="1">
+    <row r="220" ht="14.4" customHeight="1">
       <c r="B220" t="n">
         <v>3207</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" hidden="1" ht="14.4" customHeight="1">
+    <row r="221" ht="14.4" customHeight="1">
       <c r="B221" t="n">
         <v>3208</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" hidden="1" ht="14.4" customHeight="1">
+    <row r="222" ht="14.4" customHeight="1">
       <c r="B222" t="n">
         <v>3209</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" hidden="1" ht="14.4" customHeight="1">
+    <row r="223" ht="14.4" customHeight="1">
       <c r="B223" t="n">
         <v>3210</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" hidden="1" ht="14.4" customHeight="1">
+    <row r="224" ht="14.4" customHeight="1">
       <c r="B224" t="n">
         <v>3211</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" hidden="1" ht="14.4" customHeight="1">
+    <row r="225" ht="14.4" customHeight="1">
       <c r="B225" t="n">
         <v>3212</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" hidden="1" ht="14.4" customHeight="1">
+    <row r="226" ht="14.4" customHeight="1">
       <c r="B226" t="n">
         <v>3213</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" hidden="1" ht="14.4" customHeight="1">
+    <row r="227" ht="14.4" customHeight="1">
       <c r="B227" t="n">
         <v>3214</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" hidden="1" ht="14.4" customHeight="1">
+    <row r="228" ht="14.4" customHeight="1">
       <c r="B228" t="n">
         <v>3215</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" hidden="1" ht="14.4" customHeight="1">
+    <row r="229" ht="14.4" customHeight="1">
       <c r="B229" t="n">
         <v>3216</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" hidden="1" ht="14.4" customHeight="1">
+    <row r="230" ht="14.4" customHeight="1">
       <c r="B230" t="n">
         <v>3217</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" hidden="1" ht="14.4" customHeight="1">
+    <row r="231" ht="14.4" customHeight="1">
       <c r="B231" t="n">
         <v>3218</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" hidden="1" ht="14.4" customHeight="1">
+    <row r="232" ht="14.4" customHeight="1">
       <c r="B232" t="n">
         <v>3219</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" hidden="1" ht="14.4" customHeight="1">
+    <row r="233" ht="14.4" customHeight="1">
       <c r="B233" t="n">
         <v>3220</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" hidden="1" ht="14.4" customHeight="1">
+    <row r="234" ht="14.4" customHeight="1">
       <c r="B234" t="n">
         <v>3221</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" hidden="1" ht="14.4" customHeight="1">
+    <row r="235" ht="14.4" customHeight="1">
       <c r="B235" t="n">
         <v>3222</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" hidden="1" ht="14.4" customHeight="1">
+    <row r="236" ht="14.4" customHeight="1">
       <c r="B236" t="n">
         <v>3223</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" hidden="1" ht="14.4" customHeight="1">
+    <row r="237" ht="14.4" customHeight="1">
       <c r="B237" t="n">
         <v>3224</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" hidden="1" ht="14.4" customHeight="1">
+    <row r="238" ht="14.4" customHeight="1">
       <c r="B238" t="n">
         <v>3225</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" hidden="1" ht="14.4" customHeight="1">
+    <row r="239" ht="14.4" customHeight="1">
       <c r="B239" t="n">
         <v>3226</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" hidden="1" ht="14.4" customHeight="1">
+    <row r="240" ht="14.4" customHeight="1">
       <c r="B240" t="n">
         <v>3227</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" hidden="1" ht="14.4" customHeight="1">
+    <row r="241" ht="14.4" customHeight="1">
       <c r="B241" t="n">
         <v>3228</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" hidden="1" ht="14.4" customHeight="1">
+    <row r="242" ht="14.4" customHeight="1">
       <c r="B242" t="n">
         <v>3229</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" hidden="1" ht="14.4" customHeight="1">
+    <row r="243" ht="14.4" customHeight="1">
       <c r="B243" t="n">
         <v>3230</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" hidden="1" ht="14.4" customHeight="1">
+    <row r="244" ht="14.4" customHeight="1">
       <c r="B244" t="n">
         <v>3231</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" hidden="1" ht="14.4" customHeight="1">
+    <row r="245" ht="14.4" customHeight="1">
       <c r="B245" t="n">
         <v>3232</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" hidden="1" ht="14.4" customHeight="1">
+    <row r="246" ht="14.4" customHeight="1">
       <c r="B246" t="n">
         <v>3233</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" hidden="1" ht="14.4" customHeight="1">
+    <row r="247" ht="14.4" customHeight="1">
       <c r="B247" t="n">
         <v>3234</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" hidden="1" ht="14.4" customHeight="1">
+    <row r="248" ht="14.4" customHeight="1">
       <c r="B248" t="n">
         <v>3235</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" hidden="1" ht="14.4" customHeight="1">
+    <row r="249" ht="14.4" customHeight="1">
       <c r="B249" t="n">
         <v>3236</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" hidden="1" ht="14.4" customHeight="1">
+    <row r="250" ht="14.4" customHeight="1">
       <c r="B250" t="n">
         <v>3237</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" hidden="1" ht="14.4" customHeight="1">
+    <row r="251" ht="14.4" customHeight="1">
       <c r="B251" t="n">
         <v>3238</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" hidden="1" ht="14.4" customHeight="1">
+    <row r="252" ht="14.4" customHeight="1">
       <c r="B252" t="n">
         <v>3239</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" hidden="1" ht="14.4" customHeight="1">
+    <row r="253" ht="14.4" customHeight="1">
       <c r="B253" t="n">
         <v>3240</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" hidden="1" ht="14.4" customHeight="1">
+    <row r="254" ht="14.4" customHeight="1">
       <c r="B254" t="n">
         <v>3241</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" hidden="1" ht="14.4" customHeight="1">
+    <row r="255" ht="14.4" customHeight="1">
       <c r="B255" t="n">
         <v>3242</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" hidden="1" ht="14.4" customHeight="1">
+    <row r="256" ht="14.4" customHeight="1">
       <c r="B256" t="n">
         <v>3243</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" hidden="1" ht="14.4" customHeight="1">
+    <row r="257" ht="14.4" customHeight="1">
       <c r="B257" t="n">
         <v>3244</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" hidden="1" ht="14.4" customHeight="1">
+    <row r="258" ht="14.4" customHeight="1">
       <c r="B258" t="n">
         <v>3245</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" hidden="1" ht="14.4" customHeight="1">
+    <row r="259" ht="14.4" customHeight="1">
       <c r="B259" t="n">
         <v>3246</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" hidden="1" ht="14.4" customHeight="1">
+    <row r="260" ht="14.4" customHeight="1">
       <c r="B260" t="n">
         <v>3247</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" hidden="1" ht="14.4" customHeight="1">
+    <row r="261" ht="14.4" customHeight="1">
       <c r="B261" t="n">
         <v>3248</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" hidden="1" ht="14.4" customHeight="1">
+    <row r="262" ht="14.4" customHeight="1">
       <c r="B262" t="n">
         <v>3249</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" hidden="1" ht="14.4" customHeight="1">
+    <row r="263" ht="14.4" customHeight="1">
       <c r="B263" t="n">
         <v>3250</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" hidden="1" ht="14.4" customHeight="1">
+    <row r="264" ht="14.4" customHeight="1">
       <c r="B264" t="n">
         <v>3251</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" hidden="1" ht="14.4" customHeight="1">
+    <row r="265" ht="14.4" customHeight="1">
       <c r="B265" t="n">
         <v>3252</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" hidden="1" ht="14.4" customHeight="1">
+    <row r="266" ht="14.4" customHeight="1">
       <c r="B266" t="n">
         <v>3253</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" hidden="1" ht="14.4" customHeight="1">
+    <row r="267" ht="14.4" customHeight="1">
       <c r="B267" t="n">
         <v>3254</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" hidden="1" ht="14.4" customHeight="1">
+    <row r="268" ht="14.4" customHeight="1">
       <c r="B268" t="n">
         <v>3255</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" hidden="1" ht="14.4" customHeight="1">
+    <row r="269" ht="14.4" customHeight="1">
       <c r="B269" t="n">
         <v>3256</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" hidden="1" ht="14.4" customHeight="1">
+    <row r="270" ht="14.4" customHeight="1">
       <c r="B270" t="n">
         <v>3257</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" hidden="1" ht="14.4" customHeight="1">
+    <row r="271" ht="14.4" customHeight="1">
       <c r="B271" t="n">
         <v>3258</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" hidden="1" ht="14.4" customHeight="1">
+    <row r="272" ht="14.4" customHeight="1">
       <c r="B272" t="n">
         <v>3259</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" hidden="1" ht="14.4" customHeight="1">
+    <row r="273" ht="14.4" customHeight="1">
       <c r="B273" t="n">
         <v>3260</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" hidden="1" ht="14.4" customHeight="1">
+    <row r="274" ht="14.4" customHeight="1">
       <c r="B274" t="n">
         <v>3261</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" hidden="1" ht="14.4" customHeight="1">
+    <row r="275" ht="14.4" customHeight="1">
       <c r="B275" t="n">
         <v>3262</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" hidden="1" ht="14.4" customHeight="1">
+    <row r="276" ht="14.4" customHeight="1">
       <c r="B276" t="n">
         <v>3263</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" hidden="1" ht="14.4" customHeight="1">
+    <row r="277" ht="14.4" customHeight="1">
       <c r="B277" t="n">
         <v>3264</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" hidden="1" ht="14.4" customHeight="1">
+    <row r="278" ht="14.4" customHeight="1">
       <c r="B278" t="n">
         <v>3265</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" hidden="1" ht="14.4" customHeight="1">
+    <row r="279" ht="14.4" customHeight="1">
       <c r="B279" t="n">
         <v>3266</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" hidden="1" ht="14.4" customHeight="1">
+    <row r="280" ht="14.4" customHeight="1">
       <c r="B280" t="n">
         <v>3267</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" hidden="1" ht="14.4" customHeight="1">
+    <row r="281" ht="14.4" customHeight="1">
       <c r="B281" t="n">
         <v>3268</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" hidden="1" ht="14.4" customHeight="1">
+    <row r="282" ht="14.4" customHeight="1">
       <c r="B282" t="n">
         <v>3269</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" hidden="1" ht="14.4" customHeight="1">
+    <row r="283" ht="14.4" customHeight="1">
       <c r="B283" t="n">
         <v>3270</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" hidden="1" ht="14.4" customHeight="1">
+    <row r="284" ht="14.4" customHeight="1">
       <c r="B284" t="n">
         <v>3271</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" hidden="1" ht="14.4" customHeight="1">
+    <row r="285" ht="14.4" customHeight="1">
       <c r="B285" t="n">
         <v>3272</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" hidden="1" ht="14.4" customHeight="1">
+    <row r="286" ht="14.4" customHeight="1">
       <c r="B286" t="n">
         <v>3273</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" hidden="1" ht="14.4" customHeight="1">
+    <row r="287" ht="14.4" customHeight="1">
       <c r="B287" t="n">
         <v>3274</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" hidden="1" ht="14.4" customHeight="1">
+    <row r="288" ht="14.4" customHeight="1">
       <c r="B288" t="n">
         <v>3275</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" hidden="1" ht="14.4" customHeight="1">
+    <row r="289" ht="14.4" customHeight="1">
       <c r="B289" t="n">
         <v>3276</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" hidden="1" ht="14.4" customHeight="1">
+    <row r="290" ht="14.4" customHeight="1">
       <c r="B290" t="n">
         <v>3277</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" hidden="1" ht="14.4" customHeight="1">
+    <row r="291" ht="14.4" customHeight="1">
       <c r="B291" t="n">
         <v>3278</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" hidden="1" ht="14.4" customHeight="1">
+    <row r="292" ht="14.4" customHeight="1">
       <c r="B292" t="n">
         <v>3279</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" hidden="1" ht="14.4" customHeight="1">
+    <row r="293" ht="14.4" customHeight="1">
       <c r="B293" t="n">
         <v>3280</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" hidden="1" ht="14.4" customHeight="1">
+    <row r="294" ht="14.4" customHeight="1">
       <c r="B294" t="n">
         <v>3281</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" hidden="1" ht="14.4" customHeight="1">
+    <row r="295" ht="14.4" customHeight="1">
       <c r="B295" t="n">
         <v>3282</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" hidden="1" ht="14.4" customHeight="1">
+    <row r="296" ht="14.4" customHeight="1">
       <c r="B296" t="n">
         <v>3283</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" hidden="1" ht="14.4" customHeight="1">
+    <row r="297" ht="14.4" customHeight="1">
       <c r="B297" t="n">
         <v>3284</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" hidden="1" ht="14.4" customHeight="1">
+    <row r="298" ht="14.4" customHeight="1">
       <c r="B298" t="n">
         <v>3285</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" hidden="1" ht="14.4" customHeight="1">
+    <row r="299" ht="14.4" customHeight="1">
       <c r="B299" t="n">
         <v>3286</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" hidden="1" ht="14.4" customHeight="1">
+    <row r="300" ht="14.4" customHeight="1">
       <c r="B300" t="n">
         <v>3287</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" hidden="1" ht="14.4" customHeight="1">
+    <row r="301" ht="14.4" customHeight="1">
       <c r="B301" t="n">
         <v>3288</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" hidden="1" ht="14.4" customHeight="1">
+    <row r="302" ht="14.4" customHeight="1">
       <c r="B302" t="n">
         <v>3289</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" hidden="1" ht="14.4" customHeight="1">
+    <row r="303" ht="14.4" customHeight="1">
       <c r="B303" t="n">
         <v>3290</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" hidden="1" ht="14.4" customHeight="1">
+    <row r="304" ht="14.4" customHeight="1">
       <c r="B304" t="n">
         <v>3291</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" hidden="1" ht="14.4" customHeight="1">
+    <row r="305" ht="14.4" customHeight="1">
       <c r="B305" t="n">
         <v>3292</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" hidden="1" ht="14.4" customHeight="1">
+    <row r="306" ht="14.4" customHeight="1">
       <c r="B306" t="n">
         <v>3293</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" hidden="1" ht="14.4" customHeight="1">
+    <row r="307" ht="14.4" customHeight="1">
       <c r="B307" t="n">
         <v>3294</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" hidden="1" ht="14.4" customHeight="1">
+    <row r="308" ht="14.4" customHeight="1">
       <c r="B308" t="n">
         <v>3295</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" hidden="1" ht="14.4" customHeight="1">
+    <row r="309" ht="14.4" customHeight="1">
       <c r="B309" t="n">
         <v>3296</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" hidden="1" ht="14.4" customHeight="1">
+    <row r="310" ht="14.4" customHeight="1">
       <c r="B310" t="n">
         <v>3297</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" hidden="1" ht="14.4" customHeight="1">
+    <row r="311" ht="14.4" customHeight="1">
       <c r="B311" t="n">
         <v>3298</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" hidden="1" ht="14.4" customHeight="1">
+    <row r="312" ht="14.4" customHeight="1">
       <c r="B312" t="n">
         <v>3299</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" hidden="1" ht="14.4" customHeight="1">
+    <row r="313" ht="14.4" customHeight="1">
       <c r="B313" t="n">
         <v>3300</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" hidden="1" ht="14.4" customHeight="1">
+    <row r="314" ht="14.4" customHeight="1">
       <c r="B314" t="n">
         <v>3301</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" hidden="1" ht="14.4" customHeight="1">
+    <row r="315" ht="14.4" customHeight="1">
       <c r="B315" t="n">
         <v>3302</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" hidden="1" ht="14.4" customHeight="1">
+    <row r="316" ht="14.4" customHeight="1">
       <c r="B316" t="n">
         <v>3303</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" hidden="1" ht="14.4" customHeight="1">
+    <row r="317" ht="14.4" customHeight="1">
       <c r="B317" t="n">
         <v>3304</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" hidden="1" ht="14.4" customHeight="1">
+    <row r="318" ht="14.4" customHeight="1">
       <c r="B318" t="n">
         <v>3305</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" hidden="1" ht="14.4" customHeight="1">
+    <row r="319" ht="14.4" customHeight="1">
       <c r="B319" t="n">
         <v>3306</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" hidden="1" ht="14.4" customHeight="1">
+    <row r="320" ht="14.4" customHeight="1">
       <c r="B320" t="n">
         <v>3307</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" hidden="1" ht="14.4" customHeight="1">
+    <row r="321" ht="14.4" customHeight="1">
       <c r="B321" t="n">
         <v>3308</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" hidden="1" ht="14.4" customHeight="1">
+    <row r="322" ht="14.4" customHeight="1">
       <c r="B322" t="n">
         <v>3309</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" hidden="1" ht="14.4" customHeight="1">
+    <row r="323" ht="14.4" customHeight="1">
       <c r="B323" t="n">
         <v>3310</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" hidden="1" ht="14.4" customHeight="1">
+    <row r="324" ht="14.4" customHeight="1">
       <c r="B324" t="n">
         <v>3311</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" hidden="1" ht="14.4" customHeight="1">
+    <row r="325" ht="14.4" customHeight="1">
       <c r="B325" t="n">
         <v>3312</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" hidden="1" ht="14.4" customHeight="1">
+    <row r="326" ht="14.4" customHeight="1">
       <c r="B326" t="n">
         <v>3313</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" hidden="1" ht="14.4" customHeight="1">
+    <row r="327" ht="14.4" customHeight="1">
       <c r="B327" t="n">
         <v>3314</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" hidden="1" ht="14.4" customHeight="1">
+    <row r="328" ht="14.4" customHeight="1">
       <c r="B328" t="n">
         <v>3315</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" hidden="1" ht="14.4" customHeight="1">
+    <row r="329" ht="14.4" customHeight="1">
       <c r="B329" t="n">
         <v>3316</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" hidden="1" ht="14.4" customHeight="1">
+    <row r="330" ht="14.4" customHeight="1">
       <c r="B330" t="n">
         <v>3317</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" hidden="1" ht="14.4" customHeight="1">
+    <row r="331" ht="14.4" customHeight="1">
       <c r="B331" t="n">
         <v>3318</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" hidden="1" ht="14.4" customHeight="1">
+    <row r="332" ht="14.4" customHeight="1">
       <c r="B332" t="n">
         <v>3319</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" hidden="1" ht="14.4" customHeight="1">
+    <row r="333" ht="14.4" customHeight="1">
       <c r="B333" t="n">
         <v>3320</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" hidden="1" ht="14.4" customHeight="1">
+    <row r="334" ht="14.4" customHeight="1">
       <c r="B334" t="n">
         <v>3321</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" hidden="1" ht="14.4" customHeight="1">
+    <row r="335" ht="14.4" customHeight="1">
       <c r="B335" t="n">
         <v>3322</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" hidden="1" ht="14.4" customHeight="1">
+    <row r="336" ht="14.4" customHeight="1">
       <c r="B336" t="n">
         <v>3323</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" hidden="1" ht="14.4" customHeight="1">
+    <row r="337" ht="14.4" customHeight="1">
       <c r="B337" t="n">
         <v>3324</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" hidden="1" ht="14.4" customHeight="1">
+    <row r="338" ht="14.4" customHeight="1">
       <c r="B338" t="n">
         <v>3325</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" hidden="1" ht="14.4" customHeight="1">
+    <row r="339" ht="14.4" customHeight="1">
       <c r="B339" t="n">
         <v>3326</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" hidden="1" ht="14.4" customHeight="1">
+    <row r="340" ht="14.4" customHeight="1">
       <c r="B340" t="n">
         <v>3327</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" hidden="1" ht="14.4" customHeight="1">
+    <row r="341" ht="14.4" customHeight="1">
       <c r="B341" t="n">
         <v>3328</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" hidden="1" ht="14.4" customHeight="1">
+    <row r="342" ht="14.4" customHeight="1">
       <c r="B342" t="n">
         <v>3329</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" hidden="1" ht="14.4" customHeight="1">
+    <row r="343" ht="14.4" customHeight="1">
       <c r="B343" t="n">
         <v>3330</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" hidden="1" ht="14.4" customHeight="1">
+    <row r="344" ht="14.4" customHeight="1">
       <c r="B344" t="n">
         <v>3331</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" hidden="1" ht="14.4" customHeight="1">
+    <row r="345" ht="14.4" customHeight="1">
       <c r="B345" t="n">
         <v>3332</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" hidden="1" ht="14.4" customHeight="1">
+    <row r="346" ht="14.4" customHeight="1">
       <c r="B346" t="n">
         <v>3333</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" hidden="1" ht="14.4" customHeight="1">
+    <row r="347" ht="14.4" customHeight="1">
       <c r="B347" t="n">
         <v>3334</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" hidden="1" ht="14.4" customHeight="1">
+    <row r="348" ht="14.4" customHeight="1">
       <c r="B348" t="n">
         <v>3335</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" hidden="1" ht="14.4" customHeight="1">
+    <row r="349" ht="14.4" customHeight="1">
       <c r="B349" t="n">
         <v>3336</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" hidden="1" ht="14.4" customHeight="1">
+    <row r="350" ht="14.4" customHeight="1">
       <c r="B350" t="n">
         <v>3337</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" hidden="1" ht="14.4" customHeight="1">
+    <row r="351" ht="14.4" customHeight="1">
       <c r="B351" t="n">
         <v>3338</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" hidden="1" ht="14.4" customHeight="1">
+    <row r="352" ht="14.4" customHeight="1">
       <c r="B352" t="n">
         <v>3339</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" hidden="1" ht="14.4" customHeight="1">
+    <row r="353" ht="14.4" customHeight="1">
       <c r="B353" t="n">
         <v>3340</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" hidden="1" ht="14.4" customHeight="1">
+    <row r="354" ht="14.4" customHeight="1">
       <c r="B354" t="n">
         <v>3341</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" hidden="1" ht="14.4" customHeight="1">
+    <row r="355" ht="14.4" customHeight="1">
       <c r="B355" t="n">
         <v>3342</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" hidden="1" ht="14.4" customHeight="1">
+    <row r="356" ht="14.4" customHeight="1">
       <c r="B356" t="n">
         <v>3343</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" hidden="1" ht="14.4" customHeight="1">
+    <row r="357" ht="14.4" customHeight="1">
       <c r="B357" t="n">
         <v>3344</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" hidden="1" ht="14.4" customHeight="1">
+    <row r="358" ht="14.4" customHeight="1">
       <c r="B358" t="n">
         <v>3345</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" hidden="1" ht="14.4" customHeight="1">
+    <row r="359" ht="14.4" customHeight="1">
       <c r="B359" t="n">
         <v>3346</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" hidden="1" ht="14.4" customHeight="1">
+    <row r="360" ht="14.4" customHeight="1">
       <c r="B360" t="n">
         <v>3347</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" hidden="1" ht="14.4" customHeight="1">
+    <row r="361" ht="14.4" customHeight="1">
       <c r="B361" t="n">
         <v>3348</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" hidden="1" ht="14.4" customHeight="1">
+    <row r="362" ht="14.4" customHeight="1">
       <c r="B362" t="n">
         <v>3349</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" hidden="1" ht="14.4" customHeight="1">
+    <row r="363" ht="14.4" customHeight="1">
       <c r="B363" t="n">
         <v>3350</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" hidden="1" ht="14.4" customHeight="1">
+    <row r="364" ht="14.4" customHeight="1">
       <c r="B364" t="n">
         <v>3351</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" hidden="1" ht="14.4" customHeight="1">
+    <row r="365" ht="14.4" customHeight="1">
       <c r="B365" t="n">
         <v>3352</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" hidden="1" ht="14.4" customHeight="1">
+    <row r="366" ht="14.4" customHeight="1">
       <c r="B366" t="n">
         <v>3353</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" hidden="1" ht="14.4" customHeight="1">
+    <row r="367" ht="14.4" customHeight="1">
       <c r="B367" t="n">
         <v>3354</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" hidden="1" ht="14.4" customHeight="1">
+    <row r="368" ht="14.4" customHeight="1">
       <c r="B368" t="n">
         <v>3355</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" hidden="1" ht="14.4" customHeight="1">
+    <row r="369" ht="14.4" customHeight="1">
       <c r="B369" t="n">
         <v>3356</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" hidden="1" ht="14.4" customHeight="1">
+    <row r="370" ht="14.4" customHeight="1">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B370" t="n">
         <v>3357</v>
       </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Unilever FOOD</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
+      </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" hidden="1" ht="14.4" customHeight="1">
+    <row r="371" ht="14.4" customHeight="1">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B371" t="n">
         <v>3358</v>
       </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Unilever HOME CARE</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
+      </c>
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" hidden="1" ht="14.4" customHeight="1">
+    <row r="372" ht="14.4" customHeight="1">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B372" t="n">
         <v>3359</v>
       </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Unilever Personal Care</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
+      </c>
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" hidden="1" ht="14.4" customHeight="1">
+    <row r="373" ht="14.4" customHeight="1">
       <c r="B373" t="n">
         <v>3360</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" hidden="1" ht="14.4" customHeight="1">
+    <row r="374" ht="14.4" customHeight="1">
       <c r="B374" t="n">
         <v>3361</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" hidden="1" ht="14.4" customHeight="1">
+    <row r="375" ht="14.4" customHeight="1">
       <c r="B375" t="n">
         <v>3362</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" hidden="1" ht="14.4" customHeight="1">
+    <row r="376" ht="14.4" customHeight="1">
       <c r="B376" t="n">
         <v>3363</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" hidden="1" ht="14.4" customHeight="1">
+    <row r="377" ht="14.4" customHeight="1">
       <c r="B377" t="n">
         <v>3364</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" hidden="1" ht="14.4" customHeight="1">
+    <row r="378" ht="14.4" customHeight="1">
       <c r="B378" t="n">
         <v>3365</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" hidden="1" ht="14.4" customHeight="1">
+    <row r="379" ht="14.4" customHeight="1">
       <c r="B379" t="n">
         <v>3366</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" hidden="1" ht="14.4" customHeight="1">
+    <row r="380" ht="14.4" customHeight="1">
       <c r="B380" t="n">
         <v>3367</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" hidden="1" ht="14.4" customHeight="1">
+    <row r="381" ht="14.4" customHeight="1">
       <c r="B381" t="n">
         <v>3368</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" hidden="1" ht="14.4" customHeight="1">
+    <row r="382" ht="14.4" customHeight="1">
       <c r="B382" t="n">
         <v>3369</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" hidden="1" ht="14.4" customHeight="1">
+    <row r="383" ht="14.4" customHeight="1">
       <c r="B383" t="n">
         <v>3370</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" hidden="1" ht="14.4" customHeight="1">
+    <row r="384" ht="14.4" customHeight="1">
       <c r="B384" t="n">
         <v>3371</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" hidden="1" ht="14.4" customHeight="1">
+    <row r="385" ht="14.4" customHeight="1">
       <c r="B385" t="n">
         <v>3372</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" hidden="1" ht="14.4" customHeight="1">
+    <row r="386" ht="14.4" customHeight="1">
       <c r="B386" t="n">
         <v>3373</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" hidden="1" ht="14.4" customHeight="1">
+    <row r="387" ht="14.4" customHeight="1">
       <c r="B387" t="n">
         <v>3374</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" hidden="1" ht="14.4" customHeight="1">
+    <row r="388" ht="14.4" customHeight="1">
       <c r="B388" t="n">
         <v>3375</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" hidden="1" ht="14.4" customHeight="1">
+    <row r="389" ht="14.4" customHeight="1">
       <c r="B389" t="n">
         <v>3376</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" hidden="1" ht="14.4" customHeight="1">
+    <row r="390" ht="14.4" customHeight="1">
       <c r="B390" t="n">
         <v>3377</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" hidden="1" ht="14.4" customHeight="1">
+    <row r="391" ht="14.4" customHeight="1">
       <c r="B391" t="n">
         <v>3378</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" hidden="1" ht="14.4" customHeight="1">
+    <row r="392" ht="14.4" customHeight="1">
       <c r="B392" t="n">
         <v>3379</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" hidden="1" ht="14.4" customHeight="1">
+    <row r="393" ht="14.4" customHeight="1">
       <c r="B393" t="n">
         <v>3380</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" hidden="1" ht="14.4" customHeight="1">
+    <row r="394" ht="14.4" customHeight="1">
       <c r="B394" t="n">
         <v>3381</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" hidden="1" ht="14.4" customHeight="1">
+    <row r="395" ht="14.4" customHeight="1">
       <c r="B395" t="n">
         <v>3382</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" hidden="1" ht="14.4" customHeight="1">
+    <row r="396" ht="14.4" customHeight="1">
       <c r="B396" t="n">
         <v>3383</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" hidden="1" ht="14.4" customHeight="1">
+    <row r="397" ht="14.4" customHeight="1">
       <c r="B397" t="n">
         <v>3384</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" hidden="1" ht="14.4" customHeight="1">
+    <row r="398" ht="14.4" customHeight="1">
       <c r="B398" t="n">
         <v>3385</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" hidden="1" ht="14.4" customHeight="1">
+    <row r="399" ht="14.4" customHeight="1">
       <c r="B399" t="n">
         <v>3386</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" hidden="1" ht="14.4" customHeight="1">
+    <row r="400" ht="14.4" customHeight="1">
       <c r="B400" t="n">
         <v>3387</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" hidden="1" ht="14.4" customHeight="1">
+    <row r="401" ht="14.4" customHeight="1">
       <c r="B401" t="n">
         <v>3388</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" hidden="1" ht="14.4" customHeight="1">
+    <row r="402" ht="14.4" customHeight="1">
       <c r="B402" t="n">
         <v>3389</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" hidden="1" ht="14.4" customHeight="1">
+    <row r="403" ht="14.4" customHeight="1">
       <c r="B403" t="n">
         <v>3390</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" hidden="1" ht="14.4" customHeight="1">
+    <row r="404" ht="14.4" customHeight="1">
       <c r="B404" t="n">
         <v>3391</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" hidden="1" ht="14.4" customHeight="1">
+    <row r="405" ht="14.4" customHeight="1">
       <c r="B405" t="n">
         <v>3392</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" hidden="1" ht="14.4" customHeight="1">
+    <row r="406" ht="14.4" customHeight="1">
       <c r="B406" t="n">
         <v>3393</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" hidden="1" ht="14.4" customHeight="1">
+    <row r="407" ht="14.4" customHeight="1">
       <c r="B407" t="n">
         <v>3394</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" hidden="1" ht="14.4" customHeight="1">
+    <row r="408" ht="14.4" customHeight="1">
       <c r="B408" t="n">
         <v>3395</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" hidden="1" ht="14.4" customHeight="1">
+    <row r="409" ht="14.4" customHeight="1">
       <c r="B409" t="n">
         <v>3396</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" hidden="1" ht="14.4" customHeight="1">
+    <row r="410" ht="14.4" customHeight="1">
       <c r="B410" t="n">
         <v>3397</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" hidden="1" ht="14.4" customHeight="1">
+    <row r="411" ht="14.4" customHeight="1">
       <c r="B411" t="n">
         <v>3398</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" hidden="1" ht="14.4" customHeight="1">
+    <row r="412" ht="14.4" customHeight="1">
       <c r="B412" t="n">
         <v>3399</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" hidden="1" ht="14.4" customHeight="1">
+    <row r="413" ht="14.4" customHeight="1">
       <c r="B413" t="n">
         <v>3400</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" hidden="1" ht="14.4" customHeight="1">
+    <row r="414" ht="14.4" customHeight="1">
       <c r="B414" t="n">
         <v>3401</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" hidden="1" ht="14.4" customHeight="1">
+    <row r="415" ht="14.4" customHeight="1">
       <c r="B415" t="n">
         <v>3402</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" hidden="1" ht="14.4" customHeight="1">
+    <row r="416" ht="14.4" customHeight="1">
       <c r="B416" t="n">
         <v>3403</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" hidden="1" ht="14.4" customHeight="1">
+    <row r="417" ht="14.4" customHeight="1">
       <c r="B417" t="n">
         <v>3404</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" hidden="1" ht="14.4" customHeight="1">
+    <row r="418" ht="14.4" customHeight="1">
       <c r="B418" t="n">
         <v>3405</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" hidden="1" ht="14.4" customHeight="1">
+    <row r="419" ht="14.4" customHeight="1">
       <c r="B419" t="n">
         <v>3406</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" hidden="1" ht="14.4" customHeight="1">
+    <row r="420" ht="14.4" customHeight="1">
       <c r="B420" t="n">
         <v>3407</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" hidden="1" ht="14.4" customHeight="1">
+    <row r="421" ht="14.4" customHeight="1">
       <c r="B421" t="n">
         <v>3408</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" hidden="1" ht="14.4" customHeight="1">
+    <row r="422" ht="14.4" customHeight="1">
       <c r="B422" t="n">
         <v>3409</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" hidden="1" ht="14.4" customHeight="1">
+    <row r="423" ht="14.4" customHeight="1">
       <c r="B423" t="n">
         <v>3410</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" hidden="1" ht="14.4" customHeight="1">
+    <row r="424" ht="14.4" customHeight="1">
       <c r="B424" t="n">
         <v>3411</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" hidden="1" ht="14.4" customHeight="1">
+    <row r="425" ht="14.4" customHeight="1">
       <c r="B425" t="n">
         <v>3412</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" hidden="1" ht="14.4" customHeight="1">
+    <row r="426" ht="14.4" customHeight="1">
       <c r="B426" t="n">
         <v>3413</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" hidden="1" ht="14.4" customHeight="1">
+    <row r="427" ht="14.4" customHeight="1">
       <c r="B427" t="n">
         <v>3414</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" hidden="1" ht="14.4" customHeight="1">
+    <row r="428" ht="14.4" customHeight="1">
       <c r="B428" t="n">
         <v>3415</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" hidden="1" ht="14.4" customHeight="1">
+    <row r="429" ht="14.4" customHeight="1">
       <c r="B429" t="n">
         <v>3416</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" hidden="1" ht="14.4" customHeight="1">
+    <row r="430" ht="14.4" customHeight="1">
       <c r="B430" t="n">
         <v>3417</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" hidden="1" ht="14.4" customHeight="1">
+    <row r="431" ht="14.4" customHeight="1">
       <c r="B431" t="n">
         <v>3418</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" hidden="1" ht="14.4" customHeight="1">
+    <row r="432" ht="14.4" customHeight="1">
       <c r="B432" t="n">
         <v>3419</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" hidden="1" ht="14.4" customHeight="1">
+    <row r="433" ht="14.4" customHeight="1">
       <c r="B433" t="n">
         <v>3420</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" hidden="1" ht="14.4" customHeight="1">
+    <row r="434" ht="14.4" customHeight="1">
       <c r="B434" t="n">
         <v>3421</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" hidden="1" ht="14.4" customHeight="1">
+    <row r="435" ht="14.4" customHeight="1">
       <c r="B435" t="n">
         <v>3422</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" hidden="1" ht="14.4" customHeight="1">
+    <row r="436" ht="14.4" customHeight="1">
       <c r="B436" t="n">
         <v>3423</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" hidden="1" ht="14.4" customHeight="1">
+    <row r="437" ht="14.4" customHeight="1">
       <c r="B437" t="n">
         <v>3424</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" hidden="1" ht="14.4" customHeight="1">
+    <row r="438" ht="14.4" customHeight="1">
       <c r="B438" t="n">
         <v>3425</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" hidden="1" ht="14.4" customHeight="1">
+    <row r="439" ht="14.4" customHeight="1">
       <c r="B439" t="n">
         <v>3426</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" hidden="1" ht="14.4" customHeight="1">
+    <row r="440" ht="14.4" customHeight="1">
       <c r="B440" t="n">
         <v>3427</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" hidden="1" ht="14.4" customHeight="1">
+    <row r="441" ht="14.4" customHeight="1">
       <c r="B441" t="n">
         <v>3428</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" hidden="1" ht="14.4" customHeight="1">
+    <row r="442" ht="14.4" customHeight="1">
       <c r="B442" t="n">
         <v>3429</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" hidden="1" ht="14.4" customHeight="1">
+    <row r="443" ht="14.4" customHeight="1">
       <c r="B443" t="n">
         <v>3430</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" hidden="1" ht="14.4" customHeight="1">
+    <row r="444" ht="14.4" customHeight="1">
       <c r="B444" t="n">
         <v>3431</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" hidden="1" ht="14.4" customHeight="1">
+    <row r="445" ht="14.4" customHeight="1">
       <c r="B445" t="n">
         <v>3432</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" hidden="1" ht="14.4" customHeight="1">
+    <row r="446" ht="14.4" customHeight="1">
       <c r="B446" t="n">
         <v>3433</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" hidden="1" ht="14.4" customHeight="1">
+    <row r="447" ht="14.4" customHeight="1">
       <c r="B447" t="n">
         <v>3434</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" hidden="1" ht="14.4" customHeight="1">
+    <row r="448" ht="14.4" customHeight="1">
       <c r="B448" t="n">
         <v>3435</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" hidden="1" ht="14.4" customHeight="1">
+    <row r="449" ht="14.4" customHeight="1">
       <c r="B449" t="n">
         <v>3436</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" hidden="1" ht="14.4" customHeight="1">
+    <row r="450" ht="14.4" customHeight="1">
       <c r="B450" t="n">
         <v>3437</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" hidden="1" ht="14.4" customHeight="1">
+    <row r="451" ht="14.4" customHeight="1">
       <c r="B451" t="n">
         <v>3438</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" hidden="1" ht="14.4" customHeight="1">
+    <row r="452" ht="14.4" customHeight="1">
       <c r="B452" t="n">
         <v>3439</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" hidden="1" ht="14.4" customHeight="1">
+    <row r="453" ht="14.4" customHeight="1">
       <c r="B453" t="n">
         <v>3440</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" hidden="1" ht="14.4" customHeight="1">
+    <row r="454" ht="14.4" customHeight="1">
       <c r="B454" t="n">
         <v>3441</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" hidden="1" ht="14.4" customHeight="1">
+    <row r="455" ht="14.4" customHeight="1">
       <c r="B455" t="n">
         <v>3442</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" hidden="1" ht="14.4" customHeight="1">
+    <row r="456" ht="14.4" customHeight="1">
       <c r="B456" t="n">
         <v>3443</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" hidden="1" ht="14.4" customHeight="1">
+    <row r="457" ht="14.4" customHeight="1">
       <c r="B457" t="n">
         <v>3444</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" hidden="1" ht="14.4" customHeight="1">
+    <row r="458" ht="14.4" customHeight="1">
       <c r="B458" t="n">
         <v>3445</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" hidden="1" ht="14.4" customHeight="1">
+    <row r="459" ht="14.4" customHeight="1">
       <c r="B459" t="n">
         <v>3446</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" hidden="1" ht="14.4" customHeight="1">
+    <row r="460" ht="14.4" customHeight="1">
       <c r="B460" t="n">
         <v>3447</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" hidden="1" ht="14.4" customHeight="1">
+    <row r="461" ht="14.4" customHeight="1">
       <c r="B461" t="n">
         <v>3448</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" hidden="1" ht="14.4" customHeight="1">
+    <row r="462" ht="14.4" customHeight="1">
       <c r="B462" t="n">
         <v>3449</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" hidden="1" ht="14.4" customHeight="1">
+    <row r="463" ht="14.4" customHeight="1">
       <c r="B463" t="n">
         <v>3450</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" hidden="1" ht="14.4" customHeight="1">
+    <row r="464" ht="14.4" customHeight="1">
       <c r="B464" t="n">
         <v>3451</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" hidden="1" ht="14.4" customHeight="1">
+    <row r="465" ht="14.4" customHeight="1">
       <c r="B465" t="n">
         <v>3452</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" hidden="1" ht="14.4" customHeight="1">
+    <row r="466" ht="14.4" customHeight="1">
       <c r="B466" t="n">
         <v>3453</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" hidden="1" ht="14.4" customHeight="1">
+    <row r="467" ht="14.4" customHeight="1">
       <c r="B467" t="n">
         <v>3454</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" hidden="1" ht="14.4" customHeight="1">
+    <row r="468" ht="14.4" customHeight="1">
       <c r="B468" t="n">
         <v>3455</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" hidden="1" ht="14.4" customHeight="1">
+    <row r="469" ht="14.4" customHeight="1">
       <c r="B469" t="n">
         <v>3456</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" hidden="1" ht="14.4" customHeight="1">
+    <row r="470" ht="14.4" customHeight="1">
       <c r="B470" t="n">
         <v>3457</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" hidden="1" ht="14.4" customHeight="1">
+    <row r="471" ht="14.4" customHeight="1">
       <c r="B471" t="n">
         <v>3458</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" hidden="1" ht="14.4" customHeight="1">
+    <row r="472" ht="14.4" customHeight="1">
       <c r="B472" t="n">
         <v>3459</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" hidden="1" ht="14.4" customHeight="1">
+    <row r="473" ht="14.4" customHeight="1">
       <c r="B473" t="n">
         <v>3460</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" hidden="1" ht="14.4" customHeight="1">
+    <row r="474" ht="14.4" customHeight="1">
       <c r="B474" t="n">
         <v>3461</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" hidden="1" ht="14.4" customHeight="1">
+    <row r="475" ht="14.4" customHeight="1">
       <c r="B475" t="n">
         <v>3462</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" hidden="1" ht="14.4" customHeight="1">
+    <row r="476" ht="14.4" customHeight="1">
       <c r="B476" t="n">
         <v>3463</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" hidden="1" ht="14.4" customHeight="1">
+    <row r="477" ht="14.4" customHeight="1">
       <c r="B477" t="n">
         <v>3464</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" hidden="1" ht="14.4" customHeight="1">
+    <row r="478" ht="14.4" customHeight="1">
       <c r="B478" t="n">
         <v>3465</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" hidden="1" ht="14.4" customHeight="1">
+    <row r="479" ht="14.4" customHeight="1">
       <c r="B479" t="n">
         <v>3466</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" hidden="1" ht="14.4" customHeight="1">
+    <row r="480" ht="14.4" customHeight="1">
       <c r="B480" t="n">
         <v>3467</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" hidden="1" ht="14.4" customHeight="1">
+    <row r="481" ht="14.4" customHeight="1">
       <c r="B481" t="n">
         <v>3468</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" hidden="1" ht="14.4" customHeight="1">
+    <row r="482" ht="14.4" customHeight="1">
       <c r="B482" t="n">
         <v>3469</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" hidden="1" ht="14.4" customHeight="1">
+    <row r="483" ht="14.4" customHeight="1">
       <c r="B483" t="n">
         <v>3470</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" hidden="1" ht="14.4" customHeight="1">
+    <row r="484" ht="14.4" customHeight="1">
       <c r="B484" t="n">
         <v>3471</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" hidden="1" ht="14.4" customHeight="1">
+    <row r="485" ht="14.4" customHeight="1">
       <c r="B485" t="n">
         <v>3472</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" hidden="1" ht="14.4" customHeight="1">
+    <row r="486" ht="14.4" customHeight="1">
       <c r="B486" t="n">
         <v>3473</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" hidden="1" ht="14.4" customHeight="1">
+    <row r="487" ht="14.4" customHeight="1">
       <c r="B487" t="n">
         <v>3474</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" hidden="1" ht="14.4" customHeight="1">
+    <row r="488" ht="14.4" customHeight="1">
       <c r="B488" t="n">
         <v>3475</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" hidden="1" ht="14.4" customHeight="1">
+    <row r="489" ht="14.4" customHeight="1">
       <c r="B489" t="n">
         <v>3476</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" hidden="1" ht="14.4" customHeight="1">
+    <row r="490" ht="14.4" customHeight="1">
       <c r="B490" t="n">
         <v>3477</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" hidden="1" ht="14.4" customHeight="1">
+    <row r="491" ht="14.4" customHeight="1">
       <c r="B491" t="n">
         <v>3478</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" hidden="1" ht="14.4" customHeight="1">
+    <row r="492" ht="14.4" customHeight="1">
       <c r="B492" t="n">
         <v>3479</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" hidden="1" ht="14.4" customHeight="1">
+    <row r="493" ht="14.4" customHeight="1">
       <c r="B493" t="n">
         <v>3480</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" hidden="1" ht="14.4" customHeight="1">
+    <row r="494" ht="14.4" customHeight="1">
       <c r="B494" t="n">
         <v>3481</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" hidden="1" ht="14.4" customHeight="1">
+    <row r="495" ht="14.4" customHeight="1">
       <c r="B495" t="n">
         <v>3482</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" hidden="1" ht="14.4" customHeight="1">
+    <row r="496" ht="14.4" customHeight="1">
       <c r="B496" t="n">
         <v>3483</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" hidden="1" ht="14.4" customHeight="1">
+    <row r="497" ht="14.4" customHeight="1">
       <c r="B497" t="n">
         <v>3484</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" hidden="1" ht="14.4" customHeight="1">
+    <row r="498" ht="14.4" customHeight="1">
       <c r="B498" t="n">
         <v>3485</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" hidden="1" ht="14.4" customHeight="1">
+    <row r="499" ht="14.4" customHeight="1">
       <c r="B499" t="n">
         <v>3486</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" hidden="1" ht="14.4" customHeight="1">
+    <row r="500" ht="14.4" customHeight="1">
       <c r="B500" t="n">
         <v>3487</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" hidden="1" ht="14.4" customHeight="1">
+    <row r="501" ht="14.4" customHeight="1">
       <c r="B501" t="n">
         <v>3488</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" hidden="1" ht="14.4" customHeight="1">
+    <row r="502" ht="14.4" customHeight="1">
       <c r="B502" t="n">
         <v>3489</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" hidden="1" ht="14.4" customHeight="1">
+    <row r="503" ht="14.4" customHeight="1">
       <c r="B503" t="n">
         <v>3490</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" hidden="1" ht="14.4" customHeight="1">
+    <row r="504" ht="14.4" customHeight="1">
       <c r="B504" t="n">
         <v>3491</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" hidden="1" ht="14.4" customHeight="1">
+    <row r="505" ht="14.4" customHeight="1">
       <c r="B505" t="n">
         <v>3492</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" hidden="1" ht="14.4" customHeight="1">
+    <row r="506" ht="14.4" customHeight="1">
       <c r="B506" t="n">
         <v>3493</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" hidden="1" ht="14.4" customHeight="1">
+    <row r="507" ht="14.4" customHeight="1">
       <c r="B507" t="n">
         <v>3494</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" hidden="1" ht="14.4" customHeight="1">
+    <row r="508" ht="14.4" customHeight="1">
       <c r="B508" t="n">
         <v>3495</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" hidden="1" ht="14.4" customHeight="1">
+    <row r="509" ht="14.4" customHeight="1">
       <c r="B509" t="n">
         <v>3496</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" hidden="1" ht="14.4" customHeight="1">
+    <row r="510" ht="14.4" customHeight="1">
       <c r="B510" t="n">
         <v>3497</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" hidden="1" ht="14.4" customHeight="1">
+    <row r="511" ht="14.4" customHeight="1">
       <c r="B511" t="n">
         <v>3498</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" hidden="1" ht="14.4" customHeight="1">
+    <row r="512" ht="14.4" customHeight="1">
       <c r="B512" t="n">
         <v>3499</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" hidden="1" ht="14.4" customHeight="1">
+    <row r="513" ht="14.4" customHeight="1">
       <c r="B513" t="n">
         <v>3500</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" hidden="1" ht="14.4" customHeight="1">
+    <row r="514" ht="14.4" customHeight="1">
       <c r="B514" t="n">
         <v>3501</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" hidden="1" ht="14.4" customHeight="1">
+    <row r="515" ht="14.4" customHeight="1">
       <c r="B515" t="n">
         <v>3502</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" hidden="1" ht="14.4" customHeight="1">
+    <row r="516" ht="14.4" customHeight="1">
       <c r="B516" t="n">
         <v>3503</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" hidden="1" ht="14.4" customHeight="1">
+    <row r="517" ht="14.4" customHeight="1">
       <c r="B517" t="n">
         <v>3504</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" hidden="1" ht="14.4" customHeight="1">
+    <row r="518" ht="14.4" customHeight="1">
       <c r="B518" t="n">
         <v>3505</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" hidden="1" ht="14.4" customHeight="1">
+    <row r="519" ht="14.4" customHeight="1">
       <c r="B519" t="n">
         <v>3506</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" hidden="1" ht="14.4" customHeight="1">
+    <row r="520" ht="14.4" customHeight="1">
       <c r="B520" t="n">
         <v>3507</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" hidden="1" ht="14.4" customHeight="1">
+    <row r="521" ht="14.4" customHeight="1">
       <c r="B521" t="n">
         <v>3508</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" hidden="1" ht="14.4" customHeight="1">
+    <row r="522" ht="14.4" customHeight="1">
       <c r="B522" t="n">
         <v>3509</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" hidden="1" ht="14.4" customHeight="1">
+    <row r="523" ht="14.4" customHeight="1">
       <c r="B523" t="n">
         <v>3510</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" hidden="1" ht="14.4" customHeight="1">
+    <row r="524" ht="14.4" customHeight="1">
       <c r="B524" t="n">
         <v>3511</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" hidden="1" ht="14.4" customHeight="1">
+    <row r="525" ht="14.4" customHeight="1">
       <c r="B525" t="n">
         <v>3512</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" hidden="1" ht="15" customHeight="1">
+    <row r="526" ht="15" customHeight="1">
       <c r="B526" t="n">
         <v>3513</v>
       </c>
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
-    <row r="527" hidden="1" ht="15" customHeight="1">
+    <row r="527" ht="15" customHeight="1">
       <c r="B527" t="n">
         <v>3514</v>
       </c>
@@ -8469,7 +8613,7 @@
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
-    <row r="528" hidden="1" ht="15" customHeight="1">
+    <row r="528" ht="15" customHeight="1">
       <c r="B528" t="n">
         <v>3515</v>
       </c>
@@ -8481,7 +8625,7 @@
       <c r="O528" s="4" t="n"/>
       <c r="Q528" s="4" t="n"/>
     </row>
-    <row r="529" hidden="1" ht="15" customHeight="1">
+    <row r="529" ht="15" customHeight="1">
       <c r="F529" t="inlineStr">
         <is>
           <t>A</t>
@@ -8490,7 +8634,7 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
-    <row r="530" hidden="1" ht="15" customHeight="1">
+    <row r="530" ht="15" customHeight="1">
       <c r="F530" t="inlineStr">
         <is>
           <t>A</t>
@@ -8499,7 +8643,7 @@
       <c r="O530" s="4" t="n"/>
       <c r="Q530" s="4" t="n"/>
     </row>
-    <row r="531" hidden="1" ht="15" customHeight="1">
+    <row r="531" ht="15" customHeight="1">
       <c r="F531" t="inlineStr">
         <is>
           <t>A</t>
@@ -8508,7 +8652,7 @@
       <c r="O531" s="4" t="n"/>
       <c r="Q531" s="4" t="n"/>
     </row>
-    <row r="532" hidden="1" ht="15" customHeight="1">
+    <row r="532" ht="15" customHeight="1">
       <c r="F532" t="inlineStr">
         <is>
           <t>A</t>
@@ -8517,7 +8661,7 @@
       <c r="O532" s="4" t="n"/>
       <c r="Q532" s="4" t="n"/>
     </row>
-    <row r="533" hidden="1" ht="15" customHeight="1">
+    <row r="533" ht="15" customHeight="1">
       <c r="F533" t="inlineStr">
         <is>
           <t>A</t>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -434,7 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -676,7 +676,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -688,13 +687,13 @@
   </cellStyles>
   <dxfs count="7">
     <dxf>
-      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -783,7 +782,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN533" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN533"/>
+  <autoFilter ref="B1:AN533">
+    <filterColumn colId="1" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="Affinity Petcare"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="B2:AN533">
     <sortCondition ref="I1:I533"/>
   </sortState>
@@ -837,9 +842,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -877,7 +882,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -983,7 +988,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1125,7 +1130,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1138,47 +1143,47 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R533"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.6640625" customWidth="1" min="1" max="1"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
-    <col width="36.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="56.44140625" customWidth="1" min="4" max="4"/>
+    <col width="15.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
+    <col width="36.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="56.42578125" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25.88671875" customWidth="1" min="6" max="6"/>
-    <col width="15.109375" customWidth="1" min="7" max="7"/>
-    <col width="11.6640625" customWidth="1" min="8" max="8"/>
-    <col width="19.109375" customWidth="1" min="9" max="9"/>
+    <col width="25.85546875" customWidth="1" min="6" max="6"/>
+    <col width="15.140625" customWidth="1" min="7" max="7"/>
+    <col width="11.7109375" customWidth="1" min="8" max="8"/>
+    <col width="19.140625" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.109375" customWidth="1" min="11" max="11"/>
-    <col width="17.5546875" customWidth="1" min="12" max="12"/>
-    <col width="35.109375" customWidth="1" min="13" max="13"/>
-    <col width="25.33203125" customWidth="1" min="14" max="14"/>
-    <col width="33.44140625" customWidth="1" min="15" max="15"/>
+    <col width="18.140625" customWidth="1" min="11" max="11"/>
+    <col width="17.5703125" customWidth="1" min="12" max="12"/>
+    <col width="35.140625" customWidth="1" min="13" max="13"/>
+    <col width="25.28515625" customWidth="1" min="14" max="14"/>
+    <col width="33.42578125" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="35.88671875" customWidth="1" style="4" min="17" max="17"/>
+    <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="27.6640625" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.6640625" customWidth="1" min="20" max="20"/>
-    <col width="12.88671875" customWidth="1" min="21" max="23"/>
-    <col width="16.33203125" customWidth="1" min="24" max="24"/>
-    <col width="20.109375" customWidth="1" min="25" max="25"/>
-    <col width="20.5546875" customWidth="1" min="26" max="26"/>
-    <col width="14.88671875" customWidth="1" min="27" max="27"/>
+    <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
+    <col width="14.7109375" customWidth="1" min="20" max="20"/>
+    <col width="12.85546875" customWidth="1" min="21" max="23"/>
+    <col width="16.28515625" customWidth="1" min="24" max="24"/>
+    <col width="20.140625" customWidth="1" min="25" max="25"/>
+    <col width="20.5703125" customWidth="1" min="26" max="26"/>
+    <col width="14.85546875" customWidth="1" min="27" max="27"/>
     <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5546875" customWidth="1" min="29" max="29"/>
-    <col width="16.109375" customWidth="1" min="30" max="30"/>
-    <col width="16.109375" customWidth="1" style="139" min="31" max="31"/>
-    <col width="22.88671875" customWidth="1" min="32" max="32"/>
-    <col width="17.33203125" customWidth="1" min="33" max="33"/>
-    <col width="16.33203125" customWidth="1" style="140" min="34" max="34"/>
-    <col width="22.88671875" customWidth="1" min="35" max="36"/>
-    <col width="31.88671875" customWidth="1" min="37" max="37"/>
-    <col width="13.44140625" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.33203125" customWidth="1" min="41" max="41"/>
+    <col width="20.5703125" customWidth="1" min="29" max="29"/>
+    <col width="16.140625" customWidth="1" min="30" max="30"/>
+    <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
+    <col width="22.85546875" customWidth="1" min="32" max="32"/>
+    <col width="17.28515625" customWidth="1" min="33" max="33"/>
+    <col width="16.28515625" customWidth="1" style="139" min="34" max="34"/>
+    <col width="22.85546875" customWidth="1" min="35" max="36"/>
+    <col width="31.85546875" customWidth="1" min="37" max="37"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
+    <col width="33.28515625" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customHeight="1">
+    <row r="1" ht="28.9" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1270,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customFormat="1" customHeight="1" s="62">
+    <row r="2" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1354,7 +1359,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" ht="14.4" customHeight="1">
+    <row r="3" hidden="1" ht="14.45" customHeight="1">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1424,7 +1429,7 @@
       <c r="Q3" s="88" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
-    <row r="4" ht="24" customHeight="1" thickBot="1">
+    <row r="4" hidden="1" ht="24" customHeight="1" thickBot="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1508,7 +1513,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" ht="28.8" customHeight="1">
+    <row r="5" hidden="1" ht="28.9" customHeight="1">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1567,7 +1572,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1">
+    <row r="6" hidden="1" ht="14.45" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1627,7 +1632,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
+    <row r="7" hidden="1" ht="14.45" customHeight="1">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1705,7 +1710,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" ht="14.4" customHeight="1">
+    <row r="8" hidden="1" ht="14.45" customHeight="1">
       <c r="B8" t="n">
         <v>3008</v>
       </c>
@@ -1788,7 +1793,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="9" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="9" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="B9" t="n">
         <v>3009</v>
       </c>
@@ -1871,7 +1876,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="10" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1951,11 +1956,11 @@
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R10" s="141" t="n">
+      <c r="R10" s="140" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="11" ht="43.2" customHeight="1">
+    <row r="11" hidden="1" ht="43.15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2036,7 +2041,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="12" ht="14.4" customFormat="1" customHeight="1" s="27">
+    <row r="12" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="27">
       <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2100,7 +2105,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="13" ht="14.4" customHeight="1">
+    <row r="13" hidden="1" ht="14.45" customHeight="1">
       <c r="B13" t="n">
         <v>3014</v>
       </c>
@@ -2173,7 +2178,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="14" ht="30.75" customHeight="1" thickBot="1">
+    <row r="14" hidden="1" ht="30.75" customHeight="1" thickBot="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Mike/Heather</t>
@@ -2237,7 +2242,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="15" ht="29.25" customFormat="1" customHeight="1" s="79">
+    <row r="15" hidden="1" ht="29.25" customFormat="1" customHeight="1" s="79">
       <c r="A15" s="79" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2326,7 +2331,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16" hidden="1" ht="48" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2404,7 +2409,7 @@
       <c r="Q16" s="88" t="n"/>
       <c r="R16" s="23" t="n"/>
     </row>
-    <row r="17" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="17" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2449,7 +2454,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="18" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="18" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B18" t="n">
         <v>3018</v>
       </c>
@@ -2491,7 +2496,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="43.2" customFormat="1" customHeight="1" s="27">
+    <row r="19" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B19" t="n">
         <v>3019</v>
       </c>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="43.2" customHeight="1">
+    <row r="20" hidden="1" ht="43.15" customHeight="1">
       <c r="B20" t="n">
         <v>3020</v>
       </c>
@@ -2575,7 +2580,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="33" customFormat="1" customHeight="1" s="27">
+    <row r="21" hidden="1" ht="33" customFormat="1" customHeight="1" s="27">
       <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -2622,7 +2627,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30.75" customHeight="1">
+    <row r="22" hidden="1" ht="30.75" customHeight="1">
       <c r="B22" t="n">
         <v>3022</v>
       </c>
@@ -2697,7 +2702,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="23" ht="28.8" customHeight="1">
+    <row r="23" hidden="1" ht="28.9" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2781,7 +2786,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="24" ht="28.8" customHeight="1">
+    <row r="24" hidden="1" ht="28.9" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2847,7 +2852,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="43.8" customHeight="1" thickBot="1">
+    <row r="25" hidden="1" ht="43.9" customHeight="1" thickBot="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" ht="14.4" customHeight="1">
+    <row r="26" hidden="1" ht="14.45" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -2991,7 +2996,7 @@
       </c>
       <c r="Q26" s="4" t="n"/>
     </row>
-    <row r="27" ht="14.4" customHeight="1">
+    <row r="27" hidden="1" ht="14.45" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3062,7 +3067,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="28.8" customHeight="1">
+    <row r="28" hidden="1" ht="28.9" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3139,7 +3144,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="43.2" customHeight="1">
+    <row r="29" hidden="1" ht="43.15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3187,7 +3192,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="28.8" customHeight="1">
+    <row r="30" hidden="1" ht="28.9" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
@@ -3249,7 +3254,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="43.2" customHeight="1">
+    <row r="31" hidden="1" ht="43.15" customHeight="1">
       <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
@@ -3313,7 +3318,7 @@
       <c r="O31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
     </row>
-    <row r="32" ht="54" customFormat="1" customHeight="1" s="27">
+    <row r="32" hidden="1" ht="54" customFormat="1" customHeight="1" s="27">
       <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -3387,7 +3392,7 @@
       <c r="O32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
     </row>
-    <row r="33" ht="43.2" customHeight="1">
+    <row r="33" hidden="1" ht="43.15" customHeight="1">
       <c r="B33" t="n">
         <v>3035</v>
       </c>
@@ -3456,7 +3461,7 @@
       <c r="O33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
     </row>
-    <row r="34" ht="57.6" customHeight="1">
+    <row r="34" hidden="1" ht="57.6" customHeight="1">
       <c r="B34" t="n">
         <v>3035</v>
       </c>
@@ -3521,7 +3526,7 @@
       <c r="O34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
+    <row r="35" hidden="1" ht="14.45" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>Mike/Jeff</t>
@@ -3588,7 +3593,7 @@
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
+    <row r="36" hidden="1" ht="14.45" customHeight="1">
       <c r="B36" t="n">
         <v>3031</v>
       </c>
@@ -3655,7 +3660,7 @@
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
+    <row r="37" hidden="1" ht="14.45" customHeight="1">
       <c r="B37" t="n">
         <v>3056</v>
       </c>
@@ -3682,7 +3687,7 @@
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" ht="57.6" customHeight="1">
+    <row r="38" hidden="1" ht="57.6" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3750,7 +3755,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="28.8" customHeight="1">
+    <row r="39" hidden="1" ht="28.9" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3822,7 +3827,7 @@
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
     </row>
-    <row r="40" ht="43.2" customHeight="1">
+    <row r="40" hidden="1" ht="43.15" customHeight="1">
       <c r="B40" t="n">
         <v>3035</v>
       </c>
@@ -3866,7 +3871,7 @@
       <c r="O40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
     </row>
-    <row r="41" ht="28.8" customHeight="1">
+    <row r="41" hidden="1" ht="28.9" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -3939,7 +3944,7 @@
       </c>
       <c r="Q41" s="4" t="n"/>
     </row>
-    <row r="42" ht="43.2" customHeight="1">
+    <row r="42" hidden="1" ht="43.15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>US</t>
@@ -3978,7 +3983,7 @@
       <c r="O42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43" hidden="1" ht="14.45" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
@@ -4011,7 +4016,7 @@
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" ht="41.4" customHeight="1">
+    <row r="44" hidden="1" ht="41.45" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4071,7 +4076,7 @@
       <c r="O44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
     </row>
-    <row r="45" ht="28.8" customHeight="1">
+    <row r="45" hidden="1" ht="28.9" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4134,7 +4139,7 @@
       <c r="O45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
+    <row r="46" hidden="1" ht="14.45" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4191,7 +4196,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" ht="43.2" customHeight="1">
+    <row r="47" hidden="1" ht="43.15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>US</t>
@@ -4208,6 +4213,16 @@
       <c r="D47" t="inlineStr">
         <is>
           <t>NP42</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PR6</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PR6A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4230,7 +4245,7 @@
       <c r="O47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
     </row>
-    <row r="48" ht="43.2" customHeight="1">
+    <row r="48" hidden="1" ht="43.15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>US</t>
@@ -4274,7 +4289,7 @@
       <c r="O48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49" hidden="1" ht="14.45" customHeight="1">
       <c r="B49" s="130" t="n">
         <v>3041</v>
       </c>
@@ -4336,7 +4351,7 @@
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" ht="43.2" customHeight="1">
+    <row r="50" hidden="1" ht="43.15" customHeight="1">
       <c r="B50" t="n">
         <v>3063</v>
       </c>
@@ -4370,7 +4385,7 @@
       <c r="O50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
+    <row r="51" hidden="1" ht="14.45" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4397,7 +4412,7 @@
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="52" hidden="1" ht="14.45" customHeight="1">
       <c r="B52" t="n">
         <v>3044</v>
       </c>
@@ -4449,7 +4464,7 @@
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" ht="14.4" customHeight="1">
+    <row r="53" hidden="1" ht="14.45" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4476,7 +4491,7 @@
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" ht="14.4" customHeight="1">
+    <row r="54" hidden="1" ht="14.45" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4508,7 +4523,7 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1">
+    <row r="55" hidden="1" ht="14.45" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4540,7 +4555,7 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1">
+    <row r="56" hidden="1" ht="14.45" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4572,7 +4587,7 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1">
+    <row r="57" hidden="1" ht="14.45" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4604,7 +4619,7 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1">
+    <row r="58" hidden="1" ht="14.45" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4636,7 +4651,7 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1">
+    <row r="59" hidden="1" ht="14.45" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4668,7 +4683,7 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1">
+    <row r="60" hidden="1" ht="14.45" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -4681,7 +4696,7 @@
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="23" t="n"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1">
+    <row r="61" hidden="1" ht="14.45" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4713,7 +4728,7 @@
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1">
+    <row r="62" hidden="1" ht="14.45" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4745,7 +4760,7 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1">
+    <row r="63" hidden="1" ht="14.45" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4777,7 +4792,7 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1">
+    <row r="64" hidden="1" ht="14.45" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4809,7 +4824,7 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1">
+    <row r="65" hidden="1" ht="14.45" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>US</t>
@@ -4822,7 +4837,7 @@
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="23" t="n"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1">
+    <row r="66" hidden="1" ht="14.45" customHeight="1">
       <c r="B66" s="131" t="inlineStr">
         <is>
           <t>----</t>
@@ -4846,7 +4861,7 @@
       <c r="O66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1">
+    <row r="67" hidden="1" ht="14.45" customHeight="1">
       <c r="B67" t="n">
         <v>3003</v>
       </c>
@@ -4854,7 +4869,7 @@
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="23" t="n"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1">
+    <row r="68" hidden="1" ht="14.45" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>US</t>
@@ -4867,7 +4882,7 @@
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="23" t="n"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1">
+    <row r="69" hidden="1" ht="14.45" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>US</t>
@@ -4897,7 +4912,7 @@
       <c r="Q69" s="108" t="n"/>
       <c r="R69" s="66" t="n"/>
     </row>
-    <row r="70" ht="43.2" customHeight="1">
+    <row r="70" hidden="1" ht="43.15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4936,7 +4951,7 @@
       <c r="O70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1">
+    <row r="71" hidden="1" ht="14.45" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>US</t>
@@ -4962,7 +4977,7 @@
       <c r="Q71" s="108" t="n"/>
       <c r="R71" s="66" t="n"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72" hidden="1" ht="14.45" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -4994,7 +5009,7 @@
       <c r="O72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73" hidden="1" ht="14.45" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>US</t>
@@ -5020,7 +5035,7 @@
       <c r="Q73" s="108" t="n"/>
       <c r="R73" s="66" t="n"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74" hidden="1" ht="14.45" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5052,7 +5067,7 @@
       <c r="O74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75" hidden="1" ht="14.45" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5089,7 +5104,7 @@
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" ht="43.2" customHeight="1">
+    <row r="76" hidden="1" ht="43.15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>US</t>
@@ -5103,7 +5118,7 @@
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="23" t="n"/>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77" hidden="1" ht="14.45" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
@@ -5127,7 +5142,7 @@
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78" ht="14.45" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5161,7 +5176,7 @@
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" ht="57.6" customHeight="1">
+    <row r="79" hidden="1" ht="57.6" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5200,7 +5215,7 @@
       <c r="O79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
     </row>
-    <row r="80" ht="43.2" customHeight="1">
+    <row r="80" hidden="1" ht="43.15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5239,7 +5254,7 @@
       <c r="O80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
     </row>
-    <row r="81" ht="28.8" customHeight="1">
+    <row r="81" hidden="1" ht="28.9" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -5311,7 +5326,7 @@
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" ht="14.4" customHeight="1">
+    <row r="82" hidden="1" ht="14.45" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>US</t>
@@ -5333,7 +5348,7 @@
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" ht="14.4" customHeight="1">
+    <row r="83" hidden="1" ht="14.45" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>US</t>
@@ -5350,2009 +5365,2009 @@
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" ht="14.4" customHeight="1">
+    <row r="84" hidden="1" ht="14.45" customHeight="1">
       <c r="B84" t="n">
         <v>3071</v>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" ht="14.4" customHeight="1">
+    <row r="85" hidden="1" ht="14.45" customHeight="1">
       <c r="B85" t="n">
         <v>3072</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" ht="14.4" customHeight="1">
+    <row r="86" hidden="1" ht="14.45" customHeight="1">
       <c r="B86" t="n">
         <v>3073</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" ht="14.4" customHeight="1">
+    <row r="87" hidden="1" ht="14.45" customHeight="1">
       <c r="B87" t="n">
         <v>3074</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" ht="14.4" customHeight="1">
+    <row r="88" hidden="1" ht="14.45" customHeight="1">
       <c r="B88" t="n">
         <v>3075</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" ht="14.4" customHeight="1">
+    <row r="89" hidden="1" ht="14.45" customHeight="1">
       <c r="B89" t="n">
         <v>3076</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" ht="14.4" customHeight="1">
+    <row r="90" hidden="1" ht="14.45" customHeight="1">
       <c r="B90" t="n">
         <v>3077</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" ht="14.4" customHeight="1">
+    <row r="91" hidden="1" ht="14.45" customHeight="1">
       <c r="B91" t="n">
         <v>3078</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" ht="14.4" customHeight="1">
+    <row r="92" hidden="1" ht="14.45" customHeight="1">
       <c r="B92" t="n">
         <v>3079</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" ht="14.4" customHeight="1">
+    <row r="93" hidden="1" ht="14.45" customHeight="1">
       <c r="B93" t="n">
         <v>3080</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" ht="14.4" customHeight="1">
+    <row r="94" hidden="1" ht="14.45" customHeight="1">
       <c r="B94" t="n">
         <v>3081</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" ht="14.4" customHeight="1">
+    <row r="95" hidden="1" ht="14.45" customHeight="1">
       <c r="B95" t="n">
         <v>3082</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" ht="14.4" customHeight="1">
+    <row r="96" hidden="1" ht="14.45" customHeight="1">
       <c r="B96" t="n">
         <v>3083</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" ht="14.4" customHeight="1">
+    <row r="97" hidden="1" ht="14.45" customHeight="1">
       <c r="B97" t="n">
         <v>3084</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" ht="14.4" customHeight="1">
+    <row r="98" hidden="1" ht="14.45" customHeight="1">
       <c r="B98" t="n">
         <v>3085</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" ht="14.4" customHeight="1">
+    <row r="99" hidden="1" ht="14.45" customHeight="1">
       <c r="B99" t="n">
         <v>3086</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" ht="14.4" customHeight="1">
+    <row r="100" hidden="1" ht="14.45" customHeight="1">
       <c r="B100" t="n">
         <v>3087</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" ht="14.4" customHeight="1">
+    <row r="101" hidden="1" ht="14.45" customHeight="1">
       <c r="B101" t="n">
         <v>3088</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" ht="14.4" customHeight="1">
+    <row r="102" hidden="1" ht="14.45" customHeight="1">
       <c r="B102" t="n">
         <v>3089</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" ht="14.4" customHeight="1">
+    <row r="103" hidden="1" ht="14.45" customHeight="1">
       <c r="B103" t="n">
         <v>3090</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" ht="14.4" customHeight="1">
+    <row r="104" hidden="1" ht="14.45" customHeight="1">
       <c r="B104" t="n">
         <v>3091</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" ht="14.4" customHeight="1">
+    <row r="105" hidden="1" ht="14.45" customHeight="1">
       <c r="B105" t="n">
         <v>3092</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" ht="14.4" customHeight="1">
+    <row r="106" hidden="1" ht="14.45" customHeight="1">
       <c r="B106" t="n">
         <v>3093</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" ht="14.4" customHeight="1">
+    <row r="107" hidden="1" ht="14.45" customHeight="1">
       <c r="B107" t="n">
         <v>3094</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" ht="14.4" customHeight="1">
+    <row r="108" hidden="1" ht="14.45" customHeight="1">
       <c r="B108" t="n">
         <v>3095</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" ht="14.4" customHeight="1">
+    <row r="109" hidden="1" ht="14.45" customHeight="1">
       <c r="B109" t="n">
         <v>3096</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" ht="14.4" customHeight="1">
+    <row r="110" hidden="1" ht="14.45" customHeight="1">
       <c r="B110" t="n">
         <v>3097</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" ht="14.4" customHeight="1">
+    <row r="111" hidden="1" ht="14.45" customHeight="1">
       <c r="B111" t="n">
         <v>3098</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" ht="14.4" customHeight="1">
+    <row r="112" hidden="1" ht="14.45" customHeight="1">
       <c r="B112" t="n">
         <v>3099</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" ht="14.4" customHeight="1">
+    <row r="113" hidden="1" ht="14.45" customHeight="1">
       <c r="B113" t="n">
         <v>3100</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" ht="14.4" customHeight="1">
+    <row r="114" hidden="1" ht="14.45" customHeight="1">
       <c r="B114" t="n">
         <v>3101</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" ht="14.4" customHeight="1">
+    <row r="115" hidden="1" ht="14.45" customHeight="1">
       <c r="B115" t="n">
         <v>3102</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" ht="14.4" customHeight="1">
+    <row r="116" hidden="1" ht="14.45" customHeight="1">
       <c r="B116" t="n">
         <v>3103</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" ht="14.4" customHeight="1">
+    <row r="117" hidden="1" ht="14.45" customHeight="1">
       <c r="B117" t="n">
         <v>3104</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" ht="14.4" customHeight="1">
+    <row r="118" hidden="1" ht="14.45" customHeight="1">
       <c r="B118" t="n">
         <v>3105</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" ht="14.4" customHeight="1">
+    <row r="119" hidden="1" ht="14.45" customHeight="1">
       <c r="B119" t="n">
         <v>3106</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" ht="14.4" customHeight="1">
+    <row r="120" hidden="1" ht="14.45" customHeight="1">
       <c r="B120" t="n">
         <v>3107</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" ht="14.4" customHeight="1">
+    <row r="121" hidden="1" ht="14.45" customHeight="1">
       <c r="B121" t="n">
         <v>3108</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" ht="14.4" customHeight="1">
+    <row r="122" hidden="1" ht="14.45" customHeight="1">
       <c r="B122" t="n">
         <v>3109</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" ht="14.4" customHeight="1">
+    <row r="123" hidden="1" ht="14.45" customHeight="1">
       <c r="B123" t="n">
         <v>3110</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" ht="14.4" customHeight="1">
+    <row r="124" hidden="1" ht="14.45" customHeight="1">
       <c r="B124" t="n">
         <v>3111</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" ht="14.4" customHeight="1">
+    <row r="125" hidden="1" ht="14.45" customHeight="1">
       <c r="B125" t="n">
         <v>3112</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" ht="14.4" customHeight="1">
+    <row r="126" hidden="1" ht="14.45" customHeight="1">
       <c r="B126" t="n">
         <v>3113</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" ht="14.4" customHeight="1">
+    <row r="127" hidden="1" ht="14.45" customHeight="1">
       <c r="B127" t="n">
         <v>3114</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" ht="14.4" customHeight="1">
+    <row r="128" hidden="1" ht="14.45" customHeight="1">
       <c r="B128" t="n">
         <v>3115</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" ht="14.4" customHeight="1">
+    <row r="129" hidden="1" ht="14.45" customHeight="1">
       <c r="B129" t="n">
         <v>3116</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" ht="14.4" customHeight="1">
+    <row r="130" hidden="1" ht="14.45" customHeight="1">
       <c r="B130" t="n">
         <v>3117</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" ht="14.4" customHeight="1">
+    <row r="131" hidden="1" ht="14.45" customHeight="1">
       <c r="B131" t="n">
         <v>3118</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" ht="14.4" customHeight="1">
+    <row r="132" hidden="1" ht="14.45" customHeight="1">
       <c r="B132" t="n">
         <v>3119</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" ht="14.4" customHeight="1">
+    <row r="133" hidden="1" ht="14.45" customHeight="1">
       <c r="B133" t="n">
         <v>3120</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" ht="14.4" customHeight="1">
+    <row r="134" hidden="1" ht="14.45" customHeight="1">
       <c r="B134" t="n">
         <v>3121</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" ht="14.4" customHeight="1">
+    <row r="135" hidden="1" ht="14.45" customHeight="1">
       <c r="B135" t="n">
         <v>3122</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" ht="14.4" customHeight="1">
+    <row r="136" hidden="1" ht="14.45" customHeight="1">
       <c r="B136" t="n">
         <v>3123</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" ht="14.4" customHeight="1">
+    <row r="137" hidden="1" ht="14.45" customHeight="1">
       <c r="B137" t="n">
         <v>3124</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" ht="14.4" customHeight="1">
+    <row r="138" hidden="1" ht="14.45" customHeight="1">
       <c r="B138" t="n">
         <v>3125</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" ht="14.4" customHeight="1">
+    <row r="139" hidden="1" ht="14.45" customHeight="1">
       <c r="B139" t="n">
         <v>3126</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" ht="14.4" customHeight="1">
+    <row r="140" hidden="1" ht="14.45" customHeight="1">
       <c r="B140" t="n">
         <v>3127</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" ht="14.4" customHeight="1">
+    <row r="141" hidden="1" ht="14.45" customHeight="1">
       <c r="B141" t="n">
         <v>3128</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" ht="14.4" customHeight="1">
+    <row r="142" hidden="1" ht="14.45" customHeight="1">
       <c r="B142" t="n">
         <v>3129</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" ht="14.4" customHeight="1">
+    <row r="143" hidden="1" ht="14.45" customHeight="1">
       <c r="B143" t="n">
         <v>3130</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" ht="14.4" customHeight="1">
+    <row r="144" hidden="1" ht="14.45" customHeight="1">
       <c r="B144" t="n">
         <v>3131</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" ht="14.4" customHeight="1">
+    <row r="145" hidden="1" ht="14.45" customHeight="1">
       <c r="B145" t="n">
         <v>3132</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" ht="14.4" customHeight="1">
+    <row r="146" hidden="1" ht="14.45" customHeight="1">
       <c r="B146" t="n">
         <v>3133</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" ht="14.4" customHeight="1">
+    <row r="147" hidden="1" ht="14.45" customHeight="1">
       <c r="B147" t="n">
         <v>3134</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" ht="14.4" customHeight="1">
+    <row r="148" hidden="1" ht="14.45" customHeight="1">
       <c r="B148" t="n">
         <v>3135</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" ht="14.4" customHeight="1">
+    <row r="149" hidden="1" ht="14.45" customHeight="1">
       <c r="B149" t="n">
         <v>3136</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" ht="14.4" customHeight="1">
+    <row r="150" hidden="1" ht="14.45" customHeight="1">
       <c r="B150" t="n">
         <v>3137</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" ht="14.4" customHeight="1">
+    <row r="151" hidden="1" ht="14.45" customHeight="1">
       <c r="B151" t="n">
         <v>3138</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" ht="14.4" customHeight="1">
+    <row r="152" hidden="1" ht="14.45" customHeight="1">
       <c r="B152" t="n">
         <v>3139</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" ht="14.4" customHeight="1">
+    <row r="153" hidden="1" ht="14.45" customHeight="1">
       <c r="B153" t="n">
         <v>3140</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" ht="14.4" customHeight="1">
+    <row r="154" hidden="1" ht="14.45" customHeight="1">
       <c r="B154" t="n">
         <v>3141</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" ht="14.4" customHeight="1">
+    <row r="155" hidden="1" ht="14.45" customHeight="1">
       <c r="B155" t="n">
         <v>3142</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" ht="14.4" customHeight="1">
+    <row r="156" hidden="1" ht="14.45" customHeight="1">
       <c r="B156" t="n">
         <v>3143</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" ht="14.4" customHeight="1">
+    <row r="157" hidden="1" ht="14.45" customHeight="1">
       <c r="B157" t="n">
         <v>3144</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" ht="14.4" customHeight="1">
+    <row r="158" hidden="1" ht="14.45" customHeight="1">
       <c r="B158" t="n">
         <v>3145</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" ht="14.4" customHeight="1">
+    <row r="159" hidden="1" ht="14.45" customHeight="1">
       <c r="B159" t="n">
         <v>3146</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" ht="14.4" customHeight="1">
+    <row r="160" hidden="1" ht="14.45" customHeight="1">
       <c r="B160" t="n">
         <v>3147</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" ht="14.4" customHeight="1">
+    <row r="161" hidden="1" ht="14.45" customHeight="1">
       <c r="B161" t="n">
         <v>3148</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" ht="14.4" customHeight="1">
+    <row r="162" hidden="1" ht="14.45" customHeight="1">
       <c r="B162" t="n">
         <v>3149</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" ht="14.4" customHeight="1">
+    <row r="163" hidden="1" ht="14.45" customHeight="1">
       <c r="B163" t="n">
         <v>3150</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" ht="14.4" customHeight="1">
+    <row r="164" hidden="1" ht="14.45" customHeight="1">
       <c r="B164" t="n">
         <v>3151</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" ht="14.4" customHeight="1">
+    <row r="165" hidden="1" ht="14.45" customHeight="1">
       <c r="B165" t="n">
         <v>3152</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" ht="14.4" customHeight="1">
+    <row r="166" hidden="1" ht="14.45" customHeight="1">
       <c r="B166" t="n">
         <v>3153</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" ht="14.4" customHeight="1">
+    <row r="167" hidden="1" ht="14.45" customHeight="1">
       <c r="B167" t="n">
         <v>3154</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" ht="14.4" customHeight="1">
+    <row r="168" hidden="1" ht="14.45" customHeight="1">
       <c r="B168" t="n">
         <v>3155</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" ht="14.4" customHeight="1">
+    <row r="169" hidden="1" ht="14.45" customHeight="1">
       <c r="B169" t="n">
         <v>3156</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" ht="14.4" customHeight="1">
+    <row r="170" hidden="1" ht="14.45" customHeight="1">
       <c r="B170" t="n">
         <v>3157</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" ht="14.4" customHeight="1">
+    <row r="171" hidden="1" ht="14.45" customHeight="1">
       <c r="B171" t="n">
         <v>3158</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" ht="14.4" customHeight="1">
+    <row r="172" hidden="1" ht="14.45" customHeight="1">
       <c r="B172" t="n">
         <v>3159</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" ht="14.4" customHeight="1">
+    <row r="173" hidden="1" ht="14.45" customHeight="1">
       <c r="B173" t="n">
         <v>3160</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" ht="14.4" customHeight="1">
+    <row r="174" hidden="1" ht="14.45" customHeight="1">
       <c r="B174" t="n">
         <v>3161</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" ht="14.4" customHeight="1">
+    <row r="175" hidden="1" ht="14.45" customHeight="1">
       <c r="B175" t="n">
         <v>3162</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" ht="14.4" customHeight="1">
+    <row r="176" hidden="1" ht="14.45" customHeight="1">
       <c r="B176" t="n">
         <v>3163</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" ht="14.4" customHeight="1">
+    <row r="177" hidden="1" ht="14.45" customHeight="1">
       <c r="B177" t="n">
         <v>3164</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" ht="14.4" customHeight="1">
+    <row r="178" hidden="1" ht="14.45" customHeight="1">
       <c r="B178" t="n">
         <v>3165</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" ht="14.4" customHeight="1">
+    <row r="179" hidden="1" ht="14.45" customHeight="1">
       <c r="B179" t="n">
         <v>3166</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" ht="14.4" customHeight="1">
+    <row r="180" hidden="1" ht="14.45" customHeight="1">
       <c r="B180" t="n">
         <v>3167</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" ht="14.4" customHeight="1">
+    <row r="181" hidden="1" ht="14.45" customHeight="1">
       <c r="B181" t="n">
         <v>3168</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" ht="14.4" customHeight="1">
+    <row r="182" hidden="1" ht="14.45" customHeight="1">
       <c r="B182" t="n">
         <v>3169</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" ht="14.4" customHeight="1">
+    <row r="183" hidden="1" ht="14.45" customHeight="1">
       <c r="B183" t="n">
         <v>3170</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" ht="14.4" customHeight="1">
+    <row r="184" hidden="1" ht="14.45" customHeight="1">
       <c r="B184" t="n">
         <v>3171</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" ht="14.4" customHeight="1">
+    <row r="185" hidden="1" ht="14.45" customHeight="1">
       <c r="B185" t="n">
         <v>3172</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" ht="14.4" customHeight="1">
+    <row r="186" hidden="1" ht="14.45" customHeight="1">
       <c r="B186" t="n">
         <v>3173</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" ht="14.4" customHeight="1">
+    <row r="187" hidden="1" ht="14.45" customHeight="1">
       <c r="B187" t="n">
         <v>3174</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" ht="14.4" customHeight="1">
+    <row r="188" hidden="1" ht="14.45" customHeight="1">
       <c r="B188" t="n">
         <v>3175</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" ht="14.4" customHeight="1">
+    <row r="189" hidden="1" ht="14.45" customHeight="1">
       <c r="B189" t="n">
         <v>3176</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" ht="14.4" customHeight="1">
+    <row r="190" hidden="1" ht="14.45" customHeight="1">
       <c r="B190" t="n">
         <v>3177</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" ht="14.4" customHeight="1">
+    <row r="191" hidden="1" ht="14.45" customHeight="1">
       <c r="B191" t="n">
         <v>3178</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" ht="14.4" customHeight="1">
+    <row r="192" hidden="1" ht="14.45" customHeight="1">
       <c r="B192" t="n">
         <v>3179</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" ht="14.4" customHeight="1">
+    <row r="193" hidden="1" ht="14.45" customHeight="1">
       <c r="B193" t="n">
         <v>3180</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" ht="14.4" customHeight="1">
+    <row r="194" hidden="1" ht="14.45" customHeight="1">
       <c r="B194" t="n">
         <v>3181</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" ht="14.4" customHeight="1">
+    <row r="195" hidden="1" ht="14.45" customHeight="1">
       <c r="B195" t="n">
         <v>3182</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" ht="14.4" customHeight="1">
+    <row r="196" hidden="1" ht="14.45" customHeight="1">
       <c r="B196" t="n">
         <v>3183</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" ht="14.4" customHeight="1">
+    <row r="197" hidden="1" ht="14.45" customHeight="1">
       <c r="B197" t="n">
         <v>3184</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" ht="14.4" customHeight="1">
+    <row r="198" hidden="1" ht="14.45" customHeight="1">
       <c r="B198" t="n">
         <v>3185</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" ht="14.4" customHeight="1">
+    <row r="199" hidden="1" ht="14.45" customHeight="1">
       <c r="B199" t="n">
         <v>3186</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" ht="14.4" customHeight="1">
+    <row r="200" hidden="1" ht="14.45" customHeight="1">
       <c r="B200" t="n">
         <v>3187</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" ht="14.4" customHeight="1">
+    <row r="201" hidden="1" ht="14.45" customHeight="1">
       <c r="B201" t="n">
         <v>3188</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" ht="14.4" customHeight="1">
+    <row r="202" hidden="1" ht="14.45" customHeight="1">
       <c r="B202" t="n">
         <v>3189</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" ht="14.4" customHeight="1">
+    <row r="203" hidden="1" ht="14.45" customHeight="1">
       <c r="B203" t="n">
         <v>3190</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" ht="14.4" customHeight="1">
+    <row r="204" hidden="1" ht="14.45" customHeight="1">
       <c r="B204" t="n">
         <v>3191</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" ht="14.4" customHeight="1">
+    <row r="205" hidden="1" ht="14.45" customHeight="1">
       <c r="B205" t="n">
         <v>3192</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" ht="14.4" customHeight="1">
+    <row r="206" hidden="1" ht="14.45" customHeight="1">
       <c r="B206" t="n">
         <v>3193</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" ht="14.4" customHeight="1">
+    <row r="207" hidden="1" ht="14.45" customHeight="1">
       <c r="B207" t="n">
         <v>3194</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" ht="14.4" customHeight="1">
+    <row r="208" hidden="1" ht="14.45" customHeight="1">
       <c r="B208" t="n">
         <v>3195</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" ht="14.4" customHeight="1">
+    <row r="209" hidden="1" ht="14.45" customHeight="1">
       <c r="B209" t="n">
         <v>3196</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" ht="14.4" customHeight="1">
+    <row r="210" hidden="1" ht="14.45" customHeight="1">
       <c r="B210" t="n">
         <v>3197</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" ht="14.4" customHeight="1">
+    <row r="211" hidden="1" ht="14.45" customHeight="1">
       <c r="B211" t="n">
         <v>3198</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" ht="14.4" customHeight="1">
+    <row r="212" hidden="1" ht="14.45" customHeight="1">
       <c r="B212" t="n">
         <v>3199</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" ht="14.4" customHeight="1">
+    <row r="213" hidden="1" ht="14.45" customHeight="1">
       <c r="B213" t="n">
         <v>3200</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" ht="14.4" customHeight="1">
+    <row r="214" hidden="1" ht="14.45" customHeight="1">
       <c r="B214" t="n">
         <v>3201</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" ht="14.4" customHeight="1">
+    <row r="215" hidden="1" ht="14.45" customHeight="1">
       <c r="B215" t="n">
         <v>3202</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" ht="14.4" customHeight="1">
+    <row r="216" hidden="1" ht="14.45" customHeight="1">
       <c r="B216" t="n">
         <v>3203</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" ht="14.4" customHeight="1">
+    <row r="217" hidden="1" ht="14.45" customHeight="1">
       <c r="B217" t="n">
         <v>3204</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" ht="14.4" customHeight="1">
+    <row r="218" hidden="1" ht="14.45" customHeight="1">
       <c r="B218" t="n">
         <v>3205</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" ht="14.4" customHeight="1">
+    <row r="219" hidden="1" ht="14.45" customHeight="1">
       <c r="B219" t="n">
         <v>3206</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" ht="14.4" customHeight="1">
+    <row r="220" hidden="1" ht="14.45" customHeight="1">
       <c r="B220" t="n">
         <v>3207</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" ht="14.4" customHeight="1">
+    <row r="221" hidden="1" ht="14.45" customHeight="1">
       <c r="B221" t="n">
         <v>3208</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" ht="14.4" customHeight="1">
+    <row r="222" hidden="1" ht="14.45" customHeight="1">
       <c r="B222" t="n">
         <v>3209</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" ht="14.4" customHeight="1">
+    <row r="223" hidden="1" ht="14.45" customHeight="1">
       <c r="B223" t="n">
         <v>3210</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" ht="14.4" customHeight="1">
+    <row r="224" hidden="1" ht="14.45" customHeight="1">
       <c r="B224" t="n">
         <v>3211</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" ht="14.4" customHeight="1">
+    <row r="225" hidden="1" ht="14.45" customHeight="1">
       <c r="B225" t="n">
         <v>3212</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" ht="14.4" customHeight="1">
+    <row r="226" hidden="1" ht="14.45" customHeight="1">
       <c r="B226" t="n">
         <v>3213</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" ht="14.4" customHeight="1">
+    <row r="227" hidden="1" ht="14.45" customHeight="1">
       <c r="B227" t="n">
         <v>3214</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" ht="14.4" customHeight="1">
+    <row r="228" hidden="1" ht="14.45" customHeight="1">
       <c r="B228" t="n">
         <v>3215</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" ht="14.4" customHeight="1">
+    <row r="229" hidden="1" ht="14.45" customHeight="1">
       <c r="B229" t="n">
         <v>3216</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" ht="14.4" customHeight="1">
+    <row r="230" hidden="1" ht="14.45" customHeight="1">
       <c r="B230" t="n">
         <v>3217</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" ht="14.4" customHeight="1">
+    <row r="231" hidden="1" ht="14.45" customHeight="1">
       <c r="B231" t="n">
         <v>3218</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" ht="14.4" customHeight="1">
+    <row r="232" hidden="1" ht="14.45" customHeight="1">
       <c r="B232" t="n">
         <v>3219</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" ht="14.4" customHeight="1">
+    <row r="233" hidden="1" ht="14.45" customHeight="1">
       <c r="B233" t="n">
         <v>3220</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" ht="14.4" customHeight="1">
+    <row r="234" hidden="1" ht="14.45" customHeight="1">
       <c r="B234" t="n">
         <v>3221</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" ht="14.4" customHeight="1">
+    <row r="235" hidden="1" ht="14.45" customHeight="1">
       <c r="B235" t="n">
         <v>3222</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" ht="14.4" customHeight="1">
+    <row r="236" hidden="1" ht="14.45" customHeight="1">
       <c r="B236" t="n">
         <v>3223</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" ht="14.4" customHeight="1">
+    <row r="237" hidden="1" ht="14.45" customHeight="1">
       <c r="B237" t="n">
         <v>3224</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" ht="14.4" customHeight="1">
+    <row r="238" hidden="1" ht="14.45" customHeight="1">
       <c r="B238" t="n">
         <v>3225</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" ht="14.4" customHeight="1">
+    <row r="239" hidden="1" ht="14.45" customHeight="1">
       <c r="B239" t="n">
         <v>3226</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" ht="14.4" customHeight="1">
+    <row r="240" hidden="1" ht="14.45" customHeight="1">
       <c r="B240" t="n">
         <v>3227</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" ht="14.4" customHeight="1">
+    <row r="241" hidden="1" ht="14.45" customHeight="1">
       <c r="B241" t="n">
         <v>3228</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" ht="14.4" customHeight="1">
+    <row r="242" hidden="1" ht="14.45" customHeight="1">
       <c r="B242" t="n">
         <v>3229</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" ht="14.4" customHeight="1">
+    <row r="243" hidden="1" ht="14.45" customHeight="1">
       <c r="B243" t="n">
         <v>3230</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" ht="14.4" customHeight="1">
+    <row r="244" hidden="1" ht="14.45" customHeight="1">
       <c r="B244" t="n">
         <v>3231</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" ht="14.4" customHeight="1">
+    <row r="245" hidden="1" ht="14.45" customHeight="1">
       <c r="B245" t="n">
         <v>3232</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" ht="14.4" customHeight="1">
+    <row r="246" hidden="1" ht="14.45" customHeight="1">
       <c r="B246" t="n">
         <v>3233</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" ht="14.4" customHeight="1">
+    <row r="247" hidden="1" ht="14.45" customHeight="1">
       <c r="B247" t="n">
         <v>3234</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" ht="14.4" customHeight="1">
+    <row r="248" hidden="1" ht="14.45" customHeight="1">
       <c r="B248" t="n">
         <v>3235</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" ht="14.4" customHeight="1">
+    <row r="249" hidden="1" ht="14.45" customHeight="1">
       <c r="B249" t="n">
         <v>3236</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" ht="14.4" customHeight="1">
+    <row r="250" hidden="1" ht="14.45" customHeight="1">
       <c r="B250" t="n">
         <v>3237</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" ht="14.4" customHeight="1">
+    <row r="251" hidden="1" ht="14.45" customHeight="1">
       <c r="B251" t="n">
         <v>3238</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" ht="14.4" customHeight="1">
+    <row r="252" hidden="1" ht="14.45" customHeight="1">
       <c r="B252" t="n">
         <v>3239</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" ht="14.4" customHeight="1">
+    <row r="253" hidden="1" ht="14.45" customHeight="1">
       <c r="B253" t="n">
         <v>3240</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" ht="14.4" customHeight="1">
+    <row r="254" hidden="1" ht="14.45" customHeight="1">
       <c r="B254" t="n">
         <v>3241</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" ht="14.4" customHeight="1">
+    <row r="255" hidden="1" ht="14.45" customHeight="1">
       <c r="B255" t="n">
         <v>3242</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" ht="14.4" customHeight="1">
+    <row r="256" hidden="1" ht="14.45" customHeight="1">
       <c r="B256" t="n">
         <v>3243</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" ht="14.4" customHeight="1">
+    <row r="257" hidden="1" ht="14.45" customHeight="1">
       <c r="B257" t="n">
         <v>3244</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" ht="14.4" customHeight="1">
+    <row r="258" hidden="1" ht="14.45" customHeight="1">
       <c r="B258" t="n">
         <v>3245</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" ht="14.4" customHeight="1">
+    <row r="259" hidden="1" ht="14.45" customHeight="1">
       <c r="B259" t="n">
         <v>3246</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" ht="14.4" customHeight="1">
+    <row r="260" hidden="1" ht="14.45" customHeight="1">
       <c r="B260" t="n">
         <v>3247</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" ht="14.4" customHeight="1">
+    <row r="261" hidden="1" ht="14.45" customHeight="1">
       <c r="B261" t="n">
         <v>3248</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" ht="14.4" customHeight="1">
+    <row r="262" hidden="1" ht="14.45" customHeight="1">
       <c r="B262" t="n">
         <v>3249</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" ht="14.4" customHeight="1">
+    <row r="263" hidden="1" ht="14.45" customHeight="1">
       <c r="B263" t="n">
         <v>3250</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" ht="14.4" customHeight="1">
+    <row r="264" hidden="1" ht="14.45" customHeight="1">
       <c r="B264" t="n">
         <v>3251</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" ht="14.4" customHeight="1">
+    <row r="265" hidden="1" ht="14.45" customHeight="1">
       <c r="B265" t="n">
         <v>3252</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" ht="14.4" customHeight="1">
+    <row r="266" hidden="1" ht="14.45" customHeight="1">
       <c r="B266" t="n">
         <v>3253</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" ht="14.4" customHeight="1">
+    <row r="267" hidden="1" ht="14.45" customHeight="1">
       <c r="B267" t="n">
         <v>3254</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" ht="14.4" customHeight="1">
+    <row r="268" hidden="1" ht="14.45" customHeight="1">
       <c r="B268" t="n">
         <v>3255</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" ht="14.4" customHeight="1">
+    <row r="269" hidden="1" ht="14.45" customHeight="1">
       <c r="B269" t="n">
         <v>3256</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" ht="14.4" customHeight="1">
+    <row r="270" hidden="1" ht="14.45" customHeight="1">
       <c r="B270" t="n">
         <v>3257</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" ht="14.4" customHeight="1">
+    <row r="271" hidden="1" ht="14.45" customHeight="1">
       <c r="B271" t="n">
         <v>3258</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" ht="14.4" customHeight="1">
+    <row r="272" hidden="1" ht="14.45" customHeight="1">
       <c r="B272" t="n">
         <v>3259</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" ht="14.4" customHeight="1">
+    <row r="273" hidden="1" ht="14.45" customHeight="1">
       <c r="B273" t="n">
         <v>3260</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" ht="14.4" customHeight="1">
+    <row r="274" hidden="1" ht="14.45" customHeight="1">
       <c r="B274" t="n">
         <v>3261</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" ht="14.4" customHeight="1">
+    <row r="275" hidden="1" ht="14.45" customHeight="1">
       <c r="B275" t="n">
         <v>3262</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" ht="14.4" customHeight="1">
+    <row r="276" hidden="1" ht="14.45" customHeight="1">
       <c r="B276" t="n">
         <v>3263</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" ht="14.4" customHeight="1">
+    <row r="277" hidden="1" ht="14.45" customHeight="1">
       <c r="B277" t="n">
         <v>3264</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" ht="14.4" customHeight="1">
+    <row r="278" hidden="1" ht="14.45" customHeight="1">
       <c r="B278" t="n">
         <v>3265</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" ht="14.4" customHeight="1">
+    <row r="279" hidden="1" ht="14.45" customHeight="1">
       <c r="B279" t="n">
         <v>3266</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" ht="14.4" customHeight="1">
+    <row r="280" hidden="1" ht="14.45" customHeight="1">
       <c r="B280" t="n">
         <v>3267</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" ht="14.4" customHeight="1">
+    <row r="281" hidden="1" ht="14.45" customHeight="1">
       <c r="B281" t="n">
         <v>3268</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" ht="14.4" customHeight="1">
+    <row r="282" hidden="1" ht="14.45" customHeight="1">
       <c r="B282" t="n">
         <v>3269</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" ht="14.4" customHeight="1">
+    <row r="283" hidden="1" ht="14.45" customHeight="1">
       <c r="B283" t="n">
         <v>3270</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" ht="14.4" customHeight="1">
+    <row r="284" hidden="1" ht="14.45" customHeight="1">
       <c r="B284" t="n">
         <v>3271</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" ht="14.4" customHeight="1">
+    <row r="285" hidden="1" ht="14.45" customHeight="1">
       <c r="B285" t="n">
         <v>3272</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" ht="14.4" customHeight="1">
+    <row r="286" hidden="1" ht="14.45" customHeight="1">
       <c r="B286" t="n">
         <v>3273</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" ht="14.4" customHeight="1">
+    <row r="287" hidden="1" ht="14.45" customHeight="1">
       <c r="B287" t="n">
         <v>3274</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" ht="14.4" customHeight="1">
+    <row r="288" hidden="1" ht="14.45" customHeight="1">
       <c r="B288" t="n">
         <v>3275</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" ht="14.4" customHeight="1">
+    <row r="289" hidden="1" ht="14.45" customHeight="1">
       <c r="B289" t="n">
         <v>3276</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" ht="14.4" customHeight="1">
+    <row r="290" hidden="1" ht="14.45" customHeight="1">
       <c r="B290" t="n">
         <v>3277</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" ht="14.4" customHeight="1">
+    <row r="291" hidden="1" ht="14.45" customHeight="1">
       <c r="B291" t="n">
         <v>3278</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" ht="14.4" customHeight="1">
+    <row r="292" hidden="1" ht="14.45" customHeight="1">
       <c r="B292" t="n">
         <v>3279</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" ht="14.4" customHeight="1">
+    <row r="293" hidden="1" ht="14.45" customHeight="1">
       <c r="B293" t="n">
         <v>3280</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" ht="14.4" customHeight="1">
+    <row r="294" hidden="1" ht="14.45" customHeight="1">
       <c r="B294" t="n">
         <v>3281</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" ht="14.4" customHeight="1">
+    <row r="295" hidden="1" ht="14.45" customHeight="1">
       <c r="B295" t="n">
         <v>3282</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" ht="14.4" customHeight="1">
+    <row r="296" hidden="1" ht="14.45" customHeight="1">
       <c r="B296" t="n">
         <v>3283</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" ht="14.4" customHeight="1">
+    <row r="297" hidden="1" ht="14.45" customHeight="1">
       <c r="B297" t="n">
         <v>3284</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" ht="14.4" customHeight="1">
+    <row r="298" hidden="1" ht="14.45" customHeight="1">
       <c r="B298" t="n">
         <v>3285</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" ht="14.4" customHeight="1">
+    <row r="299" hidden="1" ht="14.45" customHeight="1">
       <c r="B299" t="n">
         <v>3286</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" ht="14.4" customHeight="1">
+    <row r="300" hidden="1" ht="14.45" customHeight="1">
       <c r="B300" t="n">
         <v>3287</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" ht="14.4" customHeight="1">
+    <row r="301" hidden="1" ht="14.45" customHeight="1">
       <c r="B301" t="n">
         <v>3288</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" ht="14.4" customHeight="1">
+    <row r="302" hidden="1" ht="14.45" customHeight="1">
       <c r="B302" t="n">
         <v>3289</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" ht="14.4" customHeight="1">
+    <row r="303" hidden="1" ht="14.45" customHeight="1">
       <c r="B303" t="n">
         <v>3290</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" ht="14.4" customHeight="1">
+    <row r="304" hidden="1" ht="14.45" customHeight="1">
       <c r="B304" t="n">
         <v>3291</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" ht="14.4" customHeight="1">
+    <row r="305" hidden="1" ht="14.45" customHeight="1">
       <c r="B305" t="n">
         <v>3292</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" ht="14.4" customHeight="1">
+    <row r="306" hidden="1" ht="14.45" customHeight="1">
       <c r="B306" t="n">
         <v>3293</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" ht="14.4" customHeight="1">
+    <row r="307" hidden="1" ht="14.45" customHeight="1">
       <c r="B307" t="n">
         <v>3294</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" ht="14.4" customHeight="1">
+    <row r="308" hidden="1" ht="14.45" customHeight="1">
       <c r="B308" t="n">
         <v>3295</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" ht="14.4" customHeight="1">
+    <row r="309" hidden="1" ht="14.45" customHeight="1">
       <c r="B309" t="n">
         <v>3296</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" ht="14.4" customHeight="1">
+    <row r="310" hidden="1" ht="14.45" customHeight="1">
       <c r="B310" t="n">
         <v>3297</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" ht="14.4" customHeight="1">
+    <row r="311" hidden="1" ht="14.45" customHeight="1">
       <c r="B311" t="n">
         <v>3298</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" ht="14.4" customHeight="1">
+    <row r="312" hidden="1" ht="14.45" customHeight="1">
       <c r="B312" t="n">
         <v>3299</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" ht="14.4" customHeight="1">
+    <row r="313" hidden="1" ht="14.45" customHeight="1">
       <c r="B313" t="n">
         <v>3300</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" ht="14.4" customHeight="1">
+    <row r="314" hidden="1" ht="14.45" customHeight="1">
       <c r="B314" t="n">
         <v>3301</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" ht="14.4" customHeight="1">
+    <row r="315" hidden="1" ht="14.45" customHeight="1">
       <c r="B315" t="n">
         <v>3302</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" ht="14.4" customHeight="1">
+    <row r="316" hidden="1" ht="14.45" customHeight="1">
       <c r="B316" t="n">
         <v>3303</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" ht="14.4" customHeight="1">
+    <row r="317" hidden="1" ht="14.45" customHeight="1">
       <c r="B317" t="n">
         <v>3304</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" ht="14.4" customHeight="1">
+    <row r="318" hidden="1" ht="14.45" customHeight="1">
       <c r="B318" t="n">
         <v>3305</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" ht="14.4" customHeight="1">
+    <row r="319" hidden="1" ht="14.45" customHeight="1">
       <c r="B319" t="n">
         <v>3306</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" ht="14.4" customHeight="1">
+    <row r="320" hidden="1" ht="14.45" customHeight="1">
       <c r="B320" t="n">
         <v>3307</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" ht="14.4" customHeight="1">
+    <row r="321" hidden="1" ht="14.45" customHeight="1">
       <c r="B321" t="n">
         <v>3308</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" ht="14.4" customHeight="1">
+    <row r="322" hidden="1" ht="14.45" customHeight="1">
       <c r="B322" t="n">
         <v>3309</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" ht="14.4" customHeight="1">
+    <row r="323" hidden="1" ht="14.45" customHeight="1">
       <c r="B323" t="n">
         <v>3310</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" ht="14.4" customHeight="1">
+    <row r="324" hidden="1" ht="14.45" customHeight="1">
       <c r="B324" t="n">
         <v>3311</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" ht="14.4" customHeight="1">
+    <row r="325" hidden="1" ht="14.45" customHeight="1">
       <c r="B325" t="n">
         <v>3312</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" ht="14.4" customHeight="1">
+    <row r="326" hidden="1" ht="14.45" customHeight="1">
       <c r="B326" t="n">
         <v>3313</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" ht="14.4" customHeight="1">
+    <row r="327" hidden="1" ht="14.45" customHeight="1">
       <c r="B327" t="n">
         <v>3314</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" ht="14.4" customHeight="1">
+    <row r="328" hidden="1" ht="14.45" customHeight="1">
       <c r="B328" t="n">
         <v>3315</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" ht="14.4" customHeight="1">
+    <row r="329" hidden="1" ht="14.45" customHeight="1">
       <c r="B329" t="n">
         <v>3316</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" ht="14.4" customHeight="1">
+    <row r="330" hidden="1" ht="14.45" customHeight="1">
       <c r="B330" t="n">
         <v>3317</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" ht="14.4" customHeight="1">
+    <row r="331" hidden="1" ht="14.45" customHeight="1">
       <c r="B331" t="n">
         <v>3318</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" ht="14.4" customHeight="1">
+    <row r="332" hidden="1" ht="14.45" customHeight="1">
       <c r="B332" t="n">
         <v>3319</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" ht="14.4" customHeight="1">
+    <row r="333" hidden="1" ht="14.45" customHeight="1">
       <c r="B333" t="n">
         <v>3320</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" ht="14.4" customHeight="1">
+    <row r="334" hidden="1" ht="14.45" customHeight="1">
       <c r="B334" t="n">
         <v>3321</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" ht="14.4" customHeight="1">
+    <row r="335" hidden="1" ht="14.45" customHeight="1">
       <c r="B335" t="n">
         <v>3322</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" ht="14.4" customHeight="1">
+    <row r="336" hidden="1" ht="14.45" customHeight="1">
       <c r="B336" t="n">
         <v>3323</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" ht="14.4" customHeight="1">
+    <row r="337" hidden="1" ht="14.45" customHeight="1">
       <c r="B337" t="n">
         <v>3324</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" ht="14.4" customHeight="1">
+    <row r="338" hidden="1" ht="14.45" customHeight="1">
       <c r="B338" t="n">
         <v>3325</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" ht="14.4" customHeight="1">
+    <row r="339" hidden="1" ht="14.45" customHeight="1">
       <c r="B339" t="n">
         <v>3326</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" ht="14.4" customHeight="1">
+    <row r="340" hidden="1" ht="14.45" customHeight="1">
       <c r="B340" t="n">
         <v>3327</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" ht="14.4" customHeight="1">
+    <row r="341" hidden="1" ht="14.45" customHeight="1">
       <c r="B341" t="n">
         <v>3328</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" ht="14.4" customHeight="1">
+    <row r="342" hidden="1" ht="14.45" customHeight="1">
       <c r="B342" t="n">
         <v>3329</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" ht="14.4" customHeight="1">
+    <row r="343" hidden="1" ht="14.45" customHeight="1">
       <c r="B343" t="n">
         <v>3330</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" ht="14.4" customHeight="1">
+    <row r="344" hidden="1" ht="14.45" customHeight="1">
       <c r="B344" t="n">
         <v>3331</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" ht="14.4" customHeight="1">
+    <row r="345" hidden="1" ht="14.45" customHeight="1">
       <c r="B345" t="n">
         <v>3332</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" ht="14.4" customHeight="1">
+    <row r="346" hidden="1" ht="14.45" customHeight="1">
       <c r="B346" t="n">
         <v>3333</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" ht="14.4" customHeight="1">
+    <row r="347" hidden="1" ht="14.45" customHeight="1">
       <c r="B347" t="n">
         <v>3334</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" ht="14.4" customHeight="1">
+    <row r="348" hidden="1" ht="14.45" customHeight="1">
       <c r="B348" t="n">
         <v>3335</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" ht="14.4" customHeight="1">
+    <row r="349" hidden="1" ht="14.45" customHeight="1">
       <c r="B349" t="n">
         <v>3336</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" ht="14.4" customHeight="1">
+    <row r="350" hidden="1" ht="14.45" customHeight="1">
       <c r="B350" t="n">
         <v>3337</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" ht="14.4" customHeight="1">
+    <row r="351" hidden="1" ht="14.45" customHeight="1">
       <c r="B351" t="n">
         <v>3338</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" ht="14.4" customHeight="1">
+    <row r="352" hidden="1" ht="14.45" customHeight="1">
       <c r="B352" t="n">
         <v>3339</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" ht="14.4" customHeight="1">
+    <row r="353" hidden="1" ht="14.45" customHeight="1">
       <c r="B353" t="n">
         <v>3340</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" ht="14.4" customHeight="1">
+    <row r="354" hidden="1" ht="14.45" customHeight="1">
       <c r="B354" t="n">
         <v>3341</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" ht="14.4" customHeight="1">
+    <row r="355" hidden="1" ht="14.45" customHeight="1">
       <c r="B355" t="n">
         <v>3342</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" ht="14.4" customHeight="1">
+    <row r="356" hidden="1" ht="14.45" customHeight="1">
       <c r="B356" t="n">
         <v>3343</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" ht="14.4" customHeight="1">
+    <row r="357" hidden="1" ht="14.45" customHeight="1">
       <c r="B357" t="n">
         <v>3344</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" ht="14.4" customHeight="1">
+    <row r="358" hidden="1" ht="14.45" customHeight="1">
       <c r="B358" t="n">
         <v>3345</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" ht="14.4" customHeight="1">
+    <row r="359" hidden="1" ht="14.45" customHeight="1">
       <c r="B359" t="n">
         <v>3346</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" ht="14.4" customHeight="1">
+    <row r="360" hidden="1" ht="14.45" customHeight="1">
       <c r="B360" t="n">
         <v>3347</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" ht="14.4" customHeight="1">
+    <row r="361" hidden="1" ht="14.45" customHeight="1">
       <c r="B361" t="n">
         <v>3348</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" ht="14.4" customHeight="1">
+    <row r="362" hidden="1" ht="14.45" customHeight="1">
       <c r="B362" t="n">
         <v>3349</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" ht="14.4" customHeight="1">
+    <row r="363" hidden="1" ht="14.45" customHeight="1">
       <c r="B363" t="n">
         <v>3350</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" ht="14.4" customHeight="1">
+    <row r="364" hidden="1" ht="14.45" customHeight="1">
       <c r="B364" t="n">
         <v>3351</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" ht="14.4" customHeight="1">
+    <row r="365" hidden="1" ht="14.45" customHeight="1">
       <c r="B365" t="n">
         <v>3352</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" ht="14.4" customHeight="1">
+    <row r="366" hidden="1" ht="14.45" customHeight="1">
       <c r="B366" t="n">
         <v>3353</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" ht="14.4" customHeight="1">
+    <row r="367" hidden="1" ht="14.45" customHeight="1">
       <c r="B367" t="n">
         <v>3354</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" ht="14.4" customHeight="1">
+    <row r="368" hidden="1" ht="14.45" customHeight="1">
       <c r="B368" t="n">
         <v>3355</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" ht="14.4" customHeight="1">
+    <row r="369" hidden="1" ht="14.45" customHeight="1">
       <c r="B369" t="n">
         <v>3356</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" ht="14.4" customHeight="1">
+    <row r="370" hidden="1" ht="14.45" customHeight="1">
       <c r="A370" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7409,7 +7424,7 @@
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" ht="14.4" customHeight="1">
+    <row r="371" hidden="1" ht="14.45" customHeight="1">
       <c r="A371" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7466,7 +7481,7 @@
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" ht="14.4" customHeight="1">
+    <row r="372" hidden="1" ht="14.45" customHeight="1">
       <c r="A372" t="inlineStr">
         <is>
           <t>EMEA</t>
@@ -7523,1085 +7538,1085 @@
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" ht="14.4" customHeight="1">
+    <row r="373" hidden="1" ht="14.45" customHeight="1">
       <c r="B373" t="n">
         <v>3360</v>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" ht="14.4" customHeight="1">
+    <row r="374" hidden="1" ht="14.45" customHeight="1">
       <c r="B374" t="n">
         <v>3361</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" ht="14.4" customHeight="1">
+    <row r="375" hidden="1" ht="14.45" customHeight="1">
       <c r="B375" t="n">
         <v>3362</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" ht="14.4" customHeight="1">
+    <row r="376" hidden="1" ht="14.45" customHeight="1">
       <c r="B376" t="n">
         <v>3363</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" ht="14.4" customHeight="1">
+    <row r="377" hidden="1" ht="14.45" customHeight="1">
       <c r="B377" t="n">
         <v>3364</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" ht="14.4" customHeight="1">
+    <row r="378" hidden="1" ht="14.45" customHeight="1">
       <c r="B378" t="n">
         <v>3365</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" ht="14.4" customHeight="1">
+    <row r="379" hidden="1" ht="14.45" customHeight="1">
       <c r="B379" t="n">
         <v>3366</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" ht="14.4" customHeight="1">
+    <row r="380" hidden="1" ht="14.45" customHeight="1">
       <c r="B380" t="n">
         <v>3367</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" ht="14.4" customHeight="1">
+    <row r="381" hidden="1" ht="14.45" customHeight="1">
       <c r="B381" t="n">
         <v>3368</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" ht="14.4" customHeight="1">
+    <row r="382" hidden="1" ht="14.45" customHeight="1">
       <c r="B382" t="n">
         <v>3369</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" ht="14.4" customHeight="1">
+    <row r="383" hidden="1" ht="14.45" customHeight="1">
       <c r="B383" t="n">
         <v>3370</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" ht="14.4" customHeight="1">
+    <row r="384" hidden="1" ht="14.45" customHeight="1">
       <c r="B384" t="n">
         <v>3371</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" ht="14.4" customHeight="1">
+    <row r="385" hidden="1" ht="14.45" customHeight="1">
       <c r="B385" t="n">
         <v>3372</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" ht="14.4" customHeight="1">
+    <row r="386" hidden="1" ht="14.45" customHeight="1">
       <c r="B386" t="n">
         <v>3373</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" ht="14.4" customHeight="1">
+    <row r="387" hidden="1" ht="14.45" customHeight="1">
       <c r="B387" t="n">
         <v>3374</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" ht="14.4" customHeight="1">
+    <row r="388" hidden="1" ht="14.45" customHeight="1">
       <c r="B388" t="n">
         <v>3375</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" ht="14.4" customHeight="1">
+    <row r="389" hidden="1" ht="14.45" customHeight="1">
       <c r="B389" t="n">
         <v>3376</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" ht="14.4" customHeight="1">
+    <row r="390" hidden="1" ht="14.45" customHeight="1">
       <c r="B390" t="n">
         <v>3377</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" ht="14.4" customHeight="1">
+    <row r="391" hidden="1" ht="14.45" customHeight="1">
       <c r="B391" t="n">
         <v>3378</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" ht="14.4" customHeight="1">
+    <row r="392" hidden="1" ht="14.45" customHeight="1">
       <c r="B392" t="n">
         <v>3379</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" ht="14.4" customHeight="1">
+    <row r="393" hidden="1" ht="14.45" customHeight="1">
       <c r="B393" t="n">
         <v>3380</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" ht="14.4" customHeight="1">
+    <row r="394" hidden="1" ht="14.45" customHeight="1">
       <c r="B394" t="n">
         <v>3381</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" ht="14.4" customHeight="1">
+    <row r="395" hidden="1" ht="14.45" customHeight="1">
       <c r="B395" t="n">
         <v>3382</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" ht="14.4" customHeight="1">
+    <row r="396" hidden="1" ht="14.45" customHeight="1">
       <c r="B396" t="n">
         <v>3383</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" ht="14.4" customHeight="1">
+    <row r="397" hidden="1" ht="14.45" customHeight="1">
       <c r="B397" t="n">
         <v>3384</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" ht="14.4" customHeight="1">
+    <row r="398" hidden="1" ht="14.45" customHeight="1">
       <c r="B398" t="n">
         <v>3385</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" ht="14.4" customHeight="1">
+    <row r="399" hidden="1" ht="14.45" customHeight="1">
       <c r="B399" t="n">
         <v>3386</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" ht="14.4" customHeight="1">
+    <row r="400" hidden="1" ht="14.45" customHeight="1">
       <c r="B400" t="n">
         <v>3387</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" ht="14.4" customHeight="1">
+    <row r="401" hidden="1" ht="14.45" customHeight="1">
       <c r="B401" t="n">
         <v>3388</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" ht="14.4" customHeight="1">
+    <row r="402" hidden="1" ht="14.45" customHeight="1">
       <c r="B402" t="n">
         <v>3389</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" ht="14.4" customHeight="1">
+    <row r="403" hidden="1" ht="14.45" customHeight="1">
       <c r="B403" t="n">
         <v>3390</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" ht="14.4" customHeight="1">
+    <row r="404" hidden="1" ht="14.45" customHeight="1">
       <c r="B404" t="n">
         <v>3391</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" ht="14.4" customHeight="1">
+    <row r="405" hidden="1" ht="14.45" customHeight="1">
       <c r="B405" t="n">
         <v>3392</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" ht="14.4" customHeight="1">
+    <row r="406" hidden="1" ht="14.45" customHeight="1">
       <c r="B406" t="n">
         <v>3393</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" ht="14.4" customHeight="1">
+    <row r="407" hidden="1" ht="14.45" customHeight="1">
       <c r="B407" t="n">
         <v>3394</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" ht="14.4" customHeight="1">
+    <row r="408" hidden="1" ht="14.45" customHeight="1">
       <c r="B408" t="n">
         <v>3395</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" ht="14.4" customHeight="1">
+    <row r="409" hidden="1" ht="14.45" customHeight="1">
       <c r="B409" t="n">
         <v>3396</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" ht="14.4" customHeight="1">
+    <row r="410" hidden="1" ht="14.45" customHeight="1">
       <c r="B410" t="n">
         <v>3397</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" ht="14.4" customHeight="1">
+    <row r="411" hidden="1" ht="14.45" customHeight="1">
       <c r="B411" t="n">
         <v>3398</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" ht="14.4" customHeight="1">
+    <row r="412" hidden="1" ht="14.45" customHeight="1">
       <c r="B412" t="n">
         <v>3399</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" ht="14.4" customHeight="1">
+    <row r="413" hidden="1" ht="14.45" customHeight="1">
       <c r="B413" t="n">
         <v>3400</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" ht="14.4" customHeight="1">
+    <row r="414" hidden="1" ht="14.45" customHeight="1">
       <c r="B414" t="n">
         <v>3401</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" ht="14.4" customHeight="1">
+    <row r="415" hidden="1" ht="14.45" customHeight="1">
       <c r="B415" t="n">
         <v>3402</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" ht="14.4" customHeight="1">
+    <row r="416" hidden="1" ht="14.45" customHeight="1">
       <c r="B416" t="n">
         <v>3403</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" ht="14.4" customHeight="1">
+    <row r="417" hidden="1" ht="14.45" customHeight="1">
       <c r="B417" t="n">
         <v>3404</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" ht="14.4" customHeight="1">
+    <row r="418" hidden="1" ht="14.45" customHeight="1">
       <c r="B418" t="n">
         <v>3405</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" ht="14.4" customHeight="1">
+    <row r="419" hidden="1" ht="14.45" customHeight="1">
       <c r="B419" t="n">
         <v>3406</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" ht="14.4" customHeight="1">
+    <row r="420" hidden="1" ht="14.45" customHeight="1">
       <c r="B420" t="n">
         <v>3407</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" ht="14.4" customHeight="1">
+    <row r="421" hidden="1" ht="14.45" customHeight="1">
       <c r="B421" t="n">
         <v>3408</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" ht="14.4" customHeight="1">
+    <row r="422" hidden="1" ht="14.45" customHeight="1">
       <c r="B422" t="n">
         <v>3409</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" ht="14.4" customHeight="1">
+    <row r="423" hidden="1" ht="14.45" customHeight="1">
       <c r="B423" t="n">
         <v>3410</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" ht="14.4" customHeight="1">
+    <row r="424" hidden="1" ht="14.45" customHeight="1">
       <c r="B424" t="n">
         <v>3411</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" ht="14.4" customHeight="1">
+    <row r="425" hidden="1" ht="14.45" customHeight="1">
       <c r="B425" t="n">
         <v>3412</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" ht="14.4" customHeight="1">
+    <row r="426" hidden="1" ht="14.45" customHeight="1">
       <c r="B426" t="n">
         <v>3413</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" ht="14.4" customHeight="1">
+    <row r="427" hidden="1" ht="14.45" customHeight="1">
       <c r="B427" t="n">
         <v>3414</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" ht="14.4" customHeight="1">
+    <row r="428" hidden="1" ht="14.45" customHeight="1">
       <c r="B428" t="n">
         <v>3415</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" ht="14.4" customHeight="1">
+    <row r="429" hidden="1" ht="14.45" customHeight="1">
       <c r="B429" t="n">
         <v>3416</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" ht="14.4" customHeight="1">
+    <row r="430" hidden="1" ht="14.45" customHeight="1">
       <c r="B430" t="n">
         <v>3417</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" ht="14.4" customHeight="1">
+    <row r="431" hidden="1" ht="14.45" customHeight="1">
       <c r="B431" t="n">
         <v>3418</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" ht="14.4" customHeight="1">
+    <row r="432" hidden="1" ht="14.45" customHeight="1">
       <c r="B432" t="n">
         <v>3419</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" ht="14.4" customHeight="1">
+    <row r="433" hidden="1" ht="14.45" customHeight="1">
       <c r="B433" t="n">
         <v>3420</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" ht="14.4" customHeight="1">
+    <row r="434" hidden="1" ht="14.45" customHeight="1">
       <c r="B434" t="n">
         <v>3421</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" ht="14.4" customHeight="1">
+    <row r="435" hidden="1" ht="14.45" customHeight="1">
       <c r="B435" t="n">
         <v>3422</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" ht="14.4" customHeight="1">
+    <row r="436" hidden="1" ht="14.45" customHeight="1">
       <c r="B436" t="n">
         <v>3423</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" ht="14.4" customHeight="1">
+    <row r="437" hidden="1" ht="14.45" customHeight="1">
       <c r="B437" t="n">
         <v>3424</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" ht="14.4" customHeight="1">
+    <row r="438" hidden="1" ht="14.45" customHeight="1">
       <c r="B438" t="n">
         <v>3425</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" ht="14.4" customHeight="1">
+    <row r="439" hidden="1" ht="14.45" customHeight="1">
       <c r="B439" t="n">
         <v>3426</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" ht="14.4" customHeight="1">
+    <row r="440" hidden="1" ht="14.45" customHeight="1">
       <c r="B440" t="n">
         <v>3427</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" ht="14.4" customHeight="1">
+    <row r="441" hidden="1" ht="14.45" customHeight="1">
       <c r="B441" t="n">
         <v>3428</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" ht="14.4" customHeight="1">
+    <row r="442" hidden="1" ht="14.45" customHeight="1">
       <c r="B442" t="n">
         <v>3429</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" ht="14.4" customHeight="1">
+    <row r="443" hidden="1" ht="14.45" customHeight="1">
       <c r="B443" t="n">
         <v>3430</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" ht="14.4" customHeight="1">
+    <row r="444" hidden="1" ht="14.45" customHeight="1">
       <c r="B444" t="n">
         <v>3431</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" ht="14.4" customHeight="1">
+    <row r="445" hidden="1" ht="14.45" customHeight="1">
       <c r="B445" t="n">
         <v>3432</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" ht="14.4" customHeight="1">
+    <row r="446" hidden="1" ht="14.45" customHeight="1">
       <c r="B446" t="n">
         <v>3433</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" ht="14.4" customHeight="1">
+    <row r="447" hidden="1" ht="14.45" customHeight="1">
       <c r="B447" t="n">
         <v>3434</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" ht="14.4" customHeight="1">
+    <row r="448" hidden="1" ht="14.45" customHeight="1">
       <c r="B448" t="n">
         <v>3435</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" ht="14.4" customHeight="1">
+    <row r="449" hidden="1" ht="14.45" customHeight="1">
       <c r="B449" t="n">
         <v>3436</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" ht="14.4" customHeight="1">
+    <row r="450" hidden="1" ht="14.45" customHeight="1">
       <c r="B450" t="n">
         <v>3437</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" ht="14.4" customHeight="1">
+    <row r="451" hidden="1" ht="14.45" customHeight="1">
       <c r="B451" t="n">
         <v>3438</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" ht="14.4" customHeight="1">
+    <row r="452" hidden="1" ht="14.45" customHeight="1">
       <c r="B452" t="n">
         <v>3439</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" ht="14.4" customHeight="1">
+    <row r="453" hidden="1" ht="14.45" customHeight="1">
       <c r="B453" t="n">
         <v>3440</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" ht="14.4" customHeight="1">
+    <row r="454" hidden="1" ht="14.45" customHeight="1">
       <c r="B454" t="n">
         <v>3441</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" ht="14.4" customHeight="1">
+    <row r="455" hidden="1" ht="14.45" customHeight="1">
       <c r="B455" t="n">
         <v>3442</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" ht="14.4" customHeight="1">
+    <row r="456" hidden="1" ht="14.45" customHeight="1">
       <c r="B456" t="n">
         <v>3443</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" ht="14.4" customHeight="1">
+    <row r="457" hidden="1" ht="14.45" customHeight="1">
       <c r="B457" t="n">
         <v>3444</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" ht="14.4" customHeight="1">
+    <row r="458" hidden="1" ht="14.45" customHeight="1">
       <c r="B458" t="n">
         <v>3445</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" ht="14.4" customHeight="1">
+    <row r="459" hidden="1" ht="14.45" customHeight="1">
       <c r="B459" t="n">
         <v>3446</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" ht="14.4" customHeight="1">
+    <row r="460" hidden="1" ht="14.45" customHeight="1">
       <c r="B460" t="n">
         <v>3447</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" ht="14.4" customHeight="1">
+    <row r="461" hidden="1" ht="14.45" customHeight="1">
       <c r="B461" t="n">
         <v>3448</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" ht="14.4" customHeight="1">
+    <row r="462" hidden="1" ht="14.45" customHeight="1">
       <c r="B462" t="n">
         <v>3449</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" ht="14.4" customHeight="1">
+    <row r="463" hidden="1" ht="14.45" customHeight="1">
       <c r="B463" t="n">
         <v>3450</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" ht="14.4" customHeight="1">
+    <row r="464" hidden="1" ht="14.45" customHeight="1">
       <c r="B464" t="n">
         <v>3451</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" ht="14.4" customHeight="1">
+    <row r="465" hidden="1" ht="14.45" customHeight="1">
       <c r="B465" t="n">
         <v>3452</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" ht="14.4" customHeight="1">
+    <row r="466" hidden="1" ht="14.45" customHeight="1">
       <c r="B466" t="n">
         <v>3453</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" ht="14.4" customHeight="1">
+    <row r="467" hidden="1" ht="14.45" customHeight="1">
       <c r="B467" t="n">
         <v>3454</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" ht="14.4" customHeight="1">
+    <row r="468" hidden="1" ht="14.45" customHeight="1">
       <c r="B468" t="n">
         <v>3455</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" ht="14.4" customHeight="1">
+    <row r="469" hidden="1" ht="14.45" customHeight="1">
       <c r="B469" t="n">
         <v>3456</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" ht="14.4" customHeight="1">
+    <row r="470" hidden="1" ht="14.45" customHeight="1">
       <c r="B470" t="n">
         <v>3457</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" ht="14.4" customHeight="1">
+    <row r="471" hidden="1" ht="14.45" customHeight="1">
       <c r="B471" t="n">
         <v>3458</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" ht="14.4" customHeight="1">
+    <row r="472" hidden="1" ht="14.45" customHeight="1">
       <c r="B472" t="n">
         <v>3459</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" ht="14.4" customHeight="1">
+    <row r="473" hidden="1" ht="14.45" customHeight="1">
       <c r="B473" t="n">
         <v>3460</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" ht="14.4" customHeight="1">
+    <row r="474" hidden="1" ht="14.45" customHeight="1">
       <c r="B474" t="n">
         <v>3461</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" ht="14.4" customHeight="1">
+    <row r="475" hidden="1" ht="14.45" customHeight="1">
       <c r="B475" t="n">
         <v>3462</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" ht="14.4" customHeight="1">
+    <row r="476" hidden="1" ht="14.45" customHeight="1">
       <c r="B476" t="n">
         <v>3463</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" ht="14.4" customHeight="1">
+    <row r="477" hidden="1" ht="14.45" customHeight="1">
       <c r="B477" t="n">
         <v>3464</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" ht="14.4" customHeight="1">
+    <row r="478" hidden="1" ht="14.45" customHeight="1">
       <c r="B478" t="n">
         <v>3465</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" ht="14.4" customHeight="1">
+    <row r="479" hidden="1" ht="14.45" customHeight="1">
       <c r="B479" t="n">
         <v>3466</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" ht="14.4" customHeight="1">
+    <row r="480" hidden="1" ht="14.45" customHeight="1">
       <c r="B480" t="n">
         <v>3467</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" ht="14.4" customHeight="1">
+    <row r="481" hidden="1" ht="14.45" customHeight="1">
       <c r="B481" t="n">
         <v>3468</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" ht="14.4" customHeight="1">
+    <row r="482" hidden="1" ht="14.45" customHeight="1">
       <c r="B482" t="n">
         <v>3469</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" ht="14.4" customHeight="1">
+    <row r="483" hidden="1" ht="14.45" customHeight="1">
       <c r="B483" t="n">
         <v>3470</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" ht="14.4" customHeight="1">
+    <row r="484" hidden="1" ht="14.45" customHeight="1">
       <c r="B484" t="n">
         <v>3471</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" ht="14.4" customHeight="1">
+    <row r="485" hidden="1" ht="14.45" customHeight="1">
       <c r="B485" t="n">
         <v>3472</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" ht="14.4" customHeight="1">
+    <row r="486" hidden="1" ht="14.45" customHeight="1">
       <c r="B486" t="n">
         <v>3473</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" ht="14.4" customHeight="1">
+    <row r="487" hidden="1" ht="14.45" customHeight="1">
       <c r="B487" t="n">
         <v>3474</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" ht="14.4" customHeight="1">
+    <row r="488" hidden="1" ht="14.45" customHeight="1">
       <c r="B488" t="n">
         <v>3475</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" ht="14.4" customHeight="1">
+    <row r="489" hidden="1" ht="14.45" customHeight="1">
       <c r="B489" t="n">
         <v>3476</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" ht="14.4" customHeight="1">
+    <row r="490" hidden="1" ht="14.45" customHeight="1">
       <c r="B490" t="n">
         <v>3477</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" ht="14.4" customHeight="1">
+    <row r="491" hidden="1" ht="14.45" customHeight="1">
       <c r="B491" t="n">
         <v>3478</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" ht="14.4" customHeight="1">
+    <row r="492" hidden="1" ht="14.45" customHeight="1">
       <c r="B492" t="n">
         <v>3479</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" ht="14.4" customHeight="1">
+    <row r="493" hidden="1" ht="14.45" customHeight="1">
       <c r="B493" t="n">
         <v>3480</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" ht="14.4" customHeight="1">
+    <row r="494" hidden="1" ht="14.45" customHeight="1">
       <c r="B494" t="n">
         <v>3481</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" ht="14.4" customHeight="1">
+    <row r="495" hidden="1" ht="14.45" customHeight="1">
       <c r="B495" t="n">
         <v>3482</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" ht="14.4" customHeight="1">
+    <row r="496" hidden="1" ht="14.45" customHeight="1">
       <c r="B496" t="n">
         <v>3483</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" ht="14.4" customHeight="1">
+    <row r="497" hidden="1" ht="14.45" customHeight="1">
       <c r="B497" t="n">
         <v>3484</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" ht="14.4" customHeight="1">
+    <row r="498" hidden="1" ht="14.45" customHeight="1">
       <c r="B498" t="n">
         <v>3485</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" ht="14.4" customHeight="1">
+    <row r="499" hidden="1" ht="14.45" customHeight="1">
       <c r="B499" t="n">
         <v>3486</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" ht="14.4" customHeight="1">
+    <row r="500" hidden="1" ht="14.45" customHeight="1">
       <c r="B500" t="n">
         <v>3487</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" ht="14.4" customHeight="1">
+    <row r="501" hidden="1" ht="14.45" customHeight="1">
       <c r="B501" t="n">
         <v>3488</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" ht="14.4" customHeight="1">
+    <row r="502" hidden="1" ht="14.45" customHeight="1">
       <c r="B502" t="n">
         <v>3489</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" ht="14.4" customHeight="1">
+    <row r="503" hidden="1" ht="14.45" customHeight="1">
       <c r="B503" t="n">
         <v>3490</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" ht="14.4" customHeight="1">
+    <row r="504" hidden="1" ht="14.45" customHeight="1">
       <c r="B504" t="n">
         <v>3491</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" ht="14.4" customHeight="1">
+    <row r="505" hidden="1" ht="14.45" customHeight="1">
       <c r="B505" t="n">
         <v>3492</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" ht="14.4" customHeight="1">
+    <row r="506" hidden="1" ht="14.45" customHeight="1">
       <c r="B506" t="n">
         <v>3493</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" ht="14.4" customHeight="1">
+    <row r="507" hidden="1" ht="14.45" customHeight="1">
       <c r="B507" t="n">
         <v>3494</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" ht="14.4" customHeight="1">
+    <row r="508" hidden="1" ht="14.45" customHeight="1">
       <c r="B508" t="n">
         <v>3495</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" ht="14.4" customHeight="1">
+    <row r="509" hidden="1" ht="14.45" customHeight="1">
       <c r="B509" t="n">
         <v>3496</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" ht="14.4" customHeight="1">
+    <row r="510" hidden="1" ht="14.45" customHeight="1">
       <c r="B510" t="n">
         <v>3497</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" ht="14.4" customHeight="1">
+    <row r="511" hidden="1" ht="14.45" customHeight="1">
       <c r="B511" t="n">
         <v>3498</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" ht="14.4" customHeight="1">
+    <row r="512" hidden="1" ht="14.45" customHeight="1">
       <c r="B512" t="n">
         <v>3499</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" ht="14.4" customHeight="1">
+    <row r="513" hidden="1" ht="14.45" customHeight="1">
       <c r="B513" t="n">
         <v>3500</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" ht="14.4" customHeight="1">
+    <row r="514" hidden="1" ht="14.45" customHeight="1">
       <c r="B514" t="n">
         <v>3501</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" ht="14.4" customHeight="1">
+    <row r="515" hidden="1" ht="14.45" customHeight="1">
       <c r="B515" t="n">
         <v>3502</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" ht="14.4" customHeight="1">
+    <row r="516" hidden="1" ht="14.45" customHeight="1">
       <c r="B516" t="n">
         <v>3503</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" ht="14.4" customHeight="1">
+    <row r="517" hidden="1" ht="14.45" customHeight="1">
       <c r="B517" t="n">
         <v>3504</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" ht="14.4" customHeight="1">
+    <row r="518" hidden="1" ht="14.45" customHeight="1">
       <c r="B518" t="n">
         <v>3505</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" ht="14.4" customHeight="1">
+    <row r="519" hidden="1" ht="14.45" customHeight="1">
       <c r="B519" t="n">
         <v>3506</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" ht="14.4" customHeight="1">
+    <row r="520" hidden="1" ht="14.45" customHeight="1">
       <c r="B520" t="n">
         <v>3507</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" ht="14.4" customHeight="1">
+    <row r="521" hidden="1" ht="14.45" customHeight="1">
       <c r="B521" t="n">
         <v>3508</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" ht="14.4" customHeight="1">
+    <row r="522" hidden="1" ht="14.45" customHeight="1">
       <c r="B522" t="n">
         <v>3509</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" ht="14.4" customHeight="1">
+    <row r="523" hidden="1" ht="14.45" customHeight="1">
       <c r="B523" t="n">
         <v>3510</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" ht="14.4" customHeight="1">
+    <row r="524" hidden="1" ht="14.45" customHeight="1">
       <c r="B524" t="n">
         <v>3511</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" ht="14.4" customHeight="1">
+    <row r="525" hidden="1" ht="14.45" customHeight="1">
       <c r="B525" t="n">
         <v>3512</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" ht="15" customHeight="1">
+    <row r="526" hidden="1" ht="15" customHeight="1">
       <c r="B526" t="n">
         <v>3513</v>
       </c>
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
-    <row r="527" ht="15" customHeight="1">
+    <row r="527" hidden="1" ht="15" customHeight="1">
       <c r="B527" t="n">
         <v>3514</v>
       </c>
@@ -8613,7 +8628,7 @@
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
-    <row r="528" ht="15" customHeight="1">
+    <row r="528" hidden="1" ht="15" customHeight="1">
       <c r="B528" t="n">
         <v>3515</v>
       </c>
@@ -8625,7 +8640,7 @@
       <c r="O528" s="4" t="n"/>
       <c r="Q528" s="4" t="n"/>
     </row>
-    <row r="529" ht="15" customHeight="1">
+    <row r="529" hidden="1" ht="15" customHeight="1">
       <c r="F529" t="inlineStr">
         <is>
           <t>A</t>
@@ -8634,7 +8649,7 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
-    <row r="530" ht="15" customHeight="1">
+    <row r="530" hidden="1" ht="15" customHeight="1">
       <c r="F530" t="inlineStr">
         <is>
           <t>A</t>
@@ -8643,7 +8658,7 @@
       <c r="O530" s="4" t="n"/>
       <c r="Q530" s="4" t="n"/>
     </row>
-    <row r="531" ht="15" customHeight="1">
+    <row r="531" hidden="1" ht="15" customHeight="1">
       <c r="F531" t="inlineStr">
         <is>
           <t>A</t>
@@ -8652,7 +8667,7 @@
       <c r="O531" s="4" t="n"/>
       <c r="Q531" s="4" t="n"/>
     </row>
-    <row r="532" ht="15" customHeight="1">
+    <row r="532" hidden="1" ht="15" customHeight="1">
       <c r="F532" t="inlineStr">
         <is>
           <t>A</t>
@@ -8661,7 +8676,7 @@
       <c r="O532" s="4" t="n"/>
       <c r="Q532" s="4" t="n"/>
     </row>
-    <row r="533" ht="15" customHeight="1">
+    <row r="533" hidden="1" ht="15" customHeight="1">
       <c r="F533" t="inlineStr">
         <is>
           <t>A</t>

--- a/data/instances.xlsx
+++ b/data/instances.xlsx
@@ -3,12 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10200" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Info" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Client Info'!$B$544</definedName>
+  </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -434,7 +439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -676,6 +681,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -780,18 +786,22 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="BY FC Clients"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN533" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="B1:AN533">
-    <filterColumn colId="1" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="Affinity Petcare"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState ref="B2:AN533">
-    <sortCondition ref="I1:I533"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="B1:AN534" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="B1:AN534"/>
   <tableColumns count="39">
     <tableColumn id="1" name="Client ID"/>
     <tableColumn id="2" name="Client"/>
@@ -1142,48 +1152,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R533"/>
+  <dimension ref="A1:R534"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="15.7109375" customWidth="1" min="1" max="1"/>
+    <col width="15.7109375" customWidth="1" style="139" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="130" min="2" max="2"/>
-    <col width="36.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="56.42578125" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25.85546875" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" customWidth="1" min="7" max="7"/>
-    <col width="11.7109375" customWidth="1" min="8" max="8"/>
-    <col width="19.140625" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18.140625" customWidth="1" min="11" max="11"/>
-    <col width="17.5703125" customWidth="1" min="12" max="12"/>
-    <col width="35.140625" customWidth="1" min="13" max="13"/>
-    <col width="25.28515625" customWidth="1" min="14" max="14"/>
-    <col width="33.42578125" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="36.42578125" bestFit="1" customWidth="1" style="139" min="3" max="3"/>
+    <col width="56.42578125" customWidth="1" style="139" min="4" max="4"/>
+    <col width="25" customWidth="1" style="139" min="5" max="5"/>
+    <col width="25.85546875" customWidth="1" style="139" min="6" max="6"/>
+    <col width="15.140625" customWidth="1" style="139" min="7" max="7"/>
+    <col width="11.7109375" customWidth="1" style="139" min="8" max="8"/>
+    <col width="19.140625" customWidth="1" style="139" min="9" max="9"/>
+    <col width="16" customWidth="1" style="139" min="10" max="10"/>
+    <col width="18.140625" customWidth="1" style="139" min="11" max="11"/>
+    <col width="17.5703125" customWidth="1" style="139" min="12" max="12"/>
+    <col width="35.140625" customWidth="1" style="139" min="13" max="13"/>
+    <col width="25.28515625" customWidth="1" style="139" min="14" max="14"/>
+    <col width="33.42578125" customWidth="1" style="139" min="15" max="15"/>
+    <col width="50" customWidth="1" style="139" min="16" max="16"/>
     <col width="35.85546875" customWidth="1" style="4" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" style="139" min="18" max="18"/>
     <col width="27.7109375" customWidth="1" style="4" min="19" max="19"/>
-    <col width="14.7109375" customWidth="1" min="20" max="20"/>
-    <col width="12.85546875" customWidth="1" min="21" max="23"/>
-    <col width="16.28515625" customWidth="1" min="24" max="24"/>
-    <col width="20.140625" customWidth="1" min="25" max="25"/>
-    <col width="20.5703125" customWidth="1" min="26" max="26"/>
-    <col width="14.85546875" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="20.5703125" customWidth="1" min="29" max="29"/>
-    <col width="16.140625" customWidth="1" min="30" max="30"/>
+    <col width="14.7109375" customWidth="1" style="139" min="20" max="20"/>
+    <col width="12.85546875" customWidth="1" style="139" min="21" max="23"/>
+    <col width="16.28515625" customWidth="1" style="139" min="24" max="24"/>
+    <col width="20.140625" customWidth="1" style="139" min="25" max="25"/>
+    <col width="20.5703125" customWidth="1" style="139" min="26" max="26"/>
+    <col width="14.85546875" customWidth="1" style="139" min="27" max="27"/>
+    <col width="30" customWidth="1" style="139" min="28" max="28"/>
+    <col width="20.5703125" customWidth="1" style="139" min="29" max="29"/>
+    <col width="16.140625" customWidth="1" style="139" min="30" max="30"/>
     <col width="16.140625" customWidth="1" style="53" min="31" max="31"/>
-    <col width="22.85546875" customWidth="1" min="32" max="32"/>
-    <col width="17.28515625" customWidth="1" min="33" max="33"/>
-    <col width="16.28515625" customWidth="1" style="139" min="34" max="34"/>
-    <col width="22.85546875" customWidth="1" min="35" max="36"/>
-    <col width="31.85546875" customWidth="1" min="37" max="37"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" min="38" max="38"/>
-    <col width="33.28515625" customWidth="1" min="41" max="41"/>
+    <col width="22.85546875" customWidth="1" style="139" min="32" max="32"/>
+    <col width="17.28515625" customWidth="1" style="139" min="33" max="33"/>
+    <col width="16.28515625" customWidth="1" style="140" min="34" max="34"/>
+    <col width="22.85546875" customWidth="1" style="139" min="35" max="36"/>
+    <col width="31.85546875" customWidth="1" style="139" min="37" max="37"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" style="139" min="38" max="38"/>
+    <col width="33.28515625" customWidth="1" style="139" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.9" customHeight="1">
+    <row r="1" ht="28.9" customHeight="1" s="139">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POC</t>
@@ -1275,7 +1285,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="62">
+    <row r="2" ht="14.45" customFormat="1" customHeight="1" s="62">
       <c r="A2" s="61" t="n"/>
       <c r="B2" t="n">
         <v>1722</v>
@@ -1359,7 +1369,7 @@
         <v>45005</v>
       </c>
     </row>
-    <row r="3" hidden="1" ht="14.45" customHeight="1">
+    <row r="3" ht="14.45" customHeight="1" s="139">
       <c r="A3" s="122" t="n"/>
       <c r="B3" t="n">
         <v>1722</v>
@@ -1429,7 +1439,7 @@
       <c r="Q3" s="88" t="n"/>
       <c r="R3" s="23" t="n"/>
     </row>
-    <row r="4" hidden="1" ht="24" customHeight="1" thickBot="1">
+    <row r="4" ht="24" customHeight="1" s="139" thickBot="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1513,7 +1523,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="5" hidden="1" ht="28.9" customHeight="1">
+    <row r="5" ht="28.9" customHeight="1" s="139">
       <c r="B5" s="27" t="n">
         <v>3005</v>
       </c>
@@ -1572,7 +1582,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="6" hidden="1" ht="14.45" customHeight="1">
+    <row r="6" ht="14.45" customHeight="1" s="139">
       <c r="A6" t="inlineStr">
         <is>
           <t>Jeff/Shawn</t>
@@ -1632,7 +1642,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="7" hidden="1" ht="14.45" customHeight="1">
+    <row r="7" ht="14.45" customHeight="1" s="139">
       <c r="B7" t="n">
         <v>3006</v>
       </c>
@@ -1710,7 +1720,7 @@
         <v>45140</v>
       </c>
     </row>
-    <row r="8" hidden="1" ht="14.45" customHeight="1">
+    <row r="8" ht="14.45" customHeight="1" s="139">
       <c r="B8" t="n">
         <v>3008</v>
       </c>
@@ -1793,7 +1803,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="9" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="9" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="B9" t="n">
         <v>3009</v>
       </c>
@@ -1876,7 +1886,7 @@
         <v>45299</v>
       </c>
     </row>
-    <row r="10" hidden="1" ht="30.75" customFormat="1" customHeight="1" s="27">
+    <row r="10" ht="30.75" customFormat="1" customHeight="1" s="27">
       <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Shawn</t>
@@ -1956,11 +1966,11 @@
           <t>chris.menges@gxo.com</t>
         </is>
       </c>
-      <c r="R10" s="140" t="n">
+      <c r="R10" s="141" t="n">
         <v>45516</v>
       </c>
     </row>
-    <row r="11" hidden="1" ht="43.15" customHeight="1">
+    <row r="11" ht="43.15" customHeight="1" s="139">
       <c r="A11" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2041,7 +2051,7 @@
         <v>45733</v>
       </c>
     </row>
-    <row r="12" hidden="1" ht="14.45" customFormat="1" customHeight="1" s="27">
+    <row r="12" ht="14.45" customFormat="1" customHeight="1" s="27">
       <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Mike/Lisa</t>
@@ -2105,7 +2115,7 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="13" hidden="1" ht="14.45" customHeight="1">
+    <row r="13" ht="14.45" customHeight="1" s="139">
       <c r="B13" t="n">
         <v>3014</v>
       </c>
@@ -2178,7 +2188,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="14" hidden="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="14" ht="30.75" customHeight="1" s="139" thickBot="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>Mike/Heather</t>
@@ -2242,7 +2252,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="15" hidden="1" ht="29.25" customFormat="1" customHeight="1" s="79">
+    <row r="15" ht="29.25" customFormat="1" customHeight="1" s="79">
       <c r="A15" s="79" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2331,7 +2341,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="16" hidden="1" ht="48" customHeight="1">
+    <row r="16" ht="48" customHeight="1" s="139">
       <c r="A16" t="inlineStr">
         <is>
           <t>Lisa/Linda</t>
@@ -2409,7 +2419,7 @@
       <c r="Q16" s="88" t="n"/>
       <c r="R16" s="23" t="n"/>
     </row>
-    <row r="17" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="17" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Colleen/Jeff</t>
@@ -2454,7 +2464,7 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="18" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="18" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B18" t="n">
         <v>3018</v>
       </c>
@@ -2496,7 +2506,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" ht="43.15" customFormat="1" customHeight="1" s="27">
+    <row r="19" ht="43.15" customFormat="1" customHeight="1" s="27">
       <c r="B19" t="n">
         <v>3019</v>
       </c>
@@ -2538,7 +2548,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" ht="43.15" customHeight="1">
+    <row r="20" ht="43.15" customHeight="1" s="139">
       <c r="B20" t="n">
         <v>3020</v>
       </c>
@@ -2580,7 +2590,7 @@
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" ht="33" customFormat="1" customHeight="1" s="27">
+    <row r="21" ht="33" customFormat="1" customHeight="1" s="27">
       <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
@@ -2627,7 +2637,7 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" ht="30.75" customHeight="1">
+    <row r="22" ht="30.75" customHeight="1" s="139">
       <c r="B22" t="n">
         <v>3022</v>
       </c>
@@ -2702,7 +2712,7 @@
         <v>45397</v>
       </c>
     </row>
-    <row r="23" hidden="1" ht="28.9" customHeight="1">
+    <row r="23" ht="28.9" customHeight="1" s="139">
       <c r="A23" t="inlineStr">
         <is>
           <t>Heather</t>
@@ -2786,7 +2796,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="24" hidden="1" ht="28.9" customHeight="1">
+    <row r="24" ht="28.9" customHeight="1" s="139">
       <c r="A24" t="inlineStr">
         <is>
           <t>Colleen</t>
@@ -2852,7 +2862,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" ht="43.9" customHeight="1" thickBot="1">
+    <row r="25" ht="43.9" customHeight="1" s="139" thickBot="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Heather/Shawn</t>
@@ -2920,12 +2930,7 @@
       </c>
       <c r="Q25" s="4" t="n"/>
     </row>
-    <row r="26" hidden="1" ht="14.45" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mike/Shawn</t>
-        </is>
-      </c>
+    <row r="26" ht="14.45" customHeight="1" s="139">
       <c r="B26" t="n">
         <v>3026</v>
       </c>
@@ -2996,526 +3001,563 @@
       </c>
       <c r="Q26" s="4" t="n"/>
     </row>
-    <row r="27" hidden="1" ht="14.45" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="n">
+        <v>3026</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PROJECT Bolt/Moonstone</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NP43</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MEV</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-on-les</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="14.45" customHeight="1" s="139">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B28" t="n">
         <v>3027</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Castore</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>NP17</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>PR15</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>PR15A</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>XNI</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>2023.1.0.25.0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>be40-01y-eus2</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">exec-wms-gxo-castore-les </t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>be40-023-eus2</t>
         </is>
       </c>
-      <c r="O27" s="4" t="n"/>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="O28" s="4" t="n"/>
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>mailto:brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" ht="28.9" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="28.9" customHeight="1" s="139">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
         <v>3028</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Mountain Warehouse</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NP21</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>PR17</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>PR17A</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>GPA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2023.1.0.30.0</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>2023.1.0.30.0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>be40-022-eus2</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>exec-wms-gxo-mw-les
 exec-wms-gxo-mt-les</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>be40-028-eus2</t>
         </is>
       </c>
-      <c r="N28" s="101" t="inlineStr">
+      <c r="N29" s="101" t="inlineStr">
         <is>
           <t>6111 Grayson Rd Harrisburg, PA</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n"/>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="O29" s="4" t="n"/>
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>mailto:brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" ht="43.15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="43.15" customHeight="1" s="139">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
         <v>4025</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>HP Enterprise (HPE)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>NP37</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>OMS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2023.1.0.50</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>6701 Legacy Blvd, Ste 101
 Olive Branch, MS 38654
 USA</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n"/>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="O30" s="4" t="n"/>
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>mailto:brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="30" hidden="1" ht="28.9" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="28.9" customHeight="1" s="139">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Mike/Shawn</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B31" t="n">
         <v>3033</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>WH Smith</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>NP24</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>XNE</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>bh10-002-euw</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>exec-wms-gxo-wh-smith-les</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>2353 US Highway 130
 Dayton, NJ 08810</t>
         </is>
       </c>
-      <c r="O30" s="4" t="n"/>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="O31" s="4" t="n"/>
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>mailto:brandon.conner@gxo.com</t>
         </is>
       </c>
     </row>
-    <row r="31" hidden="1" ht="43.15" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
+    <row r="32" ht="43.15" customHeight="1" s="139">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Michael/Shawn</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B32" t="n">
         <v>3035</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>RJR Plainfield</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>NP29</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>PR21</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>PR21A</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>PIR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>be40-02n-eus2</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-plainfield-les</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>600 S Perry Rd
 Plainfield, IN 46168
 USA</t>
         </is>
       </c>
-      <c r="O31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
-    </row>
-    <row r="32" hidden="1" ht="54" customFormat="1" customHeight="1" s="27">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="O32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="54" customFormat="1" customHeight="1" s="27">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Michael</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" t="n">
         <v>3035</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>RJR Orlando</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>NP32</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>PR23</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>PR23A</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>OFR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>be40-02p-eus2</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-orlando-les</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>be40-02i-eus2</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>7469 PRESIDENTS DRIVE
 ORLANDO, FL 32809
 USA</t>
         </is>
       </c>
-      <c r="O32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-    </row>
-    <row r="33" hidden="1" ht="43.15" customHeight="1">
-      <c r="B33" t="n">
+      <c r="O33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="43.15" customHeight="1" s="139">
+      <c r="B34" t="n">
         <v>3035</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>RJR Portland</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>NP31</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>PR24</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>PR24A</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>RPO</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>be40-02p-eus2</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-portland-les</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>be40-02q-eus2</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>3591 YEON AVE
 PORTLAND, OR 97210
 USA</t>
         </is>
       </c>
-      <c r="O33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n"/>
-    </row>
-    <row r="34" hidden="1" ht="57.6" customHeight="1">
-      <c r="B34" t="n">
+      <c r="O34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="57.6" customHeight="1" s="139">
+      <c r="B35" t="n">
         <v>3035</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>RJR  Rural Hall, NC</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>NP34</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>PR22</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>PR22A</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>RHN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>be40-02w-eus2</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>exec-wms-gxo-rjr-ruralhall-les</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>RJR
 200 FORUM PARKWAY
@@ -3523,103 +3565,41 @@
 USA</t>
         </is>
       </c>
-      <c r="O34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-    </row>
-    <row r="35" hidden="1" ht="14.45" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Mike/Jeff</t>
-        </is>
-      </c>
-      <c r="B35" s="130" t="n">
-        <v>3042</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>QL Template (AMAPAC)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NP25</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2023.1.0.50.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>be40-02j-eus2</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-les</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="O35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
     </row>
-    <row r="36" hidden="1" ht="14.45" customHeight="1">
-      <c r="B36" t="n">
-        <v>3031</v>
+    <row r="36" ht="14.45" customHeight="1" s="139">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mike/Jeff</t>
+        </is>
+      </c>
+      <c r="B36" s="130" t="n">
+        <v>3042</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Span.IO</t>
+          <t>QL Template (AMAPAC)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NP22</t>
+          <t>NP25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PR18</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PR18A</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FT1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3629,890 +3609,920 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2023.1.0.30.0</t>
+          <t>2023.1.0.50.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2023.1.0.30.0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>bh10-004-euw</t>
+          <t>be40-02j-eus2</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>exec-wms-gxo-span-les</t>
+          <t>exec-wms-gxo-les</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>be40-029-eus2</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
     </row>
-    <row r="37" hidden="1" ht="14.45" customHeight="1">
+    <row r="37" ht="14.45" customHeight="1" s="139">
       <c r="B37" t="n">
-        <v>3056</v>
+        <v>3031</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Riviana</t>
+          <t>Span.IO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NP38</t>
+          <t>NP22</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PR18</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PR18A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>WIL</t>
+          <t>FT1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>be40</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2023.1.0.30.0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>bh10-004-euw</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-span-les</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>be40-029-eus2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1401 EVERMAN PARKWAY, FORT WORTH, TX 76140</t>
         </is>
       </c>
       <c r="O37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
     </row>
-    <row r="38" hidden="1" ht="57.6" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="38" ht="14.45" customHeight="1" s="139">
+      <c r="B38" t="n">
+        <v>3056</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Riviana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NP38</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>WIL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="57.6" customHeight="1" s="139">
+      <c r="A39" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B39" t="n">
         <v>3030</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Toolstation</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NP2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>PR2</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>PR2A</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>BNL</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2023.1.0.30.0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Not Setup</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>exec-wms-gxo-toolstation-les</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>DC1 - Brandpuntlaan Zuid 12, 2665 NZ Bleiswijk, Netherlands
 DC2 - Prismalaan Oost, 2665 Bleiswijk, Netherlands</t>
         </is>
       </c>
-      <c r="O38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>IB/OB  - 5/12/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" hidden="1" ht="28.9" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3032</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Passenger Clothing Limited</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NP3</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PR1A</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>DN1</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2023.1.0.37.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2023.1.0.37</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>bh10-003-euw</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-passenger-les</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>bh10-002-euw</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
-        </is>
-      </c>
       <c r="O39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
-    </row>
-    <row r="40" hidden="1" ht="43.15" customHeight="1">
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>IB/OB  - 5/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28.9" customHeight="1" s="139">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B40" t="n">
+        <v>3032</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Passenger Clothing Limited</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NP3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PR1A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DN1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2023.1.0.37.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2023.1.0.37</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>bh10-003-euw</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-passenger-les</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="43.15" customHeight="1" s="139">
+      <c r="B41" t="n">
         <v>3035</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>RJR Fort Worth, TX</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NP36</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>PR27</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>PR27A</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>FTR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>4801 Mercantile Dr
 Ft Worth, TX 76137
 USA</t>
         </is>
       </c>
-      <c r="O40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
-    </row>
-    <row r="41" hidden="1" ht="28.9" customHeight="1">
-      <c r="A41" t="inlineStr">
+      <c r="O41" s="4" t="n"/>
+      <c r="Q41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="28.9" customHeight="1" s="139">
+      <c r="A42" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B42" t="n">
         <v>3034</v>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Project Phoenix Prenatal</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>NP6</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>WNL</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>bh10-006-euw</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>exec-wms-gxo-prenatal-les
 exec-wms-gxo-phoenix-les</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>bh10-009-euw</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>GXO Op Den Dries 1
 6019 RA Wessem, Netherlands</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>NP13 (PRENTAL AUTOMATION)</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="n"/>
-    </row>
-    <row r="42" hidden="1" ht="43.15" customHeight="1">
-      <c r="A42" t="inlineStr">
+      <c r="Q42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="43.15" customHeight="1" s="139">
+      <c r="A43" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B43" t="n">
         <v>3057</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Davine's Spa</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>NP40</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>MP1</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>336 Heinz St
 Mechanicsburg, PA 17055
 USA</t>
         </is>
       </c>
-      <c r="O42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n"/>
-    </row>
-    <row r="43" hidden="1" ht="14.45" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1831</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NP41</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>be40</t>
-        </is>
-      </c>
-      <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
       <c r="Q43" s="4" t="n"/>
     </row>
-    <row r="44" hidden="1" ht="41.45" customHeight="1">
+    <row r="44" ht="14.45" customHeight="1" s="139">
       <c r="A44" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1831</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NP41</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>be40</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="41.45" customHeight="1" s="139">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B45" t="n">
         <v>3036</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Kumho (EU)</t>
         </is>
       </c>
-      <c r="D44" s="107" t="inlineStr">
+      <c r="D45" s="107" t="inlineStr">
         <is>
           <t>NP4</t>
         </is>
       </c>
-      <c r="E44" s="107" t="inlineStr">
+      <c r="E45" s="107" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F44" s="107" t="n"/>
-      <c r="G44" t="inlineStr">
+      <c r="F45" s="107" t="n"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>GE1</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>2023.1.0.42.0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>bh10-004-euw</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>exec-wms-gxo-kumho-les</t>
         </is>
       </c>
-      <c r="N44" s="106" t="inlineStr">
+      <c r="N45" s="106" t="inlineStr">
         <is>
           <t>GXO Marchamalo 2 
 Calle el Ventorro
 19180 Guadalajara, ES</t>
         </is>
       </c>
-      <c r="O44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
-    </row>
-    <row r="45" hidden="1" ht="28.9" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="O45" s="4" t="n"/>
+      <c r="Q45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="28.9" customHeight="1" s="139">
+      <c r="A46" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B46" t="n">
         <v>3037</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Commscope</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>NP7</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">PR5 </t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>PR5A</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>VEE</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>2023.1.0.45.0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>bh10-00d-euw</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>exec-wms-gxo-commscope-les</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>GXO Veenendaal
 Arsenaal 2, 3905 Veenendaal, NL</t>
         </is>
       </c>
-      <c r="O45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n"/>
-    </row>
-    <row r="46" hidden="1" ht="14.45" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3038</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Unilever</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
-      </c>
       <c r="O46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
     </row>
-    <row r="47" hidden="1" ht="43.15" customHeight="1">
+    <row r="47" ht="14.45" customHeight="1" s="139">
       <c r="A47" t="inlineStr">
         <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3038</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unilever</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="43.15" customHeight="1" s="139">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" t="n">
         <v>3060</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Oh Polly</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>NP42</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>PR6</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>PR6A</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>202 Park West Dr
 West Jefferson, OH
 USA</t>
         </is>
       </c>
-      <c r="O47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-    </row>
-    <row r="48" hidden="1" ht="43.15" customHeight="1">
-      <c r="A48" t="inlineStr">
+      <c r="O48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="43.15" customHeight="1" s="139">
+      <c r="A49" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B49" t="n">
         <v>3026</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>GXO (Multi Tenant)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>NP43</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>MEV</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>Calle Guadalupana Manzana 015
 54980 Santiago Teyahualco
 Estado de México</t>
         </is>
       </c>
-      <c r="O48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
-    </row>
-    <row r="49" hidden="1" ht="14.45" customHeight="1">
-      <c r="B49" s="130" t="n">
-        <v>3041</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>QL Template (EU)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NP5</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Not Setup</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-les</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="O49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
     </row>
-    <row r="50" hidden="1" ht="43.15" customHeight="1">
-      <c r="B50" t="n">
+    <row r="50" ht="14.45" customHeight="1" s="139">
+      <c r="B50" s="130" t="n">
+        <v>3041</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QL Template (EU)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NP5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Not Setup</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-les</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="43.15" customHeight="1" s="139">
+      <c r="B51" t="n">
         <v>3063</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Nodor</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>NP45</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>DJ1</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>be40</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>2353 US-130
 Dayton, NJ 08810
 USA</t>
         </is>
       </c>
-      <c r="O50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
-    </row>
-    <row r="51" hidden="1" ht="14.45" customHeight="1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3043</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>NP10</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
       <c r="O51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
     </row>
-    <row r="52" hidden="1" ht="14.45" customHeight="1">
+    <row r="52" ht="14.45" customHeight="1" s="139">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B52" t="n">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DEV-EU</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>NP11</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>NP10</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>bh10</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2023.1.0.42.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>bh10-00q-euw</t>
         </is>
       </c>
       <c r="O52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
     </row>
-    <row r="53" hidden="1" ht="14.45" customHeight="1">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="53" ht="14.45" customHeight="1" s="139">
       <c r="B53" t="n">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>DEV-EU</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>NP12</t>
+          <t>NP11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>bh10</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2023.1.0.42.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>bh10-00q-euw</t>
         </is>
       </c>
       <c r="O53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
     </row>
-    <row r="54" hidden="1" ht="14.45" customHeight="1">
+    <row r="54" ht="14.45" customHeight="1" s="139">
       <c r="A54" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GLOBAL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ES01</t>
+          <t>Bene</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>NP12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4523,18 +4533,18 @@
       <c r="O54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
     </row>
-    <row r="55" hidden="1" ht="14.45" customHeight="1">
+    <row r="55" ht="14.45" customHeight="1" s="139">
       <c r="A55" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : SYNTHESIA</t>
+          <t>Castellbisbal multi client : GLOBAL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4555,18 +4565,18 @@
       <c r="O55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
     </row>
-    <row r="56" hidden="1" ht="14.45" customHeight="1">
+    <row r="56" ht="14.45" customHeight="1" s="139">
       <c r="A56" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : INTERCOAT</t>
+          <t>Castellbisbal multi client : SYNTHESIA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4587,18 +4597,18 @@
       <c r="O56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
     </row>
-    <row r="57" hidden="1" ht="14.45" customHeight="1">
+    <row r="57" ht="14.45" customHeight="1" s="139">
       <c r="A57" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : INTERFAT</t>
+          <t>Castellbisbal multi client : INTERCOAT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4619,18 +4629,18 @@
       <c r="O57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
     </row>
-    <row r="58" hidden="1" ht="14.45" customHeight="1">
+    <row r="58" ht="14.45" customHeight="1" s="139">
       <c r="A58" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : DEMIX</t>
+          <t>Castellbisbal multi client : INTERFAT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4651,18 +4661,18 @@
       <c r="O58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
     </row>
-    <row r="59" hidden="1" ht="14.45" customHeight="1">
+    <row r="59" ht="14.45" customHeight="1" s="139">
       <c r="A59" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GACHES</t>
+          <t>Castellbisbal multi client : DEMIX</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4683,63 +4693,63 @@
       <c r="O59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
     </row>
-    <row r="60" hidden="1" ht="14.45" customHeight="1">
+    <row r="60" ht="14.45" customHeight="1" s="139">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3000</v>
+        <v>3051</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : GACHES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
       </c>
       <c r="O60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
-      <c r="R60" s="23" t="n"/>
-    </row>
-    <row r="61" hidden="1" ht="14.45" customHeight="1">
+    </row>
+    <row r="61" ht="14.45" customHeight="1" s="139">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3052</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Castellbisbal multi client : MACDERMID</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NP9</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ES01</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
+        <v>3000</v>
       </c>
       <c r="O61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
-    </row>
-    <row r="62" hidden="1" ht="14.45" customHeight="1">
+      <c r="R61" s="23" t="n"/>
+    </row>
+    <row r="62" ht="14.45" customHeight="1" s="139">
       <c r="A62" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : ENGIPLASTE</t>
+          <t>Castellbisbal multi client : MACDERMID</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4760,18 +4770,18 @@
       <c r="O62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
     </row>
-    <row r="63" hidden="1" ht="14.45" customHeight="1">
+    <row r="63" ht="14.45" customHeight="1" s="139">
       <c r="A63" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : GLOKEM</t>
+          <t>Castellbisbal multi client : ENGIPLASTE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4792,18 +4802,18 @@
       <c r="O63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
     </row>
-    <row r="64" hidden="1" ht="14.45" customHeight="1">
+    <row r="64" ht="14.45" customHeight="1" s="139">
       <c r="A64" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Castellbisbal multi client : QUIMICALITE</t>
+          <t>Castellbisbal multi client : GLOKEM</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4824,2618 +4834,2593 @@
       <c r="O64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
     </row>
-    <row r="65" hidden="1" ht="14.45" customHeight="1">
+    <row r="65" ht="14.45" customHeight="1" s="139">
       <c r="A65" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3002</v>
+        <v>3055</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Castellbisbal multi client : QUIMICALITE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NP9</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ES01</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
       </c>
       <c r="O65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
-      <c r="R65" s="23" t="n"/>
-    </row>
-    <row r="66" hidden="1" ht="14.45" customHeight="1">
-      <c r="B66" s="131" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>QL Dev/Test Env for NP5</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NP14</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
+    </row>
+    <row r="66" ht="14.45" customHeight="1" s="139">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3002</v>
       </c>
       <c r="O66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
-    </row>
-    <row r="67" hidden="1" ht="14.45" customHeight="1">
-      <c r="B67" t="n">
-        <v>3003</v>
+      <c r="R66" s="23" t="n"/>
+    </row>
+    <row r="67" ht="14.45" customHeight="1" s="139">
+      <c r="B67" s="131" t="inlineStr">
+        <is>
+          <t>----</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>QL Dev/Test Env for NP5</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NP14</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
       </c>
       <c r="O67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="23" t="n"/>
-    </row>
-    <row r="68" hidden="1" ht="14.45" customHeight="1">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+    </row>
+    <row r="68" ht="14.45" customHeight="1" s="139">
       <c r="B68" t="n">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="O68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="23" t="n"/>
     </row>
-    <row r="69" hidden="1" ht="14.45" customHeight="1">
+    <row r="69" ht="14.45" customHeight="1" s="139">
       <c r="A69" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B69" s="27" t="n">
+      <c r="B69" t="n">
+        <v>3004</v>
+      </c>
+      <c r="O69" s="4" t="n"/>
+      <c r="Q69" s="4" t="n"/>
+      <c r="R69" s="23" t="n"/>
+    </row>
+    <row r="70" ht="14.45" customHeight="1" s="139">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="n">
         <v>3007</v>
       </c>
-      <c r="C69" s="27" t="inlineStr">
+      <c r="C70" s="27" t="inlineStr">
         <is>
           <t>Do not use, in service now as revival</t>
         </is>
       </c>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="27" t="n"/>
-      <c r="F69" s="27" t="n"/>
-      <c r="G69" s="27" t="n"/>
-      <c r="H69" s="27" t="n"/>
-      <c r="I69" s="27" t="n"/>
-      <c r="J69" s="27" t="n"/>
-      <c r="K69" s="27" t="n"/>
-      <c r="L69" s="27" t="n"/>
-      <c r="M69" s="27" t="n"/>
-      <c r="N69" s="27" t="n"/>
-      <c r="O69" s="108" t="n"/>
-      <c r="P69" s="27" t="n"/>
-      <c r="Q69" s="108" t="n"/>
-      <c r="R69" s="66" t="n"/>
-    </row>
-    <row r="70" hidden="1" ht="43.15" customHeight="1">
-      <c r="A70" t="inlineStr">
+      <c r="D70" s="27" t="n"/>
+      <c r="E70" s="27" t="n"/>
+      <c r="F70" s="27" t="n"/>
+      <c r="G70" s="27" t="n"/>
+      <c r="H70" s="27" t="n"/>
+      <c r="I70" s="27" t="n"/>
+      <c r="J70" s="27" t="n"/>
+      <c r="K70" s="27" t="n"/>
+      <c r="L70" s="27" t="n"/>
+      <c r="M70" s="27" t="n"/>
+      <c r="N70" s="27" t="n"/>
+      <c r="O70" s="108" t="n"/>
+      <c r="P70" s="27" t="n"/>
+      <c r="Q70" s="108" t="n"/>
+      <c r="R70" s="66" t="n"/>
+    </row>
+    <row r="71" ht="43.15" customHeight="1" s="139">
+      <c r="A71" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B71" t="n">
         <v>3058</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Hunkemoller</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>NP15</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>NL01</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>Sterkenburg 3-5
 1358 CG Almere
 Netherlands</t>
         </is>
       </c>
-      <c r="O70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n"/>
-    </row>
-    <row r="71" hidden="1" ht="14.45" customHeight="1">
-      <c r="A71" t="inlineStr">
+      <c r="O71" s="4" t="n"/>
+      <c r="Q71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="14.45" customHeight="1" s="139">
+      <c r="A72" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B71" s="27" t="n">
+      <c r="B72" s="27" t="n">
         <v>3012</v>
       </c>
-      <c r="C71" s="27" t="n"/>
-      <c r="D71" s="27" t="n"/>
-      <c r="E71" s="27" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="27" t="n"/>
-      <c r="J71" s="27" t="n"/>
-      <c r="K71" s="27" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="27" t="n"/>
-      <c r="N71" s="27" t="n"/>
-      <c r="O71" s="108" t="n"/>
-      <c r="P71" s="27" t="n"/>
-      <c r="Q71" s="108" t="n"/>
-      <c r="R71" s="66" t="n"/>
-    </row>
-    <row r="72" hidden="1" ht="14.45" customHeight="1">
-      <c r="A72" t="inlineStr">
+      <c r="C72" s="27" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
+      <c r="F72" s="27" t="n"/>
+      <c r="G72" s="27" t="n"/>
+      <c r="H72" s="27" t="n"/>
+      <c r="I72" s="27" t="n"/>
+      <c r="J72" s="27" t="n"/>
+      <c r="K72" s="27" t="n"/>
+      <c r="L72" s="27" t="n"/>
+      <c r="M72" s="27" t="n"/>
+      <c r="N72" s="27" t="n"/>
+      <c r="O72" s="108" t="n"/>
+      <c r="P72" s="27" t="n"/>
+      <c r="Q72" s="108" t="n"/>
+      <c r="R72" s="66" t="n"/>
+    </row>
+    <row r="73" ht="14.45" customHeight="1" s="139">
+      <c r="A73" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B73" t="n">
         <v>3059</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>BOL</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>NP16</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>NL02</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="O72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n"/>
-    </row>
-    <row r="73" hidden="1" ht="14.45" customHeight="1">
-      <c r="A73" t="inlineStr">
+      <c r="O73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n"/>
+    </row>
+    <row r="74" ht="14.45" customHeight="1" s="139">
+      <c r="A74" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B73" s="27" t="n">
+      <c r="B74" s="27" t="n">
         <v>3013</v>
       </c>
-      <c r="C73" s="27" t="n"/>
-      <c r="D73" s="27" t="n"/>
-      <c r="E73" s="27" t="n"/>
-      <c r="F73" s="27" t="n"/>
-      <c r="G73" s="27" t="n"/>
-      <c r="H73" s="27" t="n"/>
-      <c r="I73" s="27" t="n"/>
-      <c r="J73" s="27" t="n"/>
-      <c r="K73" s="27" t="n"/>
-      <c r="L73" s="27" t="n"/>
-      <c r="M73" s="27" t="n"/>
-      <c r="N73" s="27" t="n"/>
-      <c r="O73" s="108" t="n"/>
-      <c r="P73" s="27" t="n"/>
-      <c r="Q73" s="108" t="n"/>
-      <c r="R73" s="66" t="n"/>
-    </row>
-    <row r="74" hidden="1" ht="14.45" customHeight="1">
-      <c r="A74" t="inlineStr">
+      <c r="C74" s="27" t="n"/>
+      <c r="D74" s="27" t="n"/>
+      <c r="E74" s="27" t="n"/>
+      <c r="F74" s="27" t="n"/>
+      <c r="G74" s="27" t="n"/>
+      <c r="H74" s="27" t="n"/>
+      <c r="I74" s="27" t="n"/>
+      <c r="J74" s="27" t="n"/>
+      <c r="K74" s="27" t="n"/>
+      <c r="L74" s="27" t="n"/>
+      <c r="M74" s="27" t="n"/>
+      <c r="N74" s="27" t="n"/>
+      <c r="O74" s="108" t="n"/>
+      <c r="P74" s="27" t="n"/>
+      <c r="Q74" s="108" t="n"/>
+      <c r="R74" s="66" t="n"/>
+    </row>
+    <row r="75" ht="14.45" customHeight="1" s="139">
+      <c r="A75" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B75" t="n">
         <v>3061</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>DG Beauty</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>NP17</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>IT01</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>bh10</t>
-        </is>
-      </c>
-      <c r="O74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n"/>
-    </row>
-    <row r="75" hidden="1" ht="14.45" customHeight="1">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3062</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Oh Polly</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NP18</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>PL01</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Poznan, PL</t>
         </is>
       </c>
       <c r="O75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
     </row>
-    <row r="76" hidden="1" ht="43.15" customHeight="1">
+    <row r="76" ht="14.45" customHeight="1" s="139">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3015</v>
-      </c>
-      <c r="N76" s="4" t="n"/>
+        <v>3062</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Oh Polly</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NP18</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PL01</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Poznan, PL</t>
+        </is>
+      </c>
       <c r="O76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="23" t="n"/>
-    </row>
-    <row r="77" hidden="1" ht="14.45" customHeight="1">
+    </row>
+    <row r="77" ht="43.15" customHeight="1" s="139">
       <c r="A77" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B77" s="131" t="inlineStr">
-        <is>
-          <t>----</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>NP25 Dev/Test Env</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NP39</t>
-        </is>
-      </c>
+      <c r="B77" t="n">
+        <v>3015</v>
+      </c>
+      <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
-    </row>
-    <row r="78" ht="14.45" customHeight="1">
+      <c r="R77" s="23" t="n"/>
+    </row>
+    <row r="78" ht="14.45" customHeight="1" s="139">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3064 &amp; 3070</t>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B78" s="131" t="inlineStr">
+        <is>
+          <t>----</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Affinity Petcare</t>
+          <t>NP25 Dev/Test Env</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NP19</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>FR01</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>bh10</t>
+          <t>NP39</t>
         </is>
       </c>
       <c r="O78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
     </row>
-    <row r="79" hidden="1" ht="57.6" customHeight="1">
+    <row r="79" ht="14.45" customHeight="1" s="139">
       <c r="A79" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3064 &amp; 3070</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Affinity Petcare</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NP19</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>FR01</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="n"/>
+      <c r="Q79" s="4" t="n"/>
+    </row>
+    <row r="80" ht="57.6" customHeight="1" s="139">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
         <v>3065</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Columbia Sportswear Distribution SaS</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>NP20</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>FR02</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>1542 Avenue des Deux Vallees Parc d'Activites Actipole de l'A25
 9954 Raillencourt Sainte Olle
 France</t>
         </is>
       </c>
-      <c r="O79" s="4" t="n"/>
-      <c r="Q79" s="4" t="n"/>
-    </row>
-    <row r="80" hidden="1" ht="43.15" customHeight="1">
-      <c r="A80" t="inlineStr">
+      <c r="O80" s="4" t="n"/>
+      <c r="Q80" s="4" t="n"/>
+    </row>
+    <row r="81" ht="43.15" customHeight="1" s="139">
+      <c r="A81" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B81" t="n">
         <v>3066</v>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>GXO (Multi Tenant)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>NP21</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>IT02</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>bh10</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N81" s="4" t="inlineStr">
         <is>
           <t>Via della Libertà, 215
 28043 Bellinzago Novarese NO
 Italy</t>
         </is>
       </c>
-      <c r="O80" s="4" t="n"/>
-      <c r="Q80" s="4" t="n"/>
-    </row>
-    <row r="81" hidden="1" ht="28.9" customHeight="1">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>3067</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Nodor</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NP3</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PR1</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>PR1A</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>DN1</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2023.1.0.37.0</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>2023.1.0.37</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>bh10-003-euw</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-passenger-les</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>bh10-002-euw</t>
-        </is>
-      </c>
-      <c r="N81" s="4" t="inlineStr">
-        <is>
-          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
-        </is>
-      </c>
       <c r="O81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
     </row>
-    <row r="82" hidden="1" ht="14.45" customHeight="1">
+    <row r="82" ht="28.9" customHeight="1" s="139">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Nodor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NP42</t>
+          <t>NP3</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PR1A</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DN1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2023.1.0.37.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2023.1.0.37</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>bh10-003-euw</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-passenger-les</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>bh10-002-euw</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Düsseldorfer str. 85 -41541 Dormagen, Germany</t>
         </is>
       </c>
       <c r="O82" s="4" t="n"/>
       <c r="Q82" s="4" t="n"/>
     </row>
-    <row r="83" hidden="1" ht="14.45" customHeight="1">
+    <row r="83" ht="14.45" customHeight="1" s="139">
       <c r="A83" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Allied Air</t>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NP42</t>
         </is>
       </c>
       <c r="O83" s="4" t="n"/>
       <c r="Q83" s="4" t="n"/>
     </row>
-    <row r="84" hidden="1" ht="14.45" customHeight="1">
+    <row r="84" ht="14.45" customHeight="1" s="139">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="B84" t="n">
-        <v>3071</v>
+        <v>3069</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Allied Air</t>
+        </is>
       </c>
       <c r="O84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
     </row>
-    <row r="85" hidden="1" ht="14.45" customHeight="1">
+    <row r="85" ht="14.45" customHeight="1" s="139">
       <c r="B85" t="n">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="O85" s="4" t="n"/>
       <c r="Q85" s="4" t="n"/>
     </row>
-    <row r="86" hidden="1" ht="14.45" customHeight="1">
+    <row r="86" ht="14.45" customHeight="1" s="139">
       <c r="B86" t="n">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="O86" s="4" t="n"/>
       <c r="Q86" s="4" t="n"/>
     </row>
-    <row r="87" hidden="1" ht="14.45" customHeight="1">
+    <row r="87" ht="14.45" customHeight="1" s="139">
       <c r="B87" t="n">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="O87" s="4" t="n"/>
       <c r="Q87" s="4" t="n"/>
     </row>
-    <row r="88" hidden="1" ht="14.45" customHeight="1">
+    <row r="88" ht="14.45" customHeight="1" s="139">
       <c r="B88" t="n">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="O88" s="4" t="n"/>
       <c r="Q88" s="4" t="n"/>
     </row>
-    <row r="89" hidden="1" ht="14.45" customHeight="1">
+    <row r="89" ht="14.45" customHeight="1" s="139">
       <c r="B89" t="n">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="O89" s="4" t="n"/>
       <c r="Q89" s="4" t="n"/>
     </row>
-    <row r="90" hidden="1" ht="14.45" customHeight="1">
+    <row r="90" ht="14.45" customHeight="1" s="139">
       <c r="B90" t="n">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="O90" s="4" t="n"/>
       <c r="Q90" s="4" t="n"/>
     </row>
-    <row r="91" hidden="1" ht="14.45" customHeight="1">
+    <row r="91" ht="14.45" customHeight="1" s="139">
       <c r="B91" t="n">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="O91" s="4" t="n"/>
       <c r="Q91" s="4" t="n"/>
     </row>
-    <row r="92" hidden="1" ht="14.45" customHeight="1">
+    <row r="92" ht="14.45" customHeight="1" s="139">
       <c r="B92" t="n">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="O92" s="4" t="n"/>
       <c r="Q92" s="4" t="n"/>
     </row>
-    <row r="93" hidden="1" ht="14.45" customHeight="1">
+    <row r="93" ht="14.45" customHeight="1" s="139">
       <c r="B93" t="n">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="O93" s="4" t="n"/>
       <c r="Q93" s="4" t="n"/>
     </row>
-    <row r="94" hidden="1" ht="14.45" customHeight="1">
+    <row r="94" ht="14.45" customHeight="1" s="139">
       <c r="B94" t="n">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="O94" s="4" t="n"/>
       <c r="Q94" s="4" t="n"/>
     </row>
-    <row r="95" hidden="1" ht="14.45" customHeight="1">
+    <row r="95" ht="14.45" customHeight="1" s="139">
       <c r="B95" t="n">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="O95" s="4" t="n"/>
       <c r="Q95" s="4" t="n"/>
     </row>
-    <row r="96" hidden="1" ht="14.45" customHeight="1">
+    <row r="96" ht="14.45" customHeight="1" s="139">
       <c r="B96" t="n">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="O96" s="4" t="n"/>
       <c r="Q96" s="4" t="n"/>
     </row>
-    <row r="97" hidden="1" ht="14.45" customHeight="1">
+    <row r="97" ht="14.45" customHeight="1" s="139">
       <c r="B97" t="n">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="O97" s="4" t="n"/>
       <c r="Q97" s="4" t="n"/>
     </row>
-    <row r="98" hidden="1" ht="14.45" customHeight="1">
+    <row r="98" ht="14.45" customHeight="1" s="139">
       <c r="B98" t="n">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="O98" s="4" t="n"/>
       <c r="Q98" s="4" t="n"/>
     </row>
-    <row r="99" hidden="1" ht="14.45" customHeight="1">
+    <row r="99" ht="14.45" customHeight="1" s="139">
       <c r="B99" t="n">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="O99" s="4" t="n"/>
       <c r="Q99" s="4" t="n"/>
     </row>
-    <row r="100" hidden="1" ht="14.45" customHeight="1">
+    <row r="100" ht="14.45" customHeight="1" s="139">
       <c r="B100" t="n">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="O100" s="4" t="n"/>
       <c r="Q100" s="4" t="n"/>
     </row>
-    <row r="101" hidden="1" ht="14.45" customHeight="1">
+    <row r="101" ht="14.45" customHeight="1" s="139">
       <c r="B101" t="n">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="O101" s="4" t="n"/>
       <c r="Q101" s="4" t="n"/>
     </row>
-    <row r="102" hidden="1" ht="14.45" customHeight="1">
+    <row r="102" ht="14.45" customHeight="1" s="139">
       <c r="B102" t="n">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="O102" s="4" t="n"/>
       <c r="Q102" s="4" t="n"/>
     </row>
-    <row r="103" hidden="1" ht="14.45" customHeight="1">
+    <row r="103" ht="14.45" customHeight="1" s="139">
       <c r="B103" t="n">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="O103" s="4" t="n"/>
       <c r="Q103" s="4" t="n"/>
     </row>
-    <row r="104" hidden="1" ht="14.45" customHeight="1">
+    <row r="104" ht="14.45" customHeight="1" s="139">
       <c r="B104" t="n">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="O104" s="4" t="n"/>
       <c r="Q104" s="4" t="n"/>
     </row>
-    <row r="105" hidden="1" ht="14.45" customHeight="1">
+    <row r="105" ht="14.45" customHeight="1" s="139">
       <c r="B105" t="n">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="O105" s="4" t="n"/>
       <c r="Q105" s="4" t="n"/>
     </row>
-    <row r="106" hidden="1" ht="14.45" customHeight="1">
+    <row r="106" ht="14.45" customHeight="1" s="139">
       <c r="B106" t="n">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="O106" s="4" t="n"/>
       <c r="Q106" s="4" t="n"/>
     </row>
-    <row r="107" hidden="1" ht="14.45" customHeight="1">
+    <row r="107" ht="14.45" customHeight="1" s="139">
       <c r="B107" t="n">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="O107" s="4" t="n"/>
       <c r="Q107" s="4" t="n"/>
     </row>
-    <row r="108" hidden="1" ht="14.45" customHeight="1">
+    <row r="108" ht="14.45" customHeight="1" s="139">
       <c r="B108" t="n">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="O108" s="4" t="n"/>
       <c r="Q108" s="4" t="n"/>
     </row>
-    <row r="109" hidden="1" ht="14.45" customHeight="1">
+    <row r="109" ht="14.45" customHeight="1" s="139">
       <c r="B109" t="n">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="O109" s="4" t="n"/>
       <c r="Q109" s="4" t="n"/>
     </row>
-    <row r="110" hidden="1" ht="14.45" customHeight="1">
+    <row r="110" ht="14.45" customHeight="1" s="139">
       <c r="B110" t="n">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="O110" s="4" t="n"/>
       <c r="Q110" s="4" t="n"/>
     </row>
-    <row r="111" hidden="1" ht="14.45" customHeight="1">
+    <row r="111" ht="14.45" customHeight="1" s="139">
       <c r="B111" t="n">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="O111" s="4" t="n"/>
       <c r="Q111" s="4" t="n"/>
     </row>
-    <row r="112" hidden="1" ht="14.45" customHeight="1">
+    <row r="112" ht="14.45" customHeight="1" s="139">
       <c r="B112" t="n">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="O112" s="4" t="n"/>
       <c r="Q112" s="4" t="n"/>
     </row>
-    <row r="113" hidden="1" ht="14.45" customHeight="1">
+    <row r="113" ht="14.45" customHeight="1" s="139">
       <c r="B113" t="n">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="O113" s="4" t="n"/>
       <c r="Q113" s="4" t="n"/>
     </row>
-    <row r="114" hidden="1" ht="14.45" customHeight="1">
+    <row r="114" ht="14.45" customHeight="1" s="139">
       <c r="B114" t="n">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="O114" s="4" t="n"/>
       <c r="Q114" s="4" t="n"/>
     </row>
-    <row r="115" hidden="1" ht="14.45" customHeight="1">
+    <row r="115" ht="14.45" customHeight="1" s="139">
       <c r="B115" t="n">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="O115" s="4" t="n"/>
       <c r="Q115" s="4" t="n"/>
     </row>
-    <row r="116" hidden="1" ht="14.45" customHeight="1">
+    <row r="116" ht="14.45" customHeight="1" s="139">
       <c r="B116" t="n">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="O116" s="4" t="n"/>
       <c r="Q116" s="4" t="n"/>
     </row>
-    <row r="117" hidden="1" ht="14.45" customHeight="1">
+    <row r="117" ht="14.45" customHeight="1" s="139">
       <c r="B117" t="n">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="O117" s="4" t="n"/>
       <c r="Q117" s="4" t="n"/>
     </row>
-    <row r="118" hidden="1" ht="14.45" customHeight="1">
+    <row r="118" ht="14.45" customHeight="1" s="139">
       <c r="B118" t="n">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="O118" s="4" t="n"/>
       <c r="Q118" s="4" t="n"/>
     </row>
-    <row r="119" hidden="1" ht="14.45" customHeight="1">
+    <row r="119" ht="14.45" customHeight="1" s="139">
       <c r="B119" t="n">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="O119" s="4" t="n"/>
       <c r="Q119" s="4" t="n"/>
     </row>
-    <row r="120" hidden="1" ht="14.45" customHeight="1">
+    <row r="120" ht="14.45" customHeight="1" s="139">
       <c r="B120" t="n">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="O120" s="4" t="n"/>
       <c r="Q120" s="4" t="n"/>
     </row>
-    <row r="121" hidden="1" ht="14.45" customHeight="1">
+    <row r="121" ht="14.45" customHeight="1" s="139">
       <c r="B121" t="n">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="O121" s="4" t="n"/>
       <c r="Q121" s="4" t="n"/>
     </row>
-    <row r="122" hidden="1" ht="14.45" customHeight="1">
+    <row r="122" ht="14.45" customHeight="1" s="139">
       <c r="B122" t="n">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="O122" s="4" t="n"/>
       <c r="Q122" s="4" t="n"/>
     </row>
-    <row r="123" hidden="1" ht="14.45" customHeight="1">
+    <row r="123" ht="14.45" customHeight="1" s="139">
       <c r="B123" t="n">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="O123" s="4" t="n"/>
       <c r="Q123" s="4" t="n"/>
     </row>
-    <row r="124" hidden="1" ht="14.45" customHeight="1">
+    <row r="124" ht="14.45" customHeight="1" s="139">
       <c r="B124" t="n">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="O124" s="4" t="n"/>
       <c r="Q124" s="4" t="n"/>
     </row>
-    <row r="125" hidden="1" ht="14.45" customHeight="1">
+    <row r="125" ht="14.45" customHeight="1" s="139">
       <c r="B125" t="n">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="O125" s="4" t="n"/>
       <c r="Q125" s="4" t="n"/>
     </row>
-    <row r="126" hidden="1" ht="14.45" customHeight="1">
+    <row r="126" ht="14.45" customHeight="1" s="139">
       <c r="B126" t="n">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="O126" s="4" t="n"/>
       <c r="Q126" s="4" t="n"/>
     </row>
-    <row r="127" hidden="1" ht="14.45" customHeight="1">
+    <row r="127" ht="14.45" customHeight="1" s="139">
       <c r="B127" t="n">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="O127" s="4" t="n"/>
       <c r="Q127" s="4" t="n"/>
     </row>
-    <row r="128" hidden="1" ht="14.45" customHeight="1">
+    <row r="128" ht="14.45" customHeight="1" s="139">
       <c r="B128" t="n">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="O128" s="4" t="n"/>
       <c r="Q128" s="4" t="n"/>
     </row>
-    <row r="129" hidden="1" ht="14.45" customHeight="1">
+    <row r="129" ht="14.45" customHeight="1" s="139">
       <c r="B129" t="n">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="O129" s="4" t="n"/>
       <c r="Q129" s="4" t="n"/>
     </row>
-    <row r="130" hidden="1" ht="14.45" customHeight="1">
+    <row r="130" ht="14.45" customHeight="1" s="139">
       <c r="B130" t="n">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="O130" s="4" t="n"/>
       <c r="Q130" s="4" t="n"/>
     </row>
-    <row r="131" hidden="1" ht="14.45" customHeight="1">
+    <row r="131" ht="14.45" customHeight="1" s="139">
       <c r="B131" t="n">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="O131" s="4" t="n"/>
       <c r="Q131" s="4" t="n"/>
     </row>
-    <row r="132" hidden="1" ht="14.45" customHeight="1">
+    <row r="132" ht="14.45" customHeight="1" s="139">
       <c r="B132" t="n">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="O132" s="4" t="n"/>
       <c r="Q132" s="4" t="n"/>
     </row>
-    <row r="133" hidden="1" ht="14.45" customHeight="1">
+    <row r="133" ht="14.45" customHeight="1" s="139">
       <c r="B133" t="n">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="O133" s="4" t="n"/>
       <c r="Q133" s="4" t="n"/>
     </row>
-    <row r="134" hidden="1" ht="14.45" customHeight="1">
+    <row r="134" ht="14.45" customHeight="1" s="139">
       <c r="B134" t="n">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="O134" s="4" t="n"/>
       <c r="Q134" s="4" t="n"/>
     </row>
-    <row r="135" hidden="1" ht="14.45" customHeight="1">
+    <row r="135" ht="14.45" customHeight="1" s="139">
       <c r="B135" t="n">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="O135" s="4" t="n"/>
       <c r="Q135" s="4" t="n"/>
     </row>
-    <row r="136" hidden="1" ht="14.45" customHeight="1">
+    <row r="136" ht="14.45" customHeight="1" s="139">
       <c r="B136" t="n">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="O136" s="4" t="n"/>
       <c r="Q136" s="4" t="n"/>
     </row>
-    <row r="137" hidden="1" ht="14.45" customHeight="1">
+    <row r="137" ht="14.45" customHeight="1" s="139">
       <c r="B137" t="n">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="O137" s="4" t="n"/>
       <c r="Q137" s="4" t="n"/>
     </row>
-    <row r="138" hidden="1" ht="14.45" customHeight="1">
+    <row r="138" ht="14.45" customHeight="1" s="139">
       <c r="B138" t="n">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="O138" s="4" t="n"/>
       <c r="Q138" s="4" t="n"/>
     </row>
-    <row r="139" hidden="1" ht="14.45" customHeight="1">
+    <row r="139" ht="14.45" customHeight="1" s="139">
       <c r="B139" t="n">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="O139" s="4" t="n"/>
       <c r="Q139" s="4" t="n"/>
     </row>
-    <row r="140" hidden="1" ht="14.45" customHeight="1">
+    <row r="140" ht="14.45" customHeight="1" s="139">
       <c r="B140" t="n">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="O140" s="4" t="n"/>
       <c r="Q140" s="4" t="n"/>
     </row>
-    <row r="141" hidden="1" ht="14.45" customHeight="1">
+    <row r="141" ht="14.45" customHeight="1" s="139">
       <c r="B141" t="n">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="O141" s="4" t="n"/>
       <c r="Q141" s="4" t="n"/>
     </row>
-    <row r="142" hidden="1" ht="14.45" customHeight="1">
+    <row r="142" ht="14.45" customHeight="1" s="139">
       <c r="B142" t="n">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="O142" s="4" t="n"/>
       <c r="Q142" s="4" t="n"/>
     </row>
-    <row r="143" hidden="1" ht="14.45" customHeight="1">
+    <row r="143" ht="14.45" customHeight="1" s="139">
       <c r="B143" t="n">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="O143" s="4" t="n"/>
       <c r="Q143" s="4" t="n"/>
     </row>
-    <row r="144" hidden="1" ht="14.45" customHeight="1">
+    <row r="144" ht="14.45" customHeight="1" s="139">
       <c r="B144" t="n">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="O144" s="4" t="n"/>
       <c r="Q144" s="4" t="n"/>
     </row>
-    <row r="145" hidden="1" ht="14.45" customHeight="1">
+    <row r="145" ht="14.45" customHeight="1" s="139">
       <c r="B145" t="n">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="O145" s="4" t="n"/>
       <c r="Q145" s="4" t="n"/>
     </row>
-    <row r="146" hidden="1" ht="14.45" customHeight="1">
+    <row r="146" ht="14.45" customHeight="1" s="139">
       <c r="B146" t="n">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="O146" s="4" t="n"/>
       <c r="Q146" s="4" t="n"/>
     </row>
-    <row r="147" hidden="1" ht="14.45" customHeight="1">
+    <row r="147" ht="14.45" customHeight="1" s="139">
       <c r="B147" t="n">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="O147" s="4" t="n"/>
       <c r="Q147" s="4" t="n"/>
     </row>
-    <row r="148" hidden="1" ht="14.45" customHeight="1">
+    <row r="148" ht="14.45" customHeight="1" s="139">
       <c r="B148" t="n">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="O148" s="4" t="n"/>
       <c r="Q148" s="4" t="n"/>
     </row>
-    <row r="149" hidden="1" ht="14.45" customHeight="1">
+    <row r="149" ht="14.45" customHeight="1" s="139">
       <c r="B149" t="n">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="O149" s="4" t="n"/>
       <c r="Q149" s="4" t="n"/>
     </row>
-    <row r="150" hidden="1" ht="14.45" customHeight="1">
+    <row r="150" ht="14.45" customHeight="1" s="139">
       <c r="B150" t="n">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="O150" s="4" t="n"/>
       <c r="Q150" s="4" t="n"/>
     </row>
-    <row r="151" hidden="1" ht="14.45" customHeight="1">
+    <row r="151" ht="14.45" customHeight="1" s="139">
       <c r="B151" t="n">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="O151" s="4" t="n"/>
       <c r="Q151" s="4" t="n"/>
     </row>
-    <row r="152" hidden="1" ht="14.45" customHeight="1">
+    <row r="152" ht="14.45" customHeight="1" s="139">
       <c r="B152" t="n">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="O152" s="4" t="n"/>
       <c r="Q152" s="4" t="n"/>
     </row>
-    <row r="153" hidden="1" ht="14.45" customHeight="1">
+    <row r="153" ht="14.45" customHeight="1" s="139">
       <c r="B153" t="n">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="O153" s="4" t="n"/>
       <c r="Q153" s="4" t="n"/>
     </row>
-    <row r="154" hidden="1" ht="14.45" customHeight="1">
+    <row r="154" ht="14.45" customHeight="1" s="139">
       <c r="B154" t="n">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="O154" s="4" t="n"/>
       <c r="Q154" s="4" t="n"/>
     </row>
-    <row r="155" hidden="1" ht="14.45" customHeight="1">
+    <row r="155" ht="14.45" customHeight="1" s="139">
       <c r="B155" t="n">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="O155" s="4" t="n"/>
       <c r="Q155" s="4" t="n"/>
     </row>
-    <row r="156" hidden="1" ht="14.45" customHeight="1">
+    <row r="156" ht="14.45" customHeight="1" s="139">
       <c r="B156" t="n">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="O156" s="4" t="n"/>
       <c r="Q156" s="4" t="n"/>
     </row>
-    <row r="157" hidden="1" ht="14.45" customHeight="1">
+    <row r="157" ht="14.45" customHeight="1" s="139">
       <c r="B157" t="n">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="O157" s="4" t="n"/>
       <c r="Q157" s="4" t="n"/>
     </row>
-    <row r="158" hidden="1" ht="14.45" customHeight="1">
+    <row r="158" ht="14.45" customHeight="1" s="139">
       <c r="B158" t="n">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="O158" s="4" t="n"/>
       <c r="Q158" s="4" t="n"/>
     </row>
-    <row r="159" hidden="1" ht="14.45" customHeight="1">
+    <row r="159" ht="14.45" customHeight="1" s="139">
       <c r="B159" t="n">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="O159" s="4" t="n"/>
       <c r="Q159" s="4" t="n"/>
     </row>
-    <row r="160" hidden="1" ht="14.45" customHeight="1">
+    <row r="160" ht="14.45" customHeight="1" s="139">
       <c r="B160" t="n">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="O160" s="4" t="n"/>
       <c r="Q160" s="4" t="n"/>
     </row>
-    <row r="161" hidden="1" ht="14.45" customHeight="1">
+    <row r="161" ht="14.45" customHeight="1" s="139">
       <c r="B161" t="n">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="O161" s="4" t="n"/>
       <c r="Q161" s="4" t="n"/>
     </row>
-    <row r="162" hidden="1" ht="14.45" customHeight="1">
+    <row r="162" ht="14.45" customHeight="1" s="139">
       <c r="B162" t="n">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="O162" s="4" t="n"/>
       <c r="Q162" s="4" t="n"/>
     </row>
-    <row r="163" hidden="1" ht="14.45" customHeight="1">
+    <row r="163" ht="14.45" customHeight="1" s="139">
       <c r="B163" t="n">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="O163" s="4" t="n"/>
       <c r="Q163" s="4" t="n"/>
     </row>
-    <row r="164" hidden="1" ht="14.45" customHeight="1">
+    <row r="164" ht="14.45" customHeight="1" s="139">
       <c r="B164" t="n">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="O164" s="4" t="n"/>
       <c r="Q164" s="4" t="n"/>
     </row>
-    <row r="165" hidden="1" ht="14.45" customHeight="1">
+    <row r="165" ht="14.45" customHeight="1" s="139">
       <c r="B165" t="n">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="O165" s="4" t="n"/>
       <c r="Q165" s="4" t="n"/>
     </row>
-    <row r="166" hidden="1" ht="14.45" customHeight="1">
+    <row r="166" ht="14.45" customHeight="1" s="139">
       <c r="B166" t="n">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="O166" s="4" t="n"/>
       <c r="Q166" s="4" t="n"/>
     </row>
-    <row r="167" hidden="1" ht="14.45" customHeight="1">
+    <row r="167" ht="14.45" customHeight="1" s="139">
       <c r="B167" t="n">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="O167" s="4" t="n"/>
       <c r="Q167" s="4" t="n"/>
     </row>
-    <row r="168" hidden="1" ht="14.45" customHeight="1">
+    <row r="168" ht="14.45" customHeight="1" s="139">
       <c r="B168" t="n">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="O168" s="4" t="n"/>
       <c r="Q168" s="4" t="n"/>
     </row>
-    <row r="169" hidden="1" ht="14.45" customHeight="1">
+    <row r="169" ht="14.45" customHeight="1" s="139">
       <c r="B169" t="n">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="O169" s="4" t="n"/>
       <c r="Q169" s="4" t="n"/>
     </row>
-    <row r="170" hidden="1" ht="14.45" customHeight="1">
+    <row r="170" ht="14.45" customHeight="1" s="139">
       <c r="B170" t="n">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="O170" s="4" t="n"/>
       <c r="Q170" s="4" t="n"/>
     </row>
-    <row r="171" hidden="1" ht="14.45" customHeight="1">
+    <row r="171" ht="14.45" customHeight="1" s="139">
       <c r="B171" t="n">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="O171" s="4" t="n"/>
       <c r="Q171" s="4" t="n"/>
     </row>
-    <row r="172" hidden="1" ht="14.45" customHeight="1">
+    <row r="172" ht="14.45" customHeight="1" s="139">
       <c r="B172" t="n">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="O172" s="4" t="n"/>
       <c r="Q172" s="4" t="n"/>
     </row>
-    <row r="173" hidden="1" ht="14.45" customHeight="1">
+    <row r="173" ht="14.45" customHeight="1" s="139">
       <c r="B173" t="n">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="O173" s="4" t="n"/>
       <c r="Q173" s="4" t="n"/>
     </row>
-    <row r="174" hidden="1" ht="14.45" customHeight="1">
+    <row r="174" ht="14.45" customHeight="1" s="139">
       <c r="B174" t="n">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="O174" s="4" t="n"/>
       <c r="Q174" s="4" t="n"/>
     </row>
-    <row r="175" hidden="1" ht="14.45" customHeight="1">
+    <row r="175" ht="14.45" customHeight="1" s="139">
       <c r="B175" t="n">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="O175" s="4" t="n"/>
       <c r="Q175" s="4" t="n"/>
     </row>
-    <row r="176" hidden="1" ht="14.45" customHeight="1">
+    <row r="176" ht="14.45" customHeight="1" s="139">
       <c r="B176" t="n">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="O176" s="4" t="n"/>
       <c r="Q176" s="4" t="n"/>
     </row>
-    <row r="177" hidden="1" ht="14.45" customHeight="1">
+    <row r="177" ht="14.45" customHeight="1" s="139">
       <c r="B177" t="n">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="O177" s="4" t="n"/>
       <c r="Q177" s="4" t="n"/>
     </row>
-    <row r="178" hidden="1" ht="14.45" customHeight="1">
+    <row r="178" ht="14.45" customHeight="1" s="139">
       <c r="B178" t="n">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="O178" s="4" t="n"/>
       <c r="Q178" s="4" t="n"/>
     </row>
-    <row r="179" hidden="1" ht="14.45" customHeight="1">
+    <row r="179" ht="14.45" customHeight="1" s="139">
       <c r="B179" t="n">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="O179" s="4" t="n"/>
       <c r="Q179" s="4" t="n"/>
     </row>
-    <row r="180" hidden="1" ht="14.45" customHeight="1">
+    <row r="180" ht="14.45" customHeight="1" s="139">
       <c r="B180" t="n">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="O180" s="4" t="n"/>
       <c r="Q180" s="4" t="n"/>
     </row>
-    <row r="181" hidden="1" ht="14.45" customHeight="1">
+    <row r="181" ht="14.45" customHeight="1" s="139">
       <c r="B181" t="n">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="O181" s="4" t="n"/>
       <c r="Q181" s="4" t="n"/>
     </row>
-    <row r="182" hidden="1" ht="14.45" customHeight="1">
+    <row r="182" ht="14.45" customHeight="1" s="139">
       <c r="B182" t="n">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="O182" s="4" t="n"/>
       <c r="Q182" s="4" t="n"/>
     </row>
-    <row r="183" hidden="1" ht="14.45" customHeight="1">
+    <row r="183" ht="14.45" customHeight="1" s="139">
       <c r="B183" t="n">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="O183" s="4" t="n"/>
       <c r="Q183" s="4" t="n"/>
     </row>
-    <row r="184" hidden="1" ht="14.45" customHeight="1">
+    <row r="184" ht="14.45" customHeight="1" s="139">
       <c r="B184" t="n">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="O184" s="4" t="n"/>
       <c r="Q184" s="4" t="n"/>
     </row>
-    <row r="185" hidden="1" ht="14.45" customHeight="1">
+    <row r="185" ht="14.45" customHeight="1" s="139">
       <c r="B185" t="n">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="O185" s="4" t="n"/>
       <c r="Q185" s="4" t="n"/>
     </row>
-    <row r="186" hidden="1" ht="14.45" customHeight="1">
+    <row r="186" ht="14.45" customHeight="1" s="139">
       <c r="B186" t="n">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="O186" s="4" t="n"/>
       <c r="Q186" s="4" t="n"/>
     </row>
-    <row r="187" hidden="1" ht="14.45" customHeight="1">
+    <row r="187" ht="14.45" customHeight="1" s="139">
       <c r="B187" t="n">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="O187" s="4" t="n"/>
       <c r="Q187" s="4" t="n"/>
     </row>
-    <row r="188" hidden="1" ht="14.45" customHeight="1">
+    <row r="188" ht="14.45" customHeight="1" s="139">
       <c r="B188" t="n">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="O188" s="4" t="n"/>
       <c r="Q188" s="4" t="n"/>
     </row>
-    <row r="189" hidden="1" ht="14.45" customHeight="1">
+    <row r="189" ht="14.45" customHeight="1" s="139">
       <c r="B189" t="n">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="O189" s="4" t="n"/>
       <c r="Q189" s="4" t="n"/>
     </row>
-    <row r="190" hidden="1" ht="14.45" customHeight="1">
+    <row r="190" ht="14.45" customHeight="1" s="139">
       <c r="B190" t="n">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="O190" s="4" t="n"/>
       <c r="Q190" s="4" t="n"/>
     </row>
-    <row r="191" hidden="1" ht="14.45" customHeight="1">
+    <row r="191" ht="14.45" customHeight="1" s="139">
       <c r="B191" t="n">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="O191" s="4" t="n"/>
       <c r="Q191" s="4" t="n"/>
     </row>
-    <row r="192" hidden="1" ht="14.45" customHeight="1">
+    <row r="192" ht="14.45" customHeight="1" s="139">
       <c r="B192" t="n">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="O192" s="4" t="n"/>
       <c r="Q192" s="4" t="n"/>
     </row>
-    <row r="193" hidden="1" ht="14.45" customHeight="1">
+    <row r="193" ht="14.45" customHeight="1" s="139">
       <c r="B193" t="n">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="O193" s="4" t="n"/>
       <c r="Q193" s="4" t="n"/>
     </row>
-    <row r="194" hidden="1" ht="14.45" customHeight="1">
+    <row r="194" ht="14.45" customHeight="1" s="139">
       <c r="B194" t="n">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="O194" s="4" t="n"/>
       <c r="Q194" s="4" t="n"/>
     </row>
-    <row r="195" hidden="1" ht="14.45" customHeight="1">
+    <row r="195" ht="14.45" customHeight="1" s="139">
       <c r="B195" t="n">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="O195" s="4" t="n"/>
       <c r="Q195" s="4" t="n"/>
     </row>
-    <row r="196" hidden="1" ht="14.45" customHeight="1">
+    <row r="196" ht="14.45" customHeight="1" s="139">
       <c r="B196" t="n">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="O196" s="4" t="n"/>
       <c r="Q196" s="4" t="n"/>
     </row>
-    <row r="197" hidden="1" ht="14.45" customHeight="1">
+    <row r="197" ht="14.45" customHeight="1" s="139">
       <c r="B197" t="n">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="O197" s="4" t="n"/>
       <c r="Q197" s="4" t="n"/>
     </row>
-    <row r="198" hidden="1" ht="14.45" customHeight="1">
+    <row r="198" ht="14.45" customHeight="1" s="139">
       <c r="B198" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O198" s="4" t="n"/>
       <c r="Q198" s="4" t="n"/>
     </row>
-    <row r="199" hidden="1" ht="14.45" customHeight="1">
+    <row r="199" ht="14.45" customHeight="1" s="139">
       <c r="B199" t="n">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="O199" s="4" t="n"/>
       <c r="Q199" s="4" t="n"/>
     </row>
-    <row r="200" hidden="1" ht="14.45" customHeight="1">
+    <row r="200" ht="14.45" customHeight="1" s="139">
       <c r="B200" t="n">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="O200" s="4" t="n"/>
       <c r="Q200" s="4" t="n"/>
     </row>
-    <row r="201" hidden="1" ht="14.45" customHeight="1">
+    <row r="201" ht="14.45" customHeight="1" s="139">
       <c r="B201" t="n">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="O201" s="4" t="n"/>
       <c r="Q201" s="4" t="n"/>
     </row>
-    <row r="202" hidden="1" ht="14.45" customHeight="1">
+    <row r="202" ht="14.45" customHeight="1" s="139">
       <c r="B202" t="n">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="O202" s="4" t="n"/>
       <c r="Q202" s="4" t="n"/>
     </row>
-    <row r="203" hidden="1" ht="14.45" customHeight="1">
+    <row r="203" ht="14.45" customHeight="1" s="139">
       <c r="B203" t="n">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="O203" s="4" t="n"/>
       <c r="Q203" s="4" t="n"/>
     </row>
-    <row r="204" hidden="1" ht="14.45" customHeight="1">
+    <row r="204" ht="14.45" customHeight="1" s="139">
       <c r="B204" t="n">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="O204" s="4" t="n"/>
       <c r="Q204" s="4" t="n"/>
     </row>
-    <row r="205" hidden="1" ht="14.45" customHeight="1">
+    <row r="205" ht="14.45" customHeight="1" s="139">
       <c r="B205" t="n">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="O205" s="4" t="n"/>
       <c r="Q205" s="4" t="n"/>
     </row>
-    <row r="206" hidden="1" ht="14.45" customHeight="1">
+    <row r="206" ht="14.45" customHeight="1" s="139">
       <c r="B206" t="n">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="O206" s="4" t="n"/>
       <c r="Q206" s="4" t="n"/>
     </row>
-    <row r="207" hidden="1" ht="14.45" customHeight="1">
+    <row r="207" ht="14.45" customHeight="1" s="139">
       <c r="B207" t="n">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="O207" s="4" t="n"/>
       <c r="Q207" s="4" t="n"/>
     </row>
-    <row r="208" hidden="1" ht="14.45" customHeight="1">
+    <row r="208" ht="14.45" customHeight="1" s="139">
       <c r="B208" t="n">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="O208" s="4" t="n"/>
       <c r="Q208" s="4" t="n"/>
     </row>
-    <row r="209" hidden="1" ht="14.45" customHeight="1">
+    <row r="209" ht="14.45" customHeight="1" s="139">
       <c r="B209" t="n">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="O209" s="4" t="n"/>
       <c r="Q209" s="4" t="n"/>
     </row>
-    <row r="210" hidden="1" ht="14.45" customHeight="1">
+    <row r="210" ht="14.45" customHeight="1" s="139">
       <c r="B210" t="n">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="O210" s="4" t="n"/>
       <c r="Q210" s="4" t="n"/>
     </row>
-    <row r="211" hidden="1" ht="14.45" customHeight="1">
+    <row r="211" ht="14.45" customHeight="1" s="139">
       <c r="B211" t="n">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="O211" s="4" t="n"/>
       <c r="Q211" s="4" t="n"/>
     </row>
-    <row r="212" hidden="1" ht="14.45" customHeight="1">
+    <row r="212" ht="14.45" customHeight="1" s="139">
       <c r="B212" t="n">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="O212" s="4" t="n"/>
       <c r="Q212" s="4" t="n"/>
     </row>
-    <row r="213" hidden="1" ht="14.45" customHeight="1">
+    <row r="213" ht="14.45" customHeight="1" s="139">
       <c r="B213" t="n">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="O213" s="4" t="n"/>
       <c r="Q213" s="4" t="n"/>
     </row>
-    <row r="214" hidden="1" ht="14.45" customHeight="1">
+    <row r="214" ht="14.45" customHeight="1" s="139">
       <c r="B214" t="n">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="O214" s="4" t="n"/>
       <c r="Q214" s="4" t="n"/>
     </row>
-    <row r="215" hidden="1" ht="14.45" customHeight="1">
+    <row r="215" ht="14.45" customHeight="1" s="139">
       <c r="B215" t="n">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="O215" s="4" t="n"/>
       <c r="Q215" s="4" t="n"/>
     </row>
-    <row r="216" hidden="1" ht="14.45" customHeight="1">
+    <row r="216" ht="14.45" customHeight="1" s="139">
       <c r="B216" t="n">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="O216" s="4" t="n"/>
       <c r="Q216" s="4" t="n"/>
     </row>
-    <row r="217" hidden="1" ht="14.45" customHeight="1">
+    <row r="217" ht="14.45" customHeight="1" s="139">
       <c r="B217" t="n">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="O217" s="4" t="n"/>
       <c r="Q217" s="4" t="n"/>
     </row>
-    <row r="218" hidden="1" ht="14.45" customHeight="1">
+    <row r="218" ht="14.45" customHeight="1" s="139">
       <c r="B218" t="n">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="O218" s="4" t="n"/>
       <c r="Q218" s="4" t="n"/>
     </row>
-    <row r="219" hidden="1" ht="14.45" customHeight="1">
+    <row r="219" ht="14.45" customHeight="1" s="139">
       <c r="B219" t="n">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="O219" s="4" t="n"/>
       <c r="Q219" s="4" t="n"/>
     </row>
-    <row r="220" hidden="1" ht="14.45" customHeight="1">
+    <row r="220" ht="14.45" customHeight="1" s="139">
       <c r="B220" t="n">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="O220" s="4" t="n"/>
       <c r="Q220" s="4" t="n"/>
     </row>
-    <row r="221" hidden="1" ht="14.45" customHeight="1">
+    <row r="221" ht="14.45" customHeight="1" s="139">
       <c r="B221" t="n">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="O221" s="4" t="n"/>
       <c r="Q221" s="4" t="n"/>
     </row>
-    <row r="222" hidden="1" ht="14.45" customHeight="1">
+    <row r="222" ht="14.45" customHeight="1" s="139">
       <c r="B222" t="n">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="O222" s="4" t="n"/>
       <c r="Q222" s="4" t="n"/>
     </row>
-    <row r="223" hidden="1" ht="14.45" customHeight="1">
+    <row r="223" ht="14.45" customHeight="1" s="139">
       <c r="B223" t="n">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="O223" s="4" t="n"/>
       <c r="Q223" s="4" t="n"/>
     </row>
-    <row r="224" hidden="1" ht="14.45" customHeight="1">
+    <row r="224" ht="14.45" customHeight="1" s="139">
       <c r="B224" t="n">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="O224" s="4" t="n"/>
       <c r="Q224" s="4" t="n"/>
     </row>
-    <row r="225" hidden="1" ht="14.45" customHeight="1">
+    <row r="225" ht="14.45" customHeight="1" s="139">
       <c r="B225" t="n">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="O225" s="4" t="n"/>
       <c r="Q225" s="4" t="n"/>
     </row>
-    <row r="226" hidden="1" ht="14.45" customHeight="1">
+    <row r="226" ht="14.45" customHeight="1" s="139">
       <c r="B226" t="n">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="O226" s="4" t="n"/>
       <c r="Q226" s="4" t="n"/>
     </row>
-    <row r="227" hidden="1" ht="14.45" customHeight="1">
+    <row r="227" ht="14.45" customHeight="1" s="139">
       <c r="B227" t="n">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="O227" s="4" t="n"/>
       <c r="Q227" s="4" t="n"/>
     </row>
-    <row r="228" hidden="1" ht="14.45" customHeight="1">
+    <row r="228" ht="14.45" customHeight="1" s="139">
       <c r="B228" t="n">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="O228" s="4" t="n"/>
       <c r="Q228" s="4" t="n"/>
     </row>
-    <row r="229" hidden="1" ht="14.45" customHeight="1">
+    <row r="229" ht="14.45" customHeight="1" s="139">
       <c r="B229" t="n">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="O229" s="4" t="n"/>
       <c r="Q229" s="4" t="n"/>
     </row>
-    <row r="230" hidden="1" ht="14.45" customHeight="1">
+    <row r="230" ht="14.45" customHeight="1" s="139">
       <c r="B230" t="n">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="O230" s="4" t="n"/>
       <c r="Q230" s="4" t="n"/>
     </row>
-    <row r="231" hidden="1" ht="14.45" customHeight="1">
+    <row r="231" ht="14.45" customHeight="1" s="139">
       <c r="B231" t="n">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="O231" s="4" t="n"/>
       <c r="Q231" s="4" t="n"/>
     </row>
-    <row r="232" hidden="1" ht="14.45" customHeight="1">
+    <row r="232" ht="14.45" customHeight="1" s="139">
       <c r="B232" t="n">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="O232" s="4" t="n"/>
       <c r="Q232" s="4" t="n"/>
     </row>
-    <row r="233" hidden="1" ht="14.45" customHeight="1">
+    <row r="233" ht="14.45" customHeight="1" s="139">
       <c r="B233" t="n">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="O233" s="4" t="n"/>
       <c r="Q233" s="4" t="n"/>
     </row>
-    <row r="234" hidden="1" ht="14.45" customHeight="1">
+    <row r="234" ht="14.45" customHeight="1" s="139">
       <c r="B234" t="n">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="O234" s="4" t="n"/>
       <c r="Q234" s="4" t="n"/>
     </row>
-    <row r="235" hidden="1" ht="14.45" customHeight="1">
+    <row r="235" ht="14.45" customHeight="1" s="139">
       <c r="B235" t="n">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="O235" s="4" t="n"/>
       <c r="Q235" s="4" t="n"/>
     </row>
-    <row r="236" hidden="1" ht="14.45" customHeight="1">
+    <row r="236" ht="14.45" customHeight="1" s="139">
       <c r="B236" t="n">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="O236" s="4" t="n"/>
       <c r="Q236" s="4" t="n"/>
     </row>
-    <row r="237" hidden="1" ht="14.45" customHeight="1">
+    <row r="237" ht="14.45" customHeight="1" s="139">
       <c r="B237" t="n">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="O237" s="4" t="n"/>
       <c r="Q237" s="4" t="n"/>
     </row>
-    <row r="238" hidden="1" ht="14.45" customHeight="1">
+    <row r="238" ht="14.45" customHeight="1" s="139">
       <c r="B238" t="n">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="O238" s="4" t="n"/>
       <c r="Q238" s="4" t="n"/>
     </row>
-    <row r="239" hidden="1" ht="14.45" customHeight="1">
+    <row r="239" ht="14.45" customHeight="1" s="139">
       <c r="B239" t="n">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="O239" s="4" t="n"/>
       <c r="Q239" s="4" t="n"/>
     </row>
-    <row r="240" hidden="1" ht="14.45" customHeight="1">
+    <row r="240" ht="14.45" customHeight="1" s="139">
       <c r="B240" t="n">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="O240" s="4" t="n"/>
       <c r="Q240" s="4" t="n"/>
     </row>
-    <row r="241" hidden="1" ht="14.45" customHeight="1">
+    <row r="241" ht="14.45" customHeight="1" s="139">
       <c r="B241" t="n">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="O241" s="4" t="n"/>
       <c r="Q241" s="4" t="n"/>
     </row>
-    <row r="242" hidden="1" ht="14.45" customHeight="1">
+    <row r="242" ht="14.45" customHeight="1" s="139">
       <c r="B242" t="n">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="O242" s="4" t="n"/>
       <c r="Q242" s="4" t="n"/>
     </row>
-    <row r="243" hidden="1" ht="14.45" customHeight="1">
+    <row r="243" ht="14.45" customHeight="1" s="139">
       <c r="B243" t="n">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="O243" s="4" t="n"/>
       <c r="Q243" s="4" t="n"/>
     </row>
-    <row r="244" hidden="1" ht="14.45" customHeight="1">
+    <row r="244" ht="14.45" customHeight="1" s="139">
       <c r="B244" t="n">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="O244" s="4" t="n"/>
       <c r="Q244" s="4" t="n"/>
     </row>
-    <row r="245" hidden="1" ht="14.45" customHeight="1">
+    <row r="245" ht="14.45" customHeight="1" s="139">
       <c r="B245" t="n">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="O245" s="4" t="n"/>
       <c r="Q245" s="4" t="n"/>
     </row>
-    <row r="246" hidden="1" ht="14.45" customHeight="1">
+    <row r="246" ht="14.45" customHeight="1" s="139">
       <c r="B246" t="n">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="O246" s="4" t="n"/>
       <c r="Q246" s="4" t="n"/>
     </row>
-    <row r="247" hidden="1" ht="14.45" customHeight="1">
+    <row r="247" ht="14.45" customHeight="1" s="139">
       <c r="B247" t="n">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="O247" s="4" t="n"/>
       <c r="Q247" s="4" t="n"/>
     </row>
-    <row r="248" hidden="1" ht="14.45" customHeight="1">
+    <row r="248" ht="14.45" customHeight="1" s="139">
       <c r="B248" t="n">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="O248" s="4" t="n"/>
       <c r="Q248" s="4" t="n"/>
     </row>
-    <row r="249" hidden="1" ht="14.45" customHeight="1">
+    <row r="249" ht="14.45" customHeight="1" s="139">
       <c r="B249" t="n">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="O249" s="4" t="n"/>
       <c r="Q249" s="4" t="n"/>
     </row>
-    <row r="250" hidden="1" ht="14.45" customHeight="1">
+    <row r="250" ht="14.45" customHeight="1" s="139">
       <c r="B250" t="n">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="O250" s="4" t="n"/>
       <c r="Q250" s="4" t="n"/>
     </row>
-    <row r="251" hidden="1" ht="14.45" customHeight="1">
+    <row r="251" ht="14.45" customHeight="1" s="139">
       <c r="B251" t="n">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="O251" s="4" t="n"/>
       <c r="Q251" s="4" t="n"/>
     </row>
-    <row r="252" hidden="1" ht="14.45" customHeight="1">
+    <row r="252" ht="14.45" customHeight="1" s="139">
       <c r="B252" t="n">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="O252" s="4" t="n"/>
       <c r="Q252" s="4" t="n"/>
     </row>
-    <row r="253" hidden="1" ht="14.45" customHeight="1">
+    <row r="253" ht="14.45" customHeight="1" s="139">
       <c r="B253" t="n">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="O253" s="4" t="n"/>
       <c r="Q253" s="4" t="n"/>
     </row>
-    <row r="254" hidden="1" ht="14.45" customHeight="1">
+    <row r="254" ht="14.45" customHeight="1" s="139">
       <c r="B254" t="n">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="O254" s="4" t="n"/>
       <c r="Q254" s="4" t="n"/>
     </row>
-    <row r="255" hidden="1" ht="14.45" customHeight="1">
+    <row r="255" ht="14.45" customHeight="1" s="139">
       <c r="B255" t="n">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="O255" s="4" t="n"/>
       <c r="Q255" s="4" t="n"/>
     </row>
-    <row r="256" hidden="1" ht="14.45" customHeight="1">
+    <row r="256" ht="14.45" customHeight="1" s="139">
       <c r="B256" t="n">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="O256" s="4" t="n"/>
       <c r="Q256" s="4" t="n"/>
     </row>
-    <row r="257" hidden="1" ht="14.45" customHeight="1">
+    <row r="257" ht="14.45" customHeight="1" s="139">
       <c r="B257" t="n">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="O257" s="4" t="n"/>
       <c r="Q257" s="4" t="n"/>
     </row>
-    <row r="258" hidden="1" ht="14.45" customHeight="1">
+    <row r="258" ht="14.45" customHeight="1" s="139">
       <c r="B258" t="n">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="O258" s="4" t="n"/>
       <c r="Q258" s="4" t="n"/>
     </row>
-    <row r="259" hidden="1" ht="14.45" customHeight="1">
+    <row r="259" ht="14.45" customHeight="1" s="139">
       <c r="B259" t="n">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="O259" s="4" t="n"/>
       <c r="Q259" s="4" t="n"/>
     </row>
-    <row r="260" hidden="1" ht="14.45" customHeight="1">
+    <row r="260" ht="14.45" customHeight="1" s="139">
       <c r="B260" t="n">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="O260" s="4" t="n"/>
       <c r="Q260" s="4" t="n"/>
     </row>
-    <row r="261" hidden="1" ht="14.45" customHeight="1">
+    <row r="261" ht="14.45" customHeight="1" s="139">
       <c r="B261" t="n">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="O261" s="4" t="n"/>
       <c r="Q261" s="4" t="n"/>
     </row>
-    <row r="262" hidden="1" ht="14.45" customHeight="1">
+    <row r="262" ht="14.45" customHeight="1" s="139">
       <c r="B262" t="n">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="O262" s="4" t="n"/>
       <c r="Q262" s="4" t="n"/>
     </row>
-    <row r="263" hidden="1" ht="14.45" customHeight="1">
+    <row r="263" ht="14.45" customHeight="1" s="139">
       <c r="B263" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O263" s="4" t="n"/>
       <c r="Q263" s="4" t="n"/>
     </row>
-    <row r="264" hidden="1" ht="14.45" customHeight="1">
+    <row r="264" ht="14.45" customHeight="1" s="139">
       <c r="B264" t="n">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="O264" s="4" t="n"/>
       <c r="Q264" s="4" t="n"/>
     </row>
-    <row r="265" hidden="1" ht="14.45" customHeight="1">
+    <row r="265" ht="14.45" customHeight="1" s="139">
       <c r="B265" t="n">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="O265" s="4" t="n"/>
       <c r="Q265" s="4" t="n"/>
     </row>
-    <row r="266" hidden="1" ht="14.45" customHeight="1">
+    <row r="266" ht="14.45" customHeight="1" s="139">
       <c r="B266" t="n">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="O266" s="4" t="n"/>
       <c r="Q266" s="4" t="n"/>
     </row>
-    <row r="267" hidden="1" ht="14.45" customHeight="1">
+    <row r="267" ht="14.45" customHeight="1" s="139">
       <c r="B267" t="n">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="O267" s="4" t="n"/>
       <c r="Q267" s="4" t="n"/>
     </row>
-    <row r="268" hidden="1" ht="14.45" customHeight="1">
+    <row r="268" ht="14.45" customHeight="1" s="139">
       <c r="B268" t="n">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="O268" s="4" t="n"/>
       <c r="Q268" s="4" t="n"/>
     </row>
-    <row r="269" hidden="1" ht="14.45" customHeight="1">
+    <row r="269" ht="14.45" customHeight="1" s="139">
       <c r="B269" t="n">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="O269" s="4" t="n"/>
       <c r="Q269" s="4" t="n"/>
     </row>
-    <row r="270" hidden="1" ht="14.45" customHeight="1">
+    <row r="270" ht="14.45" customHeight="1" s="139">
       <c r="B270" t="n">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="O270" s="4" t="n"/>
       <c r="Q270" s="4" t="n"/>
     </row>
-    <row r="271" hidden="1" ht="14.45" customHeight="1">
+    <row r="271" ht="14.45" customHeight="1" s="139">
       <c r="B271" t="n">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="O271" s="4" t="n"/>
       <c r="Q271" s="4" t="n"/>
     </row>
-    <row r="272" hidden="1" ht="14.45" customHeight="1">
+    <row r="272" ht="14.45" customHeight="1" s="139">
       <c r="B272" t="n">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="O272" s="4" t="n"/>
       <c r="Q272" s="4" t="n"/>
     </row>
-    <row r="273" hidden="1" ht="14.45" customHeight="1">
+    <row r="273" ht="14.45" customHeight="1" s="139">
       <c r="B273" t="n">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="O273" s="4" t="n"/>
       <c r="Q273" s="4" t="n"/>
     </row>
-    <row r="274" hidden="1" ht="14.45" customHeight="1">
+    <row r="274" ht="14.45" customHeight="1" s="139">
       <c r="B274" t="n">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="O274" s="4" t="n"/>
       <c r="Q274" s="4" t="n"/>
     </row>
-    <row r="275" hidden="1" ht="14.45" customHeight="1">
+    <row r="275" ht="14.45" customHeight="1" s="139">
       <c r="B275" t="n">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="O275" s="4" t="n"/>
       <c r="Q275" s="4" t="n"/>
     </row>
-    <row r="276" hidden="1" ht="14.45" customHeight="1">
+    <row r="276" ht="14.45" customHeight="1" s="139">
       <c r="B276" t="n">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="O276" s="4" t="n"/>
       <c r="Q276" s="4" t="n"/>
     </row>
-    <row r="277" hidden="1" ht="14.45" customHeight="1">
+    <row r="277" ht="14.45" customHeight="1" s="139">
       <c r="B277" t="n">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="O277" s="4" t="n"/>
       <c r="Q277" s="4" t="n"/>
     </row>
-    <row r="278" hidden="1" ht="14.45" customHeight="1">
+    <row r="278" ht="14.45" customHeight="1" s="139">
       <c r="B278" t="n">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="O278" s="4" t="n"/>
       <c r="Q278" s="4" t="n"/>
     </row>
-    <row r="279" hidden="1" ht="14.45" customHeight="1">
+    <row r="279" ht="14.45" customHeight="1" s="139">
       <c r="B279" t="n">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="O279" s="4" t="n"/>
       <c r="Q279" s="4" t="n"/>
     </row>
-    <row r="280" hidden="1" ht="14.45" customHeight="1">
+    <row r="280" ht="14.45" customHeight="1" s="139">
       <c r="B280" t="n">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="O280" s="4" t="n"/>
       <c r="Q280" s="4" t="n"/>
     </row>
-    <row r="281" hidden="1" ht="14.45" customHeight="1">
+    <row r="281" ht="14.45" customHeight="1" s="139">
       <c r="B281" t="n">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="O281" s="4" t="n"/>
       <c r="Q281" s="4" t="n"/>
     </row>
-    <row r="282" hidden="1" ht="14.45" customHeight="1">
+    <row r="282" ht="14.45" customHeight="1" s="139">
       <c r="B282" t="n">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="O282" s="4" t="n"/>
       <c r="Q282" s="4" t="n"/>
     </row>
-    <row r="283" hidden="1" ht="14.45" customHeight="1">
+    <row r="283" ht="14.45" customHeight="1" s="139">
       <c r="B283" t="n">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="O283" s="4" t="n"/>
       <c r="Q283" s="4" t="n"/>
     </row>
-    <row r="284" hidden="1" ht="14.45" customHeight="1">
+    <row r="284" ht="14.45" customHeight="1" s="139">
       <c r="B284" t="n">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="O284" s="4" t="n"/>
       <c r="Q284" s="4" t="n"/>
     </row>
-    <row r="285" hidden="1" ht="14.45" customHeight="1">
+    <row r="285" ht="14.45" customHeight="1" s="139">
       <c r="B285" t="n">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="O285" s="4" t="n"/>
       <c r="Q285" s="4" t="n"/>
     </row>
-    <row r="286" hidden="1" ht="14.45" customHeight="1">
+    <row r="286" ht="14.45" customHeight="1" s="139">
       <c r="B286" t="n">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="O286" s="4" t="n"/>
       <c r="Q286" s="4" t="n"/>
     </row>
-    <row r="287" hidden="1" ht="14.45" customHeight="1">
+    <row r="287" ht="14.45" customHeight="1" s="139">
       <c r="B287" t="n">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="O287" s="4" t="n"/>
       <c r="Q287" s="4" t="n"/>
     </row>
-    <row r="288" hidden="1" ht="14.45" customHeight="1">
+    <row r="288" ht="14.45" customHeight="1" s="139">
       <c r="B288" t="n">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="O288" s="4" t="n"/>
       <c r="Q288" s="4" t="n"/>
     </row>
-    <row r="289" hidden="1" ht="14.45" customHeight="1">
+    <row r="289" ht="14.45" customHeight="1" s="139">
       <c r="B289" t="n">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="O289" s="4" t="n"/>
       <c r="Q289" s="4" t="n"/>
     </row>
-    <row r="290" hidden="1" ht="14.45" customHeight="1">
+    <row r="290" ht="14.45" customHeight="1" s="139">
       <c r="B290" t="n">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="O290" s="4" t="n"/>
       <c r="Q290" s="4" t="n"/>
     </row>
-    <row r="291" hidden="1" ht="14.45" customHeight="1">
+    <row r="291" ht="14.45" customHeight="1" s="139">
       <c r="B291" t="n">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="O291" s="4" t="n"/>
       <c r="Q291" s="4" t="n"/>
     </row>
-    <row r="292" hidden="1" ht="14.45" customHeight="1">
+    <row r="292" ht="14.45" customHeight="1" s="139">
       <c r="B292" t="n">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="O292" s="4" t="n"/>
       <c r="Q292" s="4" t="n"/>
     </row>
-    <row r="293" hidden="1" ht="14.45" customHeight="1">
+    <row r="293" ht="14.45" customHeight="1" s="139">
       <c r="B293" t="n">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="O293" s="4" t="n"/>
       <c r="Q293" s="4" t="n"/>
     </row>
-    <row r="294" hidden="1" ht="14.45" customHeight="1">
+    <row r="294" ht="14.45" customHeight="1" s="139">
       <c r="B294" t="n">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="O294" s="4" t="n"/>
       <c r="Q294" s="4" t="n"/>
     </row>
-    <row r="295" hidden="1" ht="14.45" customHeight="1">
+    <row r="295" ht="14.45" customHeight="1" s="139">
       <c r="B295" t="n">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="O295" s="4" t="n"/>
       <c r="Q295" s="4" t="n"/>
     </row>
-    <row r="296" hidden="1" ht="14.45" customHeight="1">
+    <row r="296" ht="14.45" customHeight="1" s="139">
       <c r="B296" t="n">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="O296" s="4" t="n"/>
       <c r="Q296" s="4" t="n"/>
     </row>
-    <row r="297" hidden="1" ht="14.45" customHeight="1">
+    <row r="297" ht="14.45" customHeight="1" s="139">
       <c r="B297" t="n">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="O297" s="4" t="n"/>
       <c r="Q297" s="4" t="n"/>
     </row>
-    <row r="298" hidden="1" ht="14.45" customHeight="1">
+    <row r="298" ht="14.45" customHeight="1" s="139">
       <c r="B298" t="n">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="O298" s="4" t="n"/>
       <c r="Q298" s="4" t="n"/>
     </row>
-    <row r="299" hidden="1" ht="14.45" customHeight="1">
+    <row r="299" ht="14.45" customHeight="1" s="139">
       <c r="B299" t="n">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="O299" s="4" t="n"/>
       <c r="Q299" s="4" t="n"/>
     </row>
-    <row r="300" hidden="1" ht="14.45" customHeight="1">
+    <row r="300" ht="14.45" customHeight="1" s="139">
       <c r="B300" t="n">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="O300" s="4" t="n"/>
       <c r="Q300" s="4" t="n"/>
     </row>
-    <row r="301" hidden="1" ht="14.45" customHeight="1">
+    <row r="301" ht="14.45" customHeight="1" s="139">
       <c r="B301" t="n">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="O301" s="4" t="n"/>
       <c r="Q301" s="4" t="n"/>
     </row>
-    <row r="302" hidden="1" ht="14.45" customHeight="1">
+    <row r="302" ht="14.45" customHeight="1" s="139">
       <c r="B302" t="n">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="O302" s="4" t="n"/>
       <c r="Q302" s="4" t="n"/>
     </row>
-    <row r="303" hidden="1" ht="14.45" customHeight="1">
+    <row r="303" ht="14.45" customHeight="1" s="139">
       <c r="B303" t="n">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="O303" s="4" t="n"/>
       <c r="Q303" s="4" t="n"/>
     </row>
-    <row r="304" hidden="1" ht="14.45" customHeight="1">
+    <row r="304" ht="14.45" customHeight="1" s="139">
       <c r="B304" t="n">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="O304" s="4" t="n"/>
       <c r="Q304" s="4" t="n"/>
     </row>
-    <row r="305" hidden="1" ht="14.45" customHeight="1">
+    <row r="305" ht="14.45" customHeight="1" s="139">
       <c r="B305" t="n">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="O305" s="4" t="n"/>
       <c r="Q305" s="4" t="n"/>
     </row>
-    <row r="306" hidden="1" ht="14.45" customHeight="1">
+    <row r="306" ht="14.45" customHeight="1" s="139">
       <c r="B306" t="n">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="O306" s="4" t="n"/>
       <c r="Q306" s="4" t="n"/>
     </row>
-    <row r="307" hidden="1" ht="14.45" customHeight="1">
+    <row r="307" ht="14.45" customHeight="1" s="139">
       <c r="B307" t="n">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="O307" s="4" t="n"/>
       <c r="Q307" s="4" t="n"/>
     </row>
-    <row r="308" hidden="1" ht="14.45" customHeight="1">
+    <row r="308" ht="14.45" customHeight="1" s="139">
       <c r="B308" t="n">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="O308" s="4" t="n"/>
       <c r="Q308" s="4" t="n"/>
     </row>
-    <row r="309" hidden="1" ht="14.45" customHeight="1">
+    <row r="309" ht="14.45" customHeight="1" s="139">
       <c r="B309" t="n">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="O309" s="4" t="n"/>
       <c r="Q309" s="4" t="n"/>
     </row>
-    <row r="310" hidden="1" ht="14.45" customHeight="1">
+    <row r="310" ht="14.45" customHeight="1" s="139">
       <c r="B310" t="n">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="O310" s="4" t="n"/>
       <c r="Q310" s="4" t="n"/>
     </row>
-    <row r="311" hidden="1" ht="14.45" customHeight="1">
+    <row r="311" ht="14.45" customHeight="1" s="139">
       <c r="B311" t="n">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="O311" s="4" t="n"/>
       <c r="Q311" s="4" t="n"/>
     </row>
-    <row r="312" hidden="1" ht="14.45" customHeight="1">
+    <row r="312" ht="14.45" customHeight="1" s="139">
       <c r="B312" t="n">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="O312" s="4" t="n"/>
       <c r="Q312" s="4" t="n"/>
     </row>
-    <row r="313" hidden="1" ht="14.45" customHeight="1">
+    <row r="313" ht="14.45" customHeight="1" s="139">
       <c r="B313" t="n">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="O313" s="4" t="n"/>
       <c r="Q313" s="4" t="n"/>
     </row>
-    <row r="314" hidden="1" ht="14.45" customHeight="1">
+    <row r="314" ht="14.45" customHeight="1" s="139">
       <c r="B314" t="n">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="O314" s="4" t="n"/>
       <c r="Q314" s="4" t="n"/>
     </row>
-    <row r="315" hidden="1" ht="14.45" customHeight="1">
+    <row r="315" ht="14.45" customHeight="1" s="139">
       <c r="B315" t="n">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="O315" s="4" t="n"/>
       <c r="Q315" s="4" t="n"/>
     </row>
-    <row r="316" hidden="1" ht="14.45" customHeight="1">
+    <row r="316" ht="14.45" customHeight="1" s="139">
       <c r="B316" t="n">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="O316" s="4" t="n"/>
       <c r="Q316" s="4" t="n"/>
     </row>
-    <row r="317" hidden="1" ht="14.45" customHeight="1">
+    <row r="317" ht="14.45" customHeight="1" s="139">
       <c r="B317" t="n">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="O317" s="4" t="n"/>
       <c r="Q317" s="4" t="n"/>
     </row>
-    <row r="318" hidden="1" ht="14.45" customHeight="1">
+    <row r="318" ht="14.45" customHeight="1" s="139">
       <c r="B318" t="n">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="O318" s="4" t="n"/>
       <c r="Q318" s="4" t="n"/>
     </row>
-    <row r="319" hidden="1" ht="14.45" customHeight="1">
+    <row r="319" ht="14.45" customHeight="1" s="139">
       <c r="B319" t="n">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="O319" s="4" t="n"/>
       <c r="Q319" s="4" t="n"/>
     </row>
-    <row r="320" hidden="1" ht="14.45" customHeight="1">
+    <row r="320" ht="14.45" customHeight="1" s="139">
       <c r="B320" t="n">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="O320" s="4" t="n"/>
       <c r="Q320" s="4" t="n"/>
     </row>
-    <row r="321" hidden="1" ht="14.45" customHeight="1">
+    <row r="321" ht="14.45" customHeight="1" s="139">
       <c r="B321" t="n">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="O321" s="4" t="n"/>
       <c r="Q321" s="4" t="n"/>
     </row>
-    <row r="322" hidden="1" ht="14.45" customHeight="1">
+    <row r="322" ht="14.45" customHeight="1" s="139">
       <c r="B322" t="n">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="O322" s="4" t="n"/>
       <c r="Q322" s="4" t="n"/>
     </row>
-    <row r="323" hidden="1" ht="14.45" customHeight="1">
+    <row r="323" ht="14.45" customHeight="1" s="139">
       <c r="B323" t="n">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="O323" s="4" t="n"/>
       <c r="Q323" s="4" t="n"/>
     </row>
-    <row r="324" hidden="1" ht="14.45" customHeight="1">
+    <row r="324" ht="14.45" customHeight="1" s="139">
       <c r="B324" t="n">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="O324" s="4" t="n"/>
       <c r="Q324" s="4" t="n"/>
     </row>
-    <row r="325" hidden="1" ht="14.45" customHeight="1">
+    <row r="325" ht="14.45" customHeight="1" s="139">
       <c r="B325" t="n">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="O325" s="4" t="n"/>
       <c r="Q325" s="4" t="n"/>
     </row>
-    <row r="326" hidden="1" ht="14.45" customHeight="1">
+    <row r="326" ht="14.45" customHeight="1" s="139">
       <c r="B326" t="n">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="O326" s="4" t="n"/>
       <c r="Q326" s="4" t="n"/>
     </row>
-    <row r="327" hidden="1" ht="14.45" customHeight="1">
+    <row r="327" ht="14.45" customHeight="1" s="139">
       <c r="B327" t="n">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="O327" s="4" t="n"/>
       <c r="Q327" s="4" t="n"/>
     </row>
-    <row r="328" hidden="1" ht="14.45" customHeight="1">
+    <row r="328" ht="14.45" customHeight="1" s="139">
       <c r="B328" t="n">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="O328" s="4" t="n"/>
       <c r="Q328" s="4" t="n"/>
     </row>
-    <row r="329" hidden="1" ht="14.45" customHeight="1">
+    <row r="329" ht="14.45" customHeight="1" s="139">
       <c r="B329" t="n">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="O329" s="4" t="n"/>
       <c r="Q329" s="4" t="n"/>
     </row>
-    <row r="330" hidden="1" ht="14.45" customHeight="1">
+    <row r="330" ht="14.45" customHeight="1" s="139">
       <c r="B330" t="n">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="O330" s="4" t="n"/>
       <c r="Q330" s="4" t="n"/>
     </row>
-    <row r="331" hidden="1" ht="14.45" customHeight="1">
+    <row r="331" ht="14.45" customHeight="1" s="139">
       <c r="B331" t="n">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="O331" s="4" t="n"/>
       <c r="Q331" s="4" t="n"/>
     </row>
-    <row r="332" hidden="1" ht="14.45" customHeight="1">
+    <row r="332" ht="14.45" customHeight="1" s="139">
       <c r="B332" t="n">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="O332" s="4" t="n"/>
       <c r="Q332" s="4" t="n"/>
     </row>
-    <row r="333" hidden="1" ht="14.45" customHeight="1">
+    <row r="333" ht="14.45" customHeight="1" s="139">
       <c r="B333" t="n">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="O333" s="4" t="n"/>
       <c r="Q333" s="4" t="n"/>
     </row>
-    <row r="334" hidden="1" ht="14.45" customHeight="1">
+    <row r="334" ht="14.45" customHeight="1" s="139">
       <c r="B334" t="n">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="O334" s="4" t="n"/>
       <c r="Q334" s="4" t="n"/>
     </row>
-    <row r="335" hidden="1" ht="14.45" customHeight="1">
+    <row r="335" ht="14.45" customHeight="1" s="139">
       <c r="B335" t="n">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="O335" s="4" t="n"/>
       <c r="Q335" s="4" t="n"/>
     </row>
-    <row r="336" hidden="1" ht="14.45" customHeight="1">
+    <row r="336" ht="14.45" customHeight="1" s="139">
       <c r="B336" t="n">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="O336" s="4" t="n"/>
       <c r="Q336" s="4" t="n"/>
     </row>
-    <row r="337" hidden="1" ht="14.45" customHeight="1">
+    <row r="337" ht="14.45" customHeight="1" s="139">
       <c r="B337" t="n">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="O337" s="4" t="n"/>
       <c r="Q337" s="4" t="n"/>
     </row>
-    <row r="338" hidden="1" ht="14.45" customHeight="1">
+    <row r="338" ht="14.45" customHeight="1" s="139">
       <c r="B338" t="n">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="O338" s="4" t="n"/>
       <c r="Q338" s="4" t="n"/>
     </row>
-    <row r="339" hidden="1" ht="14.45" customHeight="1">
+    <row r="339" ht="14.45" customHeight="1" s="139">
       <c r="B339" t="n">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="O339" s="4" t="n"/>
       <c r="Q339" s="4" t="n"/>
     </row>
-    <row r="340" hidden="1" ht="14.45" customHeight="1">
+    <row r="340" ht="14.45" customHeight="1" s="139">
       <c r="B340" t="n">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="O340" s="4" t="n"/>
       <c r="Q340" s="4" t="n"/>
     </row>
-    <row r="341" hidden="1" ht="14.45" customHeight="1">
+    <row r="341" ht="14.45" customHeight="1" s="139">
       <c r="B341" t="n">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="O341" s="4" t="n"/>
       <c r="Q341" s="4" t="n"/>
     </row>
-    <row r="342" hidden="1" ht="14.45" customHeight="1">
+    <row r="342" ht="14.45" customHeight="1" s="139">
       <c r="B342" t="n">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="O342" s="4" t="n"/>
       <c r="Q342" s="4" t="n"/>
     </row>
-    <row r="343" hidden="1" ht="14.45" customHeight="1">
+    <row r="343" ht="14.45" customHeight="1" s="139">
       <c r="B343" t="n">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="O343" s="4" t="n"/>
       <c r="Q343" s="4" t="n"/>
     </row>
-    <row r="344" hidden="1" ht="14.45" customHeight="1">
+    <row r="344" ht="14.45" customHeight="1" s="139">
       <c r="B344" t="n">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="O344" s="4" t="n"/>
       <c r="Q344" s="4" t="n"/>
     </row>
-    <row r="345" hidden="1" ht="14.45" customHeight="1">
+    <row r="345" ht="14.45" customHeight="1" s="139">
       <c r="B345" t="n">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="O345" s="4" t="n"/>
       <c r="Q345" s="4" t="n"/>
     </row>
-    <row r="346" hidden="1" ht="14.45" customHeight="1">
+    <row r="346" ht="14.45" customHeight="1" s="139">
       <c r="B346" t="n">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="O346" s="4" t="n"/>
       <c r="Q346" s="4" t="n"/>
     </row>
-    <row r="347" hidden="1" ht="14.45" customHeight="1">
+    <row r="347" ht="14.45" customHeight="1" s="139">
       <c r="B347" t="n">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="O347" s="4" t="n"/>
       <c r="Q347" s="4" t="n"/>
     </row>
-    <row r="348" hidden="1" ht="14.45" customHeight="1">
+    <row r="348" ht="14.45" customHeight="1" s="139">
       <c r="B348" t="n">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="O348" s="4" t="n"/>
       <c r="Q348" s="4" t="n"/>
     </row>
-    <row r="349" hidden="1" ht="14.45" customHeight="1">
+    <row r="349" ht="14.45" customHeight="1" s="139">
       <c r="B349" t="n">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="O349" s="4" t="n"/>
       <c r="Q349" s="4" t="n"/>
     </row>
-    <row r="350" hidden="1" ht="14.45" customHeight="1">
+    <row r="350" ht="14.45" customHeight="1" s="139">
       <c r="B350" t="n">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="O350" s="4" t="n"/>
       <c r="Q350" s="4" t="n"/>
     </row>
-    <row r="351" hidden="1" ht="14.45" customHeight="1">
+    <row r="351" ht="14.45" customHeight="1" s="139">
       <c r="B351" t="n">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="O351" s="4" t="n"/>
       <c r="Q351" s="4" t="n"/>
     </row>
-    <row r="352" hidden="1" ht="14.45" customHeight="1">
+    <row r="352" ht="14.45" customHeight="1" s="139">
       <c r="B352" t="n">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="O352" s="4" t="n"/>
       <c r="Q352" s="4" t="n"/>
     </row>
-    <row r="353" hidden="1" ht="14.45" customHeight="1">
+    <row r="353" ht="14.45" customHeight="1" s="139">
       <c r="B353" t="n">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="O353" s="4" t="n"/>
       <c r="Q353" s="4" t="n"/>
     </row>
-    <row r="354" hidden="1" ht="14.45" customHeight="1">
+    <row r="354" ht="14.45" customHeight="1" s="139">
       <c r="B354" t="n">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="O354" s="4" t="n"/>
       <c r="Q354" s="4" t="n"/>
     </row>
-    <row r="355" hidden="1" ht="14.45" customHeight="1">
+    <row r="355" ht="14.45" customHeight="1" s="139">
       <c r="B355" t="n">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="O355" s="4" t="n"/>
       <c r="Q355" s="4" t="n"/>
     </row>
-    <row r="356" hidden="1" ht="14.45" customHeight="1">
+    <row r="356" ht="14.45" customHeight="1" s="139">
       <c r="B356" t="n">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="O356" s="4" t="n"/>
       <c r="Q356" s="4" t="n"/>
     </row>
-    <row r="357" hidden="1" ht="14.45" customHeight="1">
+    <row r="357" ht="14.45" customHeight="1" s="139">
       <c r="B357" t="n">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="O357" s="4" t="n"/>
       <c r="Q357" s="4" t="n"/>
     </row>
-    <row r="358" hidden="1" ht="14.45" customHeight="1">
+    <row r="358" ht="14.45" customHeight="1" s="139">
       <c r="B358" t="n">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="O358" s="4" t="n"/>
       <c r="Q358" s="4" t="n"/>
     </row>
-    <row r="359" hidden="1" ht="14.45" customHeight="1">
+    <row r="359" ht="14.45" customHeight="1" s="139">
       <c r="B359" t="n">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="O359" s="4" t="n"/>
       <c r="Q359" s="4" t="n"/>
     </row>
-    <row r="360" hidden="1" ht="14.45" customHeight="1">
+    <row r="360" ht="14.45" customHeight="1" s="139">
       <c r="B360" t="n">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="O360" s="4" t="n"/>
       <c r="Q360" s="4" t="n"/>
     </row>
-    <row r="361" hidden="1" ht="14.45" customHeight="1">
+    <row r="361" ht="14.45" customHeight="1" s="139">
       <c r="B361" t="n">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="O361" s="4" t="n"/>
       <c r="Q361" s="4" t="n"/>
     </row>
-    <row r="362" hidden="1" ht="14.45" customHeight="1">
+    <row r="362" ht="14.45" customHeight="1" s="139">
       <c r="B362" t="n">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="O362" s="4" t="n"/>
       <c r="Q362" s="4" t="n"/>
     </row>
-    <row r="363" hidden="1" ht="14.45" customHeight="1">
+    <row r="363" ht="14.45" customHeight="1" s="139">
       <c r="B363" t="n">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="O363" s="4" t="n"/>
       <c r="Q363" s="4" t="n"/>
     </row>
-    <row r="364" hidden="1" ht="14.45" customHeight="1">
+    <row r="364" ht="14.45" customHeight="1" s="139">
       <c r="B364" t="n">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="O364" s="4" t="n"/>
       <c r="Q364" s="4" t="n"/>
     </row>
-    <row r="365" hidden="1" ht="14.45" customHeight="1">
+    <row r="365" ht="14.45" customHeight="1" s="139">
       <c r="B365" t="n">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="O365" s="4" t="n"/>
       <c r="Q365" s="4" t="n"/>
     </row>
-    <row r="366" hidden="1" ht="14.45" customHeight="1">
+    <row r="366" ht="14.45" customHeight="1" s="139">
       <c r="B366" t="n">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="O366" s="4" t="n"/>
       <c r="Q366" s="4" t="n"/>
     </row>
-    <row r="367" hidden="1" ht="14.45" customHeight="1">
+    <row r="367" ht="14.45" customHeight="1" s="139">
       <c r="B367" t="n">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="O367" s="4" t="n"/>
       <c r="Q367" s="4" t="n"/>
     </row>
-    <row r="368" hidden="1" ht="14.45" customHeight="1">
+    <row r="368" ht="14.45" customHeight="1" s="139">
       <c r="B368" t="n">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="O368" s="4" t="n"/>
       <c r="Q368" s="4" t="n"/>
     </row>
-    <row r="369" hidden="1" ht="14.45" customHeight="1">
+    <row r="369" ht="14.45" customHeight="1" s="139">
       <c r="B369" t="n">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="O369" s="4" t="n"/>
       <c r="Q369" s="4" t="n"/>
     </row>
-    <row r="370" hidden="1" ht="14.45" customHeight="1">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
+    <row r="370" ht="14.45" customHeight="1" s="139">
       <c r="B370" t="n">
-        <v>3357</v>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>Unilever FOOD</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>NP8</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>FEG</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>bh10</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>2023.1.0.45.0</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>bh10-00j-euw</t>
-        </is>
-      </c>
-      <c r="L370" t="inlineStr">
-        <is>
-          <t>exec-wms-gxo-unilever-les</t>
-        </is>
-      </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
-        </is>
+        <v>3356</v>
       </c>
       <c r="O370" s="4" t="n"/>
       <c r="Q370" s="4" t="n"/>
     </row>
-    <row r="371" hidden="1" ht="14.45" customHeight="1">
+    <row r="371" ht="14.45" customHeight="1" s="139">
       <c r="A371" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Unilever HOME CARE</t>
+          <t>Unilever FOOD</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7481,18 +7466,18 @@
       <c r="O371" s="4" t="n"/>
       <c r="Q371" s="4" t="n"/>
     </row>
-    <row r="372" hidden="1" ht="14.45" customHeight="1">
+    <row r="372" ht="14.45" customHeight="1" s="139">
       <c r="A372" t="inlineStr">
         <is>
           <t>EMEA</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Unilever Personal Care</t>
+          <t>Unilever HOME CARE</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -7538,1099 +7523,1144 @@
       <c r="O372" s="4" t="n"/>
       <c r="Q372" s="4" t="n"/>
     </row>
-    <row r="373" hidden="1" ht="14.45" customHeight="1">
+    <row r="373" ht="14.45" customHeight="1" s="139">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
       <c r="B373" t="n">
-        <v>3360</v>
+        <v>3359</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Unilever Personal Care</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>NP8</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>FEG</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>bh10</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2023.1.0.45.0</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>bh10-00j-euw</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>exec-wms-gxo-unilever-les</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>ZAC DE L ECOPARC , 45210 Ferrières-en-Gâtinais, France</t>
+        </is>
       </c>
       <c r="O373" s="4" t="n"/>
       <c r="Q373" s="4" t="n"/>
     </row>
-    <row r="374" hidden="1" ht="14.45" customHeight="1">
+    <row r="374" ht="14.45" customHeight="1" s="139">
       <c r="B374" t="n">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="O374" s="4" t="n"/>
       <c r="Q374" s="4" t="n"/>
     </row>
-    <row r="375" hidden="1" ht="14.45" customHeight="1">
+    <row r="375" ht="14.45" customHeight="1" s="139">
       <c r="B375" t="n">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="O375" s="4" t="n"/>
       <c r="Q375" s="4" t="n"/>
     </row>
-    <row r="376" hidden="1" ht="14.45" customHeight="1">
+    <row r="376" ht="14.45" customHeight="1" s="139">
       <c r="B376" t="n">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="O376" s="4" t="n"/>
       <c r="Q376" s="4" t="n"/>
     </row>
-    <row r="377" hidden="1" ht="14.45" customHeight="1">
+    <row r="377" ht="14.45" customHeight="1" s="139">
       <c r="B377" t="n">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="O377" s="4" t="n"/>
       <c r="Q377" s="4" t="n"/>
     </row>
-    <row r="378" hidden="1" ht="14.45" customHeight="1">
+    <row r="378" ht="14.45" customHeight="1" s="139">
       <c r="B378" t="n">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="O378" s="4" t="n"/>
       <c r="Q378" s="4" t="n"/>
     </row>
-    <row r="379" hidden="1" ht="14.45" customHeight="1">
+    <row r="379" ht="14.45" customHeight="1" s="139">
       <c r="B379" t="n">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="O379" s="4" t="n"/>
       <c r="Q379" s="4" t="n"/>
     </row>
-    <row r="380" hidden="1" ht="14.45" customHeight="1">
+    <row r="380" ht="14.45" customHeight="1" s="139">
       <c r="B380" t="n">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="O380" s="4" t="n"/>
       <c r="Q380" s="4" t="n"/>
     </row>
-    <row r="381" hidden="1" ht="14.45" customHeight="1">
+    <row r="381" ht="14.45" customHeight="1" s="139">
       <c r="B381" t="n">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="O381" s="4" t="n"/>
       <c r="Q381" s="4" t="n"/>
     </row>
-    <row r="382" hidden="1" ht="14.45" customHeight="1">
+    <row r="382" ht="14.45" customHeight="1" s="139">
       <c r="B382" t="n">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="O382" s="4" t="n"/>
       <c r="Q382" s="4" t="n"/>
     </row>
-    <row r="383" hidden="1" ht="14.45" customHeight="1">
+    <row r="383" ht="14.45" customHeight="1" s="139">
       <c r="B383" t="n">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="O383" s="4" t="n"/>
       <c r="Q383" s="4" t="n"/>
     </row>
-    <row r="384" hidden="1" ht="14.45" customHeight="1">
+    <row r="384" ht="14.45" customHeight="1" s="139">
       <c r="B384" t="n">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="O384" s="4" t="n"/>
       <c r="Q384" s="4" t="n"/>
     </row>
-    <row r="385" hidden="1" ht="14.45" customHeight="1">
+    <row r="385" ht="14.45" customHeight="1" s="139">
       <c r="B385" t="n">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="O385" s="4" t="n"/>
       <c r="Q385" s="4" t="n"/>
     </row>
-    <row r="386" hidden="1" ht="14.45" customHeight="1">
+    <row r="386" ht="14.45" customHeight="1" s="139">
       <c r="B386" t="n">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="O386" s="4" t="n"/>
       <c r="Q386" s="4" t="n"/>
     </row>
-    <row r="387" hidden="1" ht="14.45" customHeight="1">
+    <row r="387" ht="14.45" customHeight="1" s="139">
       <c r="B387" t="n">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="O387" s="4" t="n"/>
       <c r="Q387" s="4" t="n"/>
     </row>
-    <row r="388" hidden="1" ht="14.45" customHeight="1">
+    <row r="388" ht="14.45" customHeight="1" s="139">
       <c r="B388" t="n">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="O388" s="4" t="n"/>
       <c r="Q388" s="4" t="n"/>
     </row>
-    <row r="389" hidden="1" ht="14.45" customHeight="1">
+    <row r="389" ht="14.45" customHeight="1" s="139">
       <c r="B389" t="n">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="O389" s="4" t="n"/>
       <c r="Q389" s="4" t="n"/>
     </row>
-    <row r="390" hidden="1" ht="14.45" customHeight="1">
+    <row r="390" ht="14.45" customHeight="1" s="139">
       <c r="B390" t="n">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="O390" s="4" t="n"/>
       <c r="Q390" s="4" t="n"/>
     </row>
-    <row r="391" hidden="1" ht="14.45" customHeight="1">
+    <row r="391" ht="14.45" customHeight="1" s="139">
       <c r="B391" t="n">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="O391" s="4" t="n"/>
       <c r="Q391" s="4" t="n"/>
     </row>
-    <row r="392" hidden="1" ht="14.45" customHeight="1">
+    <row r="392" ht="14.45" customHeight="1" s="139">
       <c r="B392" t="n">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="O392" s="4" t="n"/>
       <c r="Q392" s="4" t="n"/>
     </row>
-    <row r="393" hidden="1" ht="14.45" customHeight="1">
+    <row r="393" ht="14.45" customHeight="1" s="139">
       <c r="B393" t="n">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="O393" s="4" t="n"/>
       <c r="Q393" s="4" t="n"/>
     </row>
-    <row r="394" hidden="1" ht="14.45" customHeight="1">
+    <row r="394" ht="14.45" customHeight="1" s="139">
       <c r="B394" t="n">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="O394" s="4" t="n"/>
       <c r="Q394" s="4" t="n"/>
     </row>
-    <row r="395" hidden="1" ht="14.45" customHeight="1">
+    <row r="395" ht="14.45" customHeight="1" s="139">
       <c r="B395" t="n">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="O395" s="4" t="n"/>
       <c r="Q395" s="4" t="n"/>
     </row>
-    <row r="396" hidden="1" ht="14.45" customHeight="1">
+    <row r="396" ht="14.45" customHeight="1" s="139">
       <c r="B396" t="n">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="O396" s="4" t="n"/>
       <c r="Q396" s="4" t="n"/>
     </row>
-    <row r="397" hidden="1" ht="14.45" customHeight="1">
+    <row r="397" ht="14.45" customHeight="1" s="139">
       <c r="B397" t="n">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="O397" s="4" t="n"/>
       <c r="Q397" s="4" t="n"/>
     </row>
-    <row r="398" hidden="1" ht="14.45" customHeight="1">
+    <row r="398" ht="14.45" customHeight="1" s="139">
       <c r="B398" t="n">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="O398" s="4" t="n"/>
       <c r="Q398" s="4" t="n"/>
     </row>
-    <row r="399" hidden="1" ht="14.45" customHeight="1">
+    <row r="399" ht="14.45" customHeight="1" s="139">
       <c r="B399" t="n">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="O399" s="4" t="n"/>
       <c r="Q399" s="4" t="n"/>
     </row>
-    <row r="400" hidden="1" ht="14.45" customHeight="1">
+    <row r="400" ht="14.45" customHeight="1" s="139">
       <c r="B400" t="n">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="O400" s="4" t="n"/>
       <c r="Q400" s="4" t="n"/>
     </row>
-    <row r="401" hidden="1" ht="14.45" customHeight="1">
+    <row r="401" ht="14.45" customHeight="1" s="139">
       <c r="B401" t="n">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="O401" s="4" t="n"/>
       <c r="Q401" s="4" t="n"/>
     </row>
-    <row r="402" hidden="1" ht="14.45" customHeight="1">
+    <row r="402" ht="14.45" customHeight="1" s="139">
       <c r="B402" t="n">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="O402" s="4" t="n"/>
       <c r="Q402" s="4" t="n"/>
     </row>
-    <row r="403" hidden="1" ht="14.45" customHeight="1">
+    <row r="403" ht="14.45" customHeight="1" s="139">
       <c r="B403" t="n">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="O403" s="4" t="n"/>
       <c r="Q403" s="4" t="n"/>
     </row>
-    <row r="404" hidden="1" ht="14.45" customHeight="1">
+    <row r="404" ht="14.45" customHeight="1" s="139">
       <c r="B404" t="n">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="O404" s="4" t="n"/>
       <c r="Q404" s="4" t="n"/>
     </row>
-    <row r="405" hidden="1" ht="14.45" customHeight="1">
+    <row r="405" ht="14.45" customHeight="1" s="139">
       <c r="B405" t="n">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="O405" s="4" t="n"/>
       <c r="Q405" s="4" t="n"/>
     </row>
-    <row r="406" hidden="1" ht="14.45" customHeight="1">
+    <row r="406" ht="14.45" customHeight="1" s="139">
       <c r="B406" t="n">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="O406" s="4" t="n"/>
       <c r="Q406" s="4" t="n"/>
     </row>
-    <row r="407" hidden="1" ht="14.45" customHeight="1">
+    <row r="407" ht="14.45" customHeight="1" s="139">
       <c r="B407" t="n">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="O407" s="4" t="n"/>
       <c r="Q407" s="4" t="n"/>
     </row>
-    <row r="408" hidden="1" ht="14.45" customHeight="1">
+    <row r="408" ht="14.45" customHeight="1" s="139">
       <c r="B408" t="n">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="O408" s="4" t="n"/>
       <c r="Q408" s="4" t="n"/>
     </row>
-    <row r="409" hidden="1" ht="14.45" customHeight="1">
+    <row r="409" ht="14.45" customHeight="1" s="139">
       <c r="B409" t="n">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="O409" s="4" t="n"/>
       <c r="Q409" s="4" t="n"/>
     </row>
-    <row r="410" hidden="1" ht="14.45" customHeight="1">
+    <row r="410" ht="14.45" customHeight="1" s="139">
       <c r="B410" t="n">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="O410" s="4" t="n"/>
       <c r="Q410" s="4" t="n"/>
     </row>
-    <row r="411" hidden="1" ht="14.45" customHeight="1">
+    <row r="411" ht="14.45" customHeight="1" s="139">
       <c r="B411" t="n">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="O411" s="4" t="n"/>
       <c r="Q411" s="4" t="n"/>
     </row>
-    <row r="412" hidden="1" ht="14.45" customHeight="1">
+    <row r="412" ht="14.45" customHeight="1" s="139">
       <c r="B412" t="n">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="O412" s="4" t="n"/>
       <c r="Q412" s="4" t="n"/>
     </row>
-    <row r="413" hidden="1" ht="14.45" customHeight="1">
+    <row r="413" ht="14.45" customHeight="1" s="139">
       <c r="B413" t="n">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="O413" s="4" t="n"/>
       <c r="Q413" s="4" t="n"/>
     </row>
-    <row r="414" hidden="1" ht="14.45" customHeight="1">
+    <row r="414" ht="14.45" customHeight="1" s="139">
       <c r="B414" t="n">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="O414" s="4" t="n"/>
       <c r="Q414" s="4" t="n"/>
     </row>
-    <row r="415" hidden="1" ht="14.45" customHeight="1">
+    <row r="415" ht="14.45" customHeight="1" s="139">
       <c r="B415" t="n">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="O415" s="4" t="n"/>
       <c r="Q415" s="4" t="n"/>
     </row>
-    <row r="416" hidden="1" ht="14.45" customHeight="1">
+    <row r="416" ht="14.45" customHeight="1" s="139">
       <c r="B416" t="n">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="O416" s="4" t="n"/>
       <c r="Q416" s="4" t="n"/>
     </row>
-    <row r="417" hidden="1" ht="14.45" customHeight="1">
+    <row r="417" ht="14.45" customHeight="1" s="139">
       <c r="B417" t="n">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="O417" s="4" t="n"/>
       <c r="Q417" s="4" t="n"/>
     </row>
-    <row r="418" hidden="1" ht="14.45" customHeight="1">
+    <row r="418" ht="14.45" customHeight="1" s="139">
       <c r="B418" t="n">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="O418" s="4" t="n"/>
       <c r="Q418" s="4" t="n"/>
     </row>
-    <row r="419" hidden="1" ht="14.45" customHeight="1">
+    <row r="419" ht="14.45" customHeight="1" s="139">
       <c r="B419" t="n">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="O419" s="4" t="n"/>
       <c r="Q419" s="4" t="n"/>
     </row>
-    <row r="420" hidden="1" ht="14.45" customHeight="1">
+    <row r="420" ht="14.45" customHeight="1" s="139">
       <c r="B420" t="n">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="O420" s="4" t="n"/>
       <c r="Q420" s="4" t="n"/>
     </row>
-    <row r="421" hidden="1" ht="14.45" customHeight="1">
+    <row r="421" ht="14.45" customHeight="1" s="139">
       <c r="B421" t="n">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="O421" s="4" t="n"/>
       <c r="Q421" s="4" t="n"/>
     </row>
-    <row r="422" hidden="1" ht="14.45" customHeight="1">
+    <row r="422" ht="14.45" customHeight="1" s="139">
       <c r="B422" t="n">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="O422" s="4" t="n"/>
       <c r="Q422" s="4" t="n"/>
     </row>
-    <row r="423" hidden="1" ht="14.45" customHeight="1">
+    <row r="423" ht="14.45" customHeight="1" s="139">
       <c r="B423" t="n">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="O423" s="4" t="n"/>
       <c r="Q423" s="4" t="n"/>
     </row>
-    <row r="424" hidden="1" ht="14.45" customHeight="1">
+    <row r="424" ht="14.45" customHeight="1" s="139">
       <c r="B424" t="n">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="O424" s="4" t="n"/>
       <c r="Q424" s="4" t="n"/>
     </row>
-    <row r="425" hidden="1" ht="14.45" customHeight="1">
+    <row r="425" ht="14.45" customHeight="1" s="139">
       <c r="B425" t="n">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="O425" s="4" t="n"/>
       <c r="Q425" s="4" t="n"/>
     </row>
-    <row r="426" hidden="1" ht="14.45" customHeight="1">
+    <row r="426" ht="14.45" customHeight="1" s="139">
       <c r="B426" t="n">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="O426" s="4" t="n"/>
       <c r="Q426" s="4" t="n"/>
     </row>
-    <row r="427" hidden="1" ht="14.45" customHeight="1">
+    <row r="427" ht="14.45" customHeight="1" s="139">
       <c r="B427" t="n">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="O427" s="4" t="n"/>
       <c r="Q427" s="4" t="n"/>
     </row>
-    <row r="428" hidden="1" ht="14.45" customHeight="1">
+    <row r="428" ht="14.45" customHeight="1" s="139">
       <c r="B428" t="n">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="O428" s="4" t="n"/>
       <c r="Q428" s="4" t="n"/>
     </row>
-    <row r="429" hidden="1" ht="14.45" customHeight="1">
+    <row r="429" ht="14.45" customHeight="1" s="139">
       <c r="B429" t="n">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="O429" s="4" t="n"/>
       <c r="Q429" s="4" t="n"/>
     </row>
-    <row r="430" hidden="1" ht="14.45" customHeight="1">
+    <row r="430" ht="14.45" customHeight="1" s="139">
       <c r="B430" t="n">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="O430" s="4" t="n"/>
       <c r="Q430" s="4" t="n"/>
     </row>
-    <row r="431" hidden="1" ht="14.45" customHeight="1">
+    <row r="431" ht="14.45" customHeight="1" s="139">
       <c r="B431" t="n">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="O431" s="4" t="n"/>
       <c r="Q431" s="4" t="n"/>
     </row>
-    <row r="432" hidden="1" ht="14.45" customHeight="1">
+    <row r="432" ht="14.45" customHeight="1" s="139">
       <c r="B432" t="n">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="O432" s="4" t="n"/>
       <c r="Q432" s="4" t="n"/>
     </row>
-    <row r="433" hidden="1" ht="14.45" customHeight="1">
+    <row r="433" ht="14.45" customHeight="1" s="139">
       <c r="B433" t="n">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="O433" s="4" t="n"/>
       <c r="Q433" s="4" t="n"/>
     </row>
-    <row r="434" hidden="1" ht="14.45" customHeight="1">
+    <row r="434" ht="14.45" customHeight="1" s="139">
       <c r="B434" t="n">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="O434" s="4" t="n"/>
       <c r="Q434" s="4" t="n"/>
     </row>
-    <row r="435" hidden="1" ht="14.45" customHeight="1">
+    <row r="435" ht="14.45" customHeight="1" s="139">
       <c r="B435" t="n">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="O435" s="4" t="n"/>
       <c r="Q435" s="4" t="n"/>
     </row>
-    <row r="436" hidden="1" ht="14.45" customHeight="1">
+    <row r="436" ht="14.45" customHeight="1" s="139">
       <c r="B436" t="n">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="O436" s="4" t="n"/>
       <c r="Q436" s="4" t="n"/>
     </row>
-    <row r="437" hidden="1" ht="14.45" customHeight="1">
+    <row r="437" ht="14.45" customHeight="1" s="139">
       <c r="B437" t="n">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="O437" s="4" t="n"/>
       <c r="Q437" s="4" t="n"/>
     </row>
-    <row r="438" hidden="1" ht="14.45" customHeight="1">
+    <row r="438" ht="14.45" customHeight="1" s="139">
       <c r="B438" t="n">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="O438" s="4" t="n"/>
       <c r="Q438" s="4" t="n"/>
     </row>
-    <row r="439" hidden="1" ht="14.45" customHeight="1">
+    <row r="439" ht="14.45" customHeight="1" s="139">
       <c r="B439" t="n">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="O439" s="4" t="n"/>
       <c r="Q439" s="4" t="n"/>
     </row>
-    <row r="440" hidden="1" ht="14.45" customHeight="1">
+    <row r="440" ht="14.45" customHeight="1" s="139">
       <c r="B440" t="n">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="O440" s="4" t="n"/>
       <c r="Q440" s="4" t="n"/>
     </row>
-    <row r="441" hidden="1" ht="14.45" customHeight="1">
+    <row r="441" ht="14.45" customHeight="1" s="139">
       <c r="B441" t="n">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="O441" s="4" t="n"/>
       <c r="Q441" s="4" t="n"/>
     </row>
-    <row r="442" hidden="1" ht="14.45" customHeight="1">
+    <row r="442" ht="14.45" customHeight="1" s="139">
       <c r="B442" t="n">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="O442" s="4" t="n"/>
       <c r="Q442" s="4" t="n"/>
     </row>
-    <row r="443" hidden="1" ht="14.45" customHeight="1">
+    <row r="443" ht="14.45" customHeight="1" s="139">
       <c r="B443" t="n">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="O443" s="4" t="n"/>
       <c r="Q443" s="4" t="n"/>
     </row>
-    <row r="444" hidden="1" ht="14.45" customHeight="1">
+    <row r="444" ht="14.45" customHeight="1" s="139">
       <c r="B444" t="n">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="O444" s="4" t="n"/>
       <c r="Q444" s="4" t="n"/>
     </row>
-    <row r="445" hidden="1" ht="14.45" customHeight="1">
+    <row r="445" ht="14.45" customHeight="1" s="139">
       <c r="B445" t="n">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="O445" s="4" t="n"/>
       <c r="Q445" s="4" t="n"/>
     </row>
-    <row r="446" hidden="1" ht="14.45" customHeight="1">
+    <row r="446" ht="14.45" customHeight="1" s="139">
       <c r="B446" t="n">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="O446" s="4" t="n"/>
       <c r="Q446" s="4" t="n"/>
     </row>
-    <row r="447" hidden="1" ht="14.45" customHeight="1">
+    <row r="447" ht="14.45" customHeight="1" s="139">
       <c r="B447" t="n">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="O447" s="4" t="n"/>
       <c r="Q447" s="4" t="n"/>
     </row>
-    <row r="448" hidden="1" ht="14.45" customHeight="1">
+    <row r="448" ht="14.45" customHeight="1" s="139">
       <c r="B448" t="n">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="O448" s="4" t="n"/>
       <c r="Q448" s="4" t="n"/>
     </row>
-    <row r="449" hidden="1" ht="14.45" customHeight="1">
+    <row r="449" ht="14.45" customHeight="1" s="139">
       <c r="B449" t="n">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="O449" s="4" t="n"/>
       <c r="Q449" s="4" t="n"/>
     </row>
-    <row r="450" hidden="1" ht="14.45" customHeight="1">
+    <row r="450" ht="14.45" customHeight="1" s="139">
       <c r="B450" t="n">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="O450" s="4" t="n"/>
       <c r="Q450" s="4" t="n"/>
     </row>
-    <row r="451" hidden="1" ht="14.45" customHeight="1">
+    <row r="451" ht="14.45" customHeight="1" s="139">
       <c r="B451" t="n">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="O451" s="4" t="n"/>
       <c r="Q451" s="4" t="n"/>
     </row>
-    <row r="452" hidden="1" ht="14.45" customHeight="1">
+    <row r="452" ht="14.45" customHeight="1" s="139">
       <c r="B452" t="n">
-        <v>3439</v>
+        <v>3438</v>
       </c>
       <c r="O452" s="4" t="n"/>
       <c r="Q452" s="4" t="n"/>
     </row>
-    <row r="453" hidden="1" ht="14.45" customHeight="1">
+    <row r="453" ht="14.45" customHeight="1" s="139">
       <c r="B453" t="n">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="O453" s="4" t="n"/>
       <c r="Q453" s="4" t="n"/>
     </row>
-    <row r="454" hidden="1" ht="14.45" customHeight="1">
+    <row r="454" ht="14.45" customHeight="1" s="139">
       <c r="B454" t="n">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="O454" s="4" t="n"/>
       <c r="Q454" s="4" t="n"/>
     </row>
-    <row r="455" hidden="1" ht="14.45" customHeight="1">
+    <row r="455" ht="14.45" customHeight="1" s="139">
       <c r="B455" t="n">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="O455" s="4" t="n"/>
       <c r="Q455" s="4" t="n"/>
     </row>
-    <row r="456" hidden="1" ht="14.45" customHeight="1">
+    <row r="456" ht="14.45" customHeight="1" s="139">
       <c r="B456" t="n">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="O456" s="4" t="n"/>
       <c r="Q456" s="4" t="n"/>
     </row>
-    <row r="457" hidden="1" ht="14.45" customHeight="1">
+    <row r="457" ht="14.45" customHeight="1" s="139">
       <c r="B457" t="n">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="O457" s="4" t="n"/>
       <c r="Q457" s="4" t="n"/>
     </row>
-    <row r="458" hidden="1" ht="14.45" customHeight="1">
+    <row r="458" ht="14.45" customHeight="1" s="139">
       <c r="B458" t="n">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="O458" s="4" t="n"/>
       <c r="Q458" s="4" t="n"/>
     </row>
-    <row r="459" hidden="1" ht="14.45" customHeight="1">
+    <row r="459" ht="14.45" customHeight="1" s="139">
       <c r="B459" t="n">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="O459" s="4" t="n"/>
       <c r="Q459" s="4" t="n"/>
     </row>
-    <row r="460" hidden="1" ht="14.45" customHeight="1">
+    <row r="460" ht="14.45" customHeight="1" s="139">
       <c r="B460" t="n">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="O460" s="4" t="n"/>
       <c r="Q460" s="4" t="n"/>
     </row>
-    <row r="461" hidden="1" ht="14.45" customHeight="1">
+    <row r="461" ht="14.45" customHeight="1" s="139">
       <c r="B461" t="n">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="O461" s="4" t="n"/>
       <c r="Q461" s="4" t="n"/>
     </row>
-    <row r="462" hidden="1" ht="14.45" customHeight="1">
+    <row r="462" ht="14.45" customHeight="1" s="139">
       <c r="B462" t="n">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="O462" s="4" t="n"/>
       <c r="Q462" s="4" t="n"/>
     </row>
-    <row r="463" hidden="1" ht="14.45" customHeight="1">
+    <row r="463" ht="14.45" customHeight="1" s="139">
       <c r="B463" t="n">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="O463" s="4" t="n"/>
       <c r="Q463" s="4" t="n"/>
     </row>
-    <row r="464" hidden="1" ht="14.45" customHeight="1">
+    <row r="464" ht="14.45" customHeight="1" s="139">
       <c r="B464" t="n">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="O464" s="4" t="n"/>
       <c r="Q464" s="4" t="n"/>
     </row>
-    <row r="465" hidden="1" ht="14.45" customHeight="1">
+    <row r="465" ht="14.45" customHeight="1" s="139">
       <c r="B465" t="n">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="O465" s="4" t="n"/>
       <c r="Q465" s="4" t="n"/>
     </row>
-    <row r="466" hidden="1" ht="14.45" customHeight="1">
+    <row r="466" ht="14.45" customHeight="1" s="139">
       <c r="B466" t="n">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="O466" s="4" t="n"/>
       <c r="Q466" s="4" t="n"/>
     </row>
-    <row r="467" hidden="1" ht="14.45" customHeight="1">
+    <row r="467" ht="14.45" customHeight="1" s="139">
       <c r="B467" t="n">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="O467" s="4" t="n"/>
       <c r="Q467" s="4" t="n"/>
     </row>
-    <row r="468" hidden="1" ht="14.45" customHeight="1">
+    <row r="468" ht="14.45" customHeight="1" s="139">
       <c r="B468" t="n">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="O468" s="4" t="n"/>
       <c r="Q468" s="4" t="n"/>
     </row>
-    <row r="469" hidden="1" ht="14.45" customHeight="1">
+    <row r="469" ht="14.45" customHeight="1" s="139">
       <c r="B469" t="n">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="O469" s="4" t="n"/>
       <c r="Q469" s="4" t="n"/>
     </row>
-    <row r="470" hidden="1" ht="14.45" customHeight="1">
+    <row r="470" ht="14.45" customHeight="1" s="139">
       <c r="B470" t="n">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="O470" s="4" t="n"/>
       <c r="Q470" s="4" t="n"/>
     </row>
-    <row r="471" hidden="1" ht="14.45" customHeight="1">
+    <row r="471" ht="14.45" customHeight="1" s="139">
       <c r="B471" t="n">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="O471" s="4" t="n"/>
       <c r="Q471" s="4" t="n"/>
     </row>
-    <row r="472" hidden="1" ht="14.45" customHeight="1">
+    <row r="472" ht="14.45" customHeight="1" s="139">
       <c r="B472" t="n">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="O472" s="4" t="n"/>
       <c r="Q472" s="4" t="n"/>
     </row>
-    <row r="473" hidden="1" ht="14.45" customHeight="1">
+    <row r="473" ht="14.45" customHeight="1" s="139">
       <c r="B473" t="n">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="O473" s="4" t="n"/>
       <c r="Q473" s="4" t="n"/>
     </row>
-    <row r="474" hidden="1" ht="14.45" customHeight="1">
+    <row r="474" ht="14.45" customHeight="1" s="139">
       <c r="B474" t="n">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="O474" s="4" t="n"/>
       <c r="Q474" s="4" t="n"/>
     </row>
-    <row r="475" hidden="1" ht="14.45" customHeight="1">
+    <row r="475" ht="14.45" customHeight="1" s="139">
       <c r="B475" t="n">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="O475" s="4" t="n"/>
       <c r="Q475" s="4" t="n"/>
     </row>
-    <row r="476" hidden="1" ht="14.45" customHeight="1">
+    <row r="476" ht="14.45" customHeight="1" s="139">
       <c r="B476" t="n">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="O476" s="4" t="n"/>
       <c r="Q476" s="4" t="n"/>
     </row>
-    <row r="477" hidden="1" ht="14.45" customHeight="1">
+    <row r="477" ht="14.45" customHeight="1" s="139">
       <c r="B477" t="n">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="O477" s="4" t="n"/>
       <c r="Q477" s="4" t="n"/>
     </row>
-    <row r="478" hidden="1" ht="14.45" customHeight="1">
+    <row r="478" ht="14.45" customHeight="1" s="139">
       <c r="B478" t="n">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="O478" s="4" t="n"/>
       <c r="Q478" s="4" t="n"/>
     </row>
-    <row r="479" hidden="1" ht="14.45" customHeight="1">
+    <row r="479" ht="14.45" customHeight="1" s="139">
       <c r="B479" t="n">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="O479" s="4" t="n"/>
       <c r="Q479" s="4" t="n"/>
     </row>
-    <row r="480" hidden="1" ht="14.45" customHeight="1">
+    <row r="480" ht="14.45" customHeight="1" s="139">
       <c r="B480" t="n">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="O480" s="4" t="n"/>
       <c r="Q480" s="4" t="n"/>
     </row>
-    <row r="481" hidden="1" ht="14.45" customHeight="1">
+    <row r="481" ht="14.45" customHeight="1" s="139">
       <c r="B481" t="n">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="O481" s="4" t="n"/>
       <c r="Q481" s="4" t="n"/>
     </row>
-    <row r="482" hidden="1" ht="14.45" customHeight="1">
+    <row r="482" ht="14.45" customHeight="1" s="139">
       <c r="B482" t="n">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="O482" s="4" t="n"/>
       <c r="Q482" s="4" t="n"/>
     </row>
-    <row r="483" hidden="1" ht="14.45" customHeight="1">
+    <row r="483" ht="14.45" customHeight="1" s="139">
       <c r="B483" t="n">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="O483" s="4" t="n"/>
       <c r="Q483" s="4" t="n"/>
     </row>
-    <row r="484" hidden="1" ht="14.45" customHeight="1">
+    <row r="484" ht="14.45" customHeight="1" s="139">
       <c r="B484" t="n">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="O484" s="4" t="n"/>
       <c r="Q484" s="4" t="n"/>
     </row>
-    <row r="485" hidden="1" ht="14.45" customHeight="1">
+    <row r="485" ht="14.45" customHeight="1" s="139">
       <c r="B485" t="n">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="O485" s="4" t="n"/>
       <c r="Q485" s="4" t="n"/>
     </row>
-    <row r="486" hidden="1" ht="14.45" customHeight="1">
+    <row r="486" ht="14.45" customHeight="1" s="139">
       <c r="B486" t="n">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="O486" s="4" t="n"/>
       <c r="Q486" s="4" t="n"/>
     </row>
-    <row r="487" hidden="1" ht="14.45" customHeight="1">
+    <row r="487" ht="14.45" customHeight="1" s="139">
       <c r="B487" t="n">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="O487" s="4" t="n"/>
       <c r="Q487" s="4" t="n"/>
     </row>
-    <row r="488" hidden="1" ht="14.45" customHeight="1">
+    <row r="488" ht="14.45" customHeight="1" s="139">
       <c r="B488" t="n">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="O488" s="4" t="n"/>
       <c r="Q488" s="4" t="n"/>
     </row>
-    <row r="489" hidden="1" ht="14.45" customHeight="1">
+    <row r="489" ht="14.45" customHeight="1" s="139">
       <c r="B489" t="n">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="O489" s="4" t="n"/>
       <c r="Q489" s="4" t="n"/>
     </row>
-    <row r="490" hidden="1" ht="14.45" customHeight="1">
+    <row r="490" ht="14.45" customHeight="1" s="139">
       <c r="B490" t="n">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="O490" s="4" t="n"/>
       <c r="Q490" s="4" t="n"/>
     </row>
-    <row r="491" hidden="1" ht="14.45" customHeight="1">
+    <row r="491" ht="14.45" customHeight="1" s="139">
       <c r="B491" t="n">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="O491" s="4" t="n"/>
       <c r="Q491" s="4" t="n"/>
     </row>
-    <row r="492" hidden="1" ht="14.45" customHeight="1">
+    <row r="492" ht="14.45" customHeight="1" s="139">
       <c r="B492" t="n">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="O492" s="4" t="n"/>
       <c r="Q492" s="4" t="n"/>
     </row>
-    <row r="493" hidden="1" ht="14.45" customHeight="1">
+    <row r="493" ht="14.45" customHeight="1" s="139">
       <c r="B493" t="n">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="O493" s="4" t="n"/>
       <c r="Q493" s="4" t="n"/>
     </row>
-    <row r="494" hidden="1" ht="14.45" customHeight="1">
+    <row r="494" ht="14.45" customHeight="1" s="139">
       <c r="B494" t="n">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="O494" s="4" t="n"/>
       <c r="Q494" s="4" t="n"/>
     </row>
-    <row r="495" hidden="1" ht="14.45" customHeight="1">
+    <row r="495" ht="14.45" customHeight="1" s="139">
       <c r="B495" t="n">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="O495" s="4" t="n"/>
       <c r="Q495" s="4" t="n"/>
     </row>
-    <row r="496" hidden="1" ht="14.45" customHeight="1">
+    <row r="496" ht="14.45" customHeight="1" s="139">
       <c r="B496" t="n">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="O496" s="4" t="n"/>
       <c r="Q496" s="4" t="n"/>
     </row>
-    <row r="497" hidden="1" ht="14.45" customHeight="1">
+    <row r="497" ht="14.45" customHeight="1" s="139">
       <c r="B497" t="n">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="O497" s="4" t="n"/>
       <c r="Q497" s="4" t="n"/>
     </row>
-    <row r="498" hidden="1" ht="14.45" customHeight="1">
+    <row r="498" ht="14.45" customHeight="1" s="139">
       <c r="B498" t="n">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="O498" s="4" t="n"/>
       <c r="Q498" s="4" t="n"/>
     </row>
-    <row r="499" hidden="1" ht="14.45" customHeight="1">
+    <row r="499" ht="14.45" customHeight="1" s="139">
       <c r="B499" t="n">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="O499" s="4" t="n"/>
       <c r="Q499" s="4" t="n"/>
     </row>
-    <row r="500" hidden="1" ht="14.45" customHeight="1">
+    <row r="500" ht="14.45" customHeight="1" s="139">
       <c r="B500" t="n">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="O500" s="4" t="n"/>
       <c r="Q500" s="4" t="n"/>
     </row>
-    <row r="501" hidden="1" ht="14.45" customHeight="1">
+    <row r="501" ht="14.45" customHeight="1" s="139">
       <c r="B501" t="n">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="O501" s="4" t="n"/>
       <c r="Q501" s="4" t="n"/>
     </row>
-    <row r="502" hidden="1" ht="14.45" customHeight="1">
+    <row r="502" ht="14.45" customHeight="1" s="139">
       <c r="B502" t="n">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="O502" s="4" t="n"/>
       <c r="Q502" s="4" t="n"/>
     </row>
-    <row r="503" hidden="1" ht="14.45" customHeight="1">
+    <row r="503" ht="14.45" customHeight="1" s="139">
       <c r="B503" t="n">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="O503" s="4" t="n"/>
       <c r="Q503" s="4" t="n"/>
     </row>
-    <row r="504" hidden="1" ht="14.45" customHeight="1">
+    <row r="504" ht="14.45" customHeight="1" s="139">
       <c r="B504" t="n">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="O504" s="4" t="n"/>
       <c r="Q504" s="4" t="n"/>
     </row>
-    <row r="505" hidden="1" ht="14.45" customHeight="1">
+    <row r="505" ht="14.45" customHeight="1" s="139">
       <c r="B505" t="n">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="O505" s="4" t="n"/>
       <c r="Q505" s="4" t="n"/>
     </row>
-    <row r="506" hidden="1" ht="14.45" customHeight="1">
+    <row r="506" ht="14.45" customHeight="1" s="139">
       <c r="B506" t="n">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="O506" s="4" t="n"/>
       <c r="Q506" s="4" t="n"/>
     </row>
-    <row r="507" hidden="1" ht="14.45" customHeight="1">
+    <row r="507" ht="14.45" customHeight="1" s="139">
       <c r="B507" t="n">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="O507" s="4" t="n"/>
       <c r="Q507" s="4" t="n"/>
     </row>
-    <row r="508" hidden="1" ht="14.45" customHeight="1">
+    <row r="508" ht="14.45" customHeight="1" s="139">
       <c r="B508" t="n">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="O508" s="4" t="n"/>
       <c r="Q508" s="4" t="n"/>
     </row>
-    <row r="509" hidden="1" ht="14.45" customHeight="1">
+    <row r="509" ht="14.45" customHeight="1" s="139">
       <c r="B509" t="n">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="O509" s="4" t="n"/>
       <c r="Q509" s="4" t="n"/>
     </row>
-    <row r="510" hidden="1" ht="14.45" customHeight="1">
+    <row r="510" ht="14.45" customHeight="1" s="139">
       <c r="B510" t="n">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="O510" s="4" t="n"/>
       <c r="Q510" s="4" t="n"/>
     </row>
-    <row r="511" hidden="1" ht="14.45" customHeight="1">
+    <row r="511" ht="14.45" customHeight="1" s="139">
       <c r="B511" t="n">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="O511" s="4" t="n"/>
       <c r="Q511" s="4" t="n"/>
     </row>
-    <row r="512" hidden="1" ht="14.45" customHeight="1">
+    <row r="512" ht="14.45" customHeight="1" s="139">
       <c r="B512" t="n">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="O512" s="4" t="n"/>
       <c r="Q512" s="4" t="n"/>
     </row>
-    <row r="513" hidden="1" ht="14.45" customHeight="1">
+    <row r="513" ht="14.45" customHeight="1" s="139">
       <c r="B513" t="n">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="O513" s="4" t="n"/>
       <c r="Q513" s="4" t="n"/>
     </row>
-    <row r="514" hidden="1" ht="14.45" customHeight="1">
+    <row r="514" ht="14.45" customHeight="1" s="139">
       <c r="B514" t="n">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="O514" s="4" t="n"/>
       <c r="Q514" s="4" t="n"/>
     </row>
-    <row r="515" hidden="1" ht="14.45" customHeight="1">
+    <row r="515" ht="14.45" customHeight="1" s="139">
       <c r="B515" t="n">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="O515" s="4" t="n"/>
       <c r="Q515" s="4" t="n"/>
     </row>
-    <row r="516" hidden="1" ht="14.45" customHeight="1">
+    <row r="516" ht="14.45" customHeight="1" s="139">
       <c r="B516" t="n">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="O516" s="4" t="n"/>
       <c r="Q516" s="4" t="n"/>
     </row>
-    <row r="517" hidden="1" ht="14.45" customHeight="1">
+    <row r="517" ht="14.45" customHeight="1" s="139">
       <c r="B517" t="n">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="O517" s="4" t="n"/>
       <c r="Q517" s="4" t="n"/>
     </row>
-    <row r="518" hidden="1" ht="14.45" customHeight="1">
+    <row r="518" ht="14.45" customHeight="1" s="139">
       <c r="B518" t="n">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="O518" s="4" t="n"/>
       <c r="Q518" s="4" t="n"/>
     </row>
-    <row r="519" hidden="1" ht="14.45" customHeight="1">
+    <row r="519" ht="14.45" customHeight="1" s="139">
       <c r="B519" t="n">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="O519" s="4" t="n"/>
       <c r="Q519" s="4" t="n"/>
     </row>
-    <row r="520" hidden="1" ht="14.45" customHeight="1">
+    <row r="520" ht="14.45" customHeight="1" s="139">
       <c r="B520" t="n">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="O520" s="4" t="n"/>
       <c r="Q520" s="4" t="n"/>
     </row>
-    <row r="521" hidden="1" ht="14.45" customHeight="1">
+    <row r="521" ht="14.45" customHeight="1" s="139">
       <c r="B521" t="n">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="O521" s="4" t="n"/>
       <c r="Q521" s="4" t="n"/>
     </row>
-    <row r="522" hidden="1" ht="14.45" customHeight="1">
+    <row r="522" ht="14.45" customHeight="1" s="139">
       <c r="B522" t="n">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="O522" s="4" t="n"/>
       <c r="Q522" s="4" t="n"/>
     </row>
-    <row r="523" hidden="1" ht="14.45" customHeight="1">
+    <row r="523" ht="14.45" customHeight="1" s="139">
       <c r="B523" t="n">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="O523" s="4" t="n"/>
       <c r="Q523" s="4" t="n"/>
     </row>
-    <row r="524" hidden="1" ht="14.45" customHeight="1">
+    <row r="524" ht="14.45" customHeight="1" s="139">
       <c r="B524" t="n">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="O524" s="4" t="n"/>
       <c r="Q524" s="4" t="n"/>
     </row>
-    <row r="525" hidden="1" ht="14.45" customHeight="1">
+    <row r="525" ht="14.45" customHeight="1" s="139">
       <c r="B525" t="n">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="O525" s="4" t="n"/>
       <c r="Q525" s="4" t="n"/>
     </row>
-    <row r="526" hidden="1" ht="15" customHeight="1">
+    <row r="526" ht="14.45" customHeight="1" s="139">
       <c r="B526" t="n">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="O526" s="4" t="n"/>
       <c r="Q526" s="4" t="n"/>
     </row>
-    <row r="527" hidden="1" ht="15" customHeight="1">
+    <row r="527" ht="15" customHeight="1" s="139">
       <c r="B527" t="n">
-        <v>3514</v>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>3513</v>
       </c>
       <c r="O527" s="4" t="n"/>
       <c r="Q527" s="4" t="n"/>
     </row>
-    <row r="528" hidden="1" ht="15" customHeight="1">
+    <row r="528" ht="15" customHeight="1" s="139">
       <c r="B528" t="n">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -8640,7 +8670,10 @@
       <c r="O528" s="4" t="n"/>
       <c r="Q528" s="4" t="n"/>
     </row>
-    <row r="529" hidden="1" ht="15" customHeight="1">
+    <row r="529" ht="15" customHeight="1" s="139">
+      <c r="B529" t="n">
+        <v>3515</v>
+      </c>
       <c r="F529" t="inlineStr">
         <is>
           <t>A</t>
@@ -8649,7 +8682,7 @@
       <c r="O529" s="4" t="n"/>
       <c r="Q529" s="4" t="n"/>
     </row>
-    <row r="530" hidden="1" ht="15" customHeight="1">
+    <row r="530" ht="15" customHeight="1" s="139">
       <c r="F530" t="inlineStr">
         <is>
           <t>A</t>
@@ -8658,7 +8691,7 @@
       <c r="O530" s="4" t="n"/>
       <c r="Q530" s="4" t="n"/>
     </row>
-    <row r="531" hidden="1" ht="15" customHeight="1">
+    <row r="531" ht="15" customHeight="1" s="139">
       <c r="F531" t="inlineStr">
         <is>
           <t>A</t>
@@ -8667,7 +8700,7 @@
       <c r="O531" s="4" t="n"/>
       <c r="Q531" s="4" t="n"/>
     </row>
-    <row r="532" hidden="1" ht="15" customHeight="1">
+    <row r="532" ht="15" customHeight="1" s="139">
       <c r="F532" t="inlineStr">
         <is>
           <t>A</t>
@@ -8676,7 +8709,7 @@
       <c r="O532" s="4" t="n"/>
       <c r="Q532" s="4" t="n"/>
     </row>
-    <row r="533" hidden="1" ht="15" customHeight="1">
+    <row r="533" ht="15" customHeight="1" s="139">
       <c r="F533" t="inlineStr">
         <is>
           <t>A</t>
@@ -8685,7 +8718,17 @@
       <c r="O533" s="4" t="n"/>
       <c r="Q533" s="4" t="n"/>
     </row>
+    <row r="534" ht="15" customHeight="1" s="139">
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O534" s="4" t="n"/>
+      <c r="Q534" s="4" t="n"/>
+    </row>
   </sheetData>
+  <autoFilter ref="B544"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId2"/>
@@ -8705,10 +8748,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" display="brandon.conner@gxo.com" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" display="brandon.conner@gxo.com" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" display="brandon.conner@gxo.com" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" display="brandon.conner@gxo.com" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" display="brandon.conner@gxo.com" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R29" display="brandon.conner@gxo.com" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R30" display="brandon.conner@gxo.com" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R31" display="brandon.conner@gxo.com" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
